--- a/gcc-x64/Scattered successful looukp.xlsx
+++ b/gcc-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>4.31496</v>
+        <v>4.59393</v>
       </c>
       <c r="C2" t="n">
-        <v>4.33031</v>
+        <v>3.97588</v>
       </c>
       <c r="D2" t="n">
-        <v>7.60949</v>
+        <v>7.87147</v>
       </c>
       <c r="E2" t="n">
-        <v>3.78066</v>
+        <v>4.94806</v>
       </c>
       <c r="F2" t="n">
-        <v>4.03595</v>
+        <v>4.76824</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>3.97813</v>
+        <v>4.38981</v>
       </c>
       <c r="C3" t="n">
-        <v>4.32635</v>
+        <v>3.38992</v>
       </c>
       <c r="D3" t="n">
-        <v>8.32278</v>
+        <v>8.30837</v>
       </c>
       <c r="E3" t="n">
-        <v>3.80807</v>
+        <v>4.98768</v>
       </c>
       <c r="F3" t="n">
-        <v>4.01809</v>
+        <v>4.79371</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.82248</v>
+        <v>5.00015</v>
       </c>
       <c r="C4" t="n">
-        <v>4.15755</v>
+        <v>3.77264</v>
       </c>
       <c r="D4" t="n">
-        <v>9.33165</v>
+        <v>9.149839999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>3.80423</v>
+        <v>4.41066</v>
       </c>
       <c r="F4" t="n">
-        <v>4.18143</v>
+        <v>3.98042</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.77216</v>
+        <v>5.00864</v>
       </c>
       <c r="C5" t="n">
-        <v>4.45914</v>
+        <v>3.81677</v>
       </c>
       <c r="D5" t="n">
-        <v>9.843360000000001</v>
+        <v>9.95871</v>
       </c>
       <c r="E5" t="n">
-        <v>3.79143</v>
+        <v>4.37661</v>
       </c>
       <c r="F5" t="n">
-        <v>3.95156</v>
+        <v>4.01684</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>3.77038</v>
+        <v>5.15541</v>
       </c>
       <c r="C6" t="n">
-        <v>4.02084</v>
+        <v>3.80851</v>
       </c>
       <c r="D6" t="n">
-        <v>10.5982</v>
+        <v>10.5891</v>
       </c>
       <c r="E6" t="n">
-        <v>3.83101</v>
+        <v>4.35213</v>
       </c>
       <c r="F6" t="n">
-        <v>4.27116</v>
+        <v>4.05766</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>3.77805</v>
+        <v>4.72319</v>
       </c>
       <c r="C7" t="n">
-        <v>4.42706</v>
+        <v>3.78262</v>
       </c>
       <c r="D7" t="n">
-        <v>6.5268</v>
+        <v>6.95647</v>
       </c>
       <c r="E7" t="n">
-        <v>3.88746</v>
+        <v>4.52007</v>
       </c>
       <c r="F7" t="n">
-        <v>4.13313</v>
+        <v>4.0661</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>3.84324</v>
+        <v>5.06478</v>
       </c>
       <c r="C8" t="n">
-        <v>4.44005</v>
+        <v>3.76332</v>
       </c>
       <c r="D8" t="n">
-        <v>6.91726</v>
+        <v>7.16825</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9986</v>
+        <v>4.28938</v>
       </c>
       <c r="F8" t="n">
-        <v>4.32105</v>
+        <v>5.08002</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>3.89987</v>
+        <v>4.45309</v>
       </c>
       <c r="C9" t="n">
-        <v>4.49616</v>
+        <v>4.2368</v>
       </c>
       <c r="D9" t="n">
-        <v>7.29656</v>
+        <v>7.64571</v>
       </c>
       <c r="E9" t="n">
-        <v>3.95945</v>
+        <v>4.77919</v>
       </c>
       <c r="F9" t="n">
-        <v>4.04627</v>
+        <v>4.2529</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>4.4958</v>
+        <v>4.80157</v>
       </c>
       <c r="C10" t="n">
-        <v>4.39851</v>
+        <v>3.8126</v>
       </c>
       <c r="D10" t="n">
-        <v>7.60761</v>
+        <v>8.0825</v>
       </c>
       <c r="E10" t="n">
-        <v>3.95981</v>
+        <v>5.01567</v>
       </c>
       <c r="F10" t="n">
-        <v>4.0681</v>
+        <v>4.26056</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>4.47745</v>
+        <v>4.84922</v>
       </c>
       <c r="C11" t="n">
-        <v>4.431</v>
+        <v>4.12619</v>
       </c>
       <c r="D11" t="n">
-        <v>8.121259999999999</v>
+        <v>8.630229999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>4.0262</v>
+        <v>5.04505</v>
       </c>
       <c r="F11" t="n">
-        <v>4.09668</v>
+        <v>4.29104</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>4.49347</v>
+        <v>4.85319</v>
       </c>
       <c r="C12" t="n">
-        <v>4.42885</v>
+        <v>4.13681</v>
       </c>
       <c r="D12" t="n">
-        <v>8.63367</v>
+        <v>9.20026</v>
       </c>
       <c r="E12" t="n">
-        <v>4.03378</v>
+        <v>4.90114</v>
       </c>
       <c r="F12" t="n">
-        <v>4.09969</v>
+        <v>4.31468</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>4.50736</v>
+        <v>4.85422</v>
       </c>
       <c r="C13" t="n">
-        <v>4.43982</v>
+        <v>4.17547</v>
       </c>
       <c r="D13" t="n">
-        <v>9.150169999999999</v>
+        <v>9.709669999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>4.07296</v>
+        <v>4.908</v>
       </c>
       <c r="F13" t="n">
-        <v>4.13052</v>
+        <v>4.34109</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>4.52816</v>
+        <v>5.36665</v>
       </c>
       <c r="C14" t="n">
-        <v>4.45779</v>
+        <v>4.32386</v>
       </c>
       <c r="D14" t="n">
-        <v>9.664339999999999</v>
+        <v>10.106</v>
       </c>
       <c r="E14" t="n">
-        <v>4.16541</v>
+        <v>5.1497</v>
       </c>
       <c r="F14" t="n">
-        <v>4.16058</v>
+        <v>4.36471</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>4.57116</v>
+        <v>5.86202</v>
       </c>
       <c r="C15" t="n">
-        <v>4.48004</v>
+        <v>4.35043</v>
       </c>
       <c r="D15" t="n">
-        <v>10.122</v>
+        <v>10.537</v>
       </c>
       <c r="E15" t="n">
-        <v>4.21753</v>
+        <v>5.11187</v>
       </c>
       <c r="F15" t="n">
-        <v>4.1725</v>
+        <v>4.39095</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>4.55998</v>
+        <v>5.87007</v>
       </c>
       <c r="C16" t="n">
-        <v>4.49762</v>
+        <v>4.32125</v>
       </c>
       <c r="D16" t="n">
-        <v>10.5832</v>
+        <v>11.0714</v>
       </c>
       <c r="E16" t="n">
-        <v>4.16539</v>
+        <v>5.21498</v>
       </c>
       <c r="F16" t="n">
-        <v>4.21913</v>
+        <v>4.41522</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>4.57061</v>
+        <v>4.96307</v>
       </c>
       <c r="C17" t="n">
-        <v>4.51144</v>
+        <v>4.37799</v>
       </c>
       <c r="D17" t="n">
-        <v>11.0588</v>
+        <v>11.5937</v>
       </c>
       <c r="E17" t="n">
-        <v>4.24206</v>
+        <v>4.89534</v>
       </c>
       <c r="F17" t="n">
-        <v>4.22248</v>
+        <v>4.45433</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>4.59343</v>
+        <v>5.39393</v>
       </c>
       <c r="C18" t="n">
-        <v>4.53596</v>
+        <v>4.48385</v>
       </c>
       <c r="D18" t="n">
-        <v>11.5764</v>
+        <v>12.066</v>
       </c>
       <c r="E18" t="n">
-        <v>4.25189</v>
+        <v>5.06466</v>
       </c>
       <c r="F18" t="n">
-        <v>4.25684</v>
+        <v>4.46333</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.61462</v>
+        <v>4.96959</v>
       </c>
       <c r="C19" t="n">
-        <v>4.57247</v>
+        <v>4.47445</v>
       </c>
       <c r="D19" t="n">
-        <v>11.9865</v>
+        <v>12.5311</v>
       </c>
       <c r="E19" t="n">
-        <v>4.31575</v>
+        <v>4.95466</v>
       </c>
       <c r="F19" t="n">
-        <v>4.30001</v>
+        <v>4.5015</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>4.59308</v>
+        <v>5.90191</v>
       </c>
       <c r="C20" t="n">
-        <v>4.59847</v>
+        <v>4.60264</v>
       </c>
       <c r="D20" t="n">
-        <v>12.2842</v>
+        <v>12.9733</v>
       </c>
       <c r="E20" t="n">
-        <v>4.26751</v>
+        <v>5.42822</v>
       </c>
       <c r="F20" t="n">
-        <v>4.34152</v>
+        <v>4.54261</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>4.6589</v>
+        <v>5.91759</v>
       </c>
       <c r="C21" t="n">
-        <v>4.60078</v>
+        <v>4.66437</v>
       </c>
       <c r="D21" t="n">
-        <v>8.77244</v>
+        <v>9.18296</v>
       </c>
       <c r="E21" t="n">
-        <v>4.4054</v>
+        <v>5.49995</v>
       </c>
       <c r="F21" t="n">
-        <v>4.47888</v>
+        <v>5.14521</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>4.64148</v>
+        <v>5.94274</v>
       </c>
       <c r="C22" t="n">
-        <v>4.68536</v>
+        <v>4.37634</v>
       </c>
       <c r="D22" t="n">
-        <v>9.06171</v>
+        <v>9.50516</v>
       </c>
       <c r="E22" t="n">
-        <v>4.73108</v>
+        <v>5.83531</v>
       </c>
       <c r="F22" t="n">
-        <v>5.20115</v>
+        <v>5.9188</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>4.72557</v>
+        <v>6.00499</v>
       </c>
       <c r="C23" t="n">
-        <v>5.05006</v>
+        <v>4.29927</v>
       </c>
       <c r="D23" t="n">
-        <v>9.439959999999999</v>
+        <v>9.8195</v>
       </c>
       <c r="E23" t="n">
-        <v>4.51395</v>
+        <v>5.15117</v>
       </c>
       <c r="F23" t="n">
-        <v>4.63297</v>
+        <v>5.45804</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>5.19808</v>
+        <v>6.09152</v>
       </c>
       <c r="C24" t="n">
-        <v>5.15053</v>
+        <v>4.40314</v>
       </c>
       <c r="D24" t="n">
-        <v>9.715199999999999</v>
+        <v>10.134</v>
       </c>
       <c r="E24" t="n">
-        <v>4.58191</v>
+        <v>5.1631</v>
       </c>
       <c r="F24" t="n">
-        <v>4.66502</v>
+        <v>5.33831</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>5.21526</v>
+        <v>6.15626</v>
       </c>
       <c r="C25" t="n">
-        <v>5.16707</v>
+        <v>4.36177</v>
       </c>
       <c r="D25" t="n">
-        <v>10.0687</v>
+        <v>10.5303</v>
       </c>
       <c r="E25" t="n">
-        <v>4.60287</v>
+        <v>5.24329</v>
       </c>
       <c r="F25" t="n">
-        <v>4.67909</v>
+        <v>5.51289</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>5.15347</v>
+        <v>6.0178</v>
       </c>
       <c r="C26" t="n">
-        <v>5.13443</v>
+        <v>4.378</v>
       </c>
       <c r="D26" t="n">
-        <v>10.4006</v>
+        <v>10.834</v>
       </c>
       <c r="E26" t="n">
-        <v>4.66239</v>
+        <v>5.22055</v>
       </c>
       <c r="F26" t="n">
-        <v>4.71347</v>
+        <v>5.23787</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>5.21529</v>
+        <v>6.16757</v>
       </c>
       <c r="C27" t="n">
-        <v>5.19229</v>
+        <v>4.49058</v>
       </c>
       <c r="D27" t="n">
-        <v>10.7814</v>
+        <v>11.2534</v>
       </c>
       <c r="E27" t="n">
-        <v>4.67285</v>
+        <v>5.29568</v>
       </c>
       <c r="F27" t="n">
-        <v>4.73562</v>
+        <v>5.27187</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>5.24628</v>
+        <v>6.17772</v>
       </c>
       <c r="C28" t="n">
-        <v>5.16596</v>
+        <v>4.39815</v>
       </c>
       <c r="D28" t="n">
-        <v>11.2833</v>
+        <v>11.6907</v>
       </c>
       <c r="E28" t="n">
-        <v>4.65338</v>
+        <v>5.32291</v>
       </c>
       <c r="F28" t="n">
-        <v>4.80569</v>
+        <v>5.30623</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>5.09871</v>
+        <v>6.18847</v>
       </c>
       <c r="C29" t="n">
-        <v>5.20669</v>
+        <v>4.42459</v>
       </c>
       <c r="D29" t="n">
-        <v>11.7461</v>
+        <v>12.117</v>
       </c>
       <c r="E29" t="n">
-        <v>4.76511</v>
+        <v>5.36929</v>
       </c>
       <c r="F29" t="n">
-        <v>4.83824</v>
+        <v>5.41455</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>5.10892</v>
+        <v>5.70823</v>
       </c>
       <c r="C30" t="n">
-        <v>5.23967</v>
+        <v>4.39653</v>
       </c>
       <c r="D30" t="n">
-        <v>12.1441</v>
+        <v>12.6344</v>
       </c>
       <c r="E30" t="n">
-        <v>4.78674</v>
+        <v>5.34462</v>
       </c>
       <c r="F30" t="n">
-        <v>4.84683</v>
+        <v>5.64522</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>5.12427</v>
+        <v>5.70997</v>
       </c>
       <c r="C31" t="n">
-        <v>5.24722</v>
+        <v>4.39277</v>
       </c>
       <c r="D31" t="n">
-        <v>12.5481</v>
+        <v>13.1026</v>
       </c>
       <c r="E31" t="n">
-        <v>4.75438</v>
+        <v>5.39115</v>
       </c>
       <c r="F31" t="n">
-        <v>4.87646</v>
+        <v>5.39161</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>5.13464</v>
+        <v>5.71902</v>
       </c>
       <c r="C32" t="n">
-        <v>5.27705</v>
+        <v>4.43384</v>
       </c>
       <c r="D32" t="n">
-        <v>12.9377</v>
+        <v>13.4962</v>
       </c>
       <c r="E32" t="n">
-        <v>4.82417</v>
+        <v>5.47561</v>
       </c>
       <c r="F32" t="n">
-        <v>4.86511</v>
+        <v>5.73396</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>5.15167</v>
+        <v>5.72225</v>
       </c>
       <c r="C33" t="n">
-        <v>5.30013</v>
+        <v>4.4944</v>
       </c>
       <c r="D33" t="n">
-        <v>13.2794</v>
+        <v>13.9896</v>
       </c>
       <c r="E33" t="n">
-        <v>4.84297</v>
+        <v>5.47662</v>
       </c>
       <c r="F33" t="n">
-        <v>4.92499</v>
+        <v>5.55283</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.16383</v>
+        <v>5.74812</v>
       </c>
       <c r="C34" t="n">
-        <v>5.32303</v>
+        <v>4.55485</v>
       </c>
       <c r="D34" t="n">
-        <v>13.624</v>
+        <v>14.2494</v>
       </c>
       <c r="E34" t="n">
-        <v>4.92255</v>
+        <v>5.54354</v>
       </c>
       <c r="F34" t="n">
-        <v>5.00625</v>
+        <v>5.88639</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>5.1804</v>
+        <v>5.67295</v>
       </c>
       <c r="C35" t="n">
-        <v>5.3368</v>
+        <v>4.61229</v>
       </c>
       <c r="D35" t="n">
-        <v>9.6975</v>
+        <v>10.0071</v>
       </c>
       <c r="E35" t="n">
-        <v>5.20381</v>
+        <v>5.80812</v>
       </c>
       <c r="F35" t="n">
-        <v>5.28852</v>
+        <v>6.1975</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>5.24391</v>
+        <v>6.15966</v>
       </c>
       <c r="C36" t="n">
-        <v>5.42232</v>
+        <v>4.75065</v>
       </c>
       <c r="D36" t="n">
-        <v>9.946910000000001</v>
+        <v>10.1406</v>
       </c>
       <c r="E36" t="n">
-        <v>5.9438</v>
+        <v>6.5202</v>
       </c>
       <c r="F36" t="n">
-        <v>6.0831</v>
+        <v>7.1018</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>5.47785</v>
+        <v>6.09875</v>
       </c>
       <c r="C37" t="n">
-        <v>5.68486</v>
+        <v>4.52528</v>
       </c>
       <c r="D37" t="n">
-        <v>10.1583</v>
+        <v>10.3024</v>
       </c>
       <c r="E37" t="n">
-        <v>4.93883</v>
+        <v>5.25784</v>
       </c>
       <c r="F37" t="n">
-        <v>5.07557</v>
+        <v>5.56951</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>5.64156</v>
+        <v>6.39223</v>
       </c>
       <c r="C38" t="n">
-        <v>5.83781</v>
+        <v>4.56775</v>
       </c>
       <c r="D38" t="n">
-        <v>10.2796</v>
+        <v>11.01</v>
       </c>
       <c r="E38" t="n">
-        <v>5.03711</v>
+        <v>5.306</v>
       </c>
       <c r="F38" t="n">
-        <v>5.10544</v>
+        <v>5.62708</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>5.61292</v>
+        <v>6.39644</v>
       </c>
       <c r="C39" t="n">
-        <v>5.84729</v>
+        <v>4.59011</v>
       </c>
       <c r="D39" t="n">
-        <v>10.5714</v>
+        <v>11.0637</v>
       </c>
       <c r="E39" t="n">
-        <v>5.05512</v>
+        <v>5.40123</v>
       </c>
       <c r="F39" t="n">
-        <v>5.13393</v>
+        <v>5.72543</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>5.65004</v>
+        <v>6.32753</v>
       </c>
       <c r="C40" t="n">
-        <v>5.87503</v>
+        <v>4.44669</v>
       </c>
       <c r="D40" t="n">
-        <v>10.8702</v>
+        <v>11.6694</v>
       </c>
       <c r="E40" t="n">
-        <v>5.08214</v>
+        <v>5.50495</v>
       </c>
       <c r="F40" t="n">
-        <v>5.16768</v>
+        <v>5.48762</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>5.66035</v>
+        <v>6.43485</v>
       </c>
       <c r="C41" t="n">
-        <v>5.87501</v>
+        <v>4.61165</v>
       </c>
       <c r="D41" t="n">
-        <v>11.191</v>
+        <v>12.1638</v>
       </c>
       <c r="E41" t="n">
-        <v>5.08706</v>
+        <v>5.4103</v>
       </c>
       <c r="F41" t="n">
-        <v>5.18853</v>
+        <v>5.75224</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>5.60608</v>
+        <v>6.4279</v>
       </c>
       <c r="C42" t="n">
-        <v>5.88113</v>
+        <v>4.65965</v>
       </c>
       <c r="D42" t="n">
-        <v>11.5745</v>
+        <v>12.5624</v>
       </c>
       <c r="E42" t="n">
-        <v>5.1232</v>
+        <v>5.44111</v>
       </c>
       <c r="F42" t="n">
-        <v>5.22022</v>
+        <v>5.82391</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>5.70291</v>
+        <v>6.44089</v>
       </c>
       <c r="C43" t="n">
-        <v>5.91136</v>
+        <v>4.68743</v>
       </c>
       <c r="D43" t="n">
-        <v>11.9873</v>
+        <v>12.9936</v>
       </c>
       <c r="E43" t="n">
-        <v>5.12187</v>
+        <v>5.56653</v>
       </c>
       <c r="F43" t="n">
-        <v>5.24928</v>
+        <v>5.8612</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>5.69635</v>
+        <v>6.4831</v>
       </c>
       <c r="C44" t="n">
-        <v>5.92484</v>
+        <v>4.71943</v>
       </c>
       <c r="D44" t="n">
-        <v>12.3478</v>
+        <v>13.1323</v>
       </c>
       <c r="E44" t="n">
-        <v>5.19129</v>
+        <v>5.6101</v>
       </c>
       <c r="F44" t="n">
-        <v>5.2901</v>
+        <v>5.89772</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>5.71552</v>
+        <v>6.45741</v>
       </c>
       <c r="C45" t="n">
-        <v>5.93279</v>
+        <v>4.76471</v>
       </c>
       <c r="D45" t="n">
-        <v>12.7091</v>
+        <v>13.4727</v>
       </c>
       <c r="E45" t="n">
-        <v>5.26462</v>
+        <v>5.69624</v>
       </c>
       <c r="F45" t="n">
-        <v>5.29552</v>
+        <v>6.0375</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>5.73042</v>
+        <v>6.497</v>
       </c>
       <c r="C46" t="n">
-        <v>5.97132</v>
+        <v>4.78654</v>
       </c>
       <c r="D46" t="n">
-        <v>13.1184</v>
+        <v>13.9447</v>
       </c>
       <c r="E46" t="n">
-        <v>5.33115</v>
+        <v>5.73815</v>
       </c>
       <c r="F46" t="n">
-        <v>5.36625</v>
+        <v>6.13341</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>5.74735</v>
+        <v>6.49927</v>
       </c>
       <c r="C47" t="n">
-        <v>5.98255</v>
+        <v>4.86925</v>
       </c>
       <c r="D47" t="n">
-        <v>13.3394</v>
+        <v>14.2734</v>
       </c>
       <c r="E47" t="n">
-        <v>5.46439</v>
+        <v>5.88202</v>
       </c>
       <c r="F47" t="n">
-        <v>5.47317</v>
+        <v>6.35785</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.58334</v>
+        <v>6.42788</v>
       </c>
       <c r="C48" t="n">
-        <v>6.03692</v>
+        <v>4.79648</v>
       </c>
       <c r="D48" t="n">
-        <v>13.7563</v>
+        <v>14.8013</v>
       </c>
       <c r="E48" t="n">
-        <v>5.6902</v>
+        <v>6.18006</v>
       </c>
       <c r="F48" t="n">
-        <v>5.73647</v>
+        <v>6.57212</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>5.84825</v>
+        <v>6.40106</v>
       </c>
       <c r="C49" t="n">
-        <v>6.05576</v>
+        <v>4.95126</v>
       </c>
       <c r="D49" t="n">
-        <v>14.1331</v>
+        <v>15.4255</v>
       </c>
       <c r="E49" t="n">
-        <v>6.1437</v>
+        <v>6.57734</v>
       </c>
       <c r="F49" t="n">
-        <v>6.19753</v>
+        <v>7.1137</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>5.98052</v>
+        <v>6.56998</v>
       </c>
       <c r="C50" t="n">
-        <v>6.37406</v>
+        <v>5.18069</v>
       </c>
       <c r="D50" t="n">
-        <v>10.0531</v>
+        <v>13.0511</v>
       </c>
       <c r="E50" t="n">
-        <v>6.50188</v>
+        <v>6.49077</v>
       </c>
       <c r="F50" t="n">
-        <v>6.71835</v>
+        <v>7.81873</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>6.48156</v>
+        <v>6.74552</v>
       </c>
       <c r="C51" t="n">
-        <v>6.84252</v>
+        <v>4.74356</v>
       </c>
       <c r="D51" t="n">
-        <v>10.1636</v>
+        <v>13.7673</v>
       </c>
       <c r="E51" t="n">
-        <v>5.31818</v>
+        <v>5.44694</v>
       </c>
       <c r="F51" t="n">
-        <v>5.41834</v>
+        <v>6.28674</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>7.00109</v>
+        <v>7.70664</v>
       </c>
       <c r="C52" t="n">
-        <v>7.53058</v>
+        <v>4.57018</v>
       </c>
       <c r="D52" t="n">
-        <v>10.4841</v>
+        <v>14.8543</v>
       </c>
       <c r="E52" t="n">
-        <v>5.36023</v>
+        <v>5.44883</v>
       </c>
       <c r="F52" t="n">
-        <v>5.42409</v>
+        <v>6.42532</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>6.27767</v>
+        <v>6.43808</v>
       </c>
       <c r="C53" t="n">
-        <v>6.50957</v>
+        <v>4.58716</v>
       </c>
       <c r="D53" t="n">
-        <v>10.7608</v>
+        <v>15.7302</v>
       </c>
       <c r="E53" t="n">
-        <v>5.39593</v>
+        <v>5.43066</v>
       </c>
       <c r="F53" t="n">
-        <v>5.47041</v>
+        <v>6.54257</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>6.32084</v>
+        <v>6.4705</v>
       </c>
       <c r="C54" t="n">
-        <v>6.51825</v>
+        <v>4.60442</v>
       </c>
       <c r="D54" t="n">
-        <v>11.1096</v>
+        <v>16.9569</v>
       </c>
       <c r="E54" t="n">
-        <v>5.46984</v>
+        <v>5.49127</v>
       </c>
       <c r="F54" t="n">
-        <v>5.54356</v>
+        <v>6.48125</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>6.32059</v>
+        <v>6.47428</v>
       </c>
       <c r="C55" t="n">
-        <v>6.46072</v>
+        <v>4.62592</v>
       </c>
       <c r="D55" t="n">
-        <v>11.4007</v>
+        <v>17.3317</v>
       </c>
       <c r="E55" t="n">
-        <v>5.47644</v>
+        <v>5.51345</v>
       </c>
       <c r="F55" t="n">
-        <v>5.53898</v>
+        <v>6.97075</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>6.33625</v>
+        <v>6.49992</v>
       </c>
       <c r="C56" t="n">
-        <v>6.54245</v>
+        <v>4.64571</v>
       </c>
       <c r="D56" t="n">
-        <v>11.751</v>
+        <v>17.7298</v>
       </c>
       <c r="E56" t="n">
-        <v>5.43289</v>
+        <v>5.65796</v>
       </c>
       <c r="F56" t="n">
-        <v>5.58118</v>
+        <v>6.50944</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>6.34842</v>
+        <v>6.40387</v>
       </c>
       <c r="C57" t="n">
-        <v>6.49078</v>
+        <v>4.80045</v>
       </c>
       <c r="D57" t="n">
-        <v>12.1421</v>
+        <v>19.552</v>
       </c>
       <c r="E57" t="n">
-        <v>5.54743</v>
+        <v>5.60681</v>
       </c>
       <c r="F57" t="n">
-        <v>5.64127</v>
+        <v>6.92962</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>6.36403</v>
+        <v>6.49859</v>
       </c>
       <c r="C58" t="n">
-        <v>6.50415</v>
+        <v>4.75781</v>
       </c>
       <c r="D58" t="n">
-        <v>12.5051</v>
+        <v>20.4247</v>
       </c>
       <c r="E58" t="n">
-        <v>5.60647</v>
+        <v>5.85015</v>
       </c>
       <c r="F58" t="n">
-        <v>5.63894</v>
+        <v>6.26095</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>6.34857</v>
+        <v>6.28774</v>
       </c>
       <c r="C59" t="n">
-        <v>6.48565</v>
+        <v>4.87621</v>
       </c>
       <c r="D59" t="n">
-        <v>12.8132</v>
+        <v>20.4799</v>
       </c>
       <c r="E59" t="n">
-        <v>5.698</v>
+        <v>6.0323</v>
       </c>
       <c r="F59" t="n">
-        <v>5.74553</v>
+        <v>6.28756</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>6.34388</v>
+        <v>6.49274</v>
       </c>
       <c r="C60" t="n">
-        <v>6.56294</v>
+        <v>4.83964</v>
       </c>
       <c r="D60" t="n">
-        <v>13.2786</v>
+        <v>20.7965</v>
       </c>
       <c r="E60" t="n">
-        <v>5.74993</v>
+        <v>5.98908</v>
       </c>
       <c r="F60" t="n">
-        <v>5.89405</v>
+        <v>6.5058</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>6.40839</v>
+        <v>6.51242</v>
       </c>
       <c r="C61" t="n">
-        <v>6.59113</v>
+        <v>4.92103</v>
       </c>
       <c r="D61" t="n">
-        <v>13.7115</v>
+        <v>20.8771</v>
       </c>
       <c r="E61" t="n">
-        <v>6.00055</v>
+        <v>6.17815</v>
       </c>
       <c r="F61" t="n">
-        <v>6.08634</v>
+        <v>7.86682</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>6.43134</v>
+        <v>6.45216</v>
       </c>
       <c r="C62" t="n">
-        <v>6.61179</v>
+        <v>5.09461</v>
       </c>
       <c r="D62" t="n">
-        <v>14.035</v>
+        <v>21.0243</v>
       </c>
       <c r="E62" t="n">
-        <v>6.25186</v>
+        <v>6.29049</v>
       </c>
       <c r="F62" t="n">
-        <v>6.38033</v>
+        <v>7.75881</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>6.5519</v>
+        <v>6.57544</v>
       </c>
       <c r="C63" t="n">
-        <v>6.77147</v>
+        <v>5.17598</v>
       </c>
       <c r="D63" t="n">
-        <v>14.3527</v>
+        <v>21.3461</v>
       </c>
       <c r="E63" t="n">
-        <v>6.51946</v>
+        <v>6.75522</v>
       </c>
       <c r="F63" t="n">
-        <v>6.75012</v>
+        <v>8.45595</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>6.73041</v>
+        <v>6.77927</v>
       </c>
       <c r="C64" t="n">
-        <v>7.10188</v>
+        <v>5.35417</v>
       </c>
       <c r="D64" t="n">
-        <v>10.7639</v>
+        <v>16.0277</v>
       </c>
       <c r="E64" t="n">
-        <v>6.94315</v>
+        <v>7.07722</v>
       </c>
       <c r="F64" t="n">
-        <v>7.2387</v>
+        <v>8.039020000000001</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>7.04447</v>
+        <v>7.01091</v>
       </c>
       <c r="C65" t="n">
-        <v>7.51538</v>
+        <v>10.1553</v>
       </c>
       <c r="D65" t="n">
-        <v>11.1614</v>
+        <v>15.5206</v>
       </c>
       <c r="E65" t="n">
-        <v>7.56383</v>
+        <v>7.62203</v>
       </c>
       <c r="F65" t="n">
-        <v>8.006030000000001</v>
+        <v>9.3924</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>7.54433</v>
+        <v>7.4856</v>
       </c>
       <c r="C66" t="n">
-        <v>8.1638</v>
+        <v>10.3031</v>
       </c>
       <c r="D66" t="n">
-        <v>11.5206</v>
+        <v>16.8746</v>
       </c>
       <c r="E66" t="n">
-        <v>5.69127</v>
+        <v>6.58005</v>
       </c>
       <c r="F66" t="n">
-        <v>5.96713</v>
+        <v>6.79484</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>7.46714</v>
+        <v>11.877</v>
       </c>
       <c r="C67" t="n">
-        <v>7.35774</v>
+        <v>9.33555</v>
       </c>
       <c r="D67" t="n">
-        <v>11.9651</v>
+        <v>17.5227</v>
       </c>
       <c r="E67" t="n">
-        <v>5.74399</v>
+        <v>6.97032</v>
       </c>
       <c r="F67" t="n">
-        <v>6.06343</v>
+        <v>6.87841</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>7.67496</v>
+        <v>12.1753</v>
       </c>
       <c r="C68" t="n">
-        <v>7.40677</v>
+        <v>9.48554</v>
       </c>
       <c r="D68" t="n">
-        <v>12.4935</v>
+        <v>18.7974</v>
       </c>
       <c r="E68" t="n">
-        <v>5.79752</v>
+        <v>7.30334</v>
       </c>
       <c r="F68" t="n">
-        <v>6.16314</v>
+        <v>7.1018</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>7.69116</v>
+        <v>13.1402</v>
       </c>
       <c r="C69" t="n">
-        <v>7.44308</v>
+        <v>10.4791</v>
       </c>
       <c r="D69" t="n">
-        <v>13.025</v>
+        <v>18.819</v>
       </c>
       <c r="E69" t="n">
-        <v>5.85752</v>
+        <v>7.72184</v>
       </c>
       <c r="F69" t="n">
-        <v>6.32524</v>
+        <v>7.08637</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>7.63205</v>
+        <v>11.5863</v>
       </c>
       <c r="C70" t="n">
-        <v>7.57503</v>
+        <v>8.990780000000001</v>
       </c>
       <c r="D70" t="n">
-        <v>13.7328</v>
+        <v>19.638</v>
       </c>
       <c r="E70" t="n">
-        <v>5.92633</v>
+        <v>7.58768</v>
       </c>
       <c r="F70" t="n">
-        <v>6.4074</v>
+        <v>7.20869</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>7.39256</v>
+        <v>9.686579999999999</v>
       </c>
       <c r="C71" t="n">
-        <v>7.61237</v>
+        <v>7.32941</v>
       </c>
       <c r="D71" t="n">
-        <v>14.4037</v>
+        <v>19.122</v>
       </c>
       <c r="E71" t="n">
-        <v>6.06392</v>
+        <v>7.48864</v>
       </c>
       <c r="F71" t="n">
-        <v>6.58642</v>
+        <v>7.34626</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>7.6609</v>
+        <v>13.1983</v>
       </c>
       <c r="C72" t="n">
-        <v>7.68894</v>
+        <v>10.6182</v>
       </c>
       <c r="D72" t="n">
-        <v>15.1806</v>
+        <v>20.0574</v>
       </c>
       <c r="E72" t="n">
-        <v>6.10396</v>
+        <v>7.68241</v>
       </c>
       <c r="F72" t="n">
-        <v>6.68067</v>
+        <v>7.49654</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>7.24095</v>
+        <v>13.2397</v>
       </c>
       <c r="C73" t="n">
-        <v>7.78902</v>
+        <v>10.5711</v>
       </c>
       <c r="D73" t="n">
-        <v>16.3438</v>
+        <v>19.6164</v>
       </c>
       <c r="E73" t="n">
-        <v>6.16283</v>
+        <v>7.90182</v>
       </c>
       <c r="F73" t="n">
-        <v>6.87414</v>
+        <v>7.69274</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>7.35585</v>
+        <v>8.709569999999999</v>
       </c>
       <c r="C74" t="n">
-        <v>7.8734</v>
+        <v>6.51403</v>
       </c>
       <c r="D74" t="n">
-        <v>16.652</v>
+        <v>20.7464</v>
       </c>
       <c r="E74" t="n">
-        <v>6.33298</v>
+        <v>6.39575</v>
       </c>
       <c r="F74" t="n">
-        <v>7.16244</v>
+        <v>7.57634</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>7.37294</v>
+        <v>8.72719</v>
       </c>
       <c r="C75" t="n">
-        <v>7.99517</v>
+        <v>6.58447</v>
       </c>
       <c r="D75" t="n">
-        <v>18.0245</v>
+        <v>21.5813</v>
       </c>
       <c r="E75" t="n">
-        <v>6.46813</v>
+        <v>6.86619</v>
       </c>
       <c r="F75" t="n">
-        <v>7.47918</v>
+        <v>8.957929999999999</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>7.4416</v>
+        <v>8.81236</v>
       </c>
       <c r="C76" t="n">
-        <v>8.21048</v>
+        <v>6.63454</v>
       </c>
       <c r="D76" t="n">
-        <v>19.2267</v>
+        <v>21.0771</v>
       </c>
       <c r="E76" t="n">
-        <v>6.64292</v>
+        <v>6.947</v>
       </c>
       <c r="F76" t="n">
-        <v>7.75799</v>
+        <v>8.26943</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>7.98628</v>
+        <v>12.0737</v>
       </c>
       <c r="C77" t="n">
-        <v>8.50004</v>
+        <v>9.517379999999999</v>
       </c>
       <c r="D77" t="n">
-        <v>19.8965</v>
+        <v>21.764</v>
       </c>
       <c r="E77" t="n">
-        <v>6.96852</v>
+        <v>7.20374</v>
       </c>
       <c r="F77" t="n">
-        <v>8.21813</v>
+        <v>8.913959999999999</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>7.83441</v>
+        <v>9.047280000000001</v>
       </c>
       <c r="C78" t="n">
-        <v>8.78509</v>
+        <v>6.92011</v>
       </c>
       <c r="D78" t="n">
-        <v>19.6234</v>
+        <v>20.9788</v>
       </c>
       <c r="E78" t="n">
-        <v>7.28336</v>
+        <v>7.72229</v>
       </c>
       <c r="F78" t="n">
-        <v>8.80382</v>
+        <v>14.6069</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>8.49799</v>
+        <v>10.4784</v>
       </c>
       <c r="C79" t="n">
-        <v>9.33276</v>
+        <v>16.7258</v>
       </c>
       <c r="D79" t="n">
-        <v>20.4107</v>
+        <v>21.6031</v>
       </c>
       <c r="E79" t="n">
-        <v>7.91739</v>
+        <v>8.24596</v>
       </c>
       <c r="F79" t="n">
-        <v>9.579140000000001</v>
+        <v>10.0308</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>9.04969</v>
+        <v>9.72025</v>
       </c>
       <c r="C80" t="n">
-        <v>10.0177</v>
+        <v>16.8409</v>
       </c>
       <c r="D80" t="n">
-        <v>21.6539</v>
+        <v>23.139</v>
       </c>
       <c r="E80" t="n">
-        <v>11.2894</v>
+        <v>11.8398</v>
       </c>
       <c r="F80" t="n">
-        <v>11.1244</v>
+        <v>12.033</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>18.9425</v>
+        <v>20.6395</v>
       </c>
       <c r="C81" t="n">
-        <v>15.2628</v>
+        <v>16.783</v>
       </c>
       <c r="D81" t="n">
-        <v>22.5335</v>
+        <v>23.6048</v>
       </c>
       <c r="E81" t="n">
-        <v>11.5329</v>
+        <v>12.5796</v>
       </c>
       <c r="F81" t="n">
-        <v>11.1661</v>
+        <v>12.0675</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>19.3868</v>
+        <v>20.8897</v>
       </c>
       <c r="C82" t="n">
-        <v>15.3205</v>
+        <v>17.0295</v>
       </c>
       <c r="D82" t="n">
-        <v>23.5044</v>
+        <v>24.7481</v>
       </c>
       <c r="E82" t="n">
-        <v>11.8315</v>
+        <v>12.9019</v>
       </c>
       <c r="F82" t="n">
-        <v>11.2805</v>
+        <v>12.109</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>19.5588</v>
+        <v>20.8929</v>
       </c>
       <c r="C83" t="n">
-        <v>15.4112</v>
+        <v>17.101</v>
       </c>
       <c r="D83" t="n">
-        <v>24.3977</v>
+        <v>25.5987</v>
       </c>
       <c r="E83" t="n">
-        <v>11.7305</v>
+        <v>13.2302</v>
       </c>
       <c r="F83" t="n">
-        <v>11.3832</v>
+        <v>12.3775</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>19.5411</v>
+        <v>20.9571</v>
       </c>
       <c r="C84" t="n">
-        <v>15.528</v>
+        <v>17.1523</v>
       </c>
       <c r="D84" t="n">
-        <v>25.6356</v>
+        <v>26.5534</v>
       </c>
       <c r="E84" t="n">
-        <v>12.1739</v>
+        <v>13.5418</v>
       </c>
       <c r="F84" t="n">
-        <v>11.4525</v>
+        <v>12.4272</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>19.623</v>
+        <v>20.984</v>
       </c>
       <c r="C85" t="n">
-        <v>15.5663</v>
+        <v>17.1803</v>
       </c>
       <c r="D85" t="n">
-        <v>26.7805</v>
+        <v>27.3245</v>
       </c>
       <c r="E85" t="n">
-        <v>12.4582</v>
+        <v>13.9799</v>
       </c>
       <c r="F85" t="n">
-        <v>11.6298</v>
+        <v>14.0534</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>19.7167</v>
+        <v>20.9335</v>
       </c>
       <c r="C86" t="n">
-        <v>15.681</v>
+        <v>17.1549</v>
       </c>
       <c r="D86" t="n">
-        <v>27.4819</v>
+        <v>28.6016</v>
       </c>
       <c r="E86" t="n">
-        <v>12.7486</v>
+        <v>14.2838</v>
       </c>
       <c r="F86" t="n">
-        <v>11.7609</v>
+        <v>14.2711</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>19.7728</v>
+        <v>21.018</v>
       </c>
       <c r="C87" t="n">
-        <v>15.701</v>
+        <v>17.2603</v>
       </c>
       <c r="D87" t="n">
-        <v>28.5199</v>
+        <v>29.223</v>
       </c>
       <c r="E87" t="n">
-        <v>12.8726</v>
+        <v>14.4339</v>
       </c>
       <c r="F87" t="n">
-        <v>12.005</v>
+        <v>14.1588</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>19.8133</v>
+        <v>21.2054</v>
       </c>
       <c r="C88" t="n">
-        <v>16.1978</v>
+        <v>17.4682</v>
       </c>
       <c r="D88" t="n">
-        <v>29.8817</v>
+        <v>30.6872</v>
       </c>
       <c r="E88" t="n">
-        <v>12.9699</v>
+        <v>14.3842</v>
       </c>
       <c r="F88" t="n">
-        <v>11.7946</v>
+        <v>13.4248</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>19.8084</v>
+        <v>21.171</v>
       </c>
       <c r="C89" t="n">
-        <v>16.3538</v>
+        <v>17.4594</v>
       </c>
       <c r="D89" t="n">
-        <v>30.3592</v>
+        <v>32.0915</v>
       </c>
       <c r="E89" t="n">
-        <v>13.1388</v>
+        <v>14.6744</v>
       </c>
       <c r="F89" t="n">
-        <v>12.5002</v>
+        <v>13.7305</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>20.0249</v>
+        <v>21.0784</v>
       </c>
       <c r="C90" t="n">
-        <v>16.154</v>
+        <v>17.407</v>
       </c>
       <c r="D90" t="n">
-        <v>32.2882</v>
+        <v>32.4224</v>
       </c>
       <c r="E90" t="n">
-        <v>13.3968</v>
+        <v>14.9685</v>
       </c>
       <c r="F90" t="n">
-        <v>12.5224</v>
+        <v>13.8335</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>20.0131</v>
+        <v>20.8248</v>
       </c>
       <c r="C91" t="n">
-        <v>16.3629</v>
+        <v>17.1483</v>
       </c>
       <c r="D91" t="n">
-        <v>32.7393</v>
+        <v>34.8237</v>
       </c>
       <c r="E91" t="n">
-        <v>13.6609</v>
+        <v>15.4776</v>
       </c>
       <c r="F91" t="n">
-        <v>12.7708</v>
+        <v>15.5807</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>19.9934</v>
+        <v>20.812</v>
       </c>
       <c r="C92" t="n">
-        <v>16.747</v>
+        <v>17.3127</v>
       </c>
       <c r="D92" t="n">
-        <v>31.2969</v>
+        <v>32.4689</v>
       </c>
       <c r="E92" t="n">
-        <v>14.2953</v>
+        <v>14.8672</v>
       </c>
       <c r="F92" t="n">
-        <v>13.4525</v>
+        <v>16.2546</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>20.1316</v>
+        <v>20.9508</v>
       </c>
       <c r="C93" t="n">
-        <v>17.368</v>
+        <v>17.5247</v>
       </c>
       <c r="D93" t="n">
-        <v>32.4371</v>
+        <v>33.3092</v>
       </c>
       <c r="E93" t="n">
-        <v>14.4135</v>
+        <v>16.3736</v>
       </c>
       <c r="F93" t="n">
-        <v>14.1898</v>
+        <v>16.2478</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>20.4473</v>
+        <v>21.171</v>
       </c>
       <c r="C94" t="n">
-        <v>17.9207</v>
+        <v>22.2156</v>
       </c>
       <c r="D94" t="n">
-        <v>32.5471</v>
+        <v>34.1738</v>
       </c>
       <c r="E94" t="n">
-        <v>22.1769</v>
+        <v>22.4556</v>
       </c>
       <c r="F94" t="n">
-        <v>22.0053</v>
+        <v>22.8849</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>26.518</v>
+        <v>27.789</v>
       </c>
       <c r="C95" t="n">
-        <v>24.4579</v>
+        <v>22.3665</v>
       </c>
       <c r="D95" t="n">
-        <v>33.4922</v>
+        <v>34.7951</v>
       </c>
       <c r="E95" t="n">
-        <v>22.3159</v>
+        <v>22.7339</v>
       </c>
       <c r="F95" t="n">
-        <v>22.1651</v>
+        <v>22.9764</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>26.5488</v>
+        <v>27.7598</v>
       </c>
       <c r="C96" t="n">
-        <v>24.5413</v>
+        <v>22.2725</v>
       </c>
       <c r="D96" t="n">
-        <v>34.7439</v>
+        <v>35.5544</v>
       </c>
       <c r="E96" t="n">
-        <v>22.517</v>
+        <v>22.826</v>
       </c>
       <c r="F96" t="n">
-        <v>22.1812</v>
+        <v>22.9122</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>26.5239</v>
+        <v>27.9273</v>
       </c>
       <c r="C97" t="n">
-        <v>24.5053</v>
+        <v>22.3795</v>
       </c>
       <c r="D97" t="n">
-        <v>35.2549</v>
+        <v>36.7875</v>
       </c>
       <c r="E97" t="n">
-        <v>22.7898</v>
+        <v>23.12</v>
       </c>
       <c r="F97" t="n">
-        <v>22.3689</v>
+        <v>23.2357</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>26.5117</v>
+        <v>27.9754</v>
       </c>
       <c r="C98" t="n">
-        <v>24.5961</v>
+        <v>22.3991</v>
       </c>
       <c r="D98" t="n">
-        <v>36.3839</v>
+        <v>37.2368</v>
       </c>
       <c r="E98" t="n">
-        <v>22.8804</v>
+        <v>23.2196</v>
       </c>
       <c r="F98" t="n">
-        <v>22.5768</v>
+        <v>23.227</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>26.5349</v>
+        <v>27.9454</v>
       </c>
       <c r="C99" t="n">
-        <v>24.6692</v>
+        <v>22.43</v>
       </c>
       <c r="D99" t="n">
-        <v>37.2707</v>
+        <v>38.2619</v>
       </c>
       <c r="E99" t="n">
-        <v>23.0786</v>
+        <v>23.3482</v>
       </c>
       <c r="F99" t="n">
-        <v>22.6099</v>
+        <v>23.3532</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>26.5663</v>
+        <v>28.0064</v>
       </c>
       <c r="C100" t="n">
-        <v>24.7451</v>
+        <v>22.4364</v>
       </c>
       <c r="D100" t="n">
-        <v>38.0899</v>
+        <v>39.1288</v>
       </c>
       <c r="E100" t="n">
-        <v>23.2508</v>
+        <v>23.6051</v>
       </c>
       <c r="F100" t="n">
-        <v>22.7605</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>26.56</v>
+        <v>27.9074</v>
       </c>
       <c r="C101" t="n">
-        <v>24.8074</v>
+        <v>22.4914</v>
       </c>
       <c r="D101" t="n">
-        <v>38.896</v>
+        <v>40.1793</v>
       </c>
       <c r="E101" t="n">
-        <v>23.4255</v>
+        <v>23.7377</v>
       </c>
       <c r="F101" t="n">
-        <v>22.8582</v>
+        <v>23.6468</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>26.5774</v>
+        <v>27.8962</v>
       </c>
       <c r="C102" t="n">
-        <v>24.8507</v>
+        <v>22.5503</v>
       </c>
       <c r="D102" t="n">
-        <v>39.826</v>
+        <v>41.2896</v>
       </c>
       <c r="E102" t="n">
-        <v>23.7022</v>
+        <v>23.8925</v>
       </c>
       <c r="F102" t="n">
-        <v>22.9923</v>
+        <v>23.8413</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>26.6551</v>
+        <v>27.9578</v>
       </c>
       <c r="C103" t="n">
-        <v>24.9785</v>
+        <v>22.5783</v>
       </c>
       <c r="D103" t="n">
-        <v>40.9176</v>
+        <v>42.3299</v>
       </c>
       <c r="E103" t="n">
-        <v>23.8469</v>
+        <v>24.1216</v>
       </c>
       <c r="F103" t="n">
-        <v>23.2803</v>
+        <v>24.7188</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>26.7078</v>
+        <v>28.0214</v>
       </c>
       <c r="C104" t="n">
-        <v>25.1409</v>
+        <v>22.6907</v>
       </c>
       <c r="D104" t="n">
-        <v>41.9706</v>
+        <v>43.4039</v>
       </c>
       <c r="E104" t="n">
-        <v>24.14</v>
+        <v>24.307</v>
       </c>
       <c r="F104" t="n">
-        <v>23.512</v>
+        <v>24.3794</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>26.793</v>
+        <v>28.1497</v>
       </c>
       <c r="C105" t="n">
-        <v>25.3291</v>
+        <v>22.7492</v>
       </c>
       <c r="D105" t="n">
-        <v>43.0336</v>
+        <v>44.1246</v>
       </c>
       <c r="E105" t="n">
-        <v>24.3506</v>
+        <v>24.5175</v>
       </c>
       <c r="F105" t="n">
-        <v>23.9746</v>
+        <v>24.616</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>26.9487</v>
+        <v>28.3763</v>
       </c>
       <c r="C106" t="n">
-        <v>25.4999</v>
+        <v>22.9823</v>
       </c>
       <c r="D106" t="n">
-        <v>44.0613</v>
+        <v>45.6499</v>
       </c>
       <c r="E106" t="n">
-        <v>24.7221</v>
+        <v>24.7899</v>
       </c>
       <c r="F106" t="n">
-        <v>24.3396</v>
+        <v>25.4172</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>27.1389</v>
+        <v>28.4115</v>
       </c>
       <c r="C107" t="n">
-        <v>25.9183</v>
+        <v>23.1371</v>
       </c>
       <c r="D107" t="n">
-        <v>38.0179</v>
+        <v>39.6241</v>
       </c>
       <c r="E107" t="n">
-        <v>25.0465</v>
+        <v>25.1749</v>
       </c>
       <c r="F107" t="n">
-        <v>24.9396</v>
+        <v>26.5615</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>27.3684</v>
+        <v>28.5968</v>
       </c>
       <c r="C108" t="n">
-        <v>26.4466</v>
+        <v>23.9664</v>
       </c>
       <c r="D108" t="n">
-        <v>38.8469</v>
+        <v>40.3241</v>
       </c>
       <c r="E108" t="n">
-        <v>27.9936</v>
+        <v>29.3928</v>
       </c>
       <c r="F108" t="n">
-        <v>27.7395</v>
+        <v>28.8091</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>27.7995</v>
+        <v>28.9875</v>
       </c>
       <c r="C109" t="n">
-        <v>27.3722</v>
+        <v>24.0544</v>
       </c>
       <c r="D109" t="n">
-        <v>39.3663</v>
+        <v>41.025</v>
       </c>
       <c r="E109" t="n">
-        <v>28.2815</v>
+        <v>29.5382</v>
       </c>
       <c r="F109" t="n">
-        <v>27.9577</v>
+        <v>29.0705</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>30.3889</v>
+        <v>32.0868</v>
       </c>
       <c r="C110" t="n">
-        <v>30.3375</v>
+        <v>24.1157</v>
       </c>
       <c r="D110" t="n">
-        <v>40.217</v>
+        <v>41.7092</v>
       </c>
       <c r="E110" t="n">
-        <v>28.5712</v>
+        <v>29.7661</v>
       </c>
       <c r="F110" t="n">
-        <v>28.0556</v>
+        <v>29.0356</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>30.3847</v>
+        <v>31.8415</v>
       </c>
       <c r="C111" t="n">
-        <v>30.5374</v>
+        <v>24.0959</v>
       </c>
       <c r="D111" t="n">
-        <v>40.8982</v>
+        <v>42.4794</v>
       </c>
       <c r="E111" t="n">
-        <v>28.823</v>
+        <v>29.8735</v>
       </c>
       <c r="F111" t="n">
-        <v>28.267</v>
+        <v>29.6432</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>30.435</v>
+        <v>31.9605</v>
       </c>
       <c r="C112" t="n">
-        <v>30.576</v>
+        <v>24.2584</v>
       </c>
       <c r="D112" t="n">
-        <v>41.675</v>
+        <v>43.2867</v>
       </c>
       <c r="E112" t="n">
-        <v>29.0868</v>
+        <v>30.1387</v>
       </c>
       <c r="F112" t="n">
-        <v>28.5295</v>
+        <v>29.8973</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>30.5721</v>
+        <v>32.0649</v>
       </c>
       <c r="C113" t="n">
-        <v>30.526</v>
+        <v>24.301</v>
       </c>
       <c r="D113" t="n">
-        <v>42.2982</v>
+        <v>44.1893</v>
       </c>
       <c r="E113" t="n">
-        <v>29.4429</v>
+        <v>30.2795</v>
       </c>
       <c r="F113" t="n">
-        <v>28.7124</v>
+        <v>30.0086</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>30.273</v>
+        <v>31.2677</v>
       </c>
       <c r="C114" t="n">
-        <v>30.9739</v>
+        <v>24.3562</v>
       </c>
       <c r="D114" t="n">
-        <v>43.2679</v>
+        <v>45.0463</v>
       </c>
       <c r="E114" t="n">
-        <v>29.5717</v>
+        <v>30.3915</v>
       </c>
       <c r="F114" t="n">
-        <v>28.9505</v>
+        <v>30.2929</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>30.6368</v>
+        <v>32.2765</v>
       </c>
       <c r="C115" t="n">
-        <v>30.8972</v>
+        <v>24.4562</v>
       </c>
       <c r="D115" t="n">
-        <v>44.1311</v>
+        <v>45.8362</v>
       </c>
       <c r="E115" t="n">
-        <v>29.9444</v>
+        <v>30.8263</v>
       </c>
       <c r="F115" t="n">
-        <v>29.1928</v>
+        <v>30.6573</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>30.4975</v>
+        <v>32.0813</v>
       </c>
       <c r="C116" t="n">
-        <v>30.9126</v>
+        <v>24.5153</v>
       </c>
       <c r="D116" t="n">
-        <v>45.1484</v>
+        <v>46.8215</v>
       </c>
       <c r="E116" t="n">
-        <v>30.1871</v>
+        <v>31.1155</v>
       </c>
       <c r="F116" t="n">
-        <v>29.5601</v>
+        <v>30.9789</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>30.546</v>
+        <v>32.0638</v>
       </c>
       <c r="C117" t="n">
-        <v>30.9605</v>
+        <v>24.7329</v>
       </c>
       <c r="D117" t="n">
-        <v>46.2662</v>
+        <v>47.886</v>
       </c>
       <c r="E117" t="n">
-        <v>30.4921</v>
+        <v>31.4692</v>
       </c>
       <c r="F117" t="n">
-        <v>29.8865</v>
+        <v>31.4838</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>30.5644</v>
+        <v>32.1927</v>
       </c>
       <c r="C118" t="n">
-        <v>31.4041</v>
+        <v>24.8182</v>
       </c>
       <c r="D118" t="n">
-        <v>47.3417</v>
+        <v>49.101</v>
       </c>
       <c r="E118" t="n">
-        <v>30.8474</v>
+        <v>31.7204</v>
       </c>
       <c r="F118" t="n">
-        <v>30.348</v>
+        <v>32.0301</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>30.5691</v>
+        <v>32.228</v>
       </c>
       <c r="C119" t="n">
-        <v>31.2003</v>
+        <v>25.0065</v>
       </c>
       <c r="D119" t="n">
-        <v>48.5061</v>
+        <v>50.3682</v>
       </c>
       <c r="E119" t="n">
-        <v>31.1215</v>
+        <v>32.0263</v>
       </c>
       <c r="F119" t="n">
-        <v>30.9134</v>
+        <v>32.5007</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>30.8173</v>
+        <v>32.3282</v>
       </c>
       <c r="C120" t="n">
-        <v>31.5495</v>
+        <v>25.3107</v>
       </c>
       <c r="D120" t="n">
-        <v>49.2534</v>
+        <v>51.4226</v>
       </c>
       <c r="E120" t="n">
-        <v>31.6044</v>
+        <v>32.4161</v>
       </c>
       <c r="F120" t="n">
-        <v>31.5228</v>
+        <v>33.1285</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>30.8027</v>
+        <v>32.4332</v>
       </c>
       <c r="C121" t="n">
-        <v>31.9013</v>
+        <v>25.5709</v>
       </c>
       <c r="D121" t="n">
-        <v>41.164</v>
+        <v>42.6547</v>
       </c>
       <c r="E121" t="n">
-        <v>32.2851</v>
+        <v>32.8575</v>
       </c>
       <c r="F121" t="n">
-        <v>32.5122</v>
+        <v>34.1155</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>31.1642</v>
+        <v>32.3168</v>
       </c>
       <c r="C122" t="n">
-        <v>32.4505</v>
+        <v>26.7545</v>
       </c>
       <c r="D122" t="n">
-        <v>41.7831</v>
+        <v>43.3435</v>
       </c>
       <c r="E122" t="n">
-        <v>32.9684</v>
+        <v>33.169</v>
       </c>
       <c r="F122" t="n">
-        <v>33.8598</v>
+        <v>35.3217</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>31.7547</v>
+        <v>33.1899</v>
       </c>
       <c r="C123" t="n">
-        <v>33.3985</v>
+        <v>26.8488</v>
       </c>
       <c r="D123" t="n">
-        <v>42.4838</v>
+        <v>43.7211</v>
       </c>
       <c r="E123" t="n">
-        <v>31.9622</v>
+        <v>35.2163</v>
       </c>
       <c r="F123" t="n">
-        <v>31.6018</v>
+        <v>33.7431</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>38.2078</v>
+        <v>41.2888</v>
       </c>
       <c r="C124" t="n">
-        <v>39.0054</v>
+        <v>26.957</v>
       </c>
       <c r="D124" t="n">
-        <v>42.8044</v>
+        <v>44.9487</v>
       </c>
       <c r="E124" t="n">
-        <v>32.2866</v>
+        <v>35.561</v>
       </c>
       <c r="F124" t="n">
-        <v>31.7904</v>
+        <v>34.0655</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>39.0567</v>
+        <v>41.5978</v>
       </c>
       <c r="C125" t="n">
-        <v>39.1014</v>
+        <v>27.1276</v>
       </c>
       <c r="D125" t="n">
-        <v>43.8953</v>
+        <v>45.6514</v>
       </c>
       <c r="E125" t="n">
-        <v>32.6239</v>
+        <v>35.9532</v>
       </c>
       <c r="F125" t="n">
-        <v>32.0394</v>
+        <v>34.4141</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>38.4106</v>
+        <v>41.4049</v>
       </c>
       <c r="C126" t="n">
-        <v>39.1398</v>
+        <v>27.2426</v>
       </c>
       <c r="D126" t="n">
-        <v>44.4101</v>
+        <v>46.2951</v>
       </c>
       <c r="E126" t="n">
-        <v>33.0252</v>
+        <v>36.2191</v>
       </c>
       <c r="F126" t="n">
-        <v>32.3628</v>
+        <v>34.6699</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>39.0225</v>
+        <v>41.5552</v>
       </c>
       <c r="C127" t="n">
-        <v>39.2094</v>
+        <v>27.2835</v>
       </c>
       <c r="D127" t="n">
-        <v>45.3126</v>
+        <v>47.0249</v>
       </c>
       <c r="E127" t="n">
-        <v>33.3475</v>
+        <v>36.6127</v>
       </c>
       <c r="F127" t="n">
-        <v>32.5929</v>
+        <v>34.8703</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>38.333</v>
+        <v>41.4871</v>
       </c>
       <c r="C128" t="n">
-        <v>39.2873</v>
+        <v>27.5377</v>
       </c>
       <c r="D128" t="n">
-        <v>46.1383</v>
+        <v>47.7448</v>
       </c>
       <c r="E128" t="n">
-        <v>33.6781</v>
+        <v>36.9367</v>
       </c>
       <c r="F128" t="n">
-        <v>32.9522</v>
+        <v>35.3515</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>39.1576</v>
+        <v>41.5289</v>
       </c>
       <c r="C129" t="n">
-        <v>39.3193</v>
+        <v>27.7614</v>
       </c>
       <c r="D129" t="n">
-        <v>47.3812</v>
+        <v>49.1887</v>
       </c>
       <c r="E129" t="n">
-        <v>34.0644</v>
+        <v>37.2742</v>
       </c>
       <c r="F129" t="n">
-        <v>33.3312</v>
+        <v>35.7426</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>39.1192</v>
+        <v>41.3697</v>
       </c>
       <c r="C130" t="n">
-        <v>39.5003</v>
+        <v>27.893</v>
       </c>
       <c r="D130" t="n">
-        <v>48.1236</v>
+        <v>50.0263</v>
       </c>
       <c r="E130" t="n">
-        <v>34.4544</v>
+        <v>37.6437</v>
       </c>
       <c r="F130" t="n">
-        <v>33.7828</v>
+        <v>36.1143</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>39.1716</v>
+        <v>41.5755</v>
       </c>
       <c r="C131" t="n">
-        <v>39.5776</v>
+        <v>28.2815</v>
       </c>
       <c r="D131" t="n">
-        <v>48.998</v>
+        <v>50.8919</v>
       </c>
       <c r="E131" t="n">
-        <v>34.8872</v>
+        <v>38.0007</v>
       </c>
       <c r="F131" t="n">
-        <v>34.3113</v>
+        <v>36.6357</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>39.3529</v>
+        <v>41.5746</v>
       </c>
       <c r="C132" t="n">
-        <v>39.7235</v>
+        <v>28.5736</v>
       </c>
       <c r="D132" t="n">
-        <v>49.5968</v>
+        <v>51.9928</v>
       </c>
       <c r="E132" t="n">
-        <v>35.346</v>
+        <v>38.3849</v>
       </c>
       <c r="F132" t="n">
-        <v>34.8686</v>
+        <v>37.2512</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>39.3572</v>
+        <v>41.621</v>
       </c>
       <c r="C133" t="n">
-        <v>39.9652</v>
+        <v>28.7116</v>
       </c>
       <c r="D133" t="n">
-        <v>51.4093</v>
+        <v>52.9956</v>
       </c>
       <c r="E133" t="n">
-        <v>35.6643</v>
+        <v>38.9141</v>
       </c>
       <c r="F133" t="n">
-        <v>35.5496</v>
+        <v>37.9694</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>39.3809</v>
+        <v>41.6204</v>
       </c>
       <c r="C134" t="n">
-        <v>40.3583</v>
+        <v>29.1277</v>
       </c>
       <c r="D134" t="n">
-        <v>52.3322</v>
+        <v>54.4649</v>
       </c>
       <c r="E134" t="n">
-        <v>36.2334</v>
+        <v>39.4411</v>
       </c>
       <c r="F134" t="n">
-        <v>36.3745</v>
+        <v>38.8041</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>39.7593</v>
+        <v>41.7171</v>
       </c>
       <c r="C135" t="n">
-        <v>40.6448</v>
+        <v>29.6446</v>
       </c>
       <c r="D135" t="n">
-        <v>42.9107</v>
+        <v>44.597</v>
       </c>
       <c r="E135" t="n">
-        <v>36.9261</v>
+        <v>40.2021</v>
       </c>
       <c r="F135" t="n">
-        <v>37.5209</v>
+        <v>39.8262</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>39.7099</v>
+        <v>42.262</v>
       </c>
       <c r="C136" t="n">
-        <v>41.3079</v>
+        <v>29.5943</v>
       </c>
       <c r="D136" t="n">
-        <v>43.5228</v>
+        <v>45.2446</v>
       </c>
       <c r="E136" t="n">
-        <v>38.1931</v>
+        <v>41.0479</v>
       </c>
       <c r="F136" t="n">
-        <v>39.1079</v>
+        <v>41.5385</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>40.159</v>
+        <v>42.3239</v>
       </c>
       <c r="C137" t="n">
-        <v>42.1424</v>
+        <v>29.7078</v>
       </c>
       <c r="D137" t="n">
-        <v>43.9518</v>
+        <v>45.7577</v>
       </c>
       <c r="E137" t="n">
-        <v>33.8743</v>
+        <v>38.4343</v>
       </c>
       <c r="F137" t="n">
-        <v>33.7396</v>
+        <v>36.901</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>45.8745</v>
+        <v>48.5338</v>
       </c>
       <c r="C138" t="n">
-        <v>43.8124</v>
+        <v>29.8913</v>
       </c>
       <c r="D138" t="n">
-        <v>44.6342</v>
+        <v>46.7919</v>
       </c>
       <c r="E138" t="n">
-        <v>34.3391</v>
+        <v>38.7198</v>
       </c>
       <c r="F138" t="n">
-        <v>33.9733</v>
+        <v>37.0239</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>45.8539</v>
+        <v>48.5154</v>
       </c>
       <c r="C139" t="n">
-        <v>43.8477</v>
+        <v>30.0798</v>
       </c>
       <c r="D139" t="n">
-        <v>45.5539</v>
+        <v>47.3973</v>
       </c>
       <c r="E139" t="n">
-        <v>34.6238</v>
+        <v>39.0788</v>
       </c>
       <c r="F139" t="n">
-        <v>34.2562</v>
+        <v>37.3076</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>45.8159</v>
+        <v>48.4576</v>
       </c>
       <c r="C140" t="n">
-        <v>43.3142</v>
+        <v>30.2574</v>
       </c>
       <c r="D140" t="n">
-        <v>45.9668</v>
+        <v>48.0166</v>
       </c>
       <c r="E140" t="n">
-        <v>35.1013</v>
+        <v>39.4429</v>
       </c>
       <c r="F140" t="n">
-        <v>34.6365</v>
+        <v>37.6476</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>45.0648</v>
+        <v>48.4843</v>
       </c>
       <c r="C141" t="n">
-        <v>44.0161</v>
+        <v>30.4642</v>
       </c>
       <c r="D141" t="n">
-        <v>47.0566</v>
+        <v>49.1127</v>
       </c>
       <c r="E141" t="n">
-        <v>35.4346</v>
+        <v>39.8194</v>
       </c>
       <c r="F141" t="n">
-        <v>34.9459</v>
+        <v>37.927</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>44.9816</v>
+        <v>48.0922</v>
       </c>
       <c r="C142" t="n">
-        <v>44.1419</v>
+        <v>30.6917</v>
       </c>
       <c r="D142" t="n">
-        <v>47.9874</v>
+        <v>49.7583</v>
       </c>
       <c r="E142" t="n">
-        <v>35.8391</v>
+        <v>40.1541</v>
       </c>
       <c r="F142" t="n">
-        <v>35.2698</v>
+        <v>38.2781</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>45.8257</v>
+        <v>48.4486</v>
       </c>
       <c r="C143" t="n">
-        <v>44.2426</v>
+        <v>30.9661</v>
       </c>
       <c r="D143" t="n">
-        <v>48.56</v>
+        <v>50.7215</v>
       </c>
       <c r="E143" t="n">
-        <v>36.2584</v>
+        <v>40.5437</v>
       </c>
       <c r="F143" t="n">
-        <v>35.7237</v>
+        <v>38.771</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Scattered successful looukp.xlsx
+++ b/gcc-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>4.60029</v>
+        <v>4.44811</v>
       </c>
       <c r="C2" t="n">
-        <v>3.66681</v>
+        <v>4.09577</v>
       </c>
       <c r="D2" t="n">
-        <v>8.425840000000001</v>
+        <v>8.281129999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>4.10099</v>
+        <v>4.38778</v>
       </c>
       <c r="F2" t="n">
-        <v>4.10008</v>
+        <v>3.14298</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>4.3508</v>
+        <v>4.20393</v>
       </c>
       <c r="C3" t="n">
-        <v>3.55964</v>
+        <v>3.61116</v>
       </c>
       <c r="D3" t="n">
-        <v>8.66422</v>
+        <v>8.479100000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>4.12221</v>
+        <v>3.46813</v>
       </c>
       <c r="F3" t="n">
-        <v>4.02933</v>
+        <v>4.16693</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>4.3558</v>
+        <v>3.46731</v>
       </c>
       <c r="C4" t="n">
-        <v>3.59211</v>
+        <v>3.04528</v>
       </c>
       <c r="D4" t="n">
-        <v>9.65333</v>
+        <v>9.1523</v>
       </c>
       <c r="E4" t="n">
-        <v>3.80313</v>
+        <v>3.41772</v>
       </c>
       <c r="F4" t="n">
-        <v>3.38461</v>
+        <v>4.11862</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>4.0979</v>
+        <v>4.07126</v>
       </c>
       <c r="C5" t="n">
-        <v>3.29229</v>
+        <v>3.5376</v>
       </c>
       <c r="D5" t="n">
-        <v>10.3697</v>
+        <v>10.2037</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7964</v>
+        <v>3.4774</v>
       </c>
       <c r="F5" t="n">
-        <v>3.23982</v>
+        <v>4.0725</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.15955</v>
+        <v>4.01756</v>
       </c>
       <c r="C6" t="n">
-        <v>3.32502</v>
+        <v>3.50048</v>
       </c>
       <c r="D6" t="n">
-        <v>11.007</v>
+        <v>10.9571</v>
       </c>
       <c r="E6" t="n">
-        <v>3.49141</v>
+        <v>3.83148</v>
       </c>
       <c r="F6" t="n">
-        <v>3.91336</v>
+        <v>3.68789</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>3.50898</v>
+        <v>4.2626</v>
       </c>
       <c r="C7" t="n">
-        <v>3.101</v>
+        <v>3.75504</v>
       </c>
       <c r="D7" t="n">
-        <v>7.27519</v>
+        <v>6.9781</v>
       </c>
       <c r="E7" t="n">
-        <v>3.76176</v>
+        <v>4.28207</v>
       </c>
       <c r="F7" t="n">
-        <v>4.22089</v>
+        <v>3.5644</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>3.69302</v>
+        <v>4.29548</v>
       </c>
       <c r="C8" t="n">
-        <v>3.49795</v>
+        <v>3.84619</v>
       </c>
       <c r="D8" t="n">
-        <v>7.52274</v>
+        <v>7.41715</v>
       </c>
       <c r="E8" t="n">
-        <v>3.78639</v>
+        <v>4.3667</v>
       </c>
       <c r="F8" t="n">
-        <v>4.37782</v>
+        <v>3.67412</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>4.48415</v>
+        <v>3.5785</v>
       </c>
       <c r="C9" t="n">
-        <v>3.47312</v>
+        <v>4.05681</v>
       </c>
       <c r="D9" t="n">
-        <v>7.83258</v>
+        <v>7.71442</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3144</v>
+        <v>4.40286</v>
       </c>
       <c r="F9" t="n">
-        <v>3.55359</v>
+        <v>3.68205</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>4.18545</v>
+        <v>4.22764</v>
       </c>
       <c r="C10" t="n">
-        <v>3.61413</v>
+        <v>4.0725</v>
       </c>
       <c r="D10" t="n">
-        <v>8.264570000000001</v>
+        <v>8.247249999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>4.34431</v>
+        <v>4.43533</v>
       </c>
       <c r="F10" t="n">
-        <v>3.57686</v>
+        <v>3.64359</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>4.11965</v>
+        <v>4.83817</v>
       </c>
       <c r="C11" t="n">
-        <v>3.69118</v>
+        <v>4.21156</v>
       </c>
       <c r="D11" t="n">
-        <v>8.68117</v>
+        <v>8.70209</v>
       </c>
       <c r="E11" t="n">
-        <v>4.38094</v>
+        <v>4.79023</v>
       </c>
       <c r="F11" t="n">
-        <v>3.6003</v>
+        <v>3.72354</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>4.11567</v>
+        <v>4.0727</v>
       </c>
       <c r="C12" t="n">
-        <v>3.70302</v>
+        <v>4.10211</v>
       </c>
       <c r="D12" t="n">
-        <v>9.26296</v>
+        <v>9.34553</v>
       </c>
       <c r="E12" t="n">
-        <v>4.38862</v>
+        <v>4.85979</v>
       </c>
       <c r="F12" t="n">
-        <v>3.61355</v>
+        <v>3.69175</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>4.20483</v>
+        <v>4.92601</v>
       </c>
       <c r="C13" t="n">
-        <v>3.61049</v>
+        <v>4.1735</v>
       </c>
       <c r="D13" t="n">
-        <v>9.849019999999999</v>
+        <v>9.947609999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4989</v>
+        <v>4.67995</v>
       </c>
       <c r="F13" t="n">
-        <v>3.62975</v>
+        <v>3.85211</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>5.01591</v>
+        <v>5.02088</v>
       </c>
       <c r="C14" t="n">
-        <v>3.80946</v>
+        <v>4.22971</v>
       </c>
       <c r="D14" t="n">
-        <v>10.1506</v>
+        <v>10.3041</v>
       </c>
       <c r="E14" t="n">
-        <v>4.51359</v>
+        <v>4.5613</v>
       </c>
       <c r="F14" t="n">
-        <v>3.66956</v>
+        <v>3.71661</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>4.27795</v>
+        <v>4.91517</v>
       </c>
       <c r="C15" t="n">
-        <v>3.69653</v>
+        <v>4.26049</v>
       </c>
       <c r="D15" t="n">
-        <v>10.7055</v>
+        <v>10.7547</v>
       </c>
       <c r="E15" t="n">
-        <v>4.41065</v>
+        <v>4.65569</v>
       </c>
       <c r="F15" t="n">
-        <v>3.683</v>
+        <v>3.83812</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>5.03224</v>
+        <v>4.91084</v>
       </c>
       <c r="C16" t="n">
-        <v>3.86389</v>
+        <v>4.27734</v>
       </c>
       <c r="D16" t="n">
-        <v>11.2173</v>
+        <v>11.3351</v>
       </c>
       <c r="E16" t="n">
-        <v>4.51931</v>
+        <v>5.0848</v>
       </c>
       <c r="F16" t="n">
-        <v>3.68972</v>
+        <v>3.90214</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>4.91649</v>
+        <v>4.9048</v>
       </c>
       <c r="C17" t="n">
-        <v>3.90666</v>
+        <v>4.38058</v>
       </c>
       <c r="D17" t="n">
-        <v>11.6257</v>
+        <v>11.75</v>
       </c>
       <c r="E17" t="n">
-        <v>4.64565</v>
+        <v>4.7632</v>
       </c>
       <c r="F17" t="n">
-        <v>3.72121</v>
+        <v>3.79186</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>5.04846</v>
+        <v>4.90461</v>
       </c>
       <c r="C18" t="n">
-        <v>3.9569</v>
+        <v>4.37474</v>
       </c>
       <c r="D18" t="n">
-        <v>12.1549</v>
+        <v>12.1572</v>
       </c>
       <c r="E18" t="n">
-        <v>4.75598</v>
+        <v>5.07974</v>
       </c>
       <c r="F18" t="n">
-        <v>3.79871</v>
+        <v>3.85752</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>5.06192</v>
+        <v>5.03685</v>
       </c>
       <c r="C19" t="n">
-        <v>4.0065</v>
+        <v>4.42545</v>
       </c>
       <c r="D19" t="n">
-        <v>12.7293</v>
+        <v>12.8115</v>
       </c>
       <c r="E19" t="n">
-        <v>4.62408</v>
+        <v>4.81494</v>
       </c>
       <c r="F19" t="n">
-        <v>3.78234</v>
+        <v>3.8955</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>4.95704</v>
+        <v>4.94433</v>
       </c>
       <c r="C20" t="n">
-        <v>4.06116</v>
+        <v>4.5874</v>
       </c>
       <c r="D20" t="n">
-        <v>13.0252</v>
+        <v>13.233</v>
       </c>
       <c r="E20" t="n">
-        <v>4.85583</v>
+        <v>5.20338</v>
       </c>
       <c r="F20" t="n">
-        <v>3.82406</v>
+        <v>3.96111</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>5.1001</v>
+        <v>5.008</v>
       </c>
       <c r="C21" t="n">
-        <v>4.12443</v>
+        <v>4.65448</v>
       </c>
       <c r="D21" t="n">
-        <v>9.278420000000001</v>
+        <v>9.39958</v>
       </c>
       <c r="E21" t="n">
-        <v>4.95</v>
+        <v>4.63415</v>
       </c>
       <c r="F21" t="n">
-        <v>4.65464</v>
+        <v>4.30929</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>5.12371</v>
+        <v>5.05271</v>
       </c>
       <c r="C22" t="n">
-        <v>3.80311</v>
+        <v>3.87495</v>
       </c>
       <c r="D22" t="n">
-        <v>9.52345</v>
+        <v>9.67878</v>
       </c>
       <c r="E22" t="n">
-        <v>5.25453</v>
+        <v>4.62407</v>
       </c>
       <c r="F22" t="n">
-        <v>4.90173</v>
+        <v>4.40528</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>4.82379</v>
+        <v>5.19263</v>
       </c>
       <c r="C23" t="n">
-        <v>3.74553</v>
+        <v>3.85846</v>
       </c>
       <c r="D23" t="n">
-        <v>9.86543</v>
+        <v>10.0374</v>
       </c>
       <c r="E23" t="n">
-        <v>4.54933</v>
+        <v>4.71815</v>
       </c>
       <c r="F23" t="n">
-        <v>4.42677</v>
+        <v>4.39732</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>5.16585</v>
+        <v>5.21734</v>
       </c>
       <c r="C24" t="n">
-        <v>3.78148</v>
+        <v>3.92319</v>
       </c>
       <c r="D24" t="n">
-        <v>10.102</v>
+        <v>10.3035</v>
       </c>
       <c r="E24" t="n">
-        <v>4.50996</v>
+        <v>4.7594</v>
       </c>
       <c r="F24" t="n">
-        <v>4.47123</v>
+        <v>4.42998</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>5.18745</v>
+        <v>5.20475</v>
       </c>
       <c r="C25" t="n">
-        <v>3.8371</v>
+        <v>3.93495</v>
       </c>
       <c r="D25" t="n">
-        <v>10.5112</v>
+        <v>10.7166</v>
       </c>
       <c r="E25" t="n">
-        <v>4.62446</v>
+        <v>4.70782</v>
       </c>
       <c r="F25" t="n">
-        <v>4.46407</v>
+        <v>4.48177</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>5.19662</v>
+        <v>5.23282</v>
       </c>
       <c r="C26" t="n">
-        <v>3.87528</v>
+        <v>3.93236</v>
       </c>
       <c r="D26" t="n">
-        <v>10.9287</v>
+        <v>11.1003</v>
       </c>
       <c r="E26" t="n">
-        <v>4.60612</v>
+        <v>4.73339</v>
       </c>
       <c r="F26" t="n">
-        <v>4.35985</v>
+        <v>4.30626</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>4.97468</v>
+        <v>5.18412</v>
       </c>
       <c r="C27" t="n">
-        <v>3.87799</v>
+        <v>3.96132</v>
       </c>
       <c r="D27" t="n">
-        <v>11.3204</v>
+        <v>11.5633</v>
       </c>
       <c r="E27" t="n">
-        <v>4.70639</v>
+        <v>4.78441</v>
       </c>
       <c r="F27" t="n">
-        <v>4.38807</v>
+        <v>4.32961</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>5.21326</v>
+        <v>5.11478</v>
       </c>
       <c r="C28" t="n">
-        <v>3.89943</v>
+        <v>3.94297</v>
       </c>
       <c r="D28" t="n">
-        <v>11.8039</v>
+        <v>11.9448</v>
       </c>
       <c r="E28" t="n">
-        <v>4.72271</v>
+        <v>4.81822</v>
       </c>
       <c r="F28" t="n">
-        <v>4.41895</v>
+        <v>4.3567</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>4.98739</v>
+        <v>5.20096</v>
       </c>
       <c r="C29" t="n">
-        <v>3.92495</v>
+        <v>4.03007</v>
       </c>
       <c r="D29" t="n">
-        <v>12.2489</v>
+        <v>12.3811</v>
       </c>
       <c r="E29" t="n">
-        <v>4.70781</v>
+        <v>4.81367</v>
       </c>
       <c r="F29" t="n">
-        <v>4.44743</v>
+        <v>4.38647</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>5.01184</v>
+        <v>5.29204</v>
       </c>
       <c r="C30" t="n">
-        <v>3.94954</v>
+        <v>4.25967</v>
       </c>
       <c r="D30" t="n">
-        <v>12.5686</v>
+        <v>12.8255</v>
       </c>
       <c r="E30" t="n">
-        <v>4.79641</v>
+        <v>4.90639</v>
       </c>
       <c r="F30" t="n">
-        <v>4.46586</v>
+        <v>4.51076</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>5.25298</v>
+        <v>5.18511</v>
       </c>
       <c r="C31" t="n">
-        <v>3.99077</v>
+        <v>4.10326</v>
       </c>
       <c r="D31" t="n">
-        <v>13.0811</v>
+        <v>13.2985</v>
       </c>
       <c r="E31" t="n">
-        <v>4.77272</v>
+        <v>4.89439</v>
       </c>
       <c r="F31" t="n">
-        <v>4.50375</v>
+        <v>4.55215</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>5.0283</v>
+        <v>5.13197</v>
       </c>
       <c r="C32" t="n">
-        <v>3.92095</v>
+        <v>4.15122</v>
       </c>
       <c r="D32" t="n">
-        <v>13.3214</v>
+        <v>13.6524</v>
       </c>
       <c r="E32" t="n">
-        <v>4.89802</v>
+        <v>4.97214</v>
       </c>
       <c r="F32" t="n">
-        <v>4.69883</v>
+        <v>4.57224</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>5.26346</v>
+        <v>5.26896</v>
       </c>
       <c r="C33" t="n">
-        <v>4.05653</v>
+        <v>4.19846</v>
       </c>
       <c r="D33" t="n">
-        <v>13.7505</v>
+        <v>14.0349</v>
       </c>
       <c r="E33" t="n">
-        <v>4.91015</v>
+        <v>4.95002</v>
       </c>
       <c r="F33" t="n">
-        <v>4.57891</v>
+        <v>4.66145</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.29077</v>
+        <v>5.16125</v>
       </c>
       <c r="C34" t="n">
-        <v>4.12667</v>
+        <v>4.25952</v>
       </c>
       <c r="D34" t="n">
-        <v>14.0969</v>
+        <v>14.2256</v>
       </c>
       <c r="E34" t="n">
-        <v>4.92269</v>
+        <v>4.77667</v>
       </c>
       <c r="F34" t="n">
-        <v>4.80021</v>
+        <v>4.65062</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>5.1475</v>
+        <v>5.39174</v>
       </c>
       <c r="C35" t="n">
-        <v>4.25112</v>
+        <v>4.33231</v>
       </c>
       <c r="D35" t="n">
-        <v>10.0978</v>
+        <v>10.0562</v>
       </c>
       <c r="E35" t="n">
-        <v>5.34663</v>
+        <v>4.47687</v>
       </c>
       <c r="F35" t="n">
-        <v>5.37304</v>
+        <v>4.49901</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>5.15021</v>
+        <v>5.25162</v>
       </c>
       <c r="C36" t="n">
-        <v>4.22839</v>
+        <v>4.53077</v>
       </c>
       <c r="D36" t="n">
-        <v>10.5464</v>
+        <v>10.5268</v>
       </c>
       <c r="E36" t="n">
-        <v>6.00541</v>
+        <v>4.45141</v>
       </c>
       <c r="F36" t="n">
-        <v>5.95909</v>
+        <v>4.64612</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>5.46933</v>
+        <v>5.55642</v>
       </c>
       <c r="C37" t="n">
-        <v>4.15614</v>
+        <v>4.1713</v>
       </c>
       <c r="D37" t="n">
-        <v>11.0735</v>
+        <v>11.3789</v>
       </c>
       <c r="E37" t="n">
-        <v>4.8145</v>
+        <v>4.52349</v>
       </c>
       <c r="F37" t="n">
-        <v>4.77883</v>
+        <v>4.68547</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>5.2327</v>
+        <v>5.39557</v>
       </c>
       <c r="C38" t="n">
-        <v>4.03041</v>
+        <v>3.88767</v>
       </c>
       <c r="D38" t="n">
-        <v>11.5849</v>
+        <v>11.0693</v>
       </c>
       <c r="E38" t="n">
-        <v>4.85403</v>
+        <v>4.55816</v>
       </c>
       <c r="F38" t="n">
-        <v>4.81601</v>
+        <v>4.68113</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>5.39854</v>
+        <v>5.40721</v>
       </c>
       <c r="C39" t="n">
-        <v>4.09652</v>
+        <v>3.78178</v>
       </c>
       <c r="D39" t="n">
-        <v>11.8735</v>
+        <v>11.7938</v>
       </c>
       <c r="E39" t="n">
-        <v>4.87555</v>
+        <v>4.5955</v>
       </c>
       <c r="F39" t="n">
-        <v>4.85547</v>
+        <v>4.81229</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>5.20883</v>
+        <v>5.39545</v>
       </c>
       <c r="C40" t="n">
-        <v>4.11825</v>
+        <v>3.78206</v>
       </c>
       <c r="D40" t="n">
-        <v>12.4132</v>
+        <v>12.5724</v>
       </c>
       <c r="E40" t="n">
-        <v>4.92025</v>
+        <v>4.57231</v>
       </c>
       <c r="F40" t="n">
-        <v>4.986</v>
+        <v>4.84667</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>5.24987</v>
+        <v>4.90772</v>
       </c>
       <c r="C41" t="n">
-        <v>4.14967</v>
+        <v>4.30117</v>
       </c>
       <c r="D41" t="n">
-        <v>13.0144</v>
+        <v>13.3007</v>
       </c>
       <c r="E41" t="n">
-        <v>4.96771</v>
+        <v>4.82677</v>
       </c>
       <c r="F41" t="n">
-        <v>5.03118</v>
+        <v>4.59214</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>5.24952</v>
+        <v>5.25554</v>
       </c>
       <c r="C42" t="n">
-        <v>4.16808</v>
+        <v>3.99271</v>
       </c>
       <c r="D42" t="n">
-        <v>13.563</v>
+        <v>13.6233</v>
       </c>
       <c r="E42" t="n">
-        <v>4.99374</v>
+        <v>4.70939</v>
       </c>
       <c r="F42" t="n">
-        <v>5.1524</v>
+        <v>4.96405</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>5.46356</v>
+        <v>5.37518</v>
       </c>
       <c r="C43" t="n">
-        <v>4.19069</v>
+        <v>4.13204</v>
       </c>
       <c r="D43" t="n">
-        <v>13.8387</v>
+        <v>13.9046</v>
       </c>
       <c r="E43" t="n">
-        <v>5.01876</v>
+        <v>4.92844</v>
       </c>
       <c r="F43" t="n">
-        <v>5.18229</v>
+        <v>4.74716</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>5.45515</v>
+        <v>5.22417</v>
       </c>
       <c r="C44" t="n">
-        <v>4.23641</v>
+        <v>3.98844</v>
       </c>
       <c r="D44" t="n">
-        <v>14.2321</v>
+        <v>14.1771</v>
       </c>
       <c r="E44" t="n">
-        <v>5.06899</v>
+        <v>4.77784</v>
       </c>
       <c r="F44" t="n">
-        <v>5.401</v>
+        <v>4.77723</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>5.36098</v>
+        <v>5.52141</v>
       </c>
       <c r="C45" t="n">
-        <v>4.21622</v>
+        <v>4.25387</v>
       </c>
       <c r="D45" t="n">
-        <v>14.5689</v>
+        <v>14.3739</v>
       </c>
       <c r="E45" t="n">
-        <v>5.08676</v>
+        <v>5.08118</v>
       </c>
       <c r="F45" t="n">
-        <v>5.51856</v>
+        <v>5.05035</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>5.41752</v>
+        <v>4.93518</v>
       </c>
       <c r="C46" t="n">
-        <v>4.32285</v>
+        <v>4.37697</v>
       </c>
       <c r="D46" t="n">
-        <v>15.1643</v>
+        <v>14.7719</v>
       </c>
       <c r="E46" t="n">
-        <v>5.13278</v>
+        <v>5.1365</v>
       </c>
       <c r="F46" t="n">
-        <v>5.64984</v>
+        <v>5.13354</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>5.3138</v>
+        <v>4.98229</v>
       </c>
       <c r="C47" t="n">
-        <v>4.38136</v>
+        <v>4.55139</v>
       </c>
       <c r="D47" t="n">
-        <v>15.6588</v>
+        <v>14.9539</v>
       </c>
       <c r="E47" t="n">
-        <v>5.29007</v>
+        <v>5.10378</v>
       </c>
       <c r="F47" t="n">
-        <v>5.90675</v>
+        <v>5.43617</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.12645</v>
+        <v>5.26265</v>
       </c>
       <c r="C48" t="n">
-        <v>4.46217</v>
+        <v>4.09224</v>
       </c>
       <c r="D48" t="n">
-        <v>16.6054</v>
+        <v>15.9759</v>
       </c>
       <c r="E48" t="n">
-        <v>5.5577</v>
+        <v>5.21293</v>
       </c>
       <c r="F48" t="n">
-        <v>6.14683</v>
+        <v>5.83148</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>5.48454</v>
+        <v>5.19678</v>
       </c>
       <c r="C49" t="n">
-        <v>4.62162</v>
+        <v>4.57337</v>
       </c>
       <c r="D49" t="n">
-        <v>17.634</v>
+        <v>16.4636</v>
       </c>
       <c r="E49" t="n">
-        <v>5.95721</v>
+        <v>5.607</v>
       </c>
       <c r="F49" t="n">
-        <v>6.53811</v>
+        <v>6.27514</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>5.47403</v>
+        <v>5.37611</v>
       </c>
       <c r="C50" t="n">
-        <v>4.70395</v>
+        <v>4.71233</v>
       </c>
       <c r="D50" t="n">
-        <v>15.319</v>
+        <v>14.3111</v>
       </c>
       <c r="E50" t="n">
-        <v>5.8709</v>
+        <v>4.57463</v>
       </c>
       <c r="F50" t="n">
-        <v>7.26765</v>
+        <v>5.48119</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>6.09089</v>
+        <v>5.51498</v>
       </c>
       <c r="C51" t="n">
-        <v>3.95175</v>
+        <v>3.89946</v>
       </c>
       <c r="D51" t="n">
-        <v>16.2916</v>
+        <v>15.3265</v>
       </c>
       <c r="E51" t="n">
-        <v>4.74713</v>
+        <v>4.63734</v>
       </c>
       <c r="F51" t="n">
-        <v>5.77773</v>
+        <v>5.60194</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>6.69557</v>
+        <v>6.81731</v>
       </c>
       <c r="C52" t="n">
-        <v>3.96482</v>
+        <v>4.11088</v>
       </c>
       <c r="D52" t="n">
-        <v>17.3429</v>
+        <v>16.315</v>
       </c>
       <c r="E52" t="n">
-        <v>4.78563</v>
+        <v>4.6481</v>
       </c>
       <c r="F52" t="n">
-        <v>5.97832</v>
+        <v>5.21697</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>5.53735</v>
+        <v>5.23205</v>
       </c>
       <c r="C53" t="n">
-        <v>4.01844</v>
+        <v>4.10501</v>
       </c>
       <c r="D53" t="n">
-        <v>17.3656</v>
+        <v>16.7167</v>
       </c>
       <c r="E53" t="n">
-        <v>4.98756</v>
+        <v>4.68509</v>
       </c>
       <c r="F53" t="n">
-        <v>6.03865</v>
+        <v>5.87627</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>5.4004</v>
+        <v>5.1916</v>
       </c>
       <c r="C54" t="n">
-        <v>4.08222</v>
+        <v>3.91408</v>
       </c>
       <c r="D54" t="n">
-        <v>18.6563</v>
+        <v>17.912</v>
       </c>
       <c r="E54" t="n">
-        <v>5.03304</v>
+        <v>4.71698</v>
       </c>
       <c r="F54" t="n">
-        <v>6.07601</v>
+        <v>5.82577</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>5.34718</v>
+        <v>5.17611</v>
       </c>
       <c r="C55" t="n">
-        <v>4.11524</v>
+        <v>3.97865</v>
       </c>
       <c r="D55" t="n">
-        <v>19.1854</v>
+        <v>17.7217</v>
       </c>
       <c r="E55" t="n">
-        <v>4.92576</v>
+        <v>5.02956</v>
       </c>
       <c r="F55" t="n">
-        <v>5.49485</v>
+        <v>5.31337</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>5.56739</v>
+        <v>5.43889</v>
       </c>
       <c r="C56" t="n">
-        <v>4.12941</v>
+        <v>4.15928</v>
       </c>
       <c r="D56" t="n">
-        <v>19.9191</v>
+        <v>14.8545</v>
       </c>
       <c r="E56" t="n">
-        <v>4.97093</v>
+        <v>4.80137</v>
       </c>
       <c r="F56" t="n">
-        <v>5.99524</v>
+        <v>6.01277</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>5.60422</v>
+        <v>5.57741</v>
       </c>
       <c r="C57" t="n">
-        <v>4.24318</v>
+        <v>4.26329</v>
       </c>
       <c r="D57" t="n">
-        <v>19.2109</v>
+        <v>18.4495</v>
       </c>
       <c r="E57" t="n">
-        <v>5.0743</v>
+        <v>5.11455</v>
       </c>
       <c r="F57" t="n">
-        <v>6.1702</v>
+        <v>5.67825</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>5.2949</v>
+        <v>5.17824</v>
       </c>
       <c r="C58" t="n">
-        <v>4.30167</v>
+        <v>4.03221</v>
       </c>
       <c r="D58" t="n">
-        <v>21.2193</v>
+        <v>18.1652</v>
       </c>
       <c r="E58" t="n">
-        <v>5.077</v>
+        <v>5.08219</v>
       </c>
       <c r="F58" t="n">
-        <v>5.77766</v>
+        <v>5.43118</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>5.39662</v>
+        <v>5.54963</v>
       </c>
       <c r="C59" t="n">
-        <v>4.28023</v>
+        <v>4.3865</v>
       </c>
       <c r="D59" t="n">
-        <v>21.3829</v>
+        <v>19.0818</v>
       </c>
       <c r="E59" t="n">
-        <v>5.29166</v>
+        <v>4.94414</v>
       </c>
       <c r="F59" t="n">
-        <v>5.71019</v>
+        <v>6.8671</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>5.37196</v>
+        <v>5.67297</v>
       </c>
       <c r="C60" t="n">
-        <v>4.45279</v>
+        <v>4.21019</v>
       </c>
       <c r="D60" t="n">
-        <v>21.7464</v>
+        <v>19.1155</v>
       </c>
       <c r="E60" t="n">
-        <v>5.16577</v>
+        <v>5.03623</v>
       </c>
       <c r="F60" t="n">
-        <v>7.26749</v>
+        <v>6.25918</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>5.44799</v>
+        <v>5.33954</v>
       </c>
       <c r="C61" t="n">
-        <v>4.34057</v>
+        <v>4.37639</v>
       </c>
       <c r="D61" t="n">
-        <v>21.4536</v>
+        <v>18.6075</v>
       </c>
       <c r="E61" t="n">
-        <v>5.40272</v>
+        <v>5.28009</v>
       </c>
       <c r="F61" t="n">
-        <v>7.32785</v>
+        <v>6.57125</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.54836</v>
+        <v>5.74881</v>
       </c>
       <c r="C62" t="n">
-        <v>4.56316</v>
+        <v>4.24088</v>
       </c>
       <c r="D62" t="n">
-        <v>22.497</v>
+        <v>18.3595</v>
       </c>
       <c r="E62" t="n">
-        <v>5.60117</v>
+        <v>5.43719</v>
       </c>
       <c r="F62" t="n">
-        <v>8.229990000000001</v>
+        <v>6.46074</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>5.53423</v>
+        <v>5.86279</v>
       </c>
       <c r="C63" t="n">
-        <v>4.50143</v>
+        <v>4.50982</v>
       </c>
       <c r="D63" t="n">
-        <v>22.1888</v>
+        <v>18.9169</v>
       </c>
       <c r="E63" t="n">
-        <v>5.9074</v>
+        <v>5.8434</v>
       </c>
       <c r="F63" t="n">
-        <v>7.8994</v>
+        <v>6.87789</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>5.9617</v>
+        <v>5.6496</v>
       </c>
       <c r="C64" t="n">
-        <v>4.77356</v>
+        <v>4.57376</v>
       </c>
       <c r="D64" t="n">
-        <v>15.2282</v>
+        <v>13.2437</v>
       </c>
       <c r="E64" t="n">
-        <v>6.34519</v>
+        <v>7.00594</v>
       </c>
       <c r="F64" t="n">
-        <v>7.63799</v>
+        <v>6.17349</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>6.26092</v>
+        <v>6.39593</v>
       </c>
       <c r="C65" t="n">
-        <v>9.36318</v>
+        <v>11.338</v>
       </c>
       <c r="D65" t="n">
-        <v>15.6286</v>
+        <v>14.1313</v>
       </c>
       <c r="E65" t="n">
-        <v>6.99975</v>
+        <v>7.24045</v>
       </c>
       <c r="F65" t="n">
-        <v>8.97336</v>
+        <v>6.33367</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>6.57296</v>
+        <v>6.84586</v>
       </c>
       <c r="C66" t="n">
-        <v>10.0589</v>
+        <v>11.3848</v>
       </c>
       <c r="D66" t="n">
-        <v>16.9786</v>
+        <v>15.0203</v>
       </c>
       <c r="E66" t="n">
-        <v>7.6438</v>
+        <v>8.837400000000001</v>
       </c>
       <c r="F66" t="n">
-        <v>6.32621</v>
+        <v>6.75465</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>12.6268</v>
+        <v>13.4942</v>
       </c>
       <c r="C67" t="n">
-        <v>10.7339</v>
+        <v>11.4494</v>
       </c>
       <c r="D67" t="n">
-        <v>18.0862</v>
+        <v>16.0327</v>
       </c>
       <c r="E67" t="n">
-        <v>6.70348</v>
+        <v>7.20344</v>
       </c>
       <c r="F67" t="n">
-        <v>6.54145</v>
+        <v>6.89564</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>14.4873</v>
+        <v>13.6791</v>
       </c>
       <c r="C68" t="n">
-        <v>12.0797</v>
+        <v>11.5423</v>
       </c>
       <c r="D68" t="n">
-        <v>19.2065</v>
+        <v>17.2027</v>
       </c>
       <c r="E68" t="n">
-        <v>7.51756</v>
+        <v>10.0712</v>
       </c>
       <c r="F68" t="n">
-        <v>6.84029</v>
+        <v>6.91947</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>12.3141</v>
+        <v>14.7452</v>
       </c>
       <c r="C69" t="n">
-        <v>10.3546</v>
+        <v>12.3843</v>
       </c>
       <c r="D69" t="n">
-        <v>19.7141</v>
+        <v>17.4218</v>
       </c>
       <c r="E69" t="n">
-        <v>8.624890000000001</v>
+        <v>8.121359999999999</v>
       </c>
       <c r="F69" t="n">
-        <v>6.82691</v>
+        <v>6.93794</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>11.6534</v>
+        <v>13.6139</v>
       </c>
       <c r="C70" t="n">
-        <v>9.804790000000001</v>
+        <v>11.3469</v>
       </c>
       <c r="D70" t="n">
-        <v>19.7417</v>
+        <v>17.0849</v>
       </c>
       <c r="E70" t="n">
-        <v>7.97096</v>
+        <v>9.30007</v>
       </c>
       <c r="F70" t="n">
-        <v>6.87253</v>
+        <v>6.93463</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>11.7208</v>
+        <v>13.5361</v>
       </c>
       <c r="C71" t="n">
-        <v>9.86801</v>
+        <v>11.268</v>
       </c>
       <c r="D71" t="n">
-        <v>19.8434</v>
+        <v>18.0486</v>
       </c>
       <c r="E71" t="n">
-        <v>7.94089</v>
+        <v>9.237349999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>6.98436</v>
+        <v>6.60905</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>11.7961</v>
+        <v>14.2606</v>
       </c>
       <c r="C72" t="n">
-        <v>9.909459999999999</v>
+        <v>12.0676</v>
       </c>
       <c r="D72" t="n">
-        <v>20.2277</v>
+        <v>18.5501</v>
       </c>
       <c r="E72" t="n">
-        <v>8.164429999999999</v>
+        <v>9.443619999999999</v>
       </c>
       <c r="F72" t="n">
-        <v>7.02351</v>
+        <v>6.80245</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>13.8893</v>
+        <v>14.7995</v>
       </c>
       <c r="C73" t="n">
-        <v>11.653</v>
+        <v>12.3403</v>
       </c>
       <c r="D73" t="n">
-        <v>20.3548</v>
+        <v>18.7008</v>
       </c>
       <c r="E73" t="n">
-        <v>8.422330000000001</v>
+        <v>9.64237</v>
       </c>
       <c r="F73" t="n">
-        <v>7.21356</v>
+        <v>6.9744</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>13.093</v>
+        <v>13.2988</v>
       </c>
       <c r="C74" t="n">
-        <v>11.0308</v>
+        <v>11.2746</v>
       </c>
       <c r="D74" t="n">
-        <v>20.4633</v>
+        <v>19.9825</v>
       </c>
       <c r="E74" t="n">
-        <v>8.22757</v>
+        <v>9.639150000000001</v>
       </c>
       <c r="F74" t="n">
-        <v>7.17916</v>
+        <v>7.16754</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>12.6146</v>
+        <v>13.1355</v>
       </c>
       <c r="C75" t="n">
-        <v>10.4542</v>
+        <v>11.072</v>
       </c>
       <c r="D75" t="n">
-        <v>20.6186</v>
+        <v>19.9935</v>
       </c>
       <c r="E75" t="n">
-        <v>8.145250000000001</v>
+        <v>9.82719</v>
       </c>
       <c r="F75" t="n">
-        <v>7.50739</v>
+        <v>7.46107</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>12.7458</v>
+        <v>13.0507</v>
       </c>
       <c r="C76" t="n">
-        <v>10.6015</v>
+        <v>11.071</v>
       </c>
       <c r="D76" t="n">
-        <v>20.8594</v>
+        <v>20.3517</v>
       </c>
       <c r="E76" t="n">
-        <v>7.61235</v>
+        <v>9.45914</v>
       </c>
       <c r="F76" t="n">
-        <v>7.79176</v>
+        <v>7.71512</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>11.8543</v>
+        <v>13.1098</v>
       </c>
       <c r="C77" t="n">
-        <v>9.76845</v>
+        <v>11.1491</v>
       </c>
       <c r="D77" t="n">
-        <v>22.2699</v>
+        <v>22.2257</v>
       </c>
       <c r="E77" t="n">
-        <v>7.86701</v>
+        <v>9.732279999999999</v>
       </c>
       <c r="F77" t="n">
-        <v>8.60328</v>
+        <v>9.16414</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>11.9802</v>
+        <v>15.019</v>
       </c>
       <c r="C78" t="n">
-        <v>9.90152</v>
+        <v>12.6348</v>
       </c>
       <c r="D78" t="n">
-        <v>21.7322</v>
+        <v>22.7756</v>
       </c>
       <c r="E78" t="n">
-        <v>8.470829999999999</v>
+        <v>10.185</v>
       </c>
       <c r="F78" t="n">
-        <v>10.3127</v>
+        <v>12.546</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>11.6814</v>
+        <v>11.7867</v>
       </c>
       <c r="C79" t="n">
-        <v>14.4865</v>
+        <v>13.5889</v>
       </c>
       <c r="D79" t="n">
-        <v>23.1902</v>
+        <v>23.0411</v>
       </c>
       <c r="E79" t="n">
-        <v>9.049340000000001</v>
+        <v>10.9557</v>
       </c>
       <c r="F79" t="n">
-        <v>10.0564</v>
+        <v>11.9794</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>11.9515</v>
+        <v>12.0295</v>
       </c>
       <c r="C80" t="n">
-        <v>14.5766</v>
+        <v>13.7342</v>
       </c>
       <c r="D80" t="n">
-        <v>23.6477</v>
+        <v>24.209</v>
       </c>
       <c r="E80" t="n">
-        <v>10.037</v>
+        <v>10.681</v>
       </c>
       <c r="F80" t="n">
-        <v>11.4245</v>
+        <v>12.4782</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>17.228</v>
+        <v>16.5158</v>
       </c>
       <c r="C81" t="n">
-        <v>14.5224</v>
+        <v>13.7844</v>
       </c>
       <c r="D81" t="n">
-        <v>24.5163</v>
+        <v>24.8884</v>
       </c>
       <c r="E81" t="n">
-        <v>10.5754</v>
+        <v>9.377940000000001</v>
       </c>
       <c r="F81" t="n">
-        <v>11.5496</v>
+        <v>11.8716</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>17.4795</v>
+        <v>16.6005</v>
       </c>
       <c r="C82" t="n">
-        <v>14.7826</v>
+        <v>13.8591</v>
       </c>
       <c r="D82" t="n">
-        <v>25.7835</v>
+        <v>25.3899</v>
       </c>
       <c r="E82" t="n">
-        <v>10.6491</v>
+        <v>11.1885</v>
       </c>
       <c r="F82" t="n">
-        <v>11.7009</v>
+        <v>12.4819</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>17.4128</v>
+        <v>16.679</v>
       </c>
       <c r="C83" t="n">
-        <v>14.7407</v>
+        <v>13.928</v>
       </c>
       <c r="D83" t="n">
-        <v>26.21</v>
+        <v>27.2571</v>
       </c>
       <c r="E83" t="n">
-        <v>10.7479</v>
+        <v>11.3612</v>
       </c>
       <c r="F83" t="n">
-        <v>11.784</v>
+        <v>12.734</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>17.5957</v>
+        <v>16.7741</v>
       </c>
       <c r="C84" t="n">
-        <v>14.9478</v>
+        <v>14.005</v>
       </c>
       <c r="D84" t="n">
-        <v>27.1347</v>
+        <v>27.1748</v>
       </c>
       <c r="E84" t="n">
-        <v>11.2652</v>
+        <v>12.205</v>
       </c>
       <c r="F84" t="n">
-        <v>11.8088</v>
+        <v>12.6188</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>17.5617</v>
+        <v>17.0478</v>
       </c>
       <c r="C85" t="n">
-        <v>14.8899</v>
+        <v>14.301</v>
       </c>
       <c r="D85" t="n">
-        <v>27.9107</v>
+        <v>29.1288</v>
       </c>
       <c r="E85" t="n">
-        <v>11.59</v>
+        <v>11.3508</v>
       </c>
       <c r="F85" t="n">
-        <v>12.0145</v>
+        <v>12.5733</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>17.6404</v>
+        <v>16.8774</v>
       </c>
       <c r="C86" t="n">
-        <v>15.0398</v>
+        <v>14.108</v>
       </c>
       <c r="D86" t="n">
-        <v>29.563</v>
+        <v>29.5828</v>
       </c>
       <c r="E86" t="n">
-        <v>11.8976</v>
+        <v>11.5832</v>
       </c>
       <c r="F86" t="n">
-        <v>12.1096</v>
+        <v>12.6669</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>17.6665</v>
+        <v>16.9346</v>
       </c>
       <c r="C87" t="n">
-        <v>15.0258</v>
+        <v>14.1501</v>
       </c>
       <c r="D87" t="n">
-        <v>29.7884</v>
+        <v>30.3189</v>
       </c>
       <c r="E87" t="n">
-        <v>12.0668</v>
+        <v>11.091</v>
       </c>
       <c r="F87" t="n">
-        <v>12.3616</v>
+        <v>12.2479</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>17.7638</v>
+        <v>16.9539</v>
       </c>
       <c r="C88" t="n">
-        <v>15.1533</v>
+        <v>14.1317</v>
       </c>
       <c r="D88" t="n">
-        <v>30.8104</v>
+        <v>30.6064</v>
       </c>
       <c r="E88" t="n">
-        <v>12.1575</v>
+        <v>10.9744</v>
       </c>
       <c r="F88" t="n">
-        <v>14.0638</v>
+        <v>15.3068</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>17.8836</v>
+        <v>16.7201</v>
       </c>
       <c r="C89" t="n">
-        <v>15.3195</v>
+        <v>13.8297</v>
       </c>
       <c r="D89" t="n">
-        <v>32.5146</v>
+        <v>30.966</v>
       </c>
       <c r="E89" t="n">
-        <v>12.455</v>
+        <v>11.0728</v>
       </c>
       <c r="F89" t="n">
-        <v>12.9242</v>
+        <v>12.4095</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>17.8875</v>
+        <v>16.7235</v>
       </c>
       <c r="C90" t="n">
-        <v>15.3378</v>
+        <v>13.8667</v>
       </c>
       <c r="D90" t="n">
-        <v>32.7897</v>
+        <v>32.4456</v>
       </c>
       <c r="E90" t="n">
-        <v>12.727</v>
+        <v>11.3265</v>
       </c>
       <c r="F90" t="n">
-        <v>12.7643</v>
+        <v>13.5861</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>17.999</v>
+        <v>17.2347</v>
       </c>
       <c r="C91" t="n">
-        <v>15.4233</v>
+        <v>14.4276</v>
       </c>
       <c r="D91" t="n">
-        <v>33.7052</v>
+        <v>34.6764</v>
       </c>
       <c r="E91" t="n">
-        <v>13.0314</v>
+        <v>11.6096</v>
       </c>
       <c r="F91" t="n">
-        <v>13.1984</v>
+        <v>15.9237</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>18.0531</v>
+        <v>17.2334</v>
       </c>
       <c r="C92" t="n">
-        <v>15.604</v>
+        <v>14.4053</v>
       </c>
       <c r="D92" t="n">
-        <v>31.9085</v>
+        <v>30.7861</v>
       </c>
       <c r="E92" t="n">
-        <v>13.2539</v>
+        <v>19.7055</v>
       </c>
       <c r="F92" t="n">
-        <v>17.0936</v>
+        <v>17.8448</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>18.2564</v>
+        <v>17.2924</v>
       </c>
       <c r="C93" t="n">
-        <v>15.7926</v>
+        <v>14.3721</v>
       </c>
       <c r="D93" t="n">
-        <v>32.8498</v>
+        <v>31.4975</v>
       </c>
       <c r="E93" t="n">
-        <v>13.7423</v>
+        <v>19.9165</v>
       </c>
       <c r="F93" t="n">
-        <v>17.869</v>
+        <v>17.9656</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>18.4672</v>
+        <v>17.5113</v>
       </c>
       <c r="C94" t="n">
-        <v>19.5556</v>
+        <v>19.0446</v>
       </c>
       <c r="D94" t="n">
-        <v>33.6374</v>
+        <v>32.2357</v>
       </c>
       <c r="E94" t="n">
-        <v>19.9409</v>
+        <v>20.0773</v>
       </c>
       <c r="F94" t="n">
-        <v>18.9096</v>
+        <v>18.0645</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>22.9045</v>
+        <v>22.3371</v>
       </c>
       <c r="C95" t="n">
-        <v>19.5823</v>
+        <v>19.0432</v>
       </c>
       <c r="D95" t="n">
-        <v>34.3546</v>
+        <v>33.2027</v>
       </c>
       <c r="E95" t="n">
-        <v>20.3783</v>
+        <v>20.3368</v>
       </c>
       <c r="F95" t="n">
-        <v>19.0044</v>
+        <v>18.3508</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>22.885</v>
+        <v>22.4205</v>
       </c>
       <c r="C96" t="n">
-        <v>19.5976</v>
+        <v>19.0932</v>
       </c>
       <c r="D96" t="n">
-        <v>35.4544</v>
+        <v>34.0324</v>
       </c>
       <c r="E96" t="n">
-        <v>20.5331</v>
+        <v>20.5193</v>
       </c>
       <c r="F96" t="n">
-        <v>19.0909</v>
+        <v>18.3028</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>22.9422</v>
+        <v>22.4151</v>
       </c>
       <c r="C97" t="n">
-        <v>19.6233</v>
+        <v>19.172</v>
       </c>
       <c r="D97" t="n">
-        <v>36.3606</v>
+        <v>34.9603</v>
       </c>
       <c r="E97" t="n">
-        <v>20.7194</v>
+        <v>20.6746</v>
       </c>
       <c r="F97" t="n">
-        <v>19.2026</v>
+        <v>18.597</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.9839</v>
+        <v>22.42</v>
       </c>
       <c r="C98" t="n">
-        <v>19.6581</v>
+        <v>19.1532</v>
       </c>
       <c r="D98" t="n">
-        <v>37.1335</v>
+        <v>35.6453</v>
       </c>
       <c r="E98" t="n">
-        <v>20.8932</v>
+        <v>20.8118</v>
       </c>
       <c r="F98" t="n">
-        <v>19.3596</v>
+        <v>18.7053</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>22.9398</v>
+        <v>22.3755</v>
       </c>
       <c r="C99" t="n">
-        <v>19.7072</v>
+        <v>19.2133</v>
       </c>
       <c r="D99" t="n">
-        <v>37.9091</v>
+        <v>36.575</v>
       </c>
       <c r="E99" t="n">
-        <v>20.9509</v>
+        <v>21.0235</v>
       </c>
       <c r="F99" t="n">
-        <v>19.4871</v>
+        <v>19.025</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>22.9456</v>
+        <v>22.4728</v>
       </c>
       <c r="C100" t="n">
-        <v>19.7517</v>
+        <v>19.2439</v>
       </c>
       <c r="D100" t="n">
-        <v>39.0887</v>
+        <v>38.0989</v>
       </c>
       <c r="E100" t="n">
-        <v>21.1232</v>
+        <v>21.188</v>
       </c>
       <c r="F100" t="n">
-        <v>19.656</v>
+        <v>19.2293</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>22.916</v>
+        <v>22.4299</v>
       </c>
       <c r="C101" t="n">
-        <v>19.7568</v>
+        <v>19.2899</v>
       </c>
       <c r="D101" t="n">
-        <v>39.9116</v>
+        <v>39.239</v>
       </c>
       <c r="E101" t="n">
-        <v>21.2631</v>
+        <v>21.2616</v>
       </c>
       <c r="F101" t="n">
-        <v>19.7517</v>
+        <v>19.3393</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>23.0094</v>
+        <v>22.4769</v>
       </c>
       <c r="C102" t="n">
-        <v>19.8297</v>
+        <v>19.3378</v>
       </c>
       <c r="D102" t="n">
-        <v>40.8869</v>
+        <v>40.0666</v>
       </c>
       <c r="E102" t="n">
-        <v>21.4133</v>
+        <v>21.5051</v>
       </c>
       <c r="F102" t="n">
-        <v>19.9755</v>
+        <v>19.4957</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>23.0748</v>
+        <v>22.518</v>
       </c>
       <c r="C103" t="n">
-        <v>19.8981</v>
+        <v>19.3892</v>
       </c>
       <c r="D103" t="n">
-        <v>41.8011</v>
+        <v>41.2386</v>
       </c>
       <c r="E103" t="n">
-        <v>21.5848</v>
+        <v>21.7337</v>
       </c>
       <c r="F103" t="n">
-        <v>20.2048</v>
+        <v>19.7455</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>23.1292</v>
+        <v>22.8308</v>
       </c>
       <c r="C104" t="n">
-        <v>20.0273</v>
+        <v>20.6845</v>
       </c>
       <c r="D104" t="n">
-        <v>42.8587</v>
+        <v>42.0537</v>
       </c>
       <c r="E104" t="n">
-        <v>21.8821</v>
+        <v>21.7418</v>
       </c>
       <c r="F104" t="n">
-        <v>21.0416</v>
+        <v>19.9923</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>23.2264</v>
+        <v>22.5581</v>
       </c>
       <c r="C105" t="n">
-        <v>20.0766</v>
+        <v>19.5759</v>
       </c>
       <c r="D105" t="n">
-        <v>44.7566</v>
+        <v>43.1539</v>
       </c>
       <c r="E105" t="n">
-        <v>22.1424</v>
+        <v>22.0695</v>
       </c>
       <c r="F105" t="n">
-        <v>20.8345</v>
+        <v>20.9968</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>23.3363</v>
+        <v>22.6864</v>
       </c>
       <c r="C106" t="n">
-        <v>20.2594</v>
+        <v>19.7713</v>
       </c>
       <c r="D106" t="n">
-        <v>45.7939</v>
+        <v>44.8539</v>
       </c>
       <c r="E106" t="n">
-        <v>22.4261</v>
+        <v>22.4268</v>
       </c>
       <c r="F106" t="n">
-        <v>21.3017</v>
+        <v>20.8152</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>23.5019</v>
+        <v>22.84</v>
       </c>
       <c r="C107" t="n">
-        <v>20.4774</v>
+        <v>19.9258</v>
       </c>
       <c r="D107" t="n">
-        <v>39.2954</v>
+        <v>38.0594</v>
       </c>
       <c r="E107" t="n">
-        <v>22.8184</v>
+        <v>24.9557</v>
       </c>
       <c r="F107" t="n">
-        <v>22.0057</v>
+        <v>22.9459</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>23.8443</v>
+        <v>22.9149</v>
       </c>
       <c r="C108" t="n">
-        <v>21.1772</v>
+        <v>20.6025</v>
       </c>
       <c r="D108" t="n">
-        <v>39.5939</v>
+        <v>38.8593</v>
       </c>
       <c r="E108" t="n">
-        <v>26.0632</v>
+        <v>25.5505</v>
       </c>
       <c r="F108" t="n">
-        <v>23.8894</v>
+        <v>22.8573</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>24.3203</v>
+        <v>23.6609</v>
       </c>
       <c r="C109" t="n">
-        <v>21.0972</v>
+        <v>20.6242</v>
       </c>
       <c r="D109" t="n">
-        <v>40.3379</v>
+        <v>39.5846</v>
       </c>
       <c r="E109" t="n">
-        <v>26.1943</v>
+        <v>25.4245</v>
       </c>
       <c r="F109" t="n">
-        <v>24.001</v>
+        <v>23.4001</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>26.0132</v>
+        <v>25.14</v>
       </c>
       <c r="C110" t="n">
-        <v>21.166</v>
+        <v>20.6555</v>
       </c>
       <c r="D110" t="n">
-        <v>41.4866</v>
+        <v>40.3097</v>
       </c>
       <c r="E110" t="n">
-        <v>26.5736</v>
+        <v>25.9983</v>
       </c>
       <c r="F110" t="n">
-        <v>24.0652</v>
+        <v>23.6153</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>26.2207</v>
+        <v>25.0526</v>
       </c>
       <c r="C111" t="n">
-        <v>21.2745</v>
+        <v>20.7454</v>
       </c>
       <c r="D111" t="n">
-        <v>42.3842</v>
+        <v>41.166</v>
       </c>
       <c r="E111" t="n">
-        <v>26.8265</v>
+        <v>26.2274</v>
       </c>
       <c r="F111" t="n">
-        <v>24.3872</v>
+        <v>23.8835</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>26.1576</v>
+        <v>25.04</v>
       </c>
       <c r="C112" t="n">
-        <v>21.3332</v>
+        <v>20.821</v>
       </c>
       <c r="D112" t="n">
-        <v>43.0781</v>
+        <v>41.8656</v>
       </c>
       <c r="E112" t="n">
-        <v>26.9856</v>
+        <v>26.441</v>
       </c>
       <c r="F112" t="n">
-        <v>24.6781</v>
+        <v>24.0151</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>26.1103</v>
+        <v>25.2917</v>
       </c>
       <c r="C113" t="n">
-        <v>21.357</v>
+        <v>20.8458</v>
       </c>
       <c r="D113" t="n">
-        <v>44.2054</v>
+        <v>42.9056</v>
       </c>
       <c r="E113" t="n">
-        <v>27.1808</v>
+        <v>26.7341</v>
       </c>
       <c r="F113" t="n">
-        <v>24.9171</v>
+        <v>24.2547</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>26.1076</v>
+        <v>25.3544</v>
       </c>
       <c r="C114" t="n">
-        <v>21.4501</v>
+        <v>20.97</v>
       </c>
       <c r="D114" t="n">
-        <v>44.9916</v>
+        <v>43.7009</v>
       </c>
       <c r="E114" t="n">
-        <v>27.4617</v>
+        <v>26.9614</v>
       </c>
       <c r="F114" t="n">
-        <v>25.132</v>
+        <v>24.5099</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>26.1538</v>
+        <v>25.3649</v>
       </c>
       <c r="C115" t="n">
-        <v>21.5358</v>
+        <v>21.0262</v>
       </c>
       <c r="D115" t="n">
-        <v>46.0184</v>
+        <v>44.613</v>
       </c>
       <c r="E115" t="n">
-        <v>27.6112</v>
+        <v>27.195</v>
       </c>
       <c r="F115" t="n">
-        <v>25.4717</v>
+        <v>24.839</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>26.0671</v>
+        <v>25.3787</v>
       </c>
       <c r="C116" t="n">
-        <v>21.5601</v>
+        <v>21.1605</v>
       </c>
       <c r="D116" t="n">
-        <v>46.9751</v>
+        <v>45.5346</v>
       </c>
       <c r="E116" t="n">
-        <v>27.82</v>
+        <v>27.4982</v>
       </c>
       <c r="F116" t="n">
-        <v>25.7996</v>
+        <v>25.1676</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>26.2507</v>
+        <v>25.3526</v>
       </c>
       <c r="C117" t="n">
-        <v>21.7635</v>
+        <v>21.281</v>
       </c>
       <c r="D117" t="n">
-        <v>47.9808</v>
+        <v>46.4293</v>
       </c>
       <c r="E117" t="n">
-        <v>28.1455</v>
+        <v>27.7293</v>
       </c>
       <c r="F117" t="n">
-        <v>26.2555</v>
+        <v>25.2628</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>26.2376</v>
+        <v>25.465</v>
       </c>
       <c r="C118" t="n">
-        <v>21.8589</v>
+        <v>21.4864</v>
       </c>
       <c r="D118" t="n">
-        <v>48.9251</v>
+        <v>47.6372</v>
       </c>
       <c r="E118" t="n">
-        <v>28.5124</v>
+        <v>28.0335</v>
       </c>
       <c r="F118" t="n">
-        <v>26.69</v>
+        <v>25.9482</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>26.5973</v>
+        <v>25.5375</v>
       </c>
       <c r="C119" t="n">
-        <v>22.2713</v>
+        <v>21.6575</v>
       </c>
       <c r="D119" t="n">
-        <v>50.0146</v>
+        <v>48.4542</v>
       </c>
       <c r="E119" t="n">
-        <v>28.8735</v>
+        <v>28.4364</v>
       </c>
       <c r="F119" t="n">
-        <v>27.0589</v>
+        <v>26.3977</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>26.4925</v>
+        <v>25.6911</v>
       </c>
       <c r="C120" t="n">
-        <v>22.2972</v>
+        <v>21.9567</v>
       </c>
       <c r="D120" t="n">
-        <v>50.9889</v>
+        <v>49.7972</v>
       </c>
       <c r="E120" t="n">
-        <v>29.3002</v>
+        <v>28.5592</v>
       </c>
       <c r="F120" t="n">
-        <v>28.07</v>
+        <v>27.1525</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>27.0111</v>
+        <v>25.5327</v>
       </c>
       <c r="C121" t="n">
-        <v>22.665</v>
+        <v>22.2566</v>
       </c>
       <c r="D121" t="n">
-        <v>42.6159</v>
+        <v>41.1252</v>
       </c>
       <c r="E121" t="n">
-        <v>29.6966</v>
+        <v>29.2755</v>
       </c>
       <c r="F121" t="n">
-        <v>28.7497</v>
+        <v>26.8695</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>27.0999</v>
+        <v>26.4601</v>
       </c>
       <c r="C122" t="n">
-        <v>23.7261</v>
+        <v>22.8644</v>
       </c>
       <c r="D122" t="n">
-        <v>43.2901</v>
+        <v>41.892</v>
       </c>
       <c r="E122" t="n">
-        <v>30.5389</v>
+        <v>29.6173</v>
       </c>
       <c r="F122" t="n">
-        <v>30.0453</v>
+        <v>27.152</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>27.0931</v>
+        <v>26.6805</v>
       </c>
       <c r="C123" t="n">
-        <v>23.748</v>
+        <v>22.9129</v>
       </c>
       <c r="D123" t="n">
-        <v>43.6121</v>
+        <v>42.3108</v>
       </c>
       <c r="E123" t="n">
-        <v>31.46</v>
+        <v>29.8904</v>
       </c>
       <c r="F123" t="n">
-        <v>28.1687</v>
+        <v>27.2734</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>33.0506</v>
+        <v>32.6606</v>
       </c>
       <c r="C124" t="n">
-        <v>23.8599</v>
+        <v>23.0634</v>
       </c>
       <c r="D124" t="n">
-        <v>44.636</v>
+        <v>43.6656</v>
       </c>
       <c r="E124" t="n">
-        <v>31.7153</v>
+        <v>30.1758</v>
       </c>
       <c r="F124" t="n">
-        <v>28.3562</v>
+        <v>27.6303</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>33.0793</v>
+        <v>32.6465</v>
       </c>
       <c r="C125" t="n">
-        <v>23.9484</v>
+        <v>23.1858</v>
       </c>
       <c r="D125" t="n">
-        <v>45.4088</v>
+        <v>44.508</v>
       </c>
       <c r="E125" t="n">
-        <v>32.0471</v>
+        <v>30.4608</v>
       </c>
       <c r="F125" t="n">
-        <v>28.516</v>
+        <v>27.8459</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>33.6881</v>
+        <v>32.5025</v>
       </c>
       <c r="C126" t="n">
-        <v>24.1317</v>
+        <v>23.2844</v>
       </c>
       <c r="D126" t="n">
-        <v>46.2213</v>
+        <v>44.485</v>
       </c>
       <c r="E126" t="n">
-        <v>32.3142</v>
+        <v>30.8117</v>
       </c>
       <c r="F126" t="n">
-        <v>28.8961</v>
+        <v>28.1466</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>33.8872</v>
+        <v>32.6391</v>
       </c>
       <c r="C127" t="n">
-        <v>24.3263</v>
+        <v>23.4217</v>
       </c>
       <c r="D127" t="n">
-        <v>46.7316</v>
+        <v>45.3107</v>
       </c>
       <c r="E127" t="n">
-        <v>32.5957</v>
+        <v>31.1098</v>
       </c>
       <c r="F127" t="n">
-        <v>29.1844</v>
+        <v>28.3926</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>33.7919</v>
+        <v>32.6857</v>
       </c>
       <c r="C128" t="n">
-        <v>24.4406</v>
+        <v>23.5359</v>
       </c>
       <c r="D128" t="n">
-        <v>47.9178</v>
+        <v>46.4051</v>
       </c>
       <c r="E128" t="n">
-        <v>32.8695</v>
+        <v>31.3966</v>
       </c>
       <c r="F128" t="n">
-        <v>29.4905</v>
+        <v>28.6085</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>33.753</v>
+        <v>32.6812</v>
       </c>
       <c r="C129" t="n">
-        <v>24.6175</v>
+        <v>23.7247</v>
       </c>
       <c r="D129" t="n">
-        <v>49.0591</v>
+        <v>47.1359</v>
       </c>
       <c r="E129" t="n">
-        <v>33.258</v>
+        <v>31.6516</v>
       </c>
       <c r="F129" t="n">
-        <v>29.8705</v>
+        <v>29.0234</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>33.8369</v>
+        <v>32.7444</v>
       </c>
       <c r="C130" t="n">
-        <v>24.7616</v>
+        <v>23.948</v>
       </c>
       <c r="D130" t="n">
-        <v>49.726</v>
+        <v>48.2715</v>
       </c>
       <c r="E130" t="n">
-        <v>33.5233</v>
+        <v>31.9297</v>
       </c>
       <c r="F130" t="n">
-        <v>30.2663</v>
+        <v>29.4324</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>33.9113</v>
+        <v>32.6885</v>
       </c>
       <c r="C131" t="n">
-        <v>25.0698</v>
+        <v>24.2426</v>
       </c>
       <c r="D131" t="n">
-        <v>50.4804</v>
+        <v>49.1852</v>
       </c>
       <c r="E131" t="n">
-        <v>33.8754</v>
+        <v>32.366</v>
       </c>
       <c r="F131" t="n">
-        <v>30.7657</v>
+        <v>29.8043</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>33.981</v>
+        <v>32.7832</v>
       </c>
       <c r="C132" t="n">
-        <v>25.3181</v>
+        <v>24.4957</v>
       </c>
       <c r="D132" t="n">
-        <v>51.3944</v>
+        <v>50.1405</v>
       </c>
       <c r="E132" t="n">
-        <v>34.2668</v>
+        <v>32.7278</v>
       </c>
       <c r="F132" t="n">
-        <v>31.2996</v>
+        <v>30.3816</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>34.0573</v>
+        <v>32.8161</v>
       </c>
       <c r="C133" t="n">
-        <v>25.6097</v>
+        <v>24.7944</v>
       </c>
       <c r="D133" t="n">
-        <v>52.8723</v>
+        <v>51.1015</v>
       </c>
       <c r="E133" t="n">
-        <v>34.6611</v>
+        <v>33.208</v>
       </c>
       <c r="F133" t="n">
-        <v>31.9628</v>
+        <v>31.0913</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>34.054</v>
+        <v>32.9467</v>
       </c>
       <c r="C134" t="n">
-        <v>25.9666</v>
+        <v>25.1952</v>
       </c>
       <c r="D134" t="n">
-        <v>54.2001</v>
+        <v>52.3474</v>
       </c>
       <c r="E134" t="n">
-        <v>35.2034</v>
+        <v>33.733</v>
       </c>
       <c r="F134" t="n">
-        <v>32.6084</v>
+        <v>31.8289</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>34.328</v>
+        <v>33.0917</v>
       </c>
       <c r="C135" t="n">
-        <v>26.4746</v>
+        <v>25.7294</v>
       </c>
       <c r="D135" t="n">
-        <v>44.3206</v>
+        <v>43.2468</v>
       </c>
       <c r="E135" t="n">
-        <v>35.9074</v>
+        <v>31.3672</v>
       </c>
       <c r="F135" t="n">
-        <v>33.6254</v>
+        <v>29.3654</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>34.8015</v>
+        <v>32.4129</v>
       </c>
       <c r="C136" t="n">
-        <v>25.8412</v>
+        <v>24.7258</v>
       </c>
       <c r="D136" t="n">
-        <v>45.0326</v>
+        <v>43.5667</v>
       </c>
       <c r="E136" t="n">
-        <v>36.8659</v>
+        <v>31.6867</v>
       </c>
       <c r="F136" t="n">
-        <v>35.4737</v>
+        <v>29.6156</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>35.1862</v>
+        <v>32.775</v>
       </c>
       <c r="C137" t="n">
-        <v>26.4509</v>
+        <v>24.9026</v>
       </c>
       <c r="D137" t="n">
-        <v>45.4576</v>
+        <v>44.2718</v>
       </c>
       <c r="E137" t="n">
-        <v>34.0971</v>
+        <v>32.0025</v>
       </c>
       <c r="F137" t="n">
-        <v>30.7619</v>
+        <v>29.7271</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>38.7104</v>
+        <v>37.6179</v>
       </c>
       <c r="C138" t="n">
-        <v>26.644</v>
+        <v>25.3556</v>
       </c>
       <c r="D138" t="n">
-        <v>46.2947</v>
+        <v>45.2256</v>
       </c>
       <c r="E138" t="n">
-        <v>34.2339</v>
+        <v>32.622</v>
       </c>
       <c r="F138" t="n">
-        <v>30.9915</v>
+        <v>30.1092</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>38.6955</v>
+        <v>37.6005</v>
       </c>
       <c r="C139" t="n">
-        <v>26.7601</v>
+        <v>25.5951</v>
       </c>
       <c r="D139" t="n">
-        <v>47.0899</v>
+        <v>45.3564</v>
       </c>
       <c r="E139" t="n">
-        <v>34.7203</v>
+        <v>32.8886</v>
       </c>
       <c r="F139" t="n">
-        <v>31.2822</v>
+        <v>30.2897</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>38.7323</v>
+        <v>37.6892</v>
       </c>
       <c r="C140" t="n">
-        <v>26.9555</v>
+        <v>25.718</v>
       </c>
       <c r="D140" t="n">
-        <v>47.9934</v>
+        <v>45.9785</v>
       </c>
       <c r="E140" t="n">
-        <v>34.9633</v>
+        <v>33.2029</v>
       </c>
       <c r="F140" t="n">
-        <v>31.4748</v>
+        <v>30.3694</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>38.7465</v>
+        <v>37.6641</v>
       </c>
       <c r="C141" t="n">
-        <v>27.1127</v>
+        <v>25.9289</v>
       </c>
       <c r="D141" t="n">
-        <v>48.8347</v>
+        <v>47.2774</v>
       </c>
       <c r="E141" t="n">
-        <v>35.2738</v>
+        <v>33.4404</v>
       </c>
       <c r="F141" t="n">
-        <v>31.7662</v>
+        <v>30.9194</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>38.7682</v>
+        <v>37.692</v>
       </c>
       <c r="C142" t="n">
-        <v>27.357</v>
+        <v>26.0935</v>
       </c>
       <c r="D142" t="n">
-        <v>49.7783</v>
+        <v>47.9793</v>
       </c>
       <c r="E142" t="n">
-        <v>35.3682</v>
+        <v>33.7376</v>
       </c>
       <c r="F142" t="n">
-        <v>32.0905</v>
+        <v>31.2164</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>38.8383</v>
+        <v>37.7352</v>
       </c>
       <c r="C143" t="n">
-        <v>27.5629</v>
+        <v>26.2999</v>
       </c>
       <c r="D143" t="n">
-        <v>50.5241</v>
+        <v>49.4711</v>
       </c>
       <c r="E143" t="n">
-        <v>35.6422</v>
+        <v>34.1122</v>
       </c>
       <c r="F143" t="n">
-        <v>32.4387</v>
+        <v>31.3172</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Scattered successful looukp.xlsx
+++ b/gcc-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>4.44811</v>
+        <v>3.74091</v>
       </c>
       <c r="C2" t="n">
-        <v>4.09577</v>
+        <v>3.57</v>
       </c>
       <c r="D2" t="n">
-        <v>8.281129999999999</v>
+        <v>8.06002</v>
       </c>
       <c r="E2" t="n">
-        <v>4.38778</v>
+        <v>3.89049</v>
       </c>
       <c r="F2" t="n">
-        <v>3.14298</v>
+        <v>3.46329</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>4.20393</v>
+        <v>3.694</v>
       </c>
       <c r="C3" t="n">
-        <v>3.61116</v>
+        <v>3.3623</v>
       </c>
       <c r="D3" t="n">
-        <v>8.479100000000001</v>
+        <v>8.432600000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>3.46813</v>
+        <v>3.34601</v>
       </c>
       <c r="F3" t="n">
-        <v>4.16693</v>
+        <v>3.93868</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.46731</v>
+        <v>3.46768</v>
       </c>
       <c r="C4" t="n">
-        <v>3.04528</v>
+        <v>3.04422</v>
       </c>
       <c r="D4" t="n">
-        <v>9.1523</v>
+        <v>9.11697</v>
       </c>
       <c r="E4" t="n">
-        <v>3.41772</v>
+        <v>3.51024</v>
       </c>
       <c r="F4" t="n">
-        <v>4.11862</v>
+        <v>4.20432</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>4.07126</v>
+        <v>3.80884</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5376</v>
+        <v>3.43723</v>
       </c>
       <c r="D5" t="n">
-        <v>10.2037</v>
+        <v>10.0814</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4774</v>
+        <v>3.44559</v>
       </c>
       <c r="F5" t="n">
-        <v>4.0725</v>
+        <v>4.18969</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.01756</v>
+        <v>3.93175</v>
       </c>
       <c r="C6" t="n">
-        <v>3.50048</v>
+        <v>3.4709</v>
       </c>
       <c r="D6" t="n">
-        <v>10.9571</v>
+        <v>10.9317</v>
       </c>
       <c r="E6" t="n">
-        <v>3.83148</v>
+        <v>3.89862</v>
       </c>
       <c r="F6" t="n">
-        <v>3.68789</v>
+        <v>3.80414</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>4.2626</v>
+        <v>3.74548</v>
       </c>
       <c r="C7" t="n">
-        <v>3.75504</v>
+        <v>3.5328</v>
       </c>
       <c r="D7" t="n">
-        <v>6.9781</v>
+        <v>6.98624</v>
       </c>
       <c r="E7" t="n">
-        <v>4.28207</v>
+        <v>4.16269</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5644</v>
+        <v>3.68852</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>4.29548</v>
+        <v>3.78041</v>
       </c>
       <c r="C8" t="n">
-        <v>3.84619</v>
+        <v>3.92393</v>
       </c>
       <c r="D8" t="n">
-        <v>7.41715</v>
+        <v>7.33235</v>
       </c>
       <c r="E8" t="n">
-        <v>4.3667</v>
+        <v>4.41566</v>
       </c>
       <c r="F8" t="n">
-        <v>3.67412</v>
+        <v>3.73236</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>3.5785</v>
+        <v>3.56166</v>
       </c>
       <c r="C9" t="n">
-        <v>4.05681</v>
+        <v>4.13077</v>
       </c>
       <c r="D9" t="n">
-        <v>7.71442</v>
+        <v>7.73827</v>
       </c>
       <c r="E9" t="n">
-        <v>4.40286</v>
+        <v>4.42434</v>
       </c>
       <c r="F9" t="n">
-        <v>3.68205</v>
+        <v>3.72744</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>4.22764</v>
+        <v>4.34877</v>
       </c>
       <c r="C10" t="n">
-        <v>4.0725</v>
+        <v>4.14001</v>
       </c>
       <c r="D10" t="n">
-        <v>8.247249999999999</v>
+        <v>8.24155</v>
       </c>
       <c r="E10" t="n">
-        <v>4.43533</v>
+        <v>4.49929</v>
       </c>
       <c r="F10" t="n">
-        <v>3.64359</v>
+        <v>3.7746</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>4.83817</v>
+        <v>4.97724</v>
       </c>
       <c r="C11" t="n">
-        <v>4.21156</v>
+        <v>4.09391</v>
       </c>
       <c r="D11" t="n">
-        <v>8.70209</v>
+        <v>8.75273</v>
       </c>
       <c r="E11" t="n">
-        <v>4.79023</v>
+        <v>4.79151</v>
       </c>
       <c r="F11" t="n">
-        <v>3.72354</v>
+        <v>3.74507</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>4.0727</v>
+        <v>4.07545</v>
       </c>
       <c r="C12" t="n">
-        <v>4.10211</v>
+        <v>4.0407</v>
       </c>
       <c r="D12" t="n">
-        <v>9.34553</v>
+        <v>9.34374</v>
       </c>
       <c r="E12" t="n">
-        <v>4.85979</v>
+        <v>4.89158</v>
       </c>
       <c r="F12" t="n">
-        <v>3.69175</v>
+        <v>3.76085</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>4.92601</v>
+        <v>4.96655</v>
       </c>
       <c r="C13" t="n">
-        <v>4.1735</v>
+        <v>4.38304</v>
       </c>
       <c r="D13" t="n">
-        <v>9.947609999999999</v>
+        <v>9.87567</v>
       </c>
       <c r="E13" t="n">
-        <v>4.67995</v>
+        <v>4.79614</v>
       </c>
       <c r="F13" t="n">
-        <v>3.85211</v>
+        <v>3.92704</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>5.02088</v>
+        <v>4.99337</v>
       </c>
       <c r="C14" t="n">
-        <v>4.22971</v>
+        <v>4.3112</v>
       </c>
       <c r="D14" t="n">
-        <v>10.3041</v>
+        <v>10.2636</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5613</v>
+        <v>4.62158</v>
       </c>
       <c r="F14" t="n">
-        <v>3.71661</v>
+        <v>3.8565</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>4.91517</v>
+        <v>4.98543</v>
       </c>
       <c r="C15" t="n">
-        <v>4.26049</v>
+        <v>4.44228</v>
       </c>
       <c r="D15" t="n">
-        <v>10.7547</v>
+        <v>10.7604</v>
       </c>
       <c r="E15" t="n">
-        <v>4.65569</v>
+        <v>4.65559</v>
       </c>
       <c r="F15" t="n">
-        <v>3.83812</v>
+        <v>3.936</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>4.91084</v>
+        <v>5.01323</v>
       </c>
       <c r="C16" t="n">
-        <v>4.27734</v>
+        <v>4.3659</v>
       </c>
       <c r="D16" t="n">
-        <v>11.3351</v>
+        <v>11.3364</v>
       </c>
       <c r="E16" t="n">
-        <v>5.0848</v>
+        <v>5.15679</v>
       </c>
       <c r="F16" t="n">
-        <v>3.90214</v>
+        <v>4.01101</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>4.9048</v>
+        <v>5.00866</v>
       </c>
       <c r="C17" t="n">
-        <v>4.38058</v>
+        <v>4.54942</v>
       </c>
       <c r="D17" t="n">
-        <v>11.75</v>
+        <v>11.7207</v>
       </c>
       <c r="E17" t="n">
-        <v>4.7632</v>
+        <v>4.80673</v>
       </c>
       <c r="F17" t="n">
-        <v>3.79186</v>
+        <v>3.92834</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>4.90461</v>
+        <v>5.02342</v>
       </c>
       <c r="C18" t="n">
-        <v>4.37474</v>
+        <v>4.58226</v>
       </c>
       <c r="D18" t="n">
-        <v>12.1572</v>
+        <v>12.0781</v>
       </c>
       <c r="E18" t="n">
-        <v>5.07974</v>
+        <v>4.99514</v>
       </c>
       <c r="F18" t="n">
-        <v>3.85752</v>
+        <v>3.90782</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>5.03685</v>
+        <v>5.03193</v>
       </c>
       <c r="C19" t="n">
-        <v>4.42545</v>
+        <v>4.63833</v>
       </c>
       <c r="D19" t="n">
-        <v>12.8115</v>
+        <v>12.7345</v>
       </c>
       <c r="E19" t="n">
-        <v>4.81494</v>
+        <v>4.73111</v>
       </c>
       <c r="F19" t="n">
-        <v>3.8955</v>
+        <v>3.97752</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>4.94433</v>
+        <v>5.06114</v>
       </c>
       <c r="C20" t="n">
-        <v>4.5874</v>
+        <v>4.71736</v>
       </c>
       <c r="D20" t="n">
-        <v>13.233</v>
+        <v>13.1597</v>
       </c>
       <c r="E20" t="n">
-        <v>5.20338</v>
+        <v>5.49253</v>
       </c>
       <c r="F20" t="n">
-        <v>3.96111</v>
+        <v>4.09188</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>5.008</v>
+        <v>5.08585</v>
       </c>
       <c r="C21" t="n">
-        <v>4.65448</v>
+        <v>4.7881</v>
       </c>
       <c r="D21" t="n">
-        <v>9.39958</v>
+        <v>9.3903</v>
       </c>
       <c r="E21" t="n">
-        <v>4.63415</v>
+        <v>4.4975</v>
       </c>
       <c r="F21" t="n">
-        <v>4.30929</v>
+        <v>4.47424</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>5.05271</v>
+        <v>5.11981</v>
       </c>
       <c r="C22" t="n">
-        <v>3.87495</v>
+        <v>3.98141</v>
       </c>
       <c r="D22" t="n">
-        <v>9.67878</v>
+        <v>9.681369999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>4.62407</v>
+        <v>4.65321</v>
       </c>
       <c r="F22" t="n">
-        <v>4.40528</v>
+        <v>4.59048</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>5.19263</v>
+        <v>5.02642</v>
       </c>
       <c r="C23" t="n">
-        <v>3.85846</v>
+        <v>4.00463</v>
       </c>
       <c r="D23" t="n">
-        <v>10.0374</v>
+        <v>10.0318</v>
       </c>
       <c r="E23" t="n">
-        <v>4.71815</v>
+        <v>4.75839</v>
       </c>
       <c r="F23" t="n">
-        <v>4.39732</v>
+        <v>4.54745</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>5.21734</v>
+        <v>5.23389</v>
       </c>
       <c r="C24" t="n">
-        <v>3.92319</v>
+        <v>4.03139</v>
       </c>
       <c r="D24" t="n">
-        <v>10.3035</v>
+        <v>10.3328</v>
       </c>
       <c r="E24" t="n">
-        <v>4.7594</v>
+        <v>4.79455</v>
       </c>
       <c r="F24" t="n">
-        <v>4.42998</v>
+        <v>4.58253</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>5.20475</v>
+        <v>5.24743</v>
       </c>
       <c r="C25" t="n">
-        <v>3.93495</v>
+        <v>4.04714</v>
       </c>
       <c r="D25" t="n">
-        <v>10.7166</v>
+        <v>10.7208</v>
       </c>
       <c r="E25" t="n">
-        <v>4.70782</v>
+        <v>4.79975</v>
       </c>
       <c r="F25" t="n">
-        <v>4.48177</v>
+        <v>4.66507</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>5.23282</v>
+        <v>5.25621</v>
       </c>
       <c r="C26" t="n">
-        <v>3.93236</v>
+        <v>4.05118</v>
       </c>
       <c r="D26" t="n">
-        <v>11.1003</v>
+        <v>11.0927</v>
       </c>
       <c r="E26" t="n">
-        <v>4.73339</v>
+        <v>4.8005</v>
       </c>
       <c r="F26" t="n">
-        <v>4.30626</v>
+        <v>4.63375</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>5.18412</v>
+        <v>5.10197</v>
       </c>
       <c r="C27" t="n">
-        <v>3.96132</v>
+        <v>4.06407</v>
       </c>
       <c r="D27" t="n">
-        <v>11.5633</v>
+        <v>11.5899</v>
       </c>
       <c r="E27" t="n">
-        <v>4.78441</v>
+        <v>4.86666</v>
       </c>
       <c r="F27" t="n">
-        <v>4.32961</v>
+        <v>4.64995</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>5.11478</v>
+        <v>5.12461</v>
       </c>
       <c r="C28" t="n">
-        <v>3.94297</v>
+        <v>4.05962</v>
       </c>
       <c r="D28" t="n">
-        <v>11.9448</v>
+        <v>11.9541</v>
       </c>
       <c r="E28" t="n">
-        <v>4.81822</v>
+        <v>4.92232</v>
       </c>
       <c r="F28" t="n">
-        <v>4.3567</v>
+        <v>4.71678</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>5.20096</v>
+        <v>5.13008</v>
       </c>
       <c r="C29" t="n">
-        <v>4.03007</v>
+        <v>4.08745</v>
       </c>
       <c r="D29" t="n">
-        <v>12.3811</v>
+        <v>12.4083</v>
       </c>
       <c r="E29" t="n">
-        <v>4.81367</v>
+        <v>4.95227</v>
       </c>
       <c r="F29" t="n">
-        <v>4.38647</v>
+        <v>4.7542</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>5.29204</v>
+        <v>5.2957</v>
       </c>
       <c r="C30" t="n">
-        <v>4.25967</v>
+        <v>4.25952</v>
       </c>
       <c r="D30" t="n">
-        <v>12.8255</v>
+        <v>12.85</v>
       </c>
       <c r="E30" t="n">
-        <v>4.90639</v>
+        <v>5.00928</v>
       </c>
       <c r="F30" t="n">
-        <v>4.51076</v>
+        <v>4.77243</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>5.18511</v>
+        <v>5.31977</v>
       </c>
       <c r="C31" t="n">
-        <v>4.10326</v>
+        <v>4.21356</v>
       </c>
       <c r="D31" t="n">
-        <v>13.2985</v>
+        <v>13.3674</v>
       </c>
       <c r="E31" t="n">
-        <v>4.89439</v>
+        <v>5.01643</v>
       </c>
       <c r="F31" t="n">
-        <v>4.55215</v>
+        <v>4.81824</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>5.13197</v>
+        <v>5.17673</v>
       </c>
       <c r="C32" t="n">
-        <v>4.15122</v>
+        <v>4.23235</v>
       </c>
       <c r="D32" t="n">
-        <v>13.6524</v>
+        <v>13.7367</v>
       </c>
       <c r="E32" t="n">
-        <v>4.97214</v>
+        <v>5.10085</v>
       </c>
       <c r="F32" t="n">
-        <v>4.57224</v>
+        <v>4.88345</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>5.26896</v>
+        <v>5.18848</v>
       </c>
       <c r="C33" t="n">
-        <v>4.19846</v>
+        <v>4.25751</v>
       </c>
       <c r="D33" t="n">
-        <v>14.0349</v>
+        <v>14.122</v>
       </c>
       <c r="E33" t="n">
-        <v>4.95002</v>
+        <v>5.14205</v>
       </c>
       <c r="F33" t="n">
-        <v>4.66145</v>
+        <v>4.93747</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.16125</v>
+        <v>5.21226</v>
       </c>
       <c r="C34" t="n">
-        <v>4.25952</v>
+        <v>4.34013</v>
       </c>
       <c r="D34" t="n">
-        <v>14.2256</v>
+        <v>14.5607</v>
       </c>
       <c r="E34" t="n">
-        <v>4.77667</v>
+        <v>4.89074</v>
       </c>
       <c r="F34" t="n">
-        <v>4.65062</v>
+        <v>5.08927</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>5.39174</v>
+        <v>5.32242</v>
       </c>
       <c r="C35" t="n">
-        <v>4.33231</v>
+        <v>4.39843</v>
       </c>
       <c r="D35" t="n">
-        <v>10.0562</v>
+        <v>10.5409</v>
       </c>
       <c r="E35" t="n">
-        <v>4.47687</v>
+        <v>4.61473</v>
       </c>
       <c r="F35" t="n">
-        <v>4.49901</v>
+        <v>4.90472</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>5.25162</v>
+        <v>5.25376</v>
       </c>
       <c r="C36" t="n">
-        <v>4.53077</v>
+        <v>4.46313</v>
       </c>
       <c r="D36" t="n">
-        <v>10.5268</v>
+        <v>11.1908</v>
       </c>
       <c r="E36" t="n">
-        <v>4.45141</v>
+        <v>4.68987</v>
       </c>
       <c r="F36" t="n">
-        <v>4.64612</v>
+        <v>5.03684</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>5.55642</v>
+        <v>5.35332</v>
       </c>
       <c r="C37" t="n">
-        <v>4.1713</v>
+        <v>4.25765</v>
       </c>
       <c r="D37" t="n">
-        <v>11.3789</v>
+        <v>11.9277</v>
       </c>
       <c r="E37" t="n">
-        <v>4.52349</v>
+        <v>4.727</v>
       </c>
       <c r="F37" t="n">
-        <v>4.68547</v>
+        <v>5.03754</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>5.39557</v>
+        <v>5.39919</v>
       </c>
       <c r="C38" t="n">
-        <v>3.88767</v>
+        <v>4.03949</v>
       </c>
       <c r="D38" t="n">
-        <v>11.0693</v>
+        <v>11.823</v>
       </c>
       <c r="E38" t="n">
-        <v>4.55816</v>
+        <v>4.75362</v>
       </c>
       <c r="F38" t="n">
-        <v>4.68113</v>
+        <v>4.99336</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>5.40721</v>
+        <v>5.38326</v>
       </c>
       <c r="C39" t="n">
-        <v>3.78178</v>
+        <v>4.04921</v>
       </c>
       <c r="D39" t="n">
-        <v>11.7938</v>
+        <v>12.3857</v>
       </c>
       <c r="E39" t="n">
-        <v>4.5955</v>
+        <v>4.79116</v>
       </c>
       <c r="F39" t="n">
-        <v>4.81229</v>
+        <v>5.10844</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>5.39545</v>
+        <v>5.39299</v>
       </c>
       <c r="C40" t="n">
-        <v>3.78206</v>
+        <v>4.07815</v>
       </c>
       <c r="D40" t="n">
-        <v>12.5724</v>
+        <v>13.2336</v>
       </c>
       <c r="E40" t="n">
-        <v>4.57231</v>
+        <v>4.82301</v>
       </c>
       <c r="F40" t="n">
-        <v>4.84667</v>
+        <v>5.24602</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>4.90772</v>
+        <v>4.90983</v>
       </c>
       <c r="C41" t="n">
-        <v>4.30117</v>
+        <v>4.33246</v>
       </c>
       <c r="D41" t="n">
-        <v>13.3007</v>
+        <v>13.7978</v>
       </c>
       <c r="E41" t="n">
-        <v>4.82677</v>
+        <v>5.05617</v>
       </c>
       <c r="F41" t="n">
-        <v>4.59214</v>
+        <v>4.97569</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>5.25554</v>
+        <v>5.31504</v>
       </c>
       <c r="C42" t="n">
-        <v>3.99271</v>
+        <v>4.23072</v>
       </c>
       <c r="D42" t="n">
-        <v>13.6233</v>
+        <v>14.121</v>
       </c>
       <c r="E42" t="n">
-        <v>4.70939</v>
+        <v>4.90294</v>
       </c>
       <c r="F42" t="n">
-        <v>4.96405</v>
+        <v>5.36506</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>5.37518</v>
+        <v>5.42598</v>
       </c>
       <c r="C43" t="n">
-        <v>4.13204</v>
+        <v>4.30474</v>
       </c>
       <c r="D43" t="n">
-        <v>13.9046</v>
+        <v>14.254</v>
       </c>
       <c r="E43" t="n">
-        <v>4.92844</v>
+        <v>5.3566</v>
       </c>
       <c r="F43" t="n">
-        <v>4.74716</v>
+        <v>5.04401</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>5.22417</v>
+        <v>5.26949</v>
       </c>
       <c r="C44" t="n">
-        <v>3.98844</v>
+        <v>4.23714</v>
       </c>
       <c r="D44" t="n">
-        <v>14.1771</v>
+        <v>14.4947</v>
       </c>
       <c r="E44" t="n">
-        <v>4.77784</v>
+        <v>5.21236</v>
       </c>
       <c r="F44" t="n">
-        <v>4.77723</v>
+        <v>5.08642</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>5.52141</v>
+        <v>5.56838</v>
       </c>
       <c r="C45" t="n">
-        <v>4.25387</v>
+        <v>4.36203</v>
       </c>
       <c r="D45" t="n">
-        <v>14.3739</v>
+        <v>14.5758</v>
       </c>
       <c r="E45" t="n">
-        <v>5.08118</v>
+        <v>5.65872</v>
       </c>
       <c r="F45" t="n">
-        <v>5.05035</v>
+        <v>5.39999</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.93518</v>
+        <v>4.92774</v>
       </c>
       <c r="C46" t="n">
-        <v>4.37697</v>
+        <v>4.31277</v>
       </c>
       <c r="D46" t="n">
-        <v>14.7719</v>
+        <v>15.0393</v>
       </c>
       <c r="E46" t="n">
-        <v>5.1365</v>
+        <v>5.83041</v>
       </c>
       <c r="F46" t="n">
-        <v>5.13354</v>
+        <v>5.51057</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.98229</v>
+        <v>5.00051</v>
       </c>
       <c r="C47" t="n">
-        <v>4.55139</v>
+        <v>4.58193</v>
       </c>
       <c r="D47" t="n">
-        <v>14.9539</v>
+        <v>15.3181</v>
       </c>
       <c r="E47" t="n">
-        <v>5.10378</v>
+        <v>5.34346</v>
       </c>
       <c r="F47" t="n">
-        <v>5.43617</v>
+        <v>5.84009</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.26265</v>
+        <v>5.02756</v>
       </c>
       <c r="C48" t="n">
-        <v>4.09224</v>
+        <v>4.16476</v>
       </c>
       <c r="D48" t="n">
-        <v>15.9759</v>
+        <v>15.8322</v>
       </c>
       <c r="E48" t="n">
-        <v>5.21293</v>
+        <v>5.36519</v>
       </c>
       <c r="F48" t="n">
-        <v>5.83148</v>
+        <v>6.14052</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>5.19678</v>
+        <v>5.24324</v>
       </c>
       <c r="C49" t="n">
-        <v>4.57337</v>
+        <v>4.76857</v>
       </c>
       <c r="D49" t="n">
-        <v>16.4636</v>
+        <v>16.5837</v>
       </c>
       <c r="E49" t="n">
-        <v>5.607</v>
+        <v>6.00824</v>
       </c>
       <c r="F49" t="n">
-        <v>6.27514</v>
+        <v>6.65624</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>5.37611</v>
+        <v>5.45443</v>
       </c>
       <c r="C50" t="n">
-        <v>4.71233</v>
+        <v>4.91166</v>
       </c>
       <c r="D50" t="n">
-        <v>14.3111</v>
+        <v>13.8593</v>
       </c>
       <c r="E50" t="n">
-        <v>4.57463</v>
+        <v>4.39553</v>
       </c>
       <c r="F50" t="n">
-        <v>5.48119</v>
+        <v>5.42398</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>5.51498</v>
+        <v>5.43888</v>
       </c>
       <c r="C51" t="n">
-        <v>3.89946</v>
+        <v>3.86902</v>
       </c>
       <c r="D51" t="n">
-        <v>15.3265</v>
+        <v>14.7803</v>
       </c>
       <c r="E51" t="n">
-        <v>4.63734</v>
+        <v>4.57291</v>
       </c>
       <c r="F51" t="n">
-        <v>5.60194</v>
+        <v>5.487</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>6.81731</v>
+        <v>6.84921</v>
       </c>
       <c r="C52" t="n">
-        <v>4.11088</v>
+        <v>4.12098</v>
       </c>
       <c r="D52" t="n">
-        <v>16.315</v>
+        <v>15.6219</v>
       </c>
       <c r="E52" t="n">
-        <v>4.6481</v>
+        <v>4.66402</v>
       </c>
       <c r="F52" t="n">
-        <v>5.21697</v>
+        <v>5.28666</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>5.23205</v>
+        <v>5.29208</v>
       </c>
       <c r="C53" t="n">
-        <v>4.10501</v>
+        <v>4.09192</v>
       </c>
       <c r="D53" t="n">
-        <v>16.7167</v>
+        <v>16.1388</v>
       </c>
       <c r="E53" t="n">
-        <v>4.68509</v>
+        <v>4.87729</v>
       </c>
       <c r="F53" t="n">
-        <v>5.87627</v>
+        <v>5.67147</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>5.1916</v>
+        <v>5.26574</v>
       </c>
       <c r="C54" t="n">
-        <v>3.91408</v>
+        <v>3.95744</v>
       </c>
       <c r="D54" t="n">
-        <v>17.912</v>
+        <v>17.5211</v>
       </c>
       <c r="E54" t="n">
-        <v>4.71698</v>
+        <v>4.67679</v>
       </c>
       <c r="F54" t="n">
-        <v>5.82577</v>
+        <v>5.68382</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>5.17611</v>
+        <v>5.28976</v>
       </c>
       <c r="C55" t="n">
-        <v>3.97865</v>
+        <v>3.93235</v>
       </c>
       <c r="D55" t="n">
-        <v>17.7217</v>
+        <v>17.3292</v>
       </c>
       <c r="E55" t="n">
-        <v>5.02956</v>
+        <v>4.80004</v>
       </c>
       <c r="F55" t="n">
-        <v>5.31337</v>
+        <v>5.2565</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>5.43889</v>
+        <v>5.46117</v>
       </c>
       <c r="C56" t="n">
-        <v>4.15928</v>
+        <v>4.30219</v>
       </c>
       <c r="D56" t="n">
-        <v>14.8545</v>
+        <v>15.093</v>
       </c>
       <c r="E56" t="n">
-        <v>4.80137</v>
+        <v>4.96774</v>
       </c>
       <c r="F56" t="n">
-        <v>6.01277</v>
+        <v>5.89112</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>5.57741</v>
+        <v>5.25908</v>
       </c>
       <c r="C57" t="n">
-        <v>4.26329</v>
+        <v>4.22131</v>
       </c>
       <c r="D57" t="n">
-        <v>18.4495</v>
+        <v>18.157</v>
       </c>
       <c r="E57" t="n">
-        <v>5.11455</v>
+        <v>4.99513</v>
       </c>
       <c r="F57" t="n">
-        <v>5.67825</v>
+        <v>5.52513</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>5.17824</v>
+        <v>5.33823</v>
       </c>
       <c r="C58" t="n">
-        <v>4.03221</v>
+        <v>4.08834</v>
       </c>
       <c r="D58" t="n">
-        <v>18.1652</v>
+        <v>18.167</v>
       </c>
       <c r="E58" t="n">
-        <v>5.08219</v>
+        <v>5.05902</v>
       </c>
       <c r="F58" t="n">
-        <v>5.43118</v>
+        <v>5.39716</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>5.54963</v>
+        <v>5.32811</v>
       </c>
       <c r="C59" t="n">
-        <v>4.3865</v>
+        <v>4.23184</v>
       </c>
       <c r="D59" t="n">
-        <v>19.0818</v>
+        <v>19.1666</v>
       </c>
       <c r="E59" t="n">
-        <v>4.94414</v>
+        <v>5.0421</v>
       </c>
       <c r="F59" t="n">
-        <v>6.8671</v>
+        <v>7.38401</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>5.67297</v>
+        <v>5.30946</v>
       </c>
       <c r="C60" t="n">
-        <v>4.21019</v>
+        <v>4.43868</v>
       </c>
       <c r="D60" t="n">
-        <v>19.1155</v>
+        <v>19.2315</v>
       </c>
       <c r="E60" t="n">
-        <v>5.03623</v>
+        <v>5.05308</v>
       </c>
       <c r="F60" t="n">
-        <v>6.25918</v>
+        <v>6.75495</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>5.33954</v>
+        <v>5.3679</v>
       </c>
       <c r="C61" t="n">
-        <v>4.37639</v>
+        <v>4.28904</v>
       </c>
       <c r="D61" t="n">
-        <v>18.6075</v>
+        <v>19.1744</v>
       </c>
       <c r="E61" t="n">
-        <v>5.28009</v>
+        <v>5.49798</v>
       </c>
       <c r="F61" t="n">
-        <v>6.57125</v>
+        <v>7.13255</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.74881</v>
+        <v>5.48515</v>
       </c>
       <c r="C62" t="n">
-        <v>4.24088</v>
+        <v>4.3886</v>
       </c>
       <c r="D62" t="n">
-        <v>18.3595</v>
+        <v>19.2476</v>
       </c>
       <c r="E62" t="n">
-        <v>5.43719</v>
+        <v>5.65032</v>
       </c>
       <c r="F62" t="n">
-        <v>6.46074</v>
+        <v>7.13653</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>5.86279</v>
+        <v>5.60763</v>
       </c>
       <c r="C63" t="n">
-        <v>4.50982</v>
+        <v>4.71399</v>
       </c>
       <c r="D63" t="n">
-        <v>18.9169</v>
+        <v>19.6676</v>
       </c>
       <c r="E63" t="n">
-        <v>5.8434</v>
+        <v>5.93986</v>
       </c>
       <c r="F63" t="n">
-        <v>6.87789</v>
+        <v>7.25322</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>5.6496</v>
+        <v>5.62059</v>
       </c>
       <c r="C64" t="n">
-        <v>4.57376</v>
+        <v>4.57162</v>
       </c>
       <c r="D64" t="n">
-        <v>13.2437</v>
+        <v>13.0126</v>
       </c>
       <c r="E64" t="n">
-        <v>7.00594</v>
+        <v>5.66433</v>
       </c>
       <c r="F64" t="n">
-        <v>6.17349</v>
+        <v>6.26517</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>6.39593</v>
+        <v>5.99442</v>
       </c>
       <c r="C65" t="n">
-        <v>11.338</v>
+        <v>6.87855</v>
       </c>
       <c r="D65" t="n">
-        <v>14.1313</v>
+        <v>13.751</v>
       </c>
       <c r="E65" t="n">
-        <v>7.24045</v>
+        <v>5.79199</v>
       </c>
       <c r="F65" t="n">
-        <v>6.33367</v>
+        <v>6.35856</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>6.84586</v>
+        <v>6.4379</v>
       </c>
       <c r="C66" t="n">
-        <v>11.3848</v>
+        <v>6.96963</v>
       </c>
       <c r="D66" t="n">
-        <v>15.0203</v>
+        <v>14.5494</v>
       </c>
       <c r="E66" t="n">
-        <v>8.837400000000001</v>
+        <v>6.44885</v>
       </c>
       <c r="F66" t="n">
-        <v>6.75465</v>
+        <v>6.60925</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>13.4942</v>
+        <v>8.499470000000001</v>
       </c>
       <c r="C67" t="n">
-        <v>11.4494</v>
+        <v>6.66034</v>
       </c>
       <c r="D67" t="n">
-        <v>16.0327</v>
+        <v>15.5783</v>
       </c>
       <c r="E67" t="n">
-        <v>7.20344</v>
+        <v>5.5073</v>
       </c>
       <c r="F67" t="n">
-        <v>6.89564</v>
+        <v>6.67646</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>13.6791</v>
+        <v>8.07701</v>
       </c>
       <c r="C68" t="n">
-        <v>11.5423</v>
+        <v>6.28182</v>
       </c>
       <c r="D68" t="n">
-        <v>17.2027</v>
+        <v>16.4509</v>
       </c>
       <c r="E68" t="n">
-        <v>10.0712</v>
+        <v>7.30103</v>
       </c>
       <c r="F68" t="n">
-        <v>6.91947</v>
+        <v>6.78717</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>14.7452</v>
+        <v>9.5951</v>
       </c>
       <c r="C69" t="n">
-        <v>12.3843</v>
+        <v>7.83506</v>
       </c>
       <c r="D69" t="n">
-        <v>17.4218</v>
+        <v>17.2515</v>
       </c>
       <c r="E69" t="n">
-        <v>8.121359999999999</v>
+        <v>6.11462</v>
       </c>
       <c r="F69" t="n">
-        <v>6.93794</v>
+        <v>6.82182</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>13.6139</v>
+        <v>12.0245</v>
       </c>
       <c r="C70" t="n">
-        <v>11.3469</v>
+        <v>9.75113</v>
       </c>
       <c r="D70" t="n">
-        <v>17.0849</v>
+        <v>17.5994</v>
       </c>
       <c r="E70" t="n">
-        <v>9.30007</v>
+        <v>6.70111</v>
       </c>
       <c r="F70" t="n">
-        <v>6.93463</v>
+        <v>6.77508</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>13.5361</v>
+        <v>12.4309</v>
       </c>
       <c r="C71" t="n">
-        <v>11.268</v>
+        <v>10.2107</v>
       </c>
       <c r="D71" t="n">
-        <v>18.0486</v>
+        <v>19.1394</v>
       </c>
       <c r="E71" t="n">
-        <v>9.237349999999999</v>
+        <v>8.974869999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>6.60905</v>
+        <v>6.66301</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>14.2606</v>
+        <v>9.51047</v>
       </c>
       <c r="C72" t="n">
-        <v>12.0676</v>
+        <v>7.72657</v>
       </c>
       <c r="D72" t="n">
-        <v>18.5501</v>
+        <v>19.8762</v>
       </c>
       <c r="E72" t="n">
-        <v>9.443619999999999</v>
+        <v>9.121370000000001</v>
       </c>
       <c r="F72" t="n">
-        <v>6.80245</v>
+        <v>6.78609</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>14.7995</v>
+        <v>10.5849</v>
       </c>
       <c r="C73" t="n">
-        <v>12.3403</v>
+        <v>8.616059999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>18.7008</v>
+        <v>20.1296</v>
       </c>
       <c r="E73" t="n">
-        <v>9.64237</v>
+        <v>9.25728</v>
       </c>
       <c r="F73" t="n">
-        <v>6.9744</v>
+        <v>6.91386</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>13.2988</v>
+        <v>8.27473</v>
       </c>
       <c r="C74" t="n">
-        <v>11.2746</v>
+        <v>6.53066</v>
       </c>
       <c r="D74" t="n">
-        <v>19.9825</v>
+        <v>21.5527</v>
       </c>
       <c r="E74" t="n">
-        <v>9.639150000000001</v>
+        <v>10.7252</v>
       </c>
       <c r="F74" t="n">
-        <v>7.16754</v>
+        <v>7.37382</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>13.1355</v>
+        <v>13.9561</v>
       </c>
       <c r="C75" t="n">
-        <v>11.072</v>
+        <v>11.7957</v>
       </c>
       <c r="D75" t="n">
-        <v>19.9935</v>
+        <v>21.6136</v>
       </c>
       <c r="E75" t="n">
-        <v>9.82719</v>
+        <v>11.9757</v>
       </c>
       <c r="F75" t="n">
-        <v>7.46107</v>
+        <v>7.53338</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>13.0507</v>
+        <v>14.0704</v>
       </c>
       <c r="C76" t="n">
-        <v>11.071</v>
+        <v>11.8938</v>
       </c>
       <c r="D76" t="n">
-        <v>20.3517</v>
+        <v>21.1301</v>
       </c>
       <c r="E76" t="n">
-        <v>9.45914</v>
+        <v>11.2853</v>
       </c>
       <c r="F76" t="n">
-        <v>7.71512</v>
+        <v>8.02638</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>13.1098</v>
+        <v>14.5311</v>
       </c>
       <c r="C77" t="n">
-        <v>11.1491</v>
+        <v>12.2016</v>
       </c>
       <c r="D77" t="n">
-        <v>22.2257</v>
+        <v>22.7326</v>
       </c>
       <c r="E77" t="n">
-        <v>9.732279999999999</v>
+        <v>11.5371</v>
       </c>
       <c r="F77" t="n">
-        <v>9.16414</v>
+        <v>9.58511</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>15.019</v>
+        <v>11.3218</v>
       </c>
       <c r="C78" t="n">
-        <v>12.6348</v>
+        <v>9.152509999999999</v>
       </c>
       <c r="D78" t="n">
-        <v>22.7756</v>
+        <v>22.023</v>
       </c>
       <c r="E78" t="n">
-        <v>10.185</v>
+        <v>11.9268</v>
       </c>
       <c r="F78" t="n">
-        <v>12.546</v>
+        <v>14.2449</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>11.7867</v>
+        <v>13.1089</v>
       </c>
       <c r="C79" t="n">
-        <v>13.5889</v>
+        <v>13.3193</v>
       </c>
       <c r="D79" t="n">
-        <v>23.0411</v>
+        <v>22.4607</v>
       </c>
       <c r="E79" t="n">
-        <v>10.9557</v>
+        <v>12.0969</v>
       </c>
       <c r="F79" t="n">
-        <v>11.9794</v>
+        <v>13.9223</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>12.0295</v>
+        <v>13.4407</v>
       </c>
       <c r="C80" t="n">
-        <v>13.7342</v>
+        <v>13.976</v>
       </c>
       <c r="D80" t="n">
-        <v>24.209</v>
+        <v>23.5855</v>
       </c>
       <c r="E80" t="n">
-        <v>10.681</v>
+        <v>12.3257</v>
       </c>
       <c r="F80" t="n">
-        <v>12.4782</v>
+        <v>14.4191</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>16.5158</v>
+        <v>16.7275</v>
       </c>
       <c r="C81" t="n">
-        <v>13.7844</v>
+        <v>14.0276</v>
       </c>
       <c r="D81" t="n">
-        <v>24.8884</v>
+        <v>24.5726</v>
       </c>
       <c r="E81" t="n">
-        <v>9.377940000000001</v>
+        <v>12.2622</v>
       </c>
       <c r="F81" t="n">
-        <v>11.8716</v>
+        <v>12.2035</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>16.6005</v>
+        <v>16.8147</v>
       </c>
       <c r="C82" t="n">
-        <v>13.8591</v>
+        <v>14.089</v>
       </c>
       <c r="D82" t="n">
-        <v>25.3899</v>
+        <v>25.5264</v>
       </c>
       <c r="E82" t="n">
-        <v>11.1885</v>
+        <v>12.5798</v>
       </c>
       <c r="F82" t="n">
-        <v>12.4819</v>
+        <v>14.8112</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>16.679</v>
+        <v>16.8767</v>
       </c>
       <c r="C83" t="n">
-        <v>13.928</v>
+        <v>14.14</v>
       </c>
       <c r="D83" t="n">
-        <v>27.2571</v>
+        <v>26.1853</v>
       </c>
       <c r="E83" t="n">
-        <v>11.3612</v>
+        <v>12.6948</v>
       </c>
       <c r="F83" t="n">
-        <v>12.734</v>
+        <v>14.8037</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>16.7741</v>
+        <v>16.9522</v>
       </c>
       <c r="C84" t="n">
-        <v>14.005</v>
+        <v>14.2004</v>
       </c>
       <c r="D84" t="n">
-        <v>27.1748</v>
+        <v>27.2041</v>
       </c>
       <c r="E84" t="n">
-        <v>12.205</v>
+        <v>13.0135</v>
       </c>
       <c r="F84" t="n">
-        <v>12.6188</v>
+        <v>14.8956</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>17.0478</v>
+        <v>17.1279</v>
       </c>
       <c r="C85" t="n">
-        <v>14.301</v>
+        <v>14.375</v>
       </c>
       <c r="D85" t="n">
-        <v>29.1288</v>
+        <v>28.5013</v>
       </c>
       <c r="E85" t="n">
-        <v>11.3508</v>
+        <v>12.7512</v>
       </c>
       <c r="F85" t="n">
-        <v>12.5733</v>
+        <v>11.6414</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>16.8774</v>
+        <v>17.1217</v>
       </c>
       <c r="C86" t="n">
-        <v>14.108</v>
+        <v>14.3051</v>
       </c>
       <c r="D86" t="n">
-        <v>29.5828</v>
+        <v>30.0461</v>
       </c>
       <c r="E86" t="n">
-        <v>11.5832</v>
+        <v>12.9535</v>
       </c>
       <c r="F86" t="n">
-        <v>12.6669</v>
+        <v>11.8681</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>16.9346</v>
+        <v>17.1651</v>
       </c>
       <c r="C87" t="n">
-        <v>14.1501</v>
+        <v>14.3353</v>
       </c>
       <c r="D87" t="n">
-        <v>30.3189</v>
+        <v>30.6428</v>
       </c>
       <c r="E87" t="n">
-        <v>11.091</v>
+        <v>13.3578</v>
       </c>
       <c r="F87" t="n">
-        <v>12.2479</v>
+        <v>12.319</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>16.9539</v>
+        <v>17.2245</v>
       </c>
       <c r="C88" t="n">
-        <v>14.1317</v>
+        <v>14.4399</v>
       </c>
       <c r="D88" t="n">
-        <v>30.6064</v>
+        <v>30.2044</v>
       </c>
       <c r="E88" t="n">
-        <v>10.9744</v>
+        <v>13.1868</v>
       </c>
       <c r="F88" t="n">
-        <v>15.3068</v>
+        <v>15.6417</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>16.7201</v>
+        <v>17.1963</v>
       </c>
       <c r="C89" t="n">
-        <v>13.8297</v>
+        <v>14.3999</v>
       </c>
       <c r="D89" t="n">
-        <v>30.966</v>
+        <v>30.4661</v>
       </c>
       <c r="E89" t="n">
-        <v>11.0728</v>
+        <v>13.4029</v>
       </c>
       <c r="F89" t="n">
-        <v>12.4095</v>
+        <v>12.4342</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>16.7235</v>
+        <v>17.0969</v>
       </c>
       <c r="C90" t="n">
-        <v>13.8667</v>
+        <v>14.32</v>
       </c>
       <c r="D90" t="n">
-        <v>32.4456</v>
+        <v>33.3388</v>
       </c>
       <c r="E90" t="n">
-        <v>11.3265</v>
+        <v>13.582</v>
       </c>
       <c r="F90" t="n">
-        <v>13.5861</v>
+        <v>16.0066</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>17.2347</v>
+        <v>17.4313</v>
       </c>
       <c r="C91" t="n">
-        <v>14.4276</v>
+        <v>14.5753</v>
       </c>
       <c r="D91" t="n">
-        <v>34.6764</v>
+        <v>35.2674</v>
       </c>
       <c r="E91" t="n">
-        <v>11.6096</v>
+        <v>13.8759</v>
       </c>
       <c r="F91" t="n">
-        <v>15.9237</v>
+        <v>17.2938</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>17.2334</v>
+        <v>17.5618</v>
       </c>
       <c r="C92" t="n">
-        <v>14.4053</v>
+        <v>14.7677</v>
       </c>
       <c r="D92" t="n">
-        <v>30.7861</v>
+        <v>31.1102</v>
       </c>
       <c r="E92" t="n">
-        <v>19.7055</v>
+        <v>19.9415</v>
       </c>
       <c r="F92" t="n">
-        <v>17.8448</v>
+        <v>19.3703</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.2924</v>
+        <v>17.758</v>
       </c>
       <c r="C93" t="n">
-        <v>14.3721</v>
+        <v>14.9147</v>
       </c>
       <c r="D93" t="n">
-        <v>31.4975</v>
+        <v>31.8432</v>
       </c>
       <c r="E93" t="n">
-        <v>19.9165</v>
+        <v>20.221</v>
       </c>
       <c r="F93" t="n">
-        <v>17.9656</v>
+        <v>19.5159</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>17.5113</v>
+        <v>17.8641</v>
       </c>
       <c r="C94" t="n">
-        <v>19.0446</v>
+        <v>18.8175</v>
       </c>
       <c r="D94" t="n">
-        <v>32.2357</v>
+        <v>32.5664</v>
       </c>
       <c r="E94" t="n">
-        <v>20.0773</v>
+        <v>20.8937</v>
       </c>
       <c r="F94" t="n">
-        <v>18.0645</v>
+        <v>19.6273</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>22.3371</v>
+        <v>22.2503</v>
       </c>
       <c r="C95" t="n">
-        <v>19.0432</v>
+        <v>19.0281</v>
       </c>
       <c r="D95" t="n">
-        <v>33.2027</v>
+        <v>33.5478</v>
       </c>
       <c r="E95" t="n">
-        <v>20.3368</v>
+        <v>21.0274</v>
       </c>
       <c r="F95" t="n">
-        <v>18.3508</v>
+        <v>19.6668</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>22.4205</v>
+        <v>22.2849</v>
       </c>
       <c r="C96" t="n">
-        <v>19.0932</v>
+        <v>19.0786</v>
       </c>
       <c r="D96" t="n">
-        <v>34.0324</v>
+        <v>34.4001</v>
       </c>
       <c r="E96" t="n">
-        <v>20.5193</v>
+        <v>21.1605</v>
       </c>
       <c r="F96" t="n">
-        <v>18.3028</v>
+        <v>19.8373</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>22.4151</v>
+        <v>22.302</v>
       </c>
       <c r="C97" t="n">
-        <v>19.172</v>
+        <v>19.048</v>
       </c>
       <c r="D97" t="n">
-        <v>34.9603</v>
+        <v>35.2718</v>
       </c>
       <c r="E97" t="n">
-        <v>20.6746</v>
+        <v>21.3856</v>
       </c>
       <c r="F97" t="n">
-        <v>18.597</v>
+        <v>19.8698</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.42</v>
+        <v>22.2492</v>
       </c>
       <c r="C98" t="n">
-        <v>19.1532</v>
+        <v>19.103</v>
       </c>
       <c r="D98" t="n">
-        <v>35.6453</v>
+        <v>35.9694</v>
       </c>
       <c r="E98" t="n">
-        <v>20.8118</v>
+        <v>21.4848</v>
       </c>
       <c r="F98" t="n">
-        <v>18.7053</v>
+        <v>20.0058</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>22.3755</v>
+        <v>22.2965</v>
       </c>
       <c r="C99" t="n">
-        <v>19.2133</v>
+        <v>19.1107</v>
       </c>
       <c r="D99" t="n">
-        <v>36.575</v>
+        <v>36.8641</v>
       </c>
       <c r="E99" t="n">
-        <v>21.0235</v>
+        <v>21.7196</v>
       </c>
       <c r="F99" t="n">
-        <v>19.025</v>
+        <v>20.2898</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>22.4728</v>
+        <v>22.3053</v>
       </c>
       <c r="C100" t="n">
-        <v>19.2439</v>
+        <v>19.1945</v>
       </c>
       <c r="D100" t="n">
-        <v>38.0989</v>
+        <v>38.1063</v>
       </c>
       <c r="E100" t="n">
-        <v>21.188</v>
+        <v>21.902</v>
       </c>
       <c r="F100" t="n">
-        <v>19.2293</v>
+        <v>20.2589</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>22.4299</v>
+        <v>22.3265</v>
       </c>
       <c r="C101" t="n">
-        <v>19.2899</v>
+        <v>19.1837</v>
       </c>
       <c r="D101" t="n">
-        <v>39.239</v>
+        <v>39.1594</v>
       </c>
       <c r="E101" t="n">
-        <v>21.2616</v>
+        <v>22.1186</v>
       </c>
       <c r="F101" t="n">
-        <v>19.3393</v>
+        <v>20.6018</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>22.4769</v>
+        <v>22.33</v>
       </c>
       <c r="C102" t="n">
-        <v>19.3378</v>
+        <v>19.2604</v>
       </c>
       <c r="D102" t="n">
-        <v>40.0666</v>
+        <v>39.947</v>
       </c>
       <c r="E102" t="n">
-        <v>21.5051</v>
+        <v>22.3104</v>
       </c>
       <c r="F102" t="n">
-        <v>19.4957</v>
+        <v>20.77</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>22.518</v>
+        <v>22.4197</v>
       </c>
       <c r="C103" t="n">
-        <v>19.3892</v>
+        <v>19.3165</v>
       </c>
       <c r="D103" t="n">
-        <v>41.2386</v>
+        <v>41.164</v>
       </c>
       <c r="E103" t="n">
-        <v>21.7337</v>
+        <v>22.5915</v>
       </c>
       <c r="F103" t="n">
-        <v>19.7455</v>
+        <v>20.916</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>22.8308</v>
+        <v>22.5266</v>
       </c>
       <c r="C104" t="n">
-        <v>20.6845</v>
+        <v>19.4127</v>
       </c>
       <c r="D104" t="n">
-        <v>42.0537</v>
+        <v>42.08</v>
       </c>
       <c r="E104" t="n">
-        <v>21.7418</v>
+        <v>22.8629</v>
       </c>
       <c r="F104" t="n">
-        <v>19.9923</v>
+        <v>21.2138</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>22.5581</v>
+        <v>22.6133</v>
       </c>
       <c r="C105" t="n">
-        <v>19.5759</v>
+        <v>19.5246</v>
       </c>
       <c r="D105" t="n">
-        <v>43.1539</v>
+        <v>43.0884</v>
       </c>
       <c r="E105" t="n">
-        <v>22.0695</v>
+        <v>23.2103</v>
       </c>
       <c r="F105" t="n">
-        <v>20.9968</v>
+        <v>21.9807</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>22.6864</v>
+        <v>22.6764</v>
       </c>
       <c r="C106" t="n">
-        <v>19.7713</v>
+        <v>19.6714</v>
       </c>
       <c r="D106" t="n">
-        <v>44.8539</v>
+        <v>44.4379</v>
       </c>
       <c r="E106" t="n">
-        <v>22.4268</v>
+        <v>23.76</v>
       </c>
       <c r="F106" t="n">
-        <v>20.8152</v>
+        <v>22.0861</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>22.84</v>
+        <v>22.9186</v>
       </c>
       <c r="C107" t="n">
-        <v>19.9258</v>
+        <v>19.9259</v>
       </c>
       <c r="D107" t="n">
-        <v>38.0594</v>
+        <v>38.1083</v>
       </c>
       <c r="E107" t="n">
-        <v>24.9557</v>
+        <v>25.3064</v>
       </c>
       <c r="F107" t="n">
-        <v>22.9459</v>
+        <v>24.8829</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>22.9149</v>
+        <v>23.0067</v>
       </c>
       <c r="C108" t="n">
-        <v>20.6025</v>
+        <v>20.6735</v>
       </c>
       <c r="D108" t="n">
-        <v>38.8593</v>
+        <v>38.8613</v>
       </c>
       <c r="E108" t="n">
-        <v>25.5505</v>
+        <v>25.6134</v>
       </c>
       <c r="F108" t="n">
-        <v>22.8573</v>
+        <v>25.1392</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>23.6609</v>
+        <v>23.6114</v>
       </c>
       <c r="C109" t="n">
-        <v>20.6242</v>
+        <v>20.7008</v>
       </c>
       <c r="D109" t="n">
-        <v>39.5846</v>
+        <v>39.605</v>
       </c>
       <c r="E109" t="n">
-        <v>25.4245</v>
+        <v>25.8176</v>
       </c>
       <c r="F109" t="n">
-        <v>23.4001</v>
+        <v>25.3134</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>25.14</v>
+        <v>25.1956</v>
       </c>
       <c r="C110" t="n">
-        <v>20.6555</v>
+        <v>20.713</v>
       </c>
       <c r="D110" t="n">
-        <v>40.3097</v>
+        <v>40.2778</v>
       </c>
       <c r="E110" t="n">
-        <v>25.9983</v>
+        <v>26.0359</v>
       </c>
       <c r="F110" t="n">
-        <v>23.6153</v>
+        <v>25.4718</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>25.0526</v>
+        <v>25.3665</v>
       </c>
       <c r="C111" t="n">
-        <v>20.7454</v>
+        <v>20.7657</v>
       </c>
       <c r="D111" t="n">
-        <v>41.166</v>
+        <v>41.1648</v>
       </c>
       <c r="E111" t="n">
-        <v>26.2274</v>
+        <v>26.3282</v>
       </c>
       <c r="F111" t="n">
-        <v>23.8835</v>
+        <v>25.7733</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>25.04</v>
+        <v>25.2356</v>
       </c>
       <c r="C112" t="n">
-        <v>20.821</v>
+        <v>20.8073</v>
       </c>
       <c r="D112" t="n">
-        <v>41.8656</v>
+        <v>41.8679</v>
       </c>
       <c r="E112" t="n">
-        <v>26.441</v>
+        <v>26.6281</v>
       </c>
       <c r="F112" t="n">
-        <v>24.0151</v>
+        <v>25.8031</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>25.2917</v>
+        <v>25.3093</v>
       </c>
       <c r="C113" t="n">
-        <v>20.8458</v>
+        <v>20.9358</v>
       </c>
       <c r="D113" t="n">
-        <v>42.9056</v>
+        <v>42.8834</v>
       </c>
       <c r="E113" t="n">
-        <v>26.7341</v>
+        <v>26.8949</v>
       </c>
       <c r="F113" t="n">
-        <v>24.2547</v>
+        <v>26.1804</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>25.3544</v>
+        <v>25.2504</v>
       </c>
       <c r="C114" t="n">
-        <v>20.97</v>
+        <v>21.0226</v>
       </c>
       <c r="D114" t="n">
-        <v>43.7009</v>
+        <v>43.6753</v>
       </c>
       <c r="E114" t="n">
-        <v>26.9614</v>
+        <v>27.1342</v>
       </c>
       <c r="F114" t="n">
-        <v>24.5099</v>
+        <v>26.433</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>25.3649</v>
+        <v>25.1926</v>
       </c>
       <c r="C115" t="n">
-        <v>21.0262</v>
+        <v>21.1163</v>
       </c>
       <c r="D115" t="n">
-        <v>44.613</v>
+        <v>44.5866</v>
       </c>
       <c r="E115" t="n">
-        <v>27.195</v>
+        <v>27.4265</v>
       </c>
       <c r="F115" t="n">
-        <v>24.839</v>
+        <v>26.7262</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>25.3787</v>
+        <v>25.3463</v>
       </c>
       <c r="C116" t="n">
-        <v>21.1605</v>
+        <v>21.2288</v>
       </c>
       <c r="D116" t="n">
-        <v>45.5346</v>
+        <v>45.529</v>
       </c>
       <c r="E116" t="n">
-        <v>27.4982</v>
+        <v>27.8296</v>
       </c>
       <c r="F116" t="n">
-        <v>25.1676</v>
+        <v>27.0496</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>25.3526</v>
+        <v>25.4195</v>
       </c>
       <c r="C117" t="n">
-        <v>21.281</v>
+        <v>21.366</v>
       </c>
       <c r="D117" t="n">
-        <v>46.4293</v>
+        <v>46.4074</v>
       </c>
       <c r="E117" t="n">
-        <v>27.7293</v>
+        <v>28.2106</v>
       </c>
       <c r="F117" t="n">
-        <v>25.2628</v>
+        <v>27.4325</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>25.465</v>
+        <v>25.4713</v>
       </c>
       <c r="C118" t="n">
-        <v>21.4864</v>
+        <v>21.524</v>
       </c>
       <c r="D118" t="n">
-        <v>47.6372</v>
+        <v>47.5914</v>
       </c>
       <c r="E118" t="n">
-        <v>28.0335</v>
+        <v>28.6593</v>
       </c>
       <c r="F118" t="n">
-        <v>25.9482</v>
+        <v>27.8021</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>25.5375</v>
+        <v>25.5444</v>
       </c>
       <c r="C119" t="n">
-        <v>21.6575</v>
+        <v>21.6654</v>
       </c>
       <c r="D119" t="n">
-        <v>48.4542</v>
+        <v>48.3985</v>
       </c>
       <c r="E119" t="n">
-        <v>28.4364</v>
+        <v>29.0442</v>
       </c>
       <c r="F119" t="n">
-        <v>26.3977</v>
+        <v>28.3145</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>25.6911</v>
+        <v>25.6418</v>
       </c>
       <c r="C120" t="n">
-        <v>21.9567</v>
+        <v>21.9816</v>
       </c>
       <c r="D120" t="n">
-        <v>49.7972</v>
+        <v>49.7801</v>
       </c>
       <c r="E120" t="n">
-        <v>28.5592</v>
+        <v>29.6947</v>
       </c>
       <c r="F120" t="n">
-        <v>27.1525</v>
+        <v>29.0169</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>25.5327</v>
+        <v>25.8488</v>
       </c>
       <c r="C121" t="n">
-        <v>22.2566</v>
+        <v>22.2762</v>
       </c>
       <c r="D121" t="n">
-        <v>41.1252</v>
+        <v>41.1394</v>
       </c>
       <c r="E121" t="n">
-        <v>29.2755</v>
+        <v>29.0609</v>
       </c>
       <c r="F121" t="n">
-        <v>26.8695</v>
+        <v>28.7922</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>26.4601</v>
+        <v>26.0879</v>
       </c>
       <c r="C122" t="n">
-        <v>22.8644</v>
+        <v>22.8412</v>
       </c>
       <c r="D122" t="n">
-        <v>41.892</v>
+        <v>41.8714</v>
       </c>
       <c r="E122" t="n">
-        <v>29.6173</v>
+        <v>29.3445</v>
       </c>
       <c r="F122" t="n">
-        <v>27.152</v>
+        <v>28.8211</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>26.6805</v>
+        <v>26.71</v>
       </c>
       <c r="C123" t="n">
-        <v>22.9129</v>
+        <v>22.9515</v>
       </c>
       <c r="D123" t="n">
-        <v>42.3108</v>
+        <v>42.5328</v>
       </c>
       <c r="E123" t="n">
-        <v>29.8904</v>
+        <v>29.6248</v>
       </c>
       <c r="F123" t="n">
-        <v>27.2734</v>
+        <v>29.279</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>32.6606</v>
+        <v>32.7053</v>
       </c>
       <c r="C124" t="n">
-        <v>23.0634</v>
+        <v>23.0225</v>
       </c>
       <c r="D124" t="n">
-        <v>43.6656</v>
+        <v>43.6497</v>
       </c>
       <c r="E124" t="n">
-        <v>30.1758</v>
+        <v>29.8592</v>
       </c>
       <c r="F124" t="n">
-        <v>27.6303</v>
+        <v>29.2282</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>32.6465</v>
+        <v>31.8959</v>
       </c>
       <c r="C125" t="n">
-        <v>23.1858</v>
+        <v>23.1685</v>
       </c>
       <c r="D125" t="n">
-        <v>44.508</v>
+        <v>44.4754</v>
       </c>
       <c r="E125" t="n">
-        <v>30.4608</v>
+        <v>30.1502</v>
       </c>
       <c r="F125" t="n">
-        <v>27.8459</v>
+        <v>29.6357</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>32.5025</v>
+        <v>32.5888</v>
       </c>
       <c r="C126" t="n">
-        <v>23.2844</v>
+        <v>23.2647</v>
       </c>
       <c r="D126" t="n">
-        <v>44.485</v>
+        <v>44.6181</v>
       </c>
       <c r="E126" t="n">
-        <v>30.8117</v>
+        <v>30.4741</v>
       </c>
       <c r="F126" t="n">
-        <v>28.1466</v>
+        <v>29.7606</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>32.6391</v>
+        <v>32.5689</v>
       </c>
       <c r="C127" t="n">
-        <v>23.4217</v>
+        <v>23.4276</v>
       </c>
       <c r="D127" t="n">
-        <v>45.3107</v>
+        <v>45.5252</v>
       </c>
       <c r="E127" t="n">
-        <v>31.1098</v>
+        <v>30.7744</v>
       </c>
       <c r="F127" t="n">
-        <v>28.3926</v>
+        <v>30.2638</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>32.6857</v>
+        <v>32.5856</v>
       </c>
       <c r="C128" t="n">
-        <v>23.5359</v>
+        <v>23.596</v>
       </c>
       <c r="D128" t="n">
-        <v>46.4051</v>
+        <v>46.3667</v>
       </c>
       <c r="E128" t="n">
-        <v>31.3966</v>
+        <v>31.0984</v>
       </c>
       <c r="F128" t="n">
-        <v>28.6085</v>
+        <v>30.5491</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>32.6812</v>
+        <v>32.6505</v>
       </c>
       <c r="C129" t="n">
-        <v>23.7247</v>
+        <v>23.7756</v>
       </c>
       <c r="D129" t="n">
-        <v>47.1359</v>
+        <v>47.3428</v>
       </c>
       <c r="E129" t="n">
-        <v>31.6516</v>
+        <v>31.4386</v>
       </c>
       <c r="F129" t="n">
-        <v>29.0234</v>
+        <v>30.8955</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>32.7444</v>
+        <v>32.6662</v>
       </c>
       <c r="C130" t="n">
-        <v>23.948</v>
+        <v>23.9849</v>
       </c>
       <c r="D130" t="n">
-        <v>48.2715</v>
+        <v>48.2461</v>
       </c>
       <c r="E130" t="n">
-        <v>31.9297</v>
+        <v>31.8246</v>
       </c>
       <c r="F130" t="n">
-        <v>29.4324</v>
+        <v>31.2802</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>32.6885</v>
+        <v>32.7259</v>
       </c>
       <c r="C131" t="n">
-        <v>24.2426</v>
+        <v>24.2555</v>
       </c>
       <c r="D131" t="n">
-        <v>49.1852</v>
+        <v>49.1616</v>
       </c>
       <c r="E131" t="n">
-        <v>32.366</v>
+        <v>32.2611</v>
       </c>
       <c r="F131" t="n">
-        <v>29.8043</v>
+        <v>31.775</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>32.7832</v>
+        <v>32.733</v>
       </c>
       <c r="C132" t="n">
-        <v>24.4957</v>
+        <v>24.4809</v>
       </c>
       <c r="D132" t="n">
-        <v>50.1405</v>
+        <v>50.1432</v>
       </c>
       <c r="E132" t="n">
-        <v>32.7278</v>
+        <v>32.7444</v>
       </c>
       <c r="F132" t="n">
-        <v>30.3816</v>
+        <v>32.3762</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>32.8161</v>
+        <v>32.7804</v>
       </c>
       <c r="C133" t="n">
-        <v>24.7944</v>
+        <v>24.7868</v>
       </c>
       <c r="D133" t="n">
-        <v>51.1015</v>
+        <v>50.8513</v>
       </c>
       <c r="E133" t="n">
-        <v>33.208</v>
+        <v>33.304</v>
       </c>
       <c r="F133" t="n">
-        <v>31.0913</v>
+        <v>33.0199</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>32.9467</v>
+        <v>33.0378</v>
       </c>
       <c r="C134" t="n">
-        <v>25.1952</v>
+        <v>25.2098</v>
       </c>
       <c r="D134" t="n">
-        <v>52.3474</v>
+        <v>52.335</v>
       </c>
       <c r="E134" t="n">
-        <v>33.733</v>
+        <v>33.9686</v>
       </c>
       <c r="F134" t="n">
-        <v>31.8289</v>
+        <v>33.8053</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>33.0917</v>
+        <v>33.1938</v>
       </c>
       <c r="C135" t="n">
-        <v>25.7294</v>
+        <v>25.7134</v>
       </c>
       <c r="D135" t="n">
-        <v>43.2468</v>
+        <v>43.2853</v>
       </c>
       <c r="E135" t="n">
-        <v>31.3672</v>
+        <v>31.3027</v>
       </c>
       <c r="F135" t="n">
-        <v>29.3654</v>
+        <v>30.912</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>32.4129</v>
+        <v>33.4539</v>
       </c>
       <c r="C136" t="n">
-        <v>24.7258</v>
+        <v>25.0891</v>
       </c>
       <c r="D136" t="n">
-        <v>43.5667</v>
+        <v>43.5372</v>
       </c>
       <c r="E136" t="n">
-        <v>31.6867</v>
+        <v>31.5376</v>
       </c>
       <c r="F136" t="n">
-        <v>29.6156</v>
+        <v>31.1495</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>32.775</v>
+        <v>34.0686</v>
       </c>
       <c r="C137" t="n">
-        <v>24.9026</v>
+        <v>25.1473</v>
       </c>
       <c r="D137" t="n">
-        <v>44.2718</v>
+        <v>44.2363</v>
       </c>
       <c r="E137" t="n">
-        <v>32.0025</v>
+        <v>31.786</v>
       </c>
       <c r="F137" t="n">
-        <v>29.7271</v>
+        <v>31.3942</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>37.6179</v>
+        <v>37.6232</v>
       </c>
       <c r="C138" t="n">
-        <v>25.3556</v>
+        <v>25.3564</v>
       </c>
       <c r="D138" t="n">
-        <v>45.2256</v>
+        <v>45.2132</v>
       </c>
       <c r="E138" t="n">
-        <v>32.622</v>
+        <v>31.6689</v>
       </c>
       <c r="F138" t="n">
-        <v>30.1092</v>
+        <v>31.6912</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>37.6005</v>
+        <v>37.0347</v>
       </c>
       <c r="C139" t="n">
-        <v>25.5951</v>
+        <v>25.4503</v>
       </c>
       <c r="D139" t="n">
-        <v>45.3564</v>
+        <v>45.3487</v>
       </c>
       <c r="E139" t="n">
-        <v>32.8886</v>
+        <v>32.3791</v>
       </c>
       <c r="F139" t="n">
-        <v>30.2897</v>
+        <v>31.8137</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>37.6892</v>
+        <v>37.6164</v>
       </c>
       <c r="C140" t="n">
-        <v>25.718</v>
+        <v>25.6453</v>
       </c>
       <c r="D140" t="n">
-        <v>45.9785</v>
+        <v>46.1645</v>
       </c>
       <c r="E140" t="n">
-        <v>33.2029</v>
+        <v>32.7202</v>
       </c>
       <c r="F140" t="n">
-        <v>30.3694</v>
+        <v>32.0514</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>37.6641</v>
+        <v>37.6782</v>
       </c>
       <c r="C141" t="n">
-        <v>25.9289</v>
+        <v>25.8141</v>
       </c>
       <c r="D141" t="n">
-        <v>47.2774</v>
+        <v>47.2509</v>
       </c>
       <c r="E141" t="n">
-        <v>33.4404</v>
+        <v>32.9399</v>
       </c>
       <c r="F141" t="n">
-        <v>30.9194</v>
+        <v>32.483</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>37.692</v>
+        <v>37.6941</v>
       </c>
       <c r="C142" t="n">
-        <v>26.0935</v>
+        <v>26.0447</v>
       </c>
       <c r="D142" t="n">
-        <v>47.9793</v>
+        <v>48.0124</v>
       </c>
       <c r="E142" t="n">
-        <v>33.7376</v>
+        <v>32.8044</v>
       </c>
       <c r="F142" t="n">
-        <v>31.2164</v>
+        <v>32.8975</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>37.7352</v>
+        <v>37.0945</v>
       </c>
       <c r="C143" t="n">
-        <v>26.2999</v>
+        <v>26.266</v>
       </c>
       <c r="D143" t="n">
-        <v>49.4711</v>
+        <v>49.2478</v>
       </c>
       <c r="E143" t="n">
-        <v>34.1122</v>
+        <v>33.7169</v>
       </c>
       <c r="F143" t="n">
-        <v>31.3172</v>
+        <v>33.1576</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Scattered successful looukp.xlsx
+++ b/gcc-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>3.74091</v>
+        <v>4.25936</v>
       </c>
       <c r="C2" t="n">
-        <v>3.57</v>
+        <v>3.35568</v>
       </c>
       <c r="D2" t="n">
-        <v>8.06002</v>
+        <v>8.22819</v>
       </c>
       <c r="E2" t="n">
-        <v>3.89049</v>
+        <v>3.90049</v>
       </c>
       <c r="F2" t="n">
-        <v>3.46329</v>
+        <v>3.44252</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>3.694</v>
+        <v>3.77743</v>
       </c>
       <c r="C3" t="n">
-        <v>3.3623</v>
+        <v>3.19059</v>
       </c>
       <c r="D3" t="n">
-        <v>8.432600000000001</v>
+        <v>8.518829999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>3.34601</v>
+        <v>3.40268</v>
       </c>
       <c r="F3" t="n">
-        <v>3.93868</v>
+        <v>4.08449</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.46768</v>
+        <v>3.38931</v>
       </c>
       <c r="C4" t="n">
-        <v>3.04422</v>
+        <v>2.95999</v>
       </c>
       <c r="D4" t="n">
-        <v>9.11697</v>
+        <v>9.22287</v>
       </c>
       <c r="E4" t="n">
-        <v>3.51024</v>
+        <v>3.28566</v>
       </c>
       <c r="F4" t="n">
-        <v>4.20432</v>
+        <v>4.29065</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.80884</v>
+        <v>3.79357</v>
       </c>
       <c r="C5" t="n">
-        <v>3.43723</v>
+        <v>3.25058</v>
       </c>
       <c r="D5" t="n">
-        <v>10.0814</v>
+        <v>10.4125</v>
       </c>
       <c r="E5" t="n">
-        <v>3.44559</v>
+        <v>3.31335</v>
       </c>
       <c r="F5" t="n">
-        <v>4.18969</v>
+        <v>4.21022</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>3.93175</v>
+        <v>4.01436</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4709</v>
+        <v>3.28642</v>
       </c>
       <c r="D6" t="n">
-        <v>10.9317</v>
+        <v>11.2173</v>
       </c>
       <c r="E6" t="n">
-        <v>3.89862</v>
+        <v>3.67766</v>
       </c>
       <c r="F6" t="n">
-        <v>3.80414</v>
+        <v>4.13665</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>3.74548</v>
+        <v>3.82041</v>
       </c>
       <c r="C7" t="n">
-        <v>3.5328</v>
+        <v>3.34857</v>
       </c>
       <c r="D7" t="n">
-        <v>6.98624</v>
+        <v>6.95357</v>
       </c>
       <c r="E7" t="n">
-        <v>4.16269</v>
+        <v>4.03331</v>
       </c>
       <c r="F7" t="n">
-        <v>3.68852</v>
+        <v>3.64334</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>3.78041</v>
+        <v>3.8462</v>
       </c>
       <c r="C8" t="n">
-        <v>3.92393</v>
+        <v>3.42597</v>
       </c>
       <c r="D8" t="n">
-        <v>7.33235</v>
+        <v>7.36932</v>
       </c>
       <c r="E8" t="n">
-        <v>4.41566</v>
+        <v>4.08576</v>
       </c>
       <c r="F8" t="n">
-        <v>3.73236</v>
+        <v>3.67283</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>3.56166</v>
+        <v>3.4901</v>
       </c>
       <c r="C9" t="n">
-        <v>4.13077</v>
+        <v>3.65367</v>
       </c>
       <c r="D9" t="n">
-        <v>7.73827</v>
+        <v>7.71742</v>
       </c>
       <c r="E9" t="n">
-        <v>4.42434</v>
+        <v>4.10781</v>
       </c>
       <c r="F9" t="n">
-        <v>3.72744</v>
+        <v>3.67466</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>4.34877</v>
+        <v>4.21439</v>
       </c>
       <c r="C10" t="n">
-        <v>4.14001</v>
+        <v>3.66853</v>
       </c>
       <c r="D10" t="n">
-        <v>8.24155</v>
+        <v>8.16738</v>
       </c>
       <c r="E10" t="n">
-        <v>4.49929</v>
+        <v>4.14347</v>
       </c>
       <c r="F10" t="n">
-        <v>3.7746</v>
+        <v>3.72159</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>4.97724</v>
+        <v>4.9945</v>
       </c>
       <c r="C11" t="n">
-        <v>4.09391</v>
+        <v>3.74706</v>
       </c>
       <c r="D11" t="n">
-        <v>8.75273</v>
+        <v>8.626300000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>4.79151</v>
+        <v>4.44739</v>
       </c>
       <c r="F11" t="n">
-        <v>3.74507</v>
+        <v>3.67235</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>4.07545</v>
+        <v>4.05118</v>
       </c>
       <c r="C12" t="n">
-        <v>4.0407</v>
+        <v>3.65476</v>
       </c>
       <c r="D12" t="n">
-        <v>9.34374</v>
+        <v>9.25164</v>
       </c>
       <c r="E12" t="n">
-        <v>4.89158</v>
+        <v>4.47842</v>
       </c>
       <c r="F12" t="n">
-        <v>3.76085</v>
+        <v>3.66527</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>4.96655</v>
+        <v>4.97098</v>
       </c>
       <c r="C13" t="n">
-        <v>4.38304</v>
+        <v>3.75083</v>
       </c>
       <c r="D13" t="n">
-        <v>9.87567</v>
+        <v>9.747769999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>4.79614</v>
+        <v>4.33946</v>
       </c>
       <c r="F13" t="n">
-        <v>3.92704</v>
+        <v>3.88566</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>4.99337</v>
+        <v>4.99911</v>
       </c>
       <c r="C14" t="n">
-        <v>4.3112</v>
+        <v>3.82085</v>
       </c>
       <c r="D14" t="n">
-        <v>10.2636</v>
+        <v>10.1689</v>
       </c>
       <c r="E14" t="n">
-        <v>4.62158</v>
+        <v>4.258</v>
       </c>
       <c r="F14" t="n">
-        <v>3.8565</v>
+        <v>3.79423</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>4.98543</v>
+        <v>4.98402</v>
       </c>
       <c r="C15" t="n">
-        <v>4.44228</v>
+        <v>3.80419</v>
       </c>
       <c r="D15" t="n">
-        <v>10.7604</v>
+        <v>10.5955</v>
       </c>
       <c r="E15" t="n">
-        <v>4.65559</v>
+        <v>4.38272</v>
       </c>
       <c r="F15" t="n">
-        <v>3.936</v>
+        <v>3.90732</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>5.01323</v>
+        <v>5.01249</v>
       </c>
       <c r="C16" t="n">
-        <v>4.3659</v>
+        <v>3.8659</v>
       </c>
       <c r="D16" t="n">
-        <v>11.3364</v>
+        <v>11.155</v>
       </c>
       <c r="E16" t="n">
-        <v>5.15679</v>
+        <v>4.63577</v>
       </c>
       <c r="F16" t="n">
-        <v>4.01101</v>
+        <v>3.9501</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>5.00866</v>
+        <v>5.00679</v>
       </c>
       <c r="C17" t="n">
-        <v>4.54942</v>
+        <v>3.87506</v>
       </c>
       <c r="D17" t="n">
-        <v>11.7207</v>
+        <v>11.5379</v>
       </c>
       <c r="E17" t="n">
-        <v>4.80673</v>
+        <v>4.33441</v>
       </c>
       <c r="F17" t="n">
-        <v>3.92834</v>
+        <v>3.87878</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>5.02342</v>
+        <v>5.01659</v>
       </c>
       <c r="C18" t="n">
-        <v>4.58226</v>
+        <v>3.92774</v>
       </c>
       <c r="D18" t="n">
-        <v>12.0781</v>
+        <v>11.9337</v>
       </c>
       <c r="E18" t="n">
-        <v>4.99514</v>
+        <v>4.67108</v>
       </c>
       <c r="F18" t="n">
-        <v>3.90782</v>
+        <v>3.86325</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>5.03193</v>
+        <v>5.02063</v>
       </c>
       <c r="C19" t="n">
-        <v>4.63833</v>
+        <v>3.97453</v>
       </c>
       <c r="D19" t="n">
-        <v>12.7345</v>
+        <v>12.5576</v>
       </c>
       <c r="E19" t="n">
-        <v>4.73111</v>
+        <v>4.41901</v>
       </c>
       <c r="F19" t="n">
-        <v>3.97752</v>
+        <v>3.92261</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>5.06114</v>
+        <v>5.03989</v>
       </c>
       <c r="C20" t="n">
-        <v>4.71736</v>
+        <v>4.03562</v>
       </c>
       <c r="D20" t="n">
-        <v>13.1597</v>
+        <v>13.0001</v>
       </c>
       <c r="E20" t="n">
-        <v>5.49253</v>
+        <v>4.78412</v>
       </c>
       <c r="F20" t="n">
-        <v>4.09188</v>
+        <v>4.05441</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>5.08585</v>
+        <v>5.06482</v>
       </c>
       <c r="C21" t="n">
-        <v>4.7881</v>
+        <v>4.08514</v>
       </c>
       <c r="D21" t="n">
-        <v>9.3903</v>
+        <v>9.20439</v>
       </c>
       <c r="E21" t="n">
-        <v>4.4975</v>
+        <v>4.3484</v>
       </c>
       <c r="F21" t="n">
-        <v>4.47424</v>
+        <v>4.45651</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>5.11981</v>
+        <v>5.118</v>
       </c>
       <c r="C22" t="n">
-        <v>3.98141</v>
+        <v>3.65859</v>
       </c>
       <c r="D22" t="n">
-        <v>9.681369999999999</v>
+        <v>9.50343</v>
       </c>
       <c r="E22" t="n">
-        <v>4.65321</v>
+        <v>4.37718</v>
       </c>
       <c r="F22" t="n">
-        <v>4.59048</v>
+        <v>4.60251</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>5.02642</v>
+        <v>5.14147</v>
       </c>
       <c r="C23" t="n">
-        <v>4.00463</v>
+        <v>3.64117</v>
       </c>
       <c r="D23" t="n">
-        <v>10.0318</v>
+        <v>9.847849999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>4.75839</v>
+        <v>4.46743</v>
       </c>
       <c r="F23" t="n">
-        <v>4.54745</v>
+        <v>4.54759</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>5.23389</v>
+        <v>5.15805</v>
       </c>
       <c r="C24" t="n">
-        <v>4.03139</v>
+        <v>3.71132</v>
       </c>
       <c r="D24" t="n">
-        <v>10.3328</v>
+        <v>10.1291</v>
       </c>
       <c r="E24" t="n">
-        <v>4.79455</v>
+        <v>4.48368</v>
       </c>
       <c r="F24" t="n">
-        <v>4.58253</v>
+        <v>4.58141</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>5.24743</v>
+        <v>5.17407</v>
       </c>
       <c r="C25" t="n">
-        <v>4.04714</v>
+        <v>3.71431</v>
       </c>
       <c r="D25" t="n">
-        <v>10.7208</v>
+        <v>10.5015</v>
       </c>
       <c r="E25" t="n">
-        <v>4.79975</v>
+        <v>4.49216</v>
       </c>
       <c r="F25" t="n">
-        <v>4.66507</v>
+        <v>4.67327</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>5.25621</v>
+        <v>5.18151</v>
       </c>
       <c r="C26" t="n">
-        <v>4.05118</v>
+        <v>3.71828</v>
       </c>
       <c r="D26" t="n">
-        <v>11.0927</v>
+        <v>10.9157</v>
       </c>
       <c r="E26" t="n">
-        <v>4.8005</v>
+        <v>4.47538</v>
       </c>
       <c r="F26" t="n">
-        <v>4.63375</v>
+        <v>4.49146</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>5.10197</v>
+        <v>4.96546</v>
       </c>
       <c r="C27" t="n">
-        <v>4.06407</v>
+        <v>3.77238</v>
       </c>
       <c r="D27" t="n">
-        <v>11.5899</v>
+        <v>11.3648</v>
       </c>
       <c r="E27" t="n">
-        <v>4.86666</v>
+        <v>4.55117</v>
       </c>
       <c r="F27" t="n">
-        <v>4.64995</v>
+        <v>4.51475</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>5.12461</v>
+        <v>4.9865</v>
       </c>
       <c r="C28" t="n">
-        <v>4.05962</v>
+        <v>3.74255</v>
       </c>
       <c r="D28" t="n">
-        <v>11.9541</v>
+        <v>11.7334</v>
       </c>
       <c r="E28" t="n">
-        <v>4.92232</v>
+        <v>4.58784</v>
       </c>
       <c r="F28" t="n">
-        <v>4.71678</v>
+        <v>4.58231</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>5.13008</v>
+        <v>4.98755</v>
       </c>
       <c r="C29" t="n">
-        <v>4.08745</v>
+        <v>3.82627</v>
       </c>
       <c r="D29" t="n">
-        <v>12.4083</v>
+        <v>12.1867</v>
       </c>
       <c r="E29" t="n">
-        <v>4.95227</v>
+        <v>4.61705</v>
       </c>
       <c r="F29" t="n">
-        <v>4.7542</v>
+        <v>4.62609</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>5.2957</v>
+        <v>5.21068</v>
       </c>
       <c r="C30" t="n">
-        <v>4.25952</v>
+        <v>3.84896</v>
       </c>
       <c r="D30" t="n">
-        <v>12.85</v>
+        <v>12.6113</v>
       </c>
       <c r="E30" t="n">
-        <v>5.00928</v>
+        <v>4.65763</v>
       </c>
       <c r="F30" t="n">
-        <v>4.77243</v>
+        <v>4.63022</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>5.31977</v>
+        <v>5.23712</v>
       </c>
       <c r="C31" t="n">
-        <v>4.21356</v>
+        <v>3.81791</v>
       </c>
       <c r="D31" t="n">
-        <v>13.3674</v>
+        <v>13.1508</v>
       </c>
       <c r="E31" t="n">
-        <v>5.01643</v>
+        <v>4.64126</v>
       </c>
       <c r="F31" t="n">
-        <v>4.81824</v>
+        <v>4.69552</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>5.17673</v>
+        <v>5.02891</v>
       </c>
       <c r="C32" t="n">
-        <v>4.23235</v>
+        <v>3.93777</v>
       </c>
       <c r="D32" t="n">
-        <v>13.7367</v>
+        <v>13.5294</v>
       </c>
       <c r="E32" t="n">
-        <v>5.10085</v>
+        <v>4.72314</v>
       </c>
       <c r="F32" t="n">
-        <v>4.88345</v>
+        <v>4.70967</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>5.18848</v>
+        <v>5.04919</v>
       </c>
       <c r="C33" t="n">
-        <v>4.25751</v>
+        <v>3.98299</v>
       </c>
       <c r="D33" t="n">
-        <v>14.122</v>
+        <v>13.8756</v>
       </c>
       <c r="E33" t="n">
-        <v>5.14205</v>
+        <v>4.72584</v>
       </c>
       <c r="F33" t="n">
-        <v>4.93747</v>
+        <v>4.76244</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.21226</v>
+        <v>5.06328</v>
       </c>
       <c r="C34" t="n">
-        <v>4.34013</v>
+        <v>4.00424</v>
       </c>
       <c r="D34" t="n">
-        <v>14.5607</v>
+        <v>14.1131</v>
       </c>
       <c r="E34" t="n">
-        <v>4.89074</v>
+        <v>4.72328</v>
       </c>
       <c r="F34" t="n">
-        <v>5.08927</v>
+        <v>4.92821</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>5.32242</v>
+        <v>5.28688</v>
       </c>
       <c r="C35" t="n">
-        <v>4.39843</v>
+        <v>4.02553</v>
       </c>
       <c r="D35" t="n">
-        <v>10.5409</v>
+        <v>10.1349</v>
       </c>
       <c r="E35" t="n">
-        <v>4.61473</v>
+        <v>4.47414</v>
       </c>
       <c r="F35" t="n">
-        <v>4.90472</v>
+        <v>4.79538</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>5.25376</v>
+        <v>5.14489</v>
       </c>
       <c r="C36" t="n">
-        <v>4.46313</v>
+        <v>4.13376</v>
       </c>
       <c r="D36" t="n">
-        <v>11.1908</v>
+        <v>10.4239</v>
       </c>
       <c r="E36" t="n">
-        <v>4.68987</v>
+        <v>4.52116</v>
       </c>
       <c r="F36" t="n">
-        <v>5.03684</v>
+        <v>4.92514</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>5.35332</v>
+        <v>5.24382</v>
       </c>
       <c r="C37" t="n">
-        <v>4.25765</v>
+        <v>3.9448</v>
       </c>
       <c r="D37" t="n">
-        <v>11.9277</v>
+        <v>10.9707</v>
       </c>
       <c r="E37" t="n">
-        <v>4.727</v>
+        <v>4.55978</v>
       </c>
       <c r="F37" t="n">
-        <v>5.03754</v>
+        <v>4.96782</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>5.39919</v>
+        <v>5.3206</v>
       </c>
       <c r="C38" t="n">
-        <v>4.03949</v>
+        <v>3.74772</v>
       </c>
       <c r="D38" t="n">
-        <v>11.823</v>
+        <v>10.9072</v>
       </c>
       <c r="E38" t="n">
-        <v>4.75362</v>
+        <v>4.57174</v>
       </c>
       <c r="F38" t="n">
-        <v>4.99336</v>
+        <v>4.94848</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>5.38326</v>
+        <v>5.27926</v>
       </c>
       <c r="C39" t="n">
-        <v>4.04921</v>
+        <v>3.84433</v>
       </c>
       <c r="D39" t="n">
-        <v>12.3857</v>
+        <v>11.6034</v>
       </c>
       <c r="E39" t="n">
-        <v>4.79116</v>
+        <v>4.61404</v>
       </c>
       <c r="F39" t="n">
-        <v>5.10844</v>
+        <v>5.01095</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>5.39299</v>
+        <v>5.27953</v>
       </c>
       <c r="C40" t="n">
-        <v>4.07815</v>
+        <v>3.78687</v>
       </c>
       <c r="D40" t="n">
-        <v>13.2336</v>
+        <v>12.3739</v>
       </c>
       <c r="E40" t="n">
-        <v>4.82301</v>
+        <v>4.64549</v>
       </c>
       <c r="F40" t="n">
-        <v>5.24602</v>
+        <v>5.06106</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>4.90983</v>
+        <v>5.06733</v>
       </c>
       <c r="C41" t="n">
-        <v>4.33246</v>
+        <v>4.01108</v>
       </c>
       <c r="D41" t="n">
-        <v>13.7978</v>
+        <v>12.9776</v>
       </c>
       <c r="E41" t="n">
-        <v>5.05617</v>
+        <v>4.79085</v>
       </c>
       <c r="F41" t="n">
-        <v>4.97569</v>
+        <v>5.05274</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>5.31504</v>
+        <v>5.22619</v>
       </c>
       <c r="C42" t="n">
-        <v>4.23072</v>
+        <v>3.98903</v>
       </c>
       <c r="D42" t="n">
-        <v>14.121</v>
+        <v>13.2649</v>
       </c>
       <c r="E42" t="n">
-        <v>4.90294</v>
+        <v>4.71466</v>
       </c>
       <c r="F42" t="n">
-        <v>5.36506</v>
+        <v>5.22701</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>5.42598</v>
+        <v>5.33962</v>
       </c>
       <c r="C43" t="n">
-        <v>4.30474</v>
+        <v>3.98443</v>
       </c>
       <c r="D43" t="n">
-        <v>14.254</v>
+        <v>13.471</v>
       </c>
       <c r="E43" t="n">
-        <v>5.3566</v>
+        <v>4.86647</v>
       </c>
       <c r="F43" t="n">
-        <v>5.04401</v>
+        <v>5.17205</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>5.26949</v>
+        <v>5.16134</v>
       </c>
       <c r="C44" t="n">
-        <v>4.23714</v>
+        <v>4.03599</v>
       </c>
       <c r="D44" t="n">
-        <v>14.4947</v>
+        <v>13.7617</v>
       </c>
       <c r="E44" t="n">
-        <v>5.21236</v>
+        <v>4.79945</v>
       </c>
       <c r="F44" t="n">
-        <v>5.08642</v>
+        <v>5.21136</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>5.56838</v>
+        <v>5.4643</v>
       </c>
       <c r="C45" t="n">
-        <v>4.36203</v>
+        <v>4.10764</v>
       </c>
       <c r="D45" t="n">
-        <v>14.5758</v>
+        <v>13.9889</v>
       </c>
       <c r="E45" t="n">
-        <v>5.65872</v>
+        <v>4.94637</v>
       </c>
       <c r="F45" t="n">
-        <v>5.39999</v>
+        <v>5.36113</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.92774</v>
+        <v>5.25759</v>
       </c>
       <c r="C46" t="n">
-        <v>4.31277</v>
+        <v>4.10589</v>
       </c>
       <c r="D46" t="n">
-        <v>15.0393</v>
+        <v>14.5329</v>
       </c>
       <c r="E46" t="n">
-        <v>5.83041</v>
+        <v>4.96465</v>
       </c>
       <c r="F46" t="n">
-        <v>5.51057</v>
+        <v>5.48022</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>5.00051</v>
+        <v>5.15035</v>
       </c>
       <c r="C47" t="n">
-        <v>4.58193</v>
+        <v>4.24637</v>
       </c>
       <c r="D47" t="n">
-        <v>15.3181</v>
+        <v>14.9035</v>
       </c>
       <c r="E47" t="n">
-        <v>5.34346</v>
+        <v>5.09805</v>
       </c>
       <c r="F47" t="n">
-        <v>5.84009</v>
+        <v>5.6351</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.02756</v>
+        <v>5.00522</v>
       </c>
       <c r="C48" t="n">
-        <v>4.16476</v>
+        <v>4.30682</v>
       </c>
       <c r="D48" t="n">
-        <v>15.8322</v>
+        <v>15.6287</v>
       </c>
       <c r="E48" t="n">
-        <v>5.36519</v>
+        <v>5.53762</v>
       </c>
       <c r="F48" t="n">
-        <v>6.14052</v>
+        <v>6.04301</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>5.24324</v>
+        <v>5.15338</v>
       </c>
       <c r="C49" t="n">
-        <v>4.76857</v>
+        <v>4.39516</v>
       </c>
       <c r="D49" t="n">
-        <v>16.5837</v>
+        <v>16.4598</v>
       </c>
       <c r="E49" t="n">
-        <v>6.00824</v>
+        <v>5.87017</v>
       </c>
       <c r="F49" t="n">
-        <v>6.65624</v>
+        <v>6.50175</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>5.45443</v>
+        <v>5.34114</v>
       </c>
       <c r="C50" t="n">
-        <v>4.91166</v>
+        <v>4.55723</v>
       </c>
       <c r="D50" t="n">
-        <v>13.8593</v>
+        <v>14.6081</v>
       </c>
       <c r="E50" t="n">
-        <v>4.39553</v>
+        <v>4.62172</v>
       </c>
       <c r="F50" t="n">
-        <v>5.42398</v>
+        <v>6.92004</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>5.43888</v>
+        <v>5.70669</v>
       </c>
       <c r="C51" t="n">
-        <v>3.86902</v>
+        <v>3.93765</v>
       </c>
       <c r="D51" t="n">
-        <v>14.7803</v>
+        <v>15.5631</v>
       </c>
       <c r="E51" t="n">
-        <v>4.57291</v>
+        <v>4.56478</v>
       </c>
       <c r="F51" t="n">
-        <v>5.487</v>
+        <v>6.85675</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>6.84921</v>
+        <v>6.76763</v>
       </c>
       <c r="C52" t="n">
-        <v>4.12098</v>
+        <v>3.89483</v>
       </c>
       <c r="D52" t="n">
-        <v>15.6219</v>
+        <v>16.48</v>
       </c>
       <c r="E52" t="n">
-        <v>4.66402</v>
+        <v>4.58686</v>
       </c>
       <c r="F52" t="n">
-        <v>5.28666</v>
+        <v>5.72536</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>5.29208</v>
+        <v>5.53949</v>
       </c>
       <c r="C53" t="n">
-        <v>4.09192</v>
+        <v>3.96176</v>
       </c>
       <c r="D53" t="n">
-        <v>16.1388</v>
+        <v>17.0443</v>
       </c>
       <c r="E53" t="n">
-        <v>4.87729</v>
+        <v>4.7371</v>
       </c>
       <c r="F53" t="n">
-        <v>5.67147</v>
+        <v>7.18258</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>5.26574</v>
+        <v>5.51888</v>
       </c>
       <c r="C54" t="n">
-        <v>3.95744</v>
+        <v>3.87406</v>
       </c>
       <c r="D54" t="n">
-        <v>17.5211</v>
+        <v>18.1421</v>
       </c>
       <c r="E54" t="n">
-        <v>4.67679</v>
+        <v>4.78098</v>
       </c>
       <c r="F54" t="n">
-        <v>5.68382</v>
+        <v>7.31119</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>5.28976</v>
+        <v>5.52863</v>
       </c>
       <c r="C55" t="n">
-        <v>3.93235</v>
+        <v>4.01402</v>
       </c>
       <c r="D55" t="n">
-        <v>17.3292</v>
+        <v>18.7364</v>
       </c>
       <c r="E55" t="n">
-        <v>4.80004</v>
+        <v>4.82345</v>
       </c>
       <c r="F55" t="n">
-        <v>5.2565</v>
+        <v>5.55307</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>5.46117</v>
+        <v>5.32422</v>
       </c>
       <c r="C56" t="n">
-        <v>4.30219</v>
+        <v>4.07204</v>
       </c>
       <c r="D56" t="n">
-        <v>15.093</v>
+        <v>17.8503</v>
       </c>
       <c r="E56" t="n">
-        <v>4.96774</v>
+        <v>4.8496</v>
       </c>
       <c r="F56" t="n">
-        <v>5.89112</v>
+        <v>7.51285</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>5.25908</v>
+        <v>5.58071</v>
       </c>
       <c r="C57" t="n">
-        <v>4.22131</v>
+        <v>4.21425</v>
       </c>
       <c r="D57" t="n">
-        <v>18.157</v>
+        <v>21.0244</v>
       </c>
       <c r="E57" t="n">
-        <v>4.99513</v>
+        <v>4.93212</v>
       </c>
       <c r="F57" t="n">
-        <v>5.52513</v>
+        <v>5.82257</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>5.33823</v>
+        <v>5.57396</v>
       </c>
       <c r="C58" t="n">
-        <v>4.08834</v>
+        <v>4.10986</v>
       </c>
       <c r="D58" t="n">
-        <v>18.167</v>
+        <v>21.3118</v>
       </c>
       <c r="E58" t="n">
-        <v>5.05902</v>
+        <v>4.9538</v>
       </c>
       <c r="F58" t="n">
-        <v>5.39716</v>
+        <v>5.77625</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>5.32811</v>
+        <v>5.62107</v>
       </c>
       <c r="C59" t="n">
-        <v>4.23184</v>
+        <v>4.26154</v>
       </c>
       <c r="D59" t="n">
-        <v>19.1666</v>
+        <v>21.9597</v>
       </c>
       <c r="E59" t="n">
-        <v>5.0421</v>
+        <v>4.97409</v>
       </c>
       <c r="F59" t="n">
-        <v>7.38401</v>
+        <v>7.5474</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>5.30946</v>
+        <v>5.43596</v>
       </c>
       <c r="C60" t="n">
-        <v>4.43868</v>
+        <v>4.14398</v>
       </c>
       <c r="D60" t="n">
-        <v>19.2315</v>
+        <v>21.6104</v>
       </c>
       <c r="E60" t="n">
-        <v>5.05308</v>
+        <v>5.16369</v>
       </c>
       <c r="F60" t="n">
-        <v>6.75495</v>
+        <v>7.29123</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>5.3679</v>
+        <v>5.70484</v>
       </c>
       <c r="C61" t="n">
-        <v>4.28904</v>
+        <v>4.24372</v>
       </c>
       <c r="D61" t="n">
-        <v>19.1744</v>
+        <v>22.293</v>
       </c>
       <c r="E61" t="n">
-        <v>5.49798</v>
+        <v>5.4124</v>
       </c>
       <c r="F61" t="n">
-        <v>7.13255</v>
+        <v>7.90787</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.48515</v>
+        <v>5.43403</v>
       </c>
       <c r="C62" t="n">
-        <v>4.3886</v>
+        <v>4.41338</v>
       </c>
       <c r="D62" t="n">
-        <v>19.2476</v>
+        <v>22.5535</v>
       </c>
       <c r="E62" t="n">
-        <v>5.65032</v>
+        <v>5.69205</v>
       </c>
       <c r="F62" t="n">
-        <v>7.13653</v>
+        <v>7.67933</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>5.60763</v>
+        <v>5.63414</v>
       </c>
       <c r="C63" t="n">
-        <v>4.71399</v>
+        <v>4.38031</v>
       </c>
       <c r="D63" t="n">
-        <v>19.6676</v>
+        <v>22.5962</v>
       </c>
       <c r="E63" t="n">
-        <v>5.93986</v>
+        <v>5.98506</v>
       </c>
       <c r="F63" t="n">
-        <v>7.25322</v>
+        <v>8.47363</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>5.62059</v>
+        <v>6.02332</v>
       </c>
       <c r="C64" t="n">
-        <v>4.57162</v>
+        <v>4.52782</v>
       </c>
       <c r="D64" t="n">
-        <v>13.0126</v>
+        <v>15.5593</v>
       </c>
       <c r="E64" t="n">
-        <v>5.66433</v>
+        <v>4.93028</v>
       </c>
       <c r="F64" t="n">
-        <v>6.26517</v>
+        <v>6.24642</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>5.99442</v>
+        <v>6.35373</v>
       </c>
       <c r="C65" t="n">
-        <v>6.87855</v>
+        <v>5.66505</v>
       </c>
       <c r="D65" t="n">
-        <v>13.751</v>
+        <v>16.5228</v>
       </c>
       <c r="E65" t="n">
-        <v>5.79199</v>
+        <v>5.02463</v>
       </c>
       <c r="F65" t="n">
-        <v>6.35856</v>
+        <v>6.33826</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>6.4379</v>
+        <v>6.80347</v>
       </c>
       <c r="C66" t="n">
-        <v>6.96963</v>
+        <v>5.71727</v>
       </c>
       <c r="D66" t="n">
-        <v>14.5494</v>
+        <v>17.4726</v>
       </c>
       <c r="E66" t="n">
-        <v>6.44885</v>
+        <v>5.24584</v>
       </c>
       <c r="F66" t="n">
-        <v>6.60925</v>
+        <v>6.70939</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>8.499470000000001</v>
+        <v>7.44365</v>
       </c>
       <c r="C67" t="n">
-        <v>6.66034</v>
+        <v>5.83277</v>
       </c>
       <c r="D67" t="n">
-        <v>15.5783</v>
+        <v>18.48</v>
       </c>
       <c r="E67" t="n">
-        <v>5.5073</v>
+        <v>5.14569</v>
       </c>
       <c r="F67" t="n">
-        <v>6.67646</v>
+        <v>6.81145</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>8.07701</v>
+        <v>7.19165</v>
       </c>
       <c r="C68" t="n">
-        <v>6.28182</v>
+        <v>5.65966</v>
       </c>
       <c r="D68" t="n">
-        <v>16.4509</v>
+        <v>19.3131</v>
       </c>
       <c r="E68" t="n">
-        <v>7.30103</v>
+        <v>5.67584</v>
       </c>
       <c r="F68" t="n">
-        <v>6.78717</v>
+        <v>6.97612</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>9.5951</v>
+        <v>8.23246</v>
       </c>
       <c r="C69" t="n">
-        <v>7.83506</v>
+        <v>6.6677</v>
       </c>
       <c r="D69" t="n">
-        <v>17.2515</v>
+        <v>19.9107</v>
       </c>
       <c r="E69" t="n">
-        <v>6.11462</v>
+        <v>5.28912</v>
       </c>
       <c r="F69" t="n">
-        <v>6.82182</v>
+        <v>7.05046</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>12.0245</v>
+        <v>9.312060000000001</v>
       </c>
       <c r="C70" t="n">
-        <v>9.75113</v>
+        <v>7.62346</v>
       </c>
       <c r="D70" t="n">
-        <v>17.5994</v>
+        <v>19.9282</v>
       </c>
       <c r="E70" t="n">
-        <v>6.70111</v>
+        <v>5.64468</v>
       </c>
       <c r="F70" t="n">
-        <v>6.77508</v>
+        <v>7.0994</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>12.4309</v>
+        <v>9.272130000000001</v>
       </c>
       <c r="C71" t="n">
-        <v>10.2107</v>
+        <v>7.62624</v>
       </c>
       <c r="D71" t="n">
-        <v>19.1394</v>
+        <v>20.4523</v>
       </c>
       <c r="E71" t="n">
-        <v>8.974869999999999</v>
+        <v>6.39343</v>
       </c>
       <c r="F71" t="n">
-        <v>6.66301</v>
+        <v>6.95603</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>9.51047</v>
+        <v>8.14132</v>
       </c>
       <c r="C72" t="n">
-        <v>7.72657</v>
+        <v>6.56844</v>
       </c>
       <c r="D72" t="n">
-        <v>19.8762</v>
+        <v>21.2731</v>
       </c>
       <c r="E72" t="n">
-        <v>9.121370000000001</v>
+        <v>6.52656</v>
       </c>
       <c r="F72" t="n">
-        <v>6.78609</v>
+        <v>7.07398</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>10.5849</v>
+        <v>8.636839999999999</v>
       </c>
       <c r="C73" t="n">
-        <v>8.616059999999999</v>
+        <v>6.99956</v>
       </c>
       <c r="D73" t="n">
-        <v>20.1296</v>
+        <v>22.329</v>
       </c>
       <c r="E73" t="n">
-        <v>9.25728</v>
+        <v>6.6728</v>
       </c>
       <c r="F73" t="n">
-        <v>6.91386</v>
+        <v>7.27655</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>8.27473</v>
+        <v>7.17097</v>
       </c>
       <c r="C74" t="n">
-        <v>6.53066</v>
+        <v>5.5947</v>
       </c>
       <c r="D74" t="n">
-        <v>21.5527</v>
+        <v>22.6646</v>
       </c>
       <c r="E74" t="n">
-        <v>10.7252</v>
+        <v>8.004289999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>7.37382</v>
+        <v>7.43144</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>13.9561</v>
+        <v>12.7664</v>
       </c>
       <c r="C75" t="n">
-        <v>11.7957</v>
+        <v>10.7449</v>
       </c>
       <c r="D75" t="n">
-        <v>21.6136</v>
+        <v>21.7655</v>
       </c>
       <c r="E75" t="n">
-        <v>11.9757</v>
+        <v>8.311529999999999</v>
       </c>
       <c r="F75" t="n">
-        <v>7.53338</v>
+        <v>7.71902</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>14.0704</v>
+        <v>12.4503</v>
       </c>
       <c r="C76" t="n">
-        <v>11.8938</v>
+        <v>10.6822</v>
       </c>
       <c r="D76" t="n">
-        <v>21.1301</v>
+        <v>22.3946</v>
       </c>
       <c r="E76" t="n">
-        <v>11.2853</v>
+        <v>8.71083</v>
       </c>
       <c r="F76" t="n">
-        <v>8.02638</v>
+        <v>9.20356</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>14.5311</v>
+        <v>12.2799</v>
       </c>
       <c r="C77" t="n">
-        <v>12.2016</v>
+        <v>10.449</v>
       </c>
       <c r="D77" t="n">
-        <v>22.7326</v>
+        <v>25.1488</v>
       </c>
       <c r="E77" t="n">
-        <v>11.5371</v>
+        <v>9.001860000000001</v>
       </c>
       <c r="F77" t="n">
-        <v>9.58511</v>
+        <v>12.2105</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>11.3218</v>
+        <v>9.125159999999999</v>
       </c>
       <c r="C78" t="n">
-        <v>9.152509999999999</v>
+        <v>7.51139</v>
       </c>
       <c r="D78" t="n">
-        <v>22.023</v>
+        <v>21.7061</v>
       </c>
       <c r="E78" t="n">
-        <v>11.9268</v>
+        <v>9.8195</v>
       </c>
       <c r="F78" t="n">
-        <v>14.2449</v>
+        <v>14.0774</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>13.1089</v>
+        <v>12.1668</v>
       </c>
       <c r="C79" t="n">
-        <v>13.3193</v>
+        <v>13.5053</v>
       </c>
       <c r="D79" t="n">
-        <v>22.4607</v>
+        <v>22.0343</v>
       </c>
       <c r="E79" t="n">
-        <v>12.0969</v>
+        <v>11.0159</v>
       </c>
       <c r="F79" t="n">
-        <v>13.9223</v>
+        <v>13.4606</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>13.4407</v>
+        <v>12.5569</v>
       </c>
       <c r="C80" t="n">
-        <v>13.976</v>
+        <v>14.6261</v>
       </c>
       <c r="D80" t="n">
-        <v>23.5855</v>
+        <v>23.3263</v>
       </c>
       <c r="E80" t="n">
-        <v>12.3257</v>
+        <v>10.4299</v>
       </c>
       <c r="F80" t="n">
-        <v>14.4191</v>
+        <v>13.9853</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>16.7275</v>
+        <v>17.4617</v>
       </c>
       <c r="C81" t="n">
-        <v>14.0276</v>
+        <v>14.7233</v>
       </c>
       <c r="D81" t="n">
-        <v>24.5726</v>
+        <v>24.2887</v>
       </c>
       <c r="E81" t="n">
-        <v>12.2622</v>
+        <v>10.346</v>
       </c>
       <c r="F81" t="n">
-        <v>12.2035</v>
+        <v>13.2838</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>16.8147</v>
+        <v>17.5293</v>
       </c>
       <c r="C82" t="n">
-        <v>14.089</v>
+        <v>14.7946</v>
       </c>
       <c r="D82" t="n">
-        <v>25.5264</v>
+        <v>25.165</v>
       </c>
       <c r="E82" t="n">
-        <v>12.5798</v>
+        <v>10.9825</v>
       </c>
       <c r="F82" t="n">
-        <v>14.8112</v>
+        <v>14.4336</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>16.8767</v>
+        <v>17.5893</v>
       </c>
       <c r="C83" t="n">
-        <v>14.14</v>
+        <v>14.865</v>
       </c>
       <c r="D83" t="n">
-        <v>26.1853</v>
+        <v>26.2571</v>
       </c>
       <c r="E83" t="n">
-        <v>12.6948</v>
+        <v>11.2495</v>
       </c>
       <c r="F83" t="n">
-        <v>14.8037</v>
+        <v>14.4668</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>16.9522</v>
+        <v>17.6872</v>
       </c>
       <c r="C84" t="n">
-        <v>14.2004</v>
+        <v>14.9567</v>
       </c>
       <c r="D84" t="n">
-        <v>27.2041</v>
+        <v>27.0011</v>
       </c>
       <c r="E84" t="n">
-        <v>13.0135</v>
+        <v>12.7127</v>
       </c>
       <c r="F84" t="n">
-        <v>14.8956</v>
+        <v>14.5059</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>17.1279</v>
+        <v>17.7432</v>
       </c>
       <c r="C85" t="n">
-        <v>14.375</v>
+        <v>15.0524</v>
       </c>
       <c r="D85" t="n">
-        <v>28.5013</v>
+        <v>28.3291</v>
       </c>
       <c r="E85" t="n">
-        <v>12.7512</v>
+        <v>11.7166</v>
       </c>
       <c r="F85" t="n">
-        <v>11.6414</v>
+        <v>12.1931</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>17.1217</v>
+        <v>17.807</v>
       </c>
       <c r="C86" t="n">
-        <v>14.3051</v>
+        <v>15.0824</v>
       </c>
       <c r="D86" t="n">
-        <v>30.0461</v>
+        <v>29.6464</v>
       </c>
       <c r="E86" t="n">
-        <v>12.9535</v>
+        <v>12.0045</v>
       </c>
       <c r="F86" t="n">
-        <v>11.8681</v>
+        <v>12.5047</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>17.1651</v>
+        <v>17.8558</v>
       </c>
       <c r="C87" t="n">
-        <v>14.3353</v>
+        <v>15.1352</v>
       </c>
       <c r="D87" t="n">
-        <v>30.6428</v>
+        <v>30.2771</v>
       </c>
       <c r="E87" t="n">
-        <v>13.3578</v>
+        <v>12.148</v>
       </c>
       <c r="F87" t="n">
-        <v>12.319</v>
+        <v>12.3623</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>17.2245</v>
+        <v>17.8547</v>
       </c>
       <c r="C88" t="n">
-        <v>14.4399</v>
+        <v>15.2113</v>
       </c>
       <c r="D88" t="n">
-        <v>30.2044</v>
+        <v>31.7755</v>
       </c>
       <c r="E88" t="n">
-        <v>13.1868</v>
+        <v>12.2848</v>
       </c>
       <c r="F88" t="n">
-        <v>15.6417</v>
+        <v>17.6249</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>17.1963</v>
+        <v>17.8522</v>
       </c>
       <c r="C89" t="n">
-        <v>14.3999</v>
+        <v>15.3032</v>
       </c>
       <c r="D89" t="n">
-        <v>30.4661</v>
+        <v>31.166</v>
       </c>
       <c r="E89" t="n">
-        <v>13.4029</v>
+        <v>12.6519</v>
       </c>
       <c r="F89" t="n">
-        <v>12.4342</v>
+        <v>13.8923</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>17.0969</v>
+        <v>17.9388</v>
       </c>
       <c r="C90" t="n">
-        <v>14.32</v>
+        <v>15.3484</v>
       </c>
       <c r="D90" t="n">
-        <v>33.3388</v>
+        <v>34.003</v>
       </c>
       <c r="E90" t="n">
-        <v>13.582</v>
+        <v>12.9426</v>
       </c>
       <c r="F90" t="n">
-        <v>16.0066</v>
+        <v>15.8497</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>17.4313</v>
+        <v>18.1374</v>
       </c>
       <c r="C91" t="n">
-        <v>14.5753</v>
+        <v>15.5629</v>
       </c>
       <c r="D91" t="n">
-        <v>35.2674</v>
+        <v>35.0747</v>
       </c>
       <c r="E91" t="n">
-        <v>13.8759</v>
+        <v>13.2484</v>
       </c>
       <c r="F91" t="n">
-        <v>17.2938</v>
+        <v>16.188</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>17.5618</v>
+        <v>18.2065</v>
       </c>
       <c r="C92" t="n">
-        <v>14.7677</v>
+        <v>15.6538</v>
       </c>
       <c r="D92" t="n">
-        <v>31.1102</v>
+        <v>32.0289</v>
       </c>
       <c r="E92" t="n">
-        <v>19.9415</v>
+        <v>19.1035</v>
       </c>
       <c r="F92" t="n">
-        <v>19.3703</v>
+        <v>20.1748</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.758</v>
+        <v>18.3478</v>
       </c>
       <c r="C93" t="n">
-        <v>14.9147</v>
+        <v>15.8751</v>
       </c>
       <c r="D93" t="n">
-        <v>31.8432</v>
+        <v>32.7905</v>
       </c>
       <c r="E93" t="n">
-        <v>20.221</v>
+        <v>19.8868</v>
       </c>
       <c r="F93" t="n">
-        <v>19.5159</v>
+        <v>20.354</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>17.8641</v>
+        <v>18.6283</v>
       </c>
       <c r="C94" t="n">
-        <v>18.8175</v>
+        <v>19.3788</v>
       </c>
       <c r="D94" t="n">
-        <v>32.5664</v>
+        <v>33.6</v>
       </c>
       <c r="E94" t="n">
-        <v>20.8937</v>
+        <v>20.2573</v>
       </c>
       <c r="F94" t="n">
-        <v>19.6273</v>
+        <v>20.4445</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>22.2503</v>
+        <v>23.0459</v>
       </c>
       <c r="C95" t="n">
-        <v>19.0281</v>
+        <v>19.6301</v>
       </c>
       <c r="D95" t="n">
-        <v>33.5478</v>
+        <v>34.6293</v>
       </c>
       <c r="E95" t="n">
-        <v>21.0274</v>
+        <v>20.3393</v>
       </c>
       <c r="F95" t="n">
-        <v>19.6668</v>
+        <v>20.4628</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>22.2849</v>
+        <v>23.0613</v>
       </c>
       <c r="C96" t="n">
-        <v>19.0786</v>
+        <v>19.661</v>
       </c>
       <c r="D96" t="n">
-        <v>34.4001</v>
+        <v>35.4679</v>
       </c>
       <c r="E96" t="n">
-        <v>21.1605</v>
+        <v>20.5537</v>
       </c>
       <c r="F96" t="n">
-        <v>19.8373</v>
+        <v>20.6635</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>22.302</v>
+        <v>23.2804</v>
       </c>
       <c r="C97" t="n">
-        <v>19.048</v>
+        <v>19.7072</v>
       </c>
       <c r="D97" t="n">
-        <v>35.2718</v>
+        <v>36.3345</v>
       </c>
       <c r="E97" t="n">
-        <v>21.3856</v>
+        <v>20.7844</v>
       </c>
       <c r="F97" t="n">
-        <v>19.8698</v>
+        <v>20.7172</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.2492</v>
+        <v>23.0554</v>
       </c>
       <c r="C98" t="n">
-        <v>19.103</v>
+        <v>19.7555</v>
       </c>
       <c r="D98" t="n">
-        <v>35.9694</v>
+        <v>37.0299</v>
       </c>
       <c r="E98" t="n">
-        <v>21.4848</v>
+        <v>20.9732</v>
       </c>
       <c r="F98" t="n">
-        <v>20.0058</v>
+        <v>20.839</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>22.2965</v>
+        <v>23.163</v>
       </c>
       <c r="C99" t="n">
-        <v>19.1107</v>
+        <v>19.7863</v>
       </c>
       <c r="D99" t="n">
-        <v>36.8641</v>
+        <v>38.1096</v>
       </c>
       <c r="E99" t="n">
-        <v>21.7196</v>
+        <v>21.039</v>
       </c>
       <c r="F99" t="n">
-        <v>20.2898</v>
+        <v>21.0191</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>22.3053</v>
+        <v>22.9964</v>
       </c>
       <c r="C100" t="n">
-        <v>19.1945</v>
+        <v>19.9071</v>
       </c>
       <c r="D100" t="n">
-        <v>38.1063</v>
+        <v>38.9934</v>
       </c>
       <c r="E100" t="n">
-        <v>21.902</v>
+        <v>21.154</v>
       </c>
       <c r="F100" t="n">
-        <v>20.2589</v>
+        <v>21.0841</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>22.3265</v>
+        <v>23.0959</v>
       </c>
       <c r="C101" t="n">
-        <v>19.1837</v>
+        <v>19.8506</v>
       </c>
       <c r="D101" t="n">
-        <v>39.1594</v>
+        <v>40.1235</v>
       </c>
       <c r="E101" t="n">
-        <v>22.1186</v>
+        <v>21.3402</v>
       </c>
       <c r="F101" t="n">
-        <v>20.6018</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>22.33</v>
+        <v>23.1</v>
       </c>
       <c r="C102" t="n">
-        <v>19.2604</v>
+        <v>19.8985</v>
       </c>
       <c r="D102" t="n">
-        <v>39.947</v>
+        <v>40.9455</v>
       </c>
       <c r="E102" t="n">
-        <v>22.3104</v>
+        <v>21.5908</v>
       </c>
       <c r="F102" t="n">
-        <v>20.77</v>
+        <v>21.3931</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>22.4197</v>
+        <v>23.1417</v>
       </c>
       <c r="C103" t="n">
-        <v>19.3165</v>
+        <v>19.9899</v>
       </c>
       <c r="D103" t="n">
-        <v>41.164</v>
+        <v>42.134</v>
       </c>
       <c r="E103" t="n">
-        <v>22.5915</v>
+        <v>21.6918</v>
       </c>
       <c r="F103" t="n">
-        <v>20.916</v>
+        <v>21.7071</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>22.5266</v>
+        <v>23.2044</v>
       </c>
       <c r="C104" t="n">
-        <v>19.4127</v>
+        <v>20.0785</v>
       </c>
       <c r="D104" t="n">
-        <v>42.08</v>
+        <v>43.1189</v>
       </c>
       <c r="E104" t="n">
-        <v>22.8629</v>
+        <v>21.903</v>
       </c>
       <c r="F104" t="n">
-        <v>21.2138</v>
+        <v>21.8542</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>22.6133</v>
+        <v>23.3106</v>
       </c>
       <c r="C105" t="n">
-        <v>19.5246</v>
+        <v>20.1314</v>
       </c>
       <c r="D105" t="n">
-        <v>43.0884</v>
+        <v>44.2865</v>
       </c>
       <c r="E105" t="n">
-        <v>23.2103</v>
+        <v>22.1666</v>
       </c>
       <c r="F105" t="n">
-        <v>21.9807</v>
+        <v>22.5018</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>22.6764</v>
+        <v>23.4009</v>
       </c>
       <c r="C106" t="n">
-        <v>19.6714</v>
+        <v>20.3387</v>
       </c>
       <c r="D106" t="n">
-        <v>44.4379</v>
+        <v>45.5112</v>
       </c>
       <c r="E106" t="n">
-        <v>23.76</v>
+        <v>22.4341</v>
       </c>
       <c r="F106" t="n">
-        <v>22.0861</v>
+        <v>22.5522</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>22.9186</v>
+        <v>23.5753</v>
       </c>
       <c r="C107" t="n">
-        <v>19.9259</v>
+        <v>20.5277</v>
       </c>
       <c r="D107" t="n">
-        <v>38.1083</v>
+        <v>39.279</v>
       </c>
       <c r="E107" t="n">
-        <v>25.3064</v>
+        <v>26.035</v>
       </c>
       <c r="F107" t="n">
-        <v>24.8829</v>
+        <v>25.7319</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>23.0067</v>
+        <v>23.8712</v>
       </c>
       <c r="C108" t="n">
-        <v>20.6735</v>
+        <v>21.2105</v>
       </c>
       <c r="D108" t="n">
-        <v>38.8613</v>
+        <v>40.0864</v>
       </c>
       <c r="E108" t="n">
-        <v>25.6134</v>
+        <v>26.0022</v>
       </c>
       <c r="F108" t="n">
-        <v>25.1392</v>
+        <v>25.8907</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>23.6114</v>
+        <v>24.3687</v>
       </c>
       <c r="C109" t="n">
-        <v>20.7008</v>
+        <v>21.238</v>
       </c>
       <c r="D109" t="n">
-        <v>39.605</v>
+        <v>40.8697</v>
       </c>
       <c r="E109" t="n">
-        <v>25.8176</v>
+        <v>25.8522</v>
       </c>
       <c r="F109" t="n">
-        <v>25.3134</v>
+        <v>26.2666</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>25.1956</v>
+        <v>26.2547</v>
       </c>
       <c r="C110" t="n">
-        <v>20.713</v>
+        <v>21.2699</v>
       </c>
       <c r="D110" t="n">
-        <v>40.2778</v>
+        <v>41.6111</v>
       </c>
       <c r="E110" t="n">
-        <v>26.0359</v>
+        <v>26.6042</v>
       </c>
       <c r="F110" t="n">
-        <v>25.4718</v>
+        <v>26.3289</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>25.3665</v>
+        <v>26.1971</v>
       </c>
       <c r="C111" t="n">
-        <v>20.7657</v>
+        <v>21.3062</v>
       </c>
       <c r="D111" t="n">
-        <v>41.1648</v>
+        <v>42.4952</v>
       </c>
       <c r="E111" t="n">
-        <v>26.3282</v>
+        <v>26.9633</v>
       </c>
       <c r="F111" t="n">
-        <v>25.7733</v>
+        <v>25.9321</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>25.2356</v>
+        <v>25.7175</v>
       </c>
       <c r="C112" t="n">
-        <v>20.8073</v>
+        <v>21.3811</v>
       </c>
       <c r="D112" t="n">
-        <v>41.8679</v>
+        <v>43.2345</v>
       </c>
       <c r="E112" t="n">
-        <v>26.6281</v>
+        <v>26.9612</v>
       </c>
       <c r="F112" t="n">
-        <v>25.8031</v>
+        <v>26.7086</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>25.3093</v>
+        <v>25.9943</v>
       </c>
       <c r="C113" t="n">
-        <v>20.9358</v>
+        <v>21.4632</v>
       </c>
       <c r="D113" t="n">
-        <v>42.8834</v>
+        <v>44.2095</v>
       </c>
       <c r="E113" t="n">
-        <v>26.8949</v>
+        <v>27.2382</v>
       </c>
       <c r="F113" t="n">
-        <v>26.1804</v>
+        <v>26.9925</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>25.2504</v>
+        <v>26.0701</v>
       </c>
       <c r="C114" t="n">
-        <v>21.0226</v>
+        <v>21.5141</v>
       </c>
       <c r="D114" t="n">
-        <v>43.6753</v>
+        <v>45.0767</v>
       </c>
       <c r="E114" t="n">
-        <v>27.1342</v>
+        <v>27.4535</v>
       </c>
       <c r="F114" t="n">
-        <v>26.433</v>
+        <v>27.2352</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>25.1926</v>
+        <v>26.2216</v>
       </c>
       <c r="C115" t="n">
-        <v>21.1163</v>
+        <v>21.5958</v>
       </c>
       <c r="D115" t="n">
-        <v>44.5866</v>
+        <v>46.014</v>
       </c>
       <c r="E115" t="n">
-        <v>27.4265</v>
+        <v>27.712</v>
       </c>
       <c r="F115" t="n">
-        <v>26.7262</v>
+        <v>27.5641</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>25.3463</v>
+        <v>26.2816</v>
       </c>
       <c r="C116" t="n">
-        <v>21.2288</v>
+        <v>21.7026</v>
       </c>
       <c r="D116" t="n">
-        <v>45.529</v>
+        <v>46.9637</v>
       </c>
       <c r="E116" t="n">
-        <v>27.8296</v>
+        <v>27.9345</v>
       </c>
       <c r="F116" t="n">
-        <v>27.0496</v>
+        <v>27.925</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>25.4195</v>
+        <v>26.4104</v>
       </c>
       <c r="C117" t="n">
-        <v>21.366</v>
+        <v>21.8489</v>
       </c>
       <c r="D117" t="n">
-        <v>46.4074</v>
+        <v>47.9437</v>
       </c>
       <c r="E117" t="n">
-        <v>28.2106</v>
+        <v>28.1868</v>
       </c>
       <c r="F117" t="n">
-        <v>27.4325</v>
+        <v>28.2429</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>25.4713</v>
+        <v>26.5368</v>
       </c>
       <c r="C118" t="n">
-        <v>21.524</v>
+        <v>21.9755</v>
       </c>
       <c r="D118" t="n">
-        <v>47.5914</v>
+        <v>49.0866</v>
       </c>
       <c r="E118" t="n">
-        <v>28.6593</v>
+        <v>28.4893</v>
       </c>
       <c r="F118" t="n">
-        <v>27.8021</v>
+        <v>28.6907</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>25.5444</v>
+        <v>26.4431</v>
       </c>
       <c r="C119" t="n">
-        <v>21.6654</v>
+        <v>22.2059</v>
       </c>
       <c r="D119" t="n">
-        <v>48.3985</v>
+        <v>50.037</v>
       </c>
       <c r="E119" t="n">
-        <v>29.0442</v>
+        <v>28.8699</v>
       </c>
       <c r="F119" t="n">
-        <v>28.3145</v>
+        <v>29.2136</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>25.6418</v>
+        <v>26.8858</v>
       </c>
       <c r="C120" t="n">
-        <v>21.9816</v>
+        <v>22.3619</v>
       </c>
       <c r="D120" t="n">
-        <v>49.7801</v>
+        <v>51.3329</v>
       </c>
       <c r="E120" t="n">
-        <v>29.6947</v>
+        <v>29.1937</v>
       </c>
       <c r="F120" t="n">
-        <v>29.0169</v>
+        <v>29.8181</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>25.8488</v>
+        <v>26.6324</v>
       </c>
       <c r="C121" t="n">
-        <v>22.2762</v>
+        <v>22.7136</v>
       </c>
       <c r="D121" t="n">
-        <v>41.1394</v>
+        <v>43.9832</v>
       </c>
       <c r="E121" t="n">
-        <v>29.0609</v>
+        <v>30.7219</v>
       </c>
       <c r="F121" t="n">
-        <v>28.7922</v>
+        <v>29.7144</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>26.0879</v>
+        <v>27.4242</v>
       </c>
       <c r="C122" t="n">
-        <v>22.8412</v>
+        <v>23.6602</v>
       </c>
       <c r="D122" t="n">
-        <v>41.8714</v>
+        <v>42.9006</v>
       </c>
       <c r="E122" t="n">
-        <v>29.3445</v>
+        <v>31.0919</v>
       </c>
       <c r="F122" t="n">
-        <v>28.8211</v>
+        <v>29.8995</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>26.71</v>
+        <v>27.5405</v>
       </c>
       <c r="C123" t="n">
-        <v>22.9515</v>
+        <v>23.7579</v>
       </c>
       <c r="D123" t="n">
-        <v>42.5328</v>
+        <v>43.8529</v>
       </c>
       <c r="E123" t="n">
-        <v>29.6248</v>
+        <v>31.3627</v>
       </c>
       <c r="F123" t="n">
-        <v>29.279</v>
+        <v>30.1248</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>32.7053</v>
+        <v>33.8699</v>
       </c>
       <c r="C124" t="n">
-        <v>23.0225</v>
+        <v>23.876</v>
       </c>
       <c r="D124" t="n">
-        <v>43.6497</v>
+        <v>44.6374</v>
       </c>
       <c r="E124" t="n">
-        <v>29.8592</v>
+        <v>31.709</v>
       </c>
       <c r="F124" t="n">
-        <v>29.2282</v>
+        <v>30.3293</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>31.8959</v>
+        <v>33.7576</v>
       </c>
       <c r="C125" t="n">
-        <v>23.1685</v>
+        <v>23.9875</v>
       </c>
       <c r="D125" t="n">
-        <v>44.4754</v>
+        <v>45.6491</v>
       </c>
       <c r="E125" t="n">
-        <v>30.1502</v>
+        <v>31.9782</v>
       </c>
       <c r="F125" t="n">
-        <v>29.6357</v>
+        <v>30.546</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>32.5888</v>
+        <v>33.8484</v>
       </c>
       <c r="C126" t="n">
-        <v>23.2647</v>
+        <v>24.1732</v>
       </c>
       <c r="D126" t="n">
-        <v>44.6181</v>
+        <v>46.1016</v>
       </c>
       <c r="E126" t="n">
-        <v>30.4741</v>
+        <v>32.2433</v>
       </c>
       <c r="F126" t="n">
-        <v>29.7606</v>
+        <v>30.8575</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>32.5689</v>
+        <v>33.6862</v>
       </c>
       <c r="C127" t="n">
-        <v>23.4276</v>
+        <v>24.3005</v>
       </c>
       <c r="D127" t="n">
-        <v>45.5252</v>
+        <v>47.0086</v>
       </c>
       <c r="E127" t="n">
-        <v>30.7744</v>
+        <v>32.6223</v>
       </c>
       <c r="F127" t="n">
-        <v>30.2638</v>
+        <v>31.1158</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>32.5856</v>
+        <v>33.8546</v>
       </c>
       <c r="C128" t="n">
-        <v>23.596</v>
+        <v>24.4749</v>
       </c>
       <c r="D128" t="n">
-        <v>46.3667</v>
+        <v>47.862</v>
       </c>
       <c r="E128" t="n">
-        <v>31.0984</v>
+        <v>32.8394</v>
       </c>
       <c r="F128" t="n">
-        <v>30.5491</v>
+        <v>31.5068</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>32.6505</v>
+        <v>33.7501</v>
       </c>
       <c r="C129" t="n">
-        <v>23.7756</v>
+        <v>24.6054</v>
       </c>
       <c r="D129" t="n">
-        <v>47.3428</v>
+        <v>48.919</v>
       </c>
       <c r="E129" t="n">
-        <v>31.4386</v>
+        <v>33.161</v>
       </c>
       <c r="F129" t="n">
-        <v>30.8955</v>
+        <v>31.8192</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>32.6662</v>
+        <v>33.8287</v>
       </c>
       <c r="C130" t="n">
-        <v>23.9849</v>
+        <v>24.791</v>
       </c>
       <c r="D130" t="n">
-        <v>48.2461</v>
+        <v>49.5754</v>
       </c>
       <c r="E130" t="n">
-        <v>31.8246</v>
+        <v>33.5715</v>
       </c>
       <c r="F130" t="n">
-        <v>31.2802</v>
+        <v>32.2026</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>32.7259</v>
+        <v>33.8687</v>
       </c>
       <c r="C131" t="n">
-        <v>24.2555</v>
+        <v>25.0212</v>
       </c>
       <c r="D131" t="n">
-        <v>49.1616</v>
+        <v>50.6989</v>
       </c>
       <c r="E131" t="n">
-        <v>32.2611</v>
+        <v>33.8146</v>
       </c>
       <c r="F131" t="n">
-        <v>31.775</v>
+        <v>32.6247</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>32.733</v>
+        <v>33.9818</v>
       </c>
       <c r="C132" t="n">
-        <v>24.4809</v>
+        <v>25.3949</v>
       </c>
       <c r="D132" t="n">
-        <v>50.1432</v>
+        <v>51.7073</v>
       </c>
       <c r="E132" t="n">
-        <v>32.7444</v>
+        <v>34.2254</v>
       </c>
       <c r="F132" t="n">
-        <v>32.3762</v>
+        <v>33.1506</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>32.7804</v>
+        <v>34.0064</v>
       </c>
       <c r="C133" t="n">
-        <v>24.7868</v>
+        <v>25.639</v>
       </c>
       <c r="D133" t="n">
-        <v>50.8513</v>
+        <v>52.4613</v>
       </c>
       <c r="E133" t="n">
-        <v>33.304</v>
+        <v>34.66</v>
       </c>
       <c r="F133" t="n">
-        <v>33.0199</v>
+        <v>33.8829</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>33.0378</v>
+        <v>34.1488</v>
       </c>
       <c r="C134" t="n">
-        <v>25.2098</v>
+        <v>26.0194</v>
       </c>
       <c r="D134" t="n">
-        <v>52.335</v>
+        <v>53.9753</v>
       </c>
       <c r="E134" t="n">
-        <v>33.9686</v>
+        <v>35.1359</v>
       </c>
       <c r="F134" t="n">
-        <v>33.8053</v>
+        <v>34.6094</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>33.1938</v>
+        <v>34.4131</v>
       </c>
       <c r="C135" t="n">
-        <v>25.7134</v>
+        <v>26.3855</v>
       </c>
       <c r="D135" t="n">
-        <v>43.2853</v>
+        <v>44.4723</v>
       </c>
       <c r="E135" t="n">
-        <v>31.3027</v>
+        <v>33.4802</v>
       </c>
       <c r="F135" t="n">
-        <v>30.912</v>
+        <v>31.9066</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>33.4539</v>
+        <v>34.6946</v>
       </c>
       <c r="C136" t="n">
-        <v>25.0891</v>
+        <v>26.0886</v>
       </c>
       <c r="D136" t="n">
-        <v>43.5372</v>
+        <v>45.0177</v>
       </c>
       <c r="E136" t="n">
-        <v>31.5376</v>
+        <v>31.845</v>
       </c>
       <c r="F136" t="n">
-        <v>31.1495</v>
+        <v>31.3431</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>34.0686</v>
+        <v>33.8101</v>
       </c>
       <c r="C137" t="n">
-        <v>25.1473</v>
+        <v>25.3305</v>
       </c>
       <c r="D137" t="n">
-        <v>44.2363</v>
+        <v>44.4474</v>
       </c>
       <c r="E137" t="n">
-        <v>31.786</v>
+        <v>32.1782</v>
       </c>
       <c r="F137" t="n">
-        <v>31.3942</v>
+        <v>31.5863</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>37.6232</v>
+        <v>37.7342</v>
       </c>
       <c r="C138" t="n">
-        <v>25.3564</v>
+        <v>25.4823</v>
       </c>
       <c r="D138" t="n">
-        <v>45.2132</v>
+        <v>45.4123</v>
       </c>
       <c r="E138" t="n">
-        <v>31.6689</v>
+        <v>32.6028</v>
       </c>
       <c r="F138" t="n">
-        <v>31.6912</v>
+        <v>31.8635</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>37.0347</v>
+        <v>37.7284</v>
       </c>
       <c r="C139" t="n">
-        <v>25.4503</v>
+        <v>25.6572</v>
       </c>
       <c r="D139" t="n">
-        <v>45.3487</v>
+        <v>45.3524</v>
       </c>
       <c r="E139" t="n">
-        <v>32.3791</v>
+        <v>32.8543</v>
       </c>
       <c r="F139" t="n">
-        <v>31.8137</v>
+        <v>32.1463</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>37.6164</v>
+        <v>37.7457</v>
       </c>
       <c r="C140" t="n">
-        <v>25.6453</v>
+        <v>25.7305</v>
       </c>
       <c r="D140" t="n">
-        <v>46.1645</v>
+        <v>46.3737</v>
       </c>
       <c r="E140" t="n">
-        <v>32.7202</v>
+        <v>33.1573</v>
       </c>
       <c r="F140" t="n">
-        <v>32.0514</v>
+        <v>32.3648</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>37.6782</v>
+        <v>37.7668</v>
       </c>
       <c r="C141" t="n">
-        <v>25.8141</v>
+        <v>25.9846</v>
       </c>
       <c r="D141" t="n">
-        <v>47.2509</v>
+        <v>47.4631</v>
       </c>
       <c r="E141" t="n">
-        <v>32.9399</v>
+        <v>33.4683</v>
       </c>
       <c r="F141" t="n">
-        <v>32.483</v>
+        <v>32.5866</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>37.6941</v>
+        <v>37.7993</v>
       </c>
       <c r="C142" t="n">
-        <v>26.0447</v>
+        <v>26.1201</v>
       </c>
       <c r="D142" t="n">
-        <v>48.0124</v>
+        <v>48.1054</v>
       </c>
       <c r="E142" t="n">
-        <v>32.8044</v>
+        <v>33.8128</v>
       </c>
       <c r="F142" t="n">
-        <v>32.8975</v>
+        <v>33.0193</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>37.0945</v>
+        <v>37.8768</v>
       </c>
       <c r="C143" t="n">
-        <v>26.266</v>
+        <v>26.3983</v>
       </c>
       <c r="D143" t="n">
-        <v>49.2478</v>
+        <v>49.6761</v>
       </c>
       <c r="E143" t="n">
-        <v>33.7169</v>
+        <v>34.1934</v>
       </c>
       <c r="F143" t="n">
-        <v>33.1576</v>
+        <v>33.38</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Scattered successful looukp.xlsx
+++ b/gcc-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>4.25936</v>
+        <v>3.83293</v>
       </c>
       <c r="C2" t="n">
-        <v>3.35568</v>
+        <v>3.30816</v>
       </c>
       <c r="D2" t="n">
-        <v>8.22819</v>
+        <v>8.12771</v>
       </c>
       <c r="E2" t="n">
-        <v>3.90049</v>
+        <v>4.00489</v>
       </c>
       <c r="F2" t="n">
-        <v>3.44252</v>
+        <v>3.46671</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>3.77743</v>
+        <v>4.08629</v>
       </c>
       <c r="C3" t="n">
-        <v>3.19059</v>
+        <v>3.25217</v>
       </c>
       <c r="D3" t="n">
-        <v>8.518829999999999</v>
+        <v>8.59366</v>
       </c>
       <c r="E3" t="n">
-        <v>3.40268</v>
+        <v>3.35329</v>
       </c>
       <c r="F3" t="n">
-        <v>4.08449</v>
+        <v>4.42473</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.38931</v>
+        <v>3.40294</v>
       </c>
       <c r="C4" t="n">
-        <v>2.95999</v>
+        <v>2.95596</v>
       </c>
       <c r="D4" t="n">
-        <v>9.22287</v>
+        <v>9.34075</v>
       </c>
       <c r="E4" t="n">
-        <v>3.28566</v>
+        <v>3.23746</v>
       </c>
       <c r="F4" t="n">
-        <v>4.29065</v>
+        <v>4.50614</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.79357</v>
+        <v>3.86381</v>
       </c>
       <c r="C5" t="n">
-        <v>3.25058</v>
+        <v>3.23761</v>
       </c>
       <c r="D5" t="n">
-        <v>10.4125</v>
+        <v>10.3089</v>
       </c>
       <c r="E5" t="n">
-        <v>3.31335</v>
+        <v>3.26692</v>
       </c>
       <c r="F5" t="n">
-        <v>4.21022</v>
+        <v>4.44979</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.01436</v>
+        <v>3.9907</v>
       </c>
       <c r="C6" t="n">
-        <v>3.28642</v>
+        <v>3.2574</v>
       </c>
       <c r="D6" t="n">
-        <v>11.2173</v>
+        <v>11.0128</v>
       </c>
       <c r="E6" t="n">
-        <v>3.67766</v>
+        <v>3.67094</v>
       </c>
       <c r="F6" t="n">
-        <v>4.13665</v>
+        <v>4.06037</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>3.82041</v>
+        <v>4.13665</v>
       </c>
       <c r="C7" t="n">
-        <v>3.34857</v>
+        <v>3.41107</v>
       </c>
       <c r="D7" t="n">
-        <v>6.95357</v>
+        <v>7.01575</v>
       </c>
       <c r="E7" t="n">
-        <v>4.03331</v>
+        <v>4.02397</v>
       </c>
       <c r="F7" t="n">
-        <v>3.64334</v>
+        <v>3.68316</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>3.8462</v>
+        <v>4.1654</v>
       </c>
       <c r="C8" t="n">
-        <v>3.42597</v>
+        <v>3.47663</v>
       </c>
       <c r="D8" t="n">
-        <v>7.36932</v>
+        <v>7.3939</v>
       </c>
       <c r="E8" t="n">
-        <v>4.08576</v>
+        <v>4.10915</v>
       </c>
       <c r="F8" t="n">
-        <v>3.67283</v>
+        <v>3.70676</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>3.4901</v>
+        <v>3.49878</v>
       </c>
       <c r="C9" t="n">
-        <v>3.65367</v>
+        <v>3.65662</v>
       </c>
       <c r="D9" t="n">
-        <v>7.71742</v>
+        <v>7.69679</v>
       </c>
       <c r="E9" t="n">
-        <v>4.10781</v>
+        <v>4.1407</v>
       </c>
       <c r="F9" t="n">
-        <v>3.67466</v>
+        <v>3.72308</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>4.21439</v>
+        <v>4.22227</v>
       </c>
       <c r="C10" t="n">
-        <v>3.66853</v>
+        <v>3.66907</v>
       </c>
       <c r="D10" t="n">
-        <v>8.16738</v>
+        <v>8.18088</v>
       </c>
       <c r="E10" t="n">
-        <v>4.14347</v>
+        <v>4.16583</v>
       </c>
       <c r="F10" t="n">
-        <v>3.72159</v>
+        <v>3.7638</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>4.9945</v>
+        <v>4.97958</v>
       </c>
       <c r="C11" t="n">
-        <v>3.74706</v>
+        <v>3.69843</v>
       </c>
       <c r="D11" t="n">
-        <v>8.626300000000001</v>
+        <v>8.6152</v>
       </c>
       <c r="E11" t="n">
-        <v>4.44739</v>
+        <v>4.4801</v>
       </c>
       <c r="F11" t="n">
-        <v>3.67235</v>
+        <v>3.75333</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>4.05118</v>
+        <v>4.05362</v>
       </c>
       <c r="C12" t="n">
-        <v>3.65476</v>
+        <v>3.59664</v>
       </c>
       <c r="D12" t="n">
-        <v>9.25164</v>
+        <v>9.18507</v>
       </c>
       <c r="E12" t="n">
-        <v>4.47842</v>
+        <v>4.50559</v>
       </c>
       <c r="F12" t="n">
-        <v>3.66527</v>
+        <v>3.76049</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>4.97098</v>
+        <v>4.97743</v>
       </c>
       <c r="C13" t="n">
-        <v>3.75083</v>
+        <v>3.78554</v>
       </c>
       <c r="D13" t="n">
-        <v>9.747769999999999</v>
+        <v>9.726839999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>4.33946</v>
+        <v>4.33834</v>
       </c>
       <c r="F13" t="n">
-        <v>3.88566</v>
+        <v>3.92781</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>4.99911</v>
+        <v>5.02528</v>
       </c>
       <c r="C14" t="n">
-        <v>3.82085</v>
+        <v>3.79566</v>
       </c>
       <c r="D14" t="n">
-        <v>10.1689</v>
+        <v>10.1411</v>
       </c>
       <c r="E14" t="n">
-        <v>4.258</v>
+        <v>4.28286</v>
       </c>
       <c r="F14" t="n">
-        <v>3.79423</v>
+        <v>3.84732</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>4.98402</v>
+        <v>4.98899</v>
       </c>
       <c r="C15" t="n">
-        <v>3.80419</v>
+        <v>3.83883</v>
       </c>
       <c r="D15" t="n">
-        <v>10.5955</v>
+        <v>10.5866</v>
       </c>
       <c r="E15" t="n">
-        <v>4.38272</v>
+        <v>4.38674</v>
       </c>
       <c r="F15" t="n">
-        <v>3.90732</v>
+        <v>3.96059</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>5.01249</v>
+        <v>5.04379</v>
       </c>
       <c r="C16" t="n">
-        <v>3.8659</v>
+        <v>3.83838</v>
       </c>
       <c r="D16" t="n">
-        <v>11.155</v>
+        <v>11.1959</v>
       </c>
       <c r="E16" t="n">
-        <v>4.63577</v>
+        <v>4.62979</v>
       </c>
       <c r="F16" t="n">
-        <v>3.9501</v>
+        <v>4.04992</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>5.00679</v>
+        <v>5.00717</v>
       </c>
       <c r="C17" t="n">
-        <v>3.87506</v>
+        <v>3.92366</v>
       </c>
       <c r="D17" t="n">
-        <v>11.5379</v>
+        <v>11.6037</v>
       </c>
       <c r="E17" t="n">
-        <v>4.33441</v>
+        <v>4.35995</v>
       </c>
       <c r="F17" t="n">
-        <v>3.87878</v>
+        <v>3.92879</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>5.01659</v>
+        <v>5.0165</v>
       </c>
       <c r="C18" t="n">
-        <v>3.92774</v>
+        <v>3.96701</v>
       </c>
       <c r="D18" t="n">
-        <v>11.9337</v>
+        <v>12.0007</v>
       </c>
       <c r="E18" t="n">
-        <v>4.67108</v>
+        <v>4.68832</v>
       </c>
       <c r="F18" t="n">
-        <v>3.86325</v>
+        <v>3.93594</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>5.02063</v>
+        <v>5.0299</v>
       </c>
       <c r="C19" t="n">
-        <v>3.97453</v>
+        <v>4.01446</v>
       </c>
       <c r="D19" t="n">
-        <v>12.5576</v>
+        <v>12.6031</v>
       </c>
       <c r="E19" t="n">
-        <v>4.41901</v>
+        <v>4.43303</v>
       </c>
       <c r="F19" t="n">
-        <v>3.92261</v>
+        <v>3.98162</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>5.03989</v>
+        <v>4.90745</v>
       </c>
       <c r="C20" t="n">
-        <v>4.03562</v>
+        <v>4.08882</v>
       </c>
       <c r="D20" t="n">
-        <v>13.0001</v>
+        <v>13.033</v>
       </c>
       <c r="E20" t="n">
-        <v>4.78412</v>
+        <v>4.8091</v>
       </c>
       <c r="F20" t="n">
-        <v>4.05441</v>
+        <v>4.13163</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>5.06482</v>
+        <v>5.07075</v>
       </c>
       <c r="C21" t="n">
-        <v>4.08514</v>
+        <v>4.13786</v>
       </c>
       <c r="D21" t="n">
-        <v>9.20439</v>
+        <v>9.222950000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>4.3484</v>
+        <v>4.38186</v>
       </c>
       <c r="F21" t="n">
-        <v>4.45651</v>
+        <v>4.72082</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>5.118</v>
+        <v>5.10566</v>
       </c>
       <c r="C22" t="n">
-        <v>3.65859</v>
+        <v>3.62899</v>
       </c>
       <c r="D22" t="n">
-        <v>9.50343</v>
+        <v>9.45016</v>
       </c>
       <c r="E22" t="n">
-        <v>4.37718</v>
+        <v>4.36372</v>
       </c>
       <c r="F22" t="n">
-        <v>4.60251</v>
+        <v>4.84298</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>5.14147</v>
+        <v>5.13215</v>
       </c>
       <c r="C23" t="n">
-        <v>3.64117</v>
+        <v>3.6637</v>
       </c>
       <c r="D23" t="n">
-        <v>9.847849999999999</v>
+        <v>9.8466</v>
       </c>
       <c r="E23" t="n">
-        <v>4.46743</v>
+        <v>4.45824</v>
       </c>
       <c r="F23" t="n">
-        <v>4.54759</v>
+        <v>4.80893</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>5.15805</v>
+        <v>5.11934</v>
       </c>
       <c r="C24" t="n">
-        <v>3.71132</v>
+        <v>3.68657</v>
       </c>
       <c r="D24" t="n">
-        <v>10.1291</v>
+        <v>10.1382</v>
       </c>
       <c r="E24" t="n">
-        <v>4.48368</v>
+        <v>4.49632</v>
       </c>
       <c r="F24" t="n">
-        <v>4.58141</v>
+        <v>4.84238</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>5.17407</v>
+        <v>5.17498</v>
       </c>
       <c r="C25" t="n">
-        <v>3.71431</v>
+        <v>3.69653</v>
       </c>
       <c r="D25" t="n">
-        <v>10.5015</v>
+        <v>10.5213</v>
       </c>
       <c r="E25" t="n">
-        <v>4.49216</v>
+        <v>4.48344</v>
       </c>
       <c r="F25" t="n">
-        <v>4.67327</v>
+        <v>4.90209</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>5.18151</v>
+        <v>5.18452</v>
       </c>
       <c r="C26" t="n">
-        <v>3.71828</v>
+        <v>3.70713</v>
       </c>
       <c r="D26" t="n">
-        <v>10.9157</v>
+        <v>10.901</v>
       </c>
       <c r="E26" t="n">
-        <v>4.47538</v>
+        <v>4.47805</v>
       </c>
       <c r="F26" t="n">
-        <v>4.49146</v>
+        <v>4.6797</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>4.96546</v>
+        <v>4.97534</v>
       </c>
       <c r="C27" t="n">
-        <v>3.77238</v>
+        <v>3.7542</v>
       </c>
       <c r="D27" t="n">
-        <v>11.3648</v>
+        <v>11.3483</v>
       </c>
       <c r="E27" t="n">
-        <v>4.55117</v>
+        <v>4.55392</v>
       </c>
       <c r="F27" t="n">
-        <v>4.51475</v>
+        <v>4.71283</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>4.9865</v>
+        <v>4.98967</v>
       </c>
       <c r="C28" t="n">
-        <v>3.74255</v>
+        <v>3.77239</v>
       </c>
       <c r="D28" t="n">
-        <v>11.7334</v>
+        <v>11.7377</v>
       </c>
       <c r="E28" t="n">
-        <v>4.58784</v>
+        <v>4.59384</v>
       </c>
       <c r="F28" t="n">
-        <v>4.58231</v>
+        <v>4.71711</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>4.98755</v>
+        <v>4.99483</v>
       </c>
       <c r="C29" t="n">
-        <v>3.82627</v>
+        <v>3.78824</v>
       </c>
       <c r="D29" t="n">
-        <v>12.1867</v>
+        <v>12.172</v>
       </c>
       <c r="E29" t="n">
-        <v>4.61705</v>
+        <v>4.62089</v>
       </c>
       <c r="F29" t="n">
-        <v>4.62609</v>
+        <v>4.7663</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>5.21068</v>
+        <v>5.20969</v>
       </c>
       <c r="C30" t="n">
-        <v>3.84896</v>
+        <v>3.88358</v>
       </c>
       <c r="D30" t="n">
-        <v>12.6113</v>
+        <v>12.637</v>
       </c>
       <c r="E30" t="n">
-        <v>4.65763</v>
+        <v>4.66181</v>
       </c>
       <c r="F30" t="n">
-        <v>4.63022</v>
+        <v>4.78583</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>5.23712</v>
+        <v>5.24138</v>
       </c>
       <c r="C31" t="n">
-        <v>3.81791</v>
+        <v>3.84193</v>
       </c>
       <c r="D31" t="n">
-        <v>13.1508</v>
+        <v>13.1231</v>
       </c>
       <c r="E31" t="n">
-        <v>4.64126</v>
+        <v>4.56997</v>
       </c>
       <c r="F31" t="n">
-        <v>4.69552</v>
+        <v>4.84377</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>5.02891</v>
+        <v>5.03706</v>
       </c>
       <c r="C32" t="n">
-        <v>3.93777</v>
+        <v>3.92146</v>
       </c>
       <c r="D32" t="n">
-        <v>13.5294</v>
+        <v>13.4593</v>
       </c>
       <c r="E32" t="n">
-        <v>4.72314</v>
+        <v>4.7238</v>
       </c>
       <c r="F32" t="n">
-        <v>4.70967</v>
+        <v>4.89591</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>5.04919</v>
+        <v>4.97185</v>
       </c>
       <c r="C33" t="n">
-        <v>3.98299</v>
+        <v>3.96474</v>
       </c>
       <c r="D33" t="n">
-        <v>13.8756</v>
+        <v>13.8454</v>
       </c>
       <c r="E33" t="n">
-        <v>4.72584</v>
+        <v>4.72538</v>
       </c>
       <c r="F33" t="n">
-        <v>4.76244</v>
+        <v>5.00206</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.06328</v>
+        <v>5.0727</v>
       </c>
       <c r="C34" t="n">
-        <v>4.00424</v>
+        <v>4.02919</v>
       </c>
       <c r="D34" t="n">
-        <v>14.1131</v>
+        <v>14.1712</v>
       </c>
       <c r="E34" t="n">
-        <v>4.72328</v>
+        <v>4.88215</v>
       </c>
       <c r="F34" t="n">
-        <v>4.92821</v>
+        <v>4.99091</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>5.28688</v>
+        <v>5.28793</v>
       </c>
       <c r="C35" t="n">
-        <v>4.02553</v>
+        <v>4.0177</v>
       </c>
       <c r="D35" t="n">
-        <v>10.1349</v>
+        <v>10.0995</v>
       </c>
       <c r="E35" t="n">
-        <v>4.47414</v>
+        <v>4.58205</v>
       </c>
       <c r="F35" t="n">
-        <v>4.79538</v>
+        <v>4.81822</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>5.14489</v>
+        <v>5.16119</v>
       </c>
       <c r="C36" t="n">
-        <v>4.13376</v>
+        <v>4.19893</v>
       </c>
       <c r="D36" t="n">
-        <v>10.4239</v>
+        <v>10.5546</v>
       </c>
       <c r="E36" t="n">
-        <v>4.52116</v>
+        <v>4.6245</v>
       </c>
       <c r="F36" t="n">
-        <v>4.92514</v>
+        <v>5.13876</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>5.24382</v>
+        <v>5.34439</v>
       </c>
       <c r="C37" t="n">
-        <v>3.9448</v>
+        <v>3.94468</v>
       </c>
       <c r="D37" t="n">
-        <v>10.9707</v>
+        <v>11.3472</v>
       </c>
       <c r="E37" t="n">
-        <v>4.55978</v>
+        <v>4.65163</v>
       </c>
       <c r="F37" t="n">
-        <v>4.96782</v>
+        <v>5.20335</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>5.3206</v>
+        <v>5.30262</v>
       </c>
       <c r="C38" t="n">
-        <v>3.74772</v>
+        <v>3.87615</v>
       </c>
       <c r="D38" t="n">
-        <v>10.9072</v>
+        <v>11.1705</v>
       </c>
       <c r="E38" t="n">
-        <v>4.57174</v>
+        <v>4.68101</v>
       </c>
       <c r="F38" t="n">
-        <v>4.94848</v>
+        <v>5.10588</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>5.27926</v>
+        <v>5.32162</v>
       </c>
       <c r="C39" t="n">
-        <v>3.84433</v>
+        <v>3.95004</v>
       </c>
       <c r="D39" t="n">
-        <v>11.6034</v>
+        <v>11.9319</v>
       </c>
       <c r="E39" t="n">
-        <v>4.61404</v>
+        <v>4.71905</v>
       </c>
       <c r="F39" t="n">
-        <v>5.01095</v>
+        <v>5.17563</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>5.27953</v>
+        <v>5.3361</v>
       </c>
       <c r="C40" t="n">
-        <v>3.78687</v>
+        <v>3.86823</v>
       </c>
       <c r="D40" t="n">
-        <v>12.3739</v>
+        <v>12.8806</v>
       </c>
       <c r="E40" t="n">
-        <v>4.64549</v>
+        <v>4.74608</v>
       </c>
       <c r="F40" t="n">
-        <v>5.06106</v>
+        <v>5.29998</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>5.06733</v>
+        <v>4.9242</v>
       </c>
       <c r="C41" t="n">
-        <v>4.01108</v>
+        <v>4.00844</v>
       </c>
       <c r="D41" t="n">
-        <v>12.9776</v>
+        <v>13.3863</v>
       </c>
       <c r="E41" t="n">
-        <v>4.79085</v>
+        <v>4.78328</v>
       </c>
       <c r="F41" t="n">
-        <v>5.05274</v>
+        <v>5.00057</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>5.22619</v>
+        <v>5.23015</v>
       </c>
       <c r="C42" t="n">
-        <v>3.98903</v>
+        <v>3.9405</v>
       </c>
       <c r="D42" t="n">
-        <v>13.2649</v>
+        <v>13.7797</v>
       </c>
       <c r="E42" t="n">
-        <v>4.71466</v>
+        <v>4.80295</v>
       </c>
       <c r="F42" t="n">
-        <v>5.22701</v>
+        <v>5.37106</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>5.33962</v>
+        <v>5.34522</v>
       </c>
       <c r="C43" t="n">
-        <v>3.98443</v>
+        <v>4.05459</v>
       </c>
       <c r="D43" t="n">
-        <v>13.471</v>
+        <v>14.081</v>
       </c>
       <c r="E43" t="n">
-        <v>4.86647</v>
+        <v>4.84446</v>
       </c>
       <c r="F43" t="n">
-        <v>5.17205</v>
+        <v>5.10075</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>5.16134</v>
+        <v>5.25853</v>
       </c>
       <c r="C44" t="n">
-        <v>4.03599</v>
+        <v>3.96767</v>
       </c>
       <c r="D44" t="n">
-        <v>13.7617</v>
+        <v>14.26</v>
       </c>
       <c r="E44" t="n">
-        <v>4.79945</v>
+        <v>4.88704</v>
       </c>
       <c r="F44" t="n">
-        <v>5.21136</v>
+        <v>5.12188</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>5.4643</v>
+        <v>5.46458</v>
       </c>
       <c r="C45" t="n">
-        <v>4.10764</v>
+        <v>4.12598</v>
       </c>
       <c r="D45" t="n">
-        <v>13.9889</v>
+        <v>14.2619</v>
       </c>
       <c r="E45" t="n">
-        <v>4.94637</v>
+        <v>4.93874</v>
       </c>
       <c r="F45" t="n">
-        <v>5.36113</v>
+        <v>5.43195</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>5.25759</v>
+        <v>4.87401</v>
       </c>
       <c r="C46" t="n">
-        <v>4.10589</v>
+        <v>4.18505</v>
       </c>
       <c r="D46" t="n">
-        <v>14.5329</v>
+        <v>14.8997</v>
       </c>
       <c r="E46" t="n">
-        <v>4.96465</v>
+        <v>4.96063</v>
       </c>
       <c r="F46" t="n">
-        <v>5.48022</v>
+        <v>5.54379</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>5.15035</v>
+        <v>5.00581</v>
       </c>
       <c r="C47" t="n">
-        <v>4.24637</v>
+        <v>4.23805</v>
       </c>
       <c r="D47" t="n">
-        <v>14.9035</v>
+        <v>15.0282</v>
       </c>
       <c r="E47" t="n">
-        <v>5.09805</v>
+        <v>5.19202</v>
       </c>
       <c r="F47" t="n">
-        <v>5.6351</v>
+        <v>5.75635</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.00522</v>
+        <v>5.36463</v>
       </c>
       <c r="C48" t="n">
-        <v>4.30682</v>
+        <v>4.32737</v>
       </c>
       <c r="D48" t="n">
-        <v>15.6287</v>
+        <v>15.7804</v>
       </c>
       <c r="E48" t="n">
-        <v>5.53762</v>
+        <v>5.54316</v>
       </c>
       <c r="F48" t="n">
-        <v>6.04301</v>
+        <v>6.14919</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>5.15338</v>
+        <v>5.10357</v>
       </c>
       <c r="C49" t="n">
-        <v>4.39516</v>
+        <v>4.31947</v>
       </c>
       <c r="D49" t="n">
-        <v>16.4598</v>
+        <v>16.4207</v>
       </c>
       <c r="E49" t="n">
-        <v>5.87017</v>
+        <v>5.8721</v>
       </c>
       <c r="F49" t="n">
-        <v>6.50175</v>
+        <v>6.64564</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>5.34114</v>
+        <v>5.25788</v>
       </c>
       <c r="C50" t="n">
-        <v>4.55723</v>
+        <v>4.55567</v>
       </c>
       <c r="D50" t="n">
-        <v>14.6081</v>
+        <v>14.0859</v>
       </c>
       <c r="E50" t="n">
-        <v>4.62172</v>
+        <v>4.61772</v>
       </c>
       <c r="F50" t="n">
-        <v>6.92004</v>
+        <v>6.78017</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>5.70669</v>
+        <v>5.37675</v>
       </c>
       <c r="C51" t="n">
-        <v>3.93765</v>
+        <v>3.8458</v>
       </c>
       <c r="D51" t="n">
-        <v>15.5631</v>
+        <v>14.982</v>
       </c>
       <c r="E51" t="n">
-        <v>4.56478</v>
+        <v>4.63743</v>
       </c>
       <c r="F51" t="n">
-        <v>6.85675</v>
+        <v>6.79247</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>6.76763</v>
+        <v>6.76903</v>
       </c>
       <c r="C52" t="n">
-        <v>3.89483</v>
+        <v>3.98451</v>
       </c>
       <c r="D52" t="n">
-        <v>16.48</v>
+        <v>15.7967</v>
       </c>
       <c r="E52" t="n">
-        <v>4.58686</v>
+        <v>4.68378</v>
       </c>
       <c r="F52" t="n">
-        <v>5.72536</v>
+        <v>5.75902</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>5.53949</v>
+        <v>5.54028</v>
       </c>
       <c r="C53" t="n">
-        <v>3.96176</v>
+        <v>3.9308</v>
       </c>
       <c r="D53" t="n">
-        <v>17.0443</v>
+        <v>16.7016</v>
       </c>
       <c r="E53" t="n">
-        <v>4.7371</v>
+        <v>4.72582</v>
       </c>
       <c r="F53" t="n">
-        <v>7.18258</v>
+        <v>7.26609</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>5.51888</v>
+        <v>5.52582</v>
       </c>
       <c r="C54" t="n">
-        <v>3.87406</v>
+        <v>3.91968</v>
       </c>
       <c r="D54" t="n">
-        <v>18.1421</v>
+        <v>17.9485</v>
       </c>
       <c r="E54" t="n">
-        <v>4.78098</v>
+        <v>4.76925</v>
       </c>
       <c r="F54" t="n">
-        <v>7.31119</v>
+        <v>7.38772</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>5.52863</v>
+        <v>5.53615</v>
       </c>
       <c r="C55" t="n">
-        <v>4.01402</v>
+        <v>4.00526</v>
       </c>
       <c r="D55" t="n">
-        <v>18.7364</v>
+        <v>18.6009</v>
       </c>
       <c r="E55" t="n">
-        <v>4.82345</v>
+        <v>4.81126</v>
       </c>
       <c r="F55" t="n">
-        <v>5.55307</v>
+        <v>5.59628</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>5.32422</v>
+        <v>5.3355</v>
       </c>
       <c r="C56" t="n">
-        <v>4.07204</v>
+        <v>4.02611</v>
       </c>
       <c r="D56" t="n">
-        <v>17.8503</v>
+        <v>17.6608</v>
       </c>
       <c r="E56" t="n">
-        <v>4.8496</v>
+        <v>4.82036</v>
       </c>
       <c r="F56" t="n">
-        <v>7.51285</v>
+        <v>7.57909</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>5.58071</v>
+        <v>5.57556</v>
       </c>
       <c r="C57" t="n">
-        <v>4.21425</v>
+        <v>4.05722</v>
       </c>
       <c r="D57" t="n">
-        <v>21.0244</v>
+        <v>21.1035</v>
       </c>
       <c r="E57" t="n">
-        <v>4.93212</v>
+        <v>4.91654</v>
       </c>
       <c r="F57" t="n">
-        <v>5.82257</v>
+        <v>5.88526</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>5.57396</v>
+        <v>5.5801</v>
       </c>
       <c r="C58" t="n">
-        <v>4.10986</v>
+        <v>3.97641</v>
       </c>
       <c r="D58" t="n">
-        <v>21.3118</v>
+        <v>21.3673</v>
       </c>
       <c r="E58" t="n">
-        <v>4.9538</v>
+        <v>4.99532</v>
       </c>
       <c r="F58" t="n">
-        <v>5.77625</v>
+        <v>5.74319</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>5.62107</v>
+        <v>5.61796</v>
       </c>
       <c r="C59" t="n">
-        <v>4.26154</v>
+        <v>4.11626</v>
       </c>
       <c r="D59" t="n">
-        <v>21.9597</v>
+        <v>21.7175</v>
       </c>
       <c r="E59" t="n">
-        <v>4.97409</v>
+        <v>5.07521</v>
       </c>
       <c r="F59" t="n">
-        <v>7.5474</v>
+        <v>7.98693</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>5.43596</v>
+        <v>5.42279</v>
       </c>
       <c r="C60" t="n">
-        <v>4.14398</v>
+        <v>4.22527</v>
       </c>
       <c r="D60" t="n">
-        <v>21.6104</v>
+        <v>21.4132</v>
       </c>
       <c r="E60" t="n">
-        <v>5.16369</v>
+        <v>5.21002</v>
       </c>
       <c r="F60" t="n">
-        <v>7.29123</v>
+        <v>7.27033</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>5.70484</v>
+        <v>5.70482</v>
       </c>
       <c r="C61" t="n">
-        <v>4.24372</v>
+        <v>4.14791</v>
       </c>
       <c r="D61" t="n">
-        <v>22.293</v>
+        <v>21.7318</v>
       </c>
       <c r="E61" t="n">
-        <v>5.4124</v>
+        <v>5.27833</v>
       </c>
       <c r="F61" t="n">
-        <v>7.90787</v>
+        <v>7.60693</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.43403</v>
+        <v>5.50274</v>
       </c>
       <c r="C62" t="n">
-        <v>4.41338</v>
+        <v>4.29426</v>
       </c>
       <c r="D62" t="n">
-        <v>22.5535</v>
+        <v>21.9697</v>
       </c>
       <c r="E62" t="n">
-        <v>5.69205</v>
+        <v>5.55344</v>
       </c>
       <c r="F62" t="n">
-        <v>7.67933</v>
+        <v>7.57382</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>5.63414</v>
+        <v>5.61158</v>
       </c>
       <c r="C63" t="n">
-        <v>4.38031</v>
+        <v>4.44696</v>
       </c>
       <c r="D63" t="n">
-        <v>22.5962</v>
+        <v>21.9866</v>
       </c>
       <c r="E63" t="n">
-        <v>5.98506</v>
+        <v>5.84271</v>
       </c>
       <c r="F63" t="n">
-        <v>8.47363</v>
+        <v>8.62017</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>6.02332</v>
+        <v>6.02597</v>
       </c>
       <c r="C64" t="n">
-        <v>4.52782</v>
+        <v>4.50369</v>
       </c>
       <c r="D64" t="n">
-        <v>15.5593</v>
+        <v>14.9859</v>
       </c>
       <c r="E64" t="n">
-        <v>4.93028</v>
+        <v>5.29933</v>
       </c>
       <c r="F64" t="n">
-        <v>6.24642</v>
+        <v>5.96268</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>6.35373</v>
+        <v>6.35163</v>
       </c>
       <c r="C65" t="n">
-        <v>5.66505</v>
+        <v>8.074210000000001</v>
       </c>
       <c r="D65" t="n">
-        <v>16.5228</v>
+        <v>15.9233</v>
       </c>
       <c r="E65" t="n">
-        <v>5.02463</v>
+        <v>5.26981</v>
       </c>
       <c r="F65" t="n">
-        <v>6.33826</v>
+        <v>6.06511</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>6.80347</v>
+        <v>6.81437</v>
       </c>
       <c r="C66" t="n">
-        <v>5.71727</v>
+        <v>8.19242</v>
       </c>
       <c r="D66" t="n">
-        <v>17.4726</v>
+        <v>16.9359</v>
       </c>
       <c r="E66" t="n">
-        <v>5.24584</v>
+        <v>5.71794</v>
       </c>
       <c r="F66" t="n">
-        <v>6.70939</v>
+        <v>6.39625</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>7.44365</v>
+        <v>9.65127</v>
       </c>
       <c r="C67" t="n">
-        <v>5.83277</v>
+        <v>7.93876</v>
       </c>
       <c r="D67" t="n">
-        <v>18.48</v>
+        <v>18.0782</v>
       </c>
       <c r="E67" t="n">
-        <v>5.14569</v>
+        <v>5.6043</v>
       </c>
       <c r="F67" t="n">
-        <v>6.81145</v>
+        <v>6.51495</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>7.19165</v>
+        <v>9.5662</v>
       </c>
       <c r="C68" t="n">
-        <v>5.65966</v>
+        <v>7.87808</v>
       </c>
       <c r="D68" t="n">
-        <v>19.3131</v>
+        <v>18.9461</v>
       </c>
       <c r="E68" t="n">
-        <v>5.67584</v>
+        <v>6.5073</v>
       </c>
       <c r="F68" t="n">
-        <v>6.97612</v>
+        <v>6.63415</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>8.23246</v>
+        <v>10.4852</v>
       </c>
       <c r="C69" t="n">
-        <v>6.6677</v>
+        <v>8.660450000000001</v>
       </c>
       <c r="D69" t="n">
-        <v>19.9107</v>
+        <v>19.5695</v>
       </c>
       <c r="E69" t="n">
-        <v>5.28912</v>
+        <v>6.10313</v>
       </c>
       <c r="F69" t="n">
-        <v>7.05046</v>
+        <v>6.71925</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>9.312060000000001</v>
+        <v>10.8023</v>
       </c>
       <c r="C70" t="n">
-        <v>7.62346</v>
+        <v>8.937290000000001</v>
       </c>
       <c r="D70" t="n">
-        <v>19.9282</v>
+        <v>19.3721</v>
       </c>
       <c r="E70" t="n">
-        <v>5.64468</v>
+        <v>6.49906</v>
       </c>
       <c r="F70" t="n">
-        <v>7.0994</v>
+        <v>6.66916</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>9.272130000000001</v>
+        <v>10.7401</v>
       </c>
       <c r="C71" t="n">
-        <v>7.62624</v>
+        <v>8.890370000000001</v>
       </c>
       <c r="D71" t="n">
-        <v>20.4523</v>
+        <v>19.7653</v>
       </c>
       <c r="E71" t="n">
-        <v>6.39343</v>
+        <v>7.02996</v>
       </c>
       <c r="F71" t="n">
-        <v>6.95603</v>
+        <v>6.90249</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>8.14132</v>
+        <v>10.6074</v>
       </c>
       <c r="C72" t="n">
-        <v>6.56844</v>
+        <v>8.865769999999999</v>
       </c>
       <c r="D72" t="n">
-        <v>21.2731</v>
+        <v>20.129</v>
       </c>
       <c r="E72" t="n">
-        <v>6.52656</v>
+        <v>7.26363</v>
       </c>
       <c r="F72" t="n">
-        <v>7.07398</v>
+        <v>7.13718</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>8.636839999999999</v>
+        <v>10.7816</v>
       </c>
       <c r="C73" t="n">
-        <v>6.99956</v>
+        <v>8.90554</v>
       </c>
       <c r="D73" t="n">
-        <v>22.329</v>
+        <v>20.1313</v>
       </c>
       <c r="E73" t="n">
-        <v>6.6728</v>
+        <v>7.47144</v>
       </c>
       <c r="F73" t="n">
-        <v>7.27655</v>
+        <v>7.29427</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>7.17097</v>
+        <v>9.590120000000001</v>
       </c>
       <c r="C74" t="n">
-        <v>5.5947</v>
+        <v>7.85835</v>
       </c>
       <c r="D74" t="n">
-        <v>22.6646</v>
+        <v>20.6887</v>
       </c>
       <c r="E74" t="n">
-        <v>8.004289999999999</v>
+        <v>7.05103</v>
       </c>
       <c r="F74" t="n">
-        <v>7.43144</v>
+        <v>7.13408</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>12.7664</v>
+        <v>10.4818</v>
       </c>
       <c r="C75" t="n">
-        <v>10.7449</v>
+        <v>8.55273</v>
       </c>
       <c r="D75" t="n">
-        <v>21.7655</v>
+        <v>20.7434</v>
       </c>
       <c r="E75" t="n">
-        <v>8.311529999999999</v>
+        <v>7.26915</v>
       </c>
       <c r="F75" t="n">
-        <v>7.71902</v>
+        <v>7.47911</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>12.4503</v>
+        <v>10.1344</v>
       </c>
       <c r="C76" t="n">
-        <v>10.6822</v>
+        <v>8.34315</v>
       </c>
       <c r="D76" t="n">
-        <v>22.3946</v>
+        <v>21.0445</v>
       </c>
       <c r="E76" t="n">
-        <v>8.71083</v>
+        <v>7.36099</v>
       </c>
       <c r="F76" t="n">
-        <v>9.20356</v>
+        <v>8.516389999999999</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>12.2799</v>
+        <v>9.996270000000001</v>
       </c>
       <c r="C77" t="n">
-        <v>10.449</v>
+        <v>8.235810000000001</v>
       </c>
       <c r="D77" t="n">
-        <v>25.1488</v>
+        <v>24.1244</v>
       </c>
       <c r="E77" t="n">
-        <v>9.001860000000001</v>
+        <v>7.657</v>
       </c>
       <c r="F77" t="n">
-        <v>12.2105</v>
+        <v>11.4275</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>9.125159999999999</v>
+        <v>11.3492</v>
       </c>
       <c r="C78" t="n">
-        <v>7.51139</v>
+        <v>9.57896</v>
       </c>
       <c r="D78" t="n">
-        <v>21.7061</v>
+        <v>21.5539</v>
       </c>
       <c r="E78" t="n">
-        <v>9.8195</v>
+        <v>10.0011</v>
       </c>
       <c r="F78" t="n">
-        <v>14.0774</v>
+        <v>11.9553</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>12.1668</v>
+        <v>9.454510000000001</v>
       </c>
       <c r="C79" t="n">
-        <v>13.5053</v>
+        <v>13.9244</v>
       </c>
       <c r="D79" t="n">
-        <v>22.0343</v>
+        <v>22.0851</v>
       </c>
       <c r="E79" t="n">
-        <v>11.0159</v>
+        <v>10.6957</v>
       </c>
       <c r="F79" t="n">
-        <v>13.4606</v>
+        <v>11.6153</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>12.5569</v>
+        <v>9.707520000000001</v>
       </c>
       <c r="C80" t="n">
-        <v>14.6261</v>
+        <v>14.5987</v>
       </c>
       <c r="D80" t="n">
-        <v>23.3263</v>
+        <v>23.386</v>
       </c>
       <c r="E80" t="n">
-        <v>10.4299</v>
+        <v>10.5914</v>
       </c>
       <c r="F80" t="n">
-        <v>13.9853</v>
+        <v>12.0427</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>17.4617</v>
+        <v>17.4348</v>
       </c>
       <c r="C81" t="n">
-        <v>14.7233</v>
+        <v>14.6933</v>
       </c>
       <c r="D81" t="n">
-        <v>24.2887</v>
+        <v>24.3836</v>
       </c>
       <c r="E81" t="n">
-        <v>10.346</v>
+        <v>10.2663</v>
       </c>
       <c r="F81" t="n">
-        <v>13.2838</v>
+        <v>13.1465</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>17.5293</v>
+        <v>17.5442</v>
       </c>
       <c r="C82" t="n">
-        <v>14.7946</v>
+        <v>14.7763</v>
       </c>
       <c r="D82" t="n">
-        <v>25.165</v>
+        <v>25.1886</v>
       </c>
       <c r="E82" t="n">
-        <v>10.9825</v>
+        <v>11.2108</v>
       </c>
       <c r="F82" t="n">
-        <v>14.4336</v>
+        <v>12.2155</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>17.5893</v>
+        <v>17.5874</v>
       </c>
       <c r="C83" t="n">
-        <v>14.865</v>
+        <v>14.8493</v>
       </c>
       <c r="D83" t="n">
-        <v>26.2571</v>
+        <v>26.3459</v>
       </c>
       <c r="E83" t="n">
-        <v>11.2495</v>
+        <v>11.3006</v>
       </c>
       <c r="F83" t="n">
-        <v>14.4668</v>
+        <v>12.3404</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>17.6872</v>
+        <v>17.6745</v>
       </c>
       <c r="C84" t="n">
-        <v>14.9567</v>
+        <v>14.9391</v>
       </c>
       <c r="D84" t="n">
-        <v>27.0011</v>
+        <v>26.9978</v>
       </c>
       <c r="E84" t="n">
-        <v>12.7127</v>
+        <v>12.0756</v>
       </c>
       <c r="F84" t="n">
-        <v>14.5059</v>
+        <v>12.5586</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>17.7432</v>
+        <v>17.867</v>
       </c>
       <c r="C85" t="n">
-        <v>15.0524</v>
+        <v>15.1645</v>
       </c>
       <c r="D85" t="n">
-        <v>28.3291</v>
+        <v>28.2851</v>
       </c>
       <c r="E85" t="n">
-        <v>11.7166</v>
+        <v>11.7598</v>
       </c>
       <c r="F85" t="n">
-        <v>12.1931</v>
+        <v>13.0364</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>17.807</v>
+        <v>17.8055</v>
       </c>
       <c r="C86" t="n">
-        <v>15.0824</v>
+        <v>15.0643</v>
       </c>
       <c r="D86" t="n">
-        <v>29.6464</v>
+        <v>29.5427</v>
       </c>
       <c r="E86" t="n">
-        <v>12.0045</v>
+        <v>12.0534</v>
       </c>
       <c r="F86" t="n">
-        <v>12.5047</v>
+        <v>13.3314</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>17.8558</v>
+        <v>17.8424</v>
       </c>
       <c r="C87" t="n">
-        <v>15.1352</v>
+        <v>15.1417</v>
       </c>
       <c r="D87" t="n">
-        <v>30.2771</v>
+        <v>30.0164</v>
       </c>
       <c r="E87" t="n">
-        <v>12.148</v>
+        <v>12.0917</v>
       </c>
       <c r="F87" t="n">
-        <v>12.3623</v>
+        <v>12.7008</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>17.8547</v>
+        <v>17.7782</v>
       </c>
       <c r="C88" t="n">
-        <v>15.2113</v>
+        <v>15.1322</v>
       </c>
       <c r="D88" t="n">
-        <v>31.7755</v>
+        <v>32.4458</v>
       </c>
       <c r="E88" t="n">
-        <v>12.2848</v>
+        <v>12.1365</v>
       </c>
       <c r="F88" t="n">
-        <v>17.6249</v>
+        <v>18.0142</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>17.8522</v>
+        <v>17.7829</v>
       </c>
       <c r="C89" t="n">
-        <v>15.3032</v>
+        <v>15.1287</v>
       </c>
       <c r="D89" t="n">
-        <v>31.166</v>
+        <v>31.6914</v>
       </c>
       <c r="E89" t="n">
-        <v>12.6519</v>
+        <v>12.3858</v>
       </c>
       <c r="F89" t="n">
-        <v>13.8923</v>
+        <v>13.015</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>17.9388</v>
+        <v>17.7927</v>
       </c>
       <c r="C90" t="n">
-        <v>15.3484</v>
+        <v>15.16</v>
       </c>
       <c r="D90" t="n">
-        <v>34.003</v>
+        <v>33.3411</v>
       </c>
       <c r="E90" t="n">
-        <v>12.9426</v>
+        <v>12.6209</v>
       </c>
       <c r="F90" t="n">
-        <v>15.8497</v>
+        <v>13.4425</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>18.1374</v>
+        <v>18.1136</v>
       </c>
       <c r="C91" t="n">
-        <v>15.5629</v>
+        <v>15.5115</v>
       </c>
       <c r="D91" t="n">
-        <v>35.0747</v>
+        <v>34.4982</v>
       </c>
       <c r="E91" t="n">
-        <v>13.2484</v>
+        <v>12.9407</v>
       </c>
       <c r="F91" t="n">
-        <v>16.188</v>
+        <v>14.6761</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>18.2065</v>
+        <v>18.0764</v>
       </c>
       <c r="C92" t="n">
-        <v>15.6538</v>
+        <v>15.5431</v>
       </c>
       <c r="D92" t="n">
-        <v>32.0289</v>
+        <v>31.909</v>
       </c>
       <c r="E92" t="n">
-        <v>19.1035</v>
+        <v>19.8388</v>
       </c>
       <c r="F92" t="n">
-        <v>20.1748</v>
+        <v>20.0075</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>18.3478</v>
+        <v>18.2059</v>
       </c>
       <c r="C93" t="n">
-        <v>15.8751</v>
+        <v>15.6339</v>
       </c>
       <c r="D93" t="n">
-        <v>32.7905</v>
+        <v>32.6326</v>
       </c>
       <c r="E93" t="n">
-        <v>19.8868</v>
+        <v>19.9092</v>
       </c>
       <c r="F93" t="n">
-        <v>20.354</v>
+        <v>20.1315</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>18.6283</v>
+        <v>18.4689</v>
       </c>
       <c r="C94" t="n">
-        <v>19.3788</v>
+        <v>19.455</v>
       </c>
       <c r="D94" t="n">
-        <v>33.6</v>
+        <v>33.5162</v>
       </c>
       <c r="E94" t="n">
-        <v>20.2573</v>
+        <v>19.46</v>
       </c>
       <c r="F94" t="n">
-        <v>20.4445</v>
+        <v>20.2653</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>23.0459</v>
+        <v>22.8318</v>
       </c>
       <c r="C95" t="n">
-        <v>19.6301</v>
+        <v>19.6169</v>
       </c>
       <c r="D95" t="n">
-        <v>34.6293</v>
+        <v>34.482</v>
       </c>
       <c r="E95" t="n">
-        <v>20.3393</v>
+        <v>20.4068</v>
       </c>
       <c r="F95" t="n">
-        <v>20.4628</v>
+        <v>20.3499</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>23.0613</v>
+        <v>23.0845</v>
       </c>
       <c r="C96" t="n">
-        <v>19.661</v>
+        <v>19.5898</v>
       </c>
       <c r="D96" t="n">
-        <v>35.4679</v>
+        <v>35.2576</v>
       </c>
       <c r="E96" t="n">
-        <v>20.5537</v>
+        <v>20.5837</v>
       </c>
       <c r="F96" t="n">
-        <v>20.6635</v>
+        <v>20.4709</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>23.2804</v>
+        <v>23.0241</v>
       </c>
       <c r="C97" t="n">
-        <v>19.7072</v>
+        <v>19.6647</v>
       </c>
       <c r="D97" t="n">
-        <v>36.3345</v>
+        <v>36.2269</v>
       </c>
       <c r="E97" t="n">
-        <v>20.7844</v>
+        <v>20.7679</v>
       </c>
       <c r="F97" t="n">
-        <v>20.7172</v>
+        <v>20.5588</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>23.0554</v>
+        <v>23.1288</v>
       </c>
       <c r="C98" t="n">
-        <v>19.7555</v>
+        <v>19.6285</v>
       </c>
       <c r="D98" t="n">
-        <v>37.0299</v>
+        <v>36.9297</v>
       </c>
       <c r="E98" t="n">
-        <v>20.9732</v>
+        <v>20.8968</v>
       </c>
       <c r="F98" t="n">
-        <v>20.839</v>
+        <v>20.7073</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>23.163</v>
+        <v>23.0903</v>
       </c>
       <c r="C99" t="n">
-        <v>19.7863</v>
+        <v>19.684</v>
       </c>
       <c r="D99" t="n">
-        <v>38.1096</v>
+        <v>37.8944</v>
       </c>
       <c r="E99" t="n">
-        <v>21.039</v>
+        <v>21.2024</v>
       </c>
       <c r="F99" t="n">
-        <v>21.0191</v>
+        <v>20.8377</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>22.9964</v>
+        <v>22.984</v>
       </c>
       <c r="C100" t="n">
-        <v>19.9071</v>
+        <v>19.7754</v>
       </c>
       <c r="D100" t="n">
-        <v>38.9934</v>
+        <v>38.8997</v>
       </c>
       <c r="E100" t="n">
-        <v>21.154</v>
+        <v>21.1652</v>
       </c>
       <c r="F100" t="n">
-        <v>21.0841</v>
+        <v>20.9471</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>23.0959</v>
+        <v>23.0332</v>
       </c>
       <c r="C101" t="n">
-        <v>19.8506</v>
+        <v>19.8711</v>
       </c>
       <c r="D101" t="n">
-        <v>40.1235</v>
+        <v>40.0672</v>
       </c>
       <c r="E101" t="n">
-        <v>21.3402</v>
+        <v>21.3174</v>
       </c>
       <c r="F101" t="n">
-        <v>21.16</v>
+        <v>21.1487</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>23.1</v>
+        <v>23.2452</v>
       </c>
       <c r="C102" t="n">
-        <v>19.8985</v>
+        <v>19.762</v>
       </c>
       <c r="D102" t="n">
         <v>40.9455</v>
       </c>
       <c r="E102" t="n">
-        <v>21.5908</v>
+        <v>21.5717</v>
       </c>
       <c r="F102" t="n">
-        <v>21.3931</v>
+        <v>21.2739</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>23.1417</v>
+        <v>23.2824</v>
       </c>
       <c r="C103" t="n">
-        <v>19.9899</v>
+        <v>19.8747</v>
       </c>
       <c r="D103" t="n">
-        <v>42.134</v>
+        <v>42.111</v>
       </c>
       <c r="E103" t="n">
-        <v>21.6918</v>
+        <v>21.6786</v>
       </c>
       <c r="F103" t="n">
-        <v>21.7071</v>
+        <v>21.5108</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>23.2044</v>
+        <v>23.2549</v>
       </c>
       <c r="C104" t="n">
-        <v>20.0785</v>
+        <v>19.9707</v>
       </c>
       <c r="D104" t="n">
-        <v>43.1189</v>
+        <v>43.1118</v>
       </c>
       <c r="E104" t="n">
-        <v>21.903</v>
+        <v>21.9856</v>
       </c>
       <c r="F104" t="n">
-        <v>21.8542</v>
+        <v>21.7315</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>23.3106</v>
+        <v>23.2266</v>
       </c>
       <c r="C105" t="n">
-        <v>20.1314</v>
+        <v>20.1227</v>
       </c>
       <c r="D105" t="n">
-        <v>44.2865</v>
+        <v>44.2341</v>
       </c>
       <c r="E105" t="n">
-        <v>22.1666</v>
+        <v>22.1763</v>
       </c>
       <c r="F105" t="n">
-        <v>22.5018</v>
+        <v>22.4613</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>23.4009</v>
+        <v>23.4023</v>
       </c>
       <c r="C106" t="n">
-        <v>20.3387</v>
+        <v>20.2249</v>
       </c>
       <c r="D106" t="n">
-        <v>45.5112</v>
+        <v>45.7459</v>
       </c>
       <c r="E106" t="n">
-        <v>22.4341</v>
+        <v>22.463</v>
       </c>
       <c r="F106" t="n">
-        <v>22.5522</v>
+        <v>22.466</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>23.5753</v>
+        <v>23.5697</v>
       </c>
       <c r="C107" t="n">
-        <v>20.5277</v>
+        <v>20.5346</v>
       </c>
       <c r="D107" t="n">
-        <v>39.279</v>
+        <v>39.1766</v>
       </c>
       <c r="E107" t="n">
-        <v>26.035</v>
+        <v>25.899</v>
       </c>
       <c r="F107" t="n">
-        <v>25.7319</v>
+        <v>25.6534</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>23.8712</v>
+        <v>23.8996</v>
       </c>
       <c r="C108" t="n">
-        <v>21.2105</v>
+        <v>21.184</v>
       </c>
       <c r="D108" t="n">
-        <v>40.0864</v>
+        <v>40.0494</v>
       </c>
       <c r="E108" t="n">
-        <v>26.0022</v>
+        <v>26.2033</v>
       </c>
       <c r="F108" t="n">
-        <v>25.8907</v>
+        <v>25.6393</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>24.3687</v>
+        <v>24.4411</v>
       </c>
       <c r="C109" t="n">
-        <v>21.238</v>
+        <v>21.2863</v>
       </c>
       <c r="D109" t="n">
-        <v>40.8697</v>
+        <v>40.8602</v>
       </c>
       <c r="E109" t="n">
-        <v>25.8522</v>
+        <v>26.067</v>
       </c>
       <c r="F109" t="n">
-        <v>26.2666</v>
+        <v>25.4351</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>26.2547</v>
+        <v>26.0598</v>
       </c>
       <c r="C110" t="n">
-        <v>21.2699</v>
+        <v>21.3168</v>
       </c>
       <c r="D110" t="n">
-        <v>41.6111</v>
+        <v>41.5952</v>
       </c>
       <c r="E110" t="n">
-        <v>26.6042</v>
+        <v>26.232</v>
       </c>
       <c r="F110" t="n">
-        <v>26.3289</v>
+        <v>26.2105</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>26.1971</v>
+        <v>26.1729</v>
       </c>
       <c r="C111" t="n">
-        <v>21.3062</v>
+        <v>21.2713</v>
       </c>
       <c r="D111" t="n">
-        <v>42.4952</v>
+        <v>42.4719</v>
       </c>
       <c r="E111" t="n">
-        <v>26.9633</v>
+        <v>26.8921</v>
       </c>
       <c r="F111" t="n">
-        <v>25.9321</v>
+        <v>25.8885</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>25.7175</v>
+        <v>25.7923</v>
       </c>
       <c r="C112" t="n">
-        <v>21.3811</v>
+        <v>21.4068</v>
       </c>
       <c r="D112" t="n">
-        <v>43.2345</v>
+        <v>43.1887</v>
       </c>
       <c r="E112" t="n">
-        <v>26.9612</v>
+        <v>27.1426</v>
       </c>
       <c r="F112" t="n">
-        <v>26.7086</v>
+        <v>26.7467</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>25.9943</v>
+        <v>26.2934</v>
       </c>
       <c r="C113" t="n">
-        <v>21.4632</v>
+        <v>21.4104</v>
       </c>
       <c r="D113" t="n">
-        <v>44.2095</v>
+        <v>44.1635</v>
       </c>
       <c r="E113" t="n">
-        <v>27.2382</v>
+        <v>27.2302</v>
       </c>
       <c r="F113" t="n">
-        <v>26.9925</v>
+        <v>26.9872</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>26.0701</v>
+        <v>26.1931</v>
       </c>
       <c r="C114" t="n">
-        <v>21.5141</v>
+        <v>21.5224</v>
       </c>
       <c r="D114" t="n">
-        <v>45.0767</v>
+        <v>45.02</v>
       </c>
       <c r="E114" t="n">
-        <v>27.4535</v>
+        <v>27.3666</v>
       </c>
       <c r="F114" t="n">
-        <v>27.2352</v>
+        <v>27.1693</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>26.2216</v>
+        <v>26.2132</v>
       </c>
       <c r="C115" t="n">
-        <v>21.5958</v>
+        <v>21.6076</v>
       </c>
       <c r="D115" t="n">
-        <v>46.014</v>
+        <v>45.9534</v>
       </c>
       <c r="E115" t="n">
-        <v>27.712</v>
+        <v>27.6017</v>
       </c>
       <c r="F115" t="n">
-        <v>27.5641</v>
+        <v>27.4595</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>26.2816</v>
+        <v>26.2634</v>
       </c>
       <c r="C116" t="n">
-        <v>21.7026</v>
+        <v>21.6748</v>
       </c>
       <c r="D116" t="n">
-        <v>46.9637</v>
+        <v>46.9246</v>
       </c>
       <c r="E116" t="n">
-        <v>27.9345</v>
+        <v>27.8718</v>
       </c>
       <c r="F116" t="n">
-        <v>27.925</v>
+        <v>27.7735</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>26.4104</v>
+        <v>26.3452</v>
       </c>
       <c r="C117" t="n">
-        <v>21.8489</v>
+        <v>21.8351</v>
       </c>
       <c r="D117" t="n">
-        <v>47.9437</v>
+        <v>47.8806</v>
       </c>
       <c r="E117" t="n">
-        <v>28.1868</v>
+        <v>28.1912</v>
       </c>
       <c r="F117" t="n">
-        <v>28.2429</v>
+        <v>28.215</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>26.5368</v>
+        <v>26.3335</v>
       </c>
       <c r="C118" t="n">
-        <v>21.9755</v>
+        <v>21.9695</v>
       </c>
       <c r="D118" t="n">
-        <v>49.0866</v>
+        <v>49.0624</v>
       </c>
       <c r="E118" t="n">
-        <v>28.4893</v>
+        <v>28.4002</v>
       </c>
       <c r="F118" t="n">
-        <v>28.6907</v>
+        <v>28.1008</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>26.4431</v>
+        <v>26.6321</v>
       </c>
       <c r="C119" t="n">
-        <v>22.2059</v>
+        <v>22.1019</v>
       </c>
       <c r="D119" t="n">
-        <v>50.037</v>
+        <v>49.984</v>
       </c>
       <c r="E119" t="n">
-        <v>28.8699</v>
+        <v>28.6403</v>
       </c>
       <c r="F119" t="n">
-        <v>29.2136</v>
+        <v>28.9124</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>26.8858</v>
+        <v>26.549</v>
       </c>
       <c r="C120" t="n">
-        <v>22.3619</v>
+        <v>22.4226</v>
       </c>
       <c r="D120" t="n">
-        <v>51.3329</v>
+        <v>51.3031</v>
       </c>
       <c r="E120" t="n">
-        <v>29.1937</v>
+        <v>29.1061</v>
       </c>
       <c r="F120" t="n">
-        <v>29.8181</v>
+        <v>29.7864</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>26.6324</v>
+        <v>26.7671</v>
       </c>
       <c r="C121" t="n">
-        <v>22.7136</v>
+        <v>22.6667</v>
       </c>
       <c r="D121" t="n">
-        <v>43.9832</v>
+        <v>42.5841</v>
       </c>
       <c r="E121" t="n">
-        <v>30.7219</v>
+        <v>30.8312</v>
       </c>
       <c r="F121" t="n">
-        <v>29.7144</v>
+        <v>29.8023</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>27.4242</v>
+        <v>26.8577</v>
       </c>
       <c r="C122" t="n">
-        <v>23.6602</v>
+        <v>23.7316</v>
       </c>
       <c r="D122" t="n">
-        <v>42.9006</v>
+        <v>43.4043</v>
       </c>
       <c r="E122" t="n">
-        <v>31.0919</v>
+        <v>31.1655</v>
       </c>
       <c r="F122" t="n">
-        <v>29.8995</v>
+        <v>29.7614</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>27.5405</v>
+        <v>27.3501</v>
       </c>
       <c r="C123" t="n">
-        <v>23.7579</v>
+        <v>23.8459</v>
       </c>
       <c r="D123" t="n">
-        <v>43.8529</v>
+        <v>43.737</v>
       </c>
       <c r="E123" t="n">
-        <v>31.3627</v>
+        <v>31.5618</v>
       </c>
       <c r="F123" t="n">
-        <v>30.1248</v>
+        <v>30.1394</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>33.8699</v>
+        <v>33.8251</v>
       </c>
       <c r="C124" t="n">
-        <v>23.876</v>
+        <v>23.919</v>
       </c>
       <c r="D124" t="n">
-        <v>44.6374</v>
+        <v>44.9542</v>
       </c>
       <c r="E124" t="n">
-        <v>31.709</v>
+        <v>31.7624</v>
       </c>
       <c r="F124" t="n">
-        <v>30.3293</v>
+        <v>30.1942</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>33.7576</v>
+        <v>33.0034</v>
       </c>
       <c r="C125" t="n">
-        <v>23.9875</v>
+        <v>24.0902</v>
       </c>
       <c r="D125" t="n">
-        <v>45.6491</v>
+        <v>45.5195</v>
       </c>
       <c r="E125" t="n">
-        <v>31.9782</v>
+        <v>31.9788</v>
       </c>
       <c r="F125" t="n">
-        <v>30.546</v>
+        <v>30.7166</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>33.8484</v>
+        <v>33.5996</v>
       </c>
       <c r="C126" t="n">
-        <v>24.1732</v>
+        <v>24.2696</v>
       </c>
       <c r="D126" t="n">
-        <v>46.1016</v>
+        <v>46.3321</v>
       </c>
       <c r="E126" t="n">
-        <v>32.2433</v>
+        <v>32.4145</v>
       </c>
       <c r="F126" t="n">
-        <v>30.8575</v>
+        <v>31.0212</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>33.6862</v>
+        <v>34.0124</v>
       </c>
       <c r="C127" t="n">
-        <v>24.3005</v>
+        <v>24.3267</v>
       </c>
       <c r="D127" t="n">
-        <v>47.0086</v>
+        <v>47.1623</v>
       </c>
       <c r="E127" t="n">
-        <v>32.6223</v>
+        <v>32.6844</v>
       </c>
       <c r="F127" t="n">
-        <v>31.1158</v>
+        <v>31.1833</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>33.8546</v>
+        <v>33.8571</v>
       </c>
       <c r="C128" t="n">
-        <v>24.4749</v>
+        <v>24.5076</v>
       </c>
       <c r="D128" t="n">
-        <v>47.862</v>
+        <v>48.0792</v>
       </c>
       <c r="E128" t="n">
-        <v>32.8394</v>
+        <v>32.9679</v>
       </c>
       <c r="F128" t="n">
-        <v>31.5068</v>
+        <v>31.6008</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>33.7501</v>
+        <v>33.9515</v>
       </c>
       <c r="C129" t="n">
-        <v>24.6054</v>
+        <v>24.6552</v>
       </c>
       <c r="D129" t="n">
-        <v>48.919</v>
+        <v>49.0401</v>
       </c>
       <c r="E129" t="n">
-        <v>33.161</v>
+        <v>33.3056</v>
       </c>
       <c r="F129" t="n">
-        <v>31.8192</v>
+        <v>31.8817</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>33.8287</v>
+        <v>33.9875</v>
       </c>
       <c r="C130" t="n">
-        <v>24.791</v>
+        <v>24.8961</v>
       </c>
       <c r="D130" t="n">
-        <v>49.5754</v>
+        <v>49.9703</v>
       </c>
       <c r="E130" t="n">
-        <v>33.5715</v>
+        <v>33.5617</v>
       </c>
       <c r="F130" t="n">
-        <v>32.2026</v>
+        <v>32.3318</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>33.8687</v>
+        <v>34.0498</v>
       </c>
       <c r="C131" t="n">
-        <v>25.0212</v>
+        <v>25.0903</v>
       </c>
       <c r="D131" t="n">
-        <v>50.6989</v>
+        <v>50.8809</v>
       </c>
       <c r="E131" t="n">
-        <v>33.8146</v>
+        <v>33.8848</v>
       </c>
       <c r="F131" t="n">
-        <v>32.6247</v>
+        <v>32.5184</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>33.9818</v>
+        <v>34.0244</v>
       </c>
       <c r="C132" t="n">
-        <v>25.3949</v>
+        <v>25.3881</v>
       </c>
       <c r="D132" t="n">
-        <v>51.7073</v>
+        <v>51.9611</v>
       </c>
       <c r="E132" t="n">
-        <v>34.2254</v>
+        <v>34.4153</v>
       </c>
       <c r="F132" t="n">
-        <v>33.1506</v>
+        <v>33.2767</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>34.0064</v>
+        <v>34.1833</v>
       </c>
       <c r="C133" t="n">
-        <v>25.639</v>
+        <v>25.6968</v>
       </c>
       <c r="D133" t="n">
-        <v>52.4613</v>
+        <v>52.9491</v>
       </c>
       <c r="E133" t="n">
-        <v>34.66</v>
+        <v>34.744</v>
       </c>
       <c r="F133" t="n">
-        <v>33.8829</v>
+        <v>33.9358</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>34.1488</v>
+        <v>34.2575</v>
       </c>
       <c r="C134" t="n">
-        <v>26.0194</v>
+        <v>26.0774</v>
       </c>
       <c r="D134" t="n">
-        <v>53.9753</v>
+        <v>54.1817</v>
       </c>
       <c r="E134" t="n">
-        <v>35.1359</v>
+        <v>35.1891</v>
       </c>
       <c r="F134" t="n">
-        <v>34.6094</v>
+        <v>34.5628</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>34.4131</v>
+        <v>33.7924</v>
       </c>
       <c r="C135" t="n">
-        <v>26.3855</v>
+        <v>26.5256</v>
       </c>
       <c r="D135" t="n">
-        <v>44.4723</v>
+        <v>44.6069</v>
       </c>
       <c r="E135" t="n">
-        <v>33.4802</v>
+        <v>33.3872</v>
       </c>
       <c r="F135" t="n">
-        <v>31.9066</v>
+        <v>32.1842</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>34.6946</v>
+        <v>33.6404</v>
       </c>
       <c r="C136" t="n">
-        <v>26.0886</v>
+        <v>26.3746</v>
       </c>
       <c r="D136" t="n">
-        <v>45.0177</v>
+        <v>44.8912</v>
       </c>
       <c r="E136" t="n">
-        <v>31.845</v>
+        <v>33.7023</v>
       </c>
       <c r="F136" t="n">
-        <v>31.3431</v>
+        <v>32.3764</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>33.8101</v>
+        <v>34.3924</v>
       </c>
       <c r="C137" t="n">
-        <v>25.3305</v>
+        <v>26.5615</v>
       </c>
       <c r="D137" t="n">
-        <v>44.4474</v>
+        <v>45.608</v>
       </c>
       <c r="E137" t="n">
-        <v>32.1782</v>
+        <v>34.0856</v>
       </c>
       <c r="F137" t="n">
-        <v>31.5863</v>
+        <v>32.4762</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>37.7342</v>
+        <v>38.9049</v>
       </c>
       <c r="C138" t="n">
-        <v>25.4823</v>
+        <v>26.6466</v>
       </c>
       <c r="D138" t="n">
-        <v>45.4123</v>
+        <v>46.6595</v>
       </c>
       <c r="E138" t="n">
-        <v>32.6028</v>
+        <v>34.47</v>
       </c>
       <c r="F138" t="n">
-        <v>31.8635</v>
+        <v>32.7511</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>37.7284</v>
+        <v>38.2825</v>
       </c>
       <c r="C139" t="n">
-        <v>25.6572</v>
+        <v>26.8611</v>
       </c>
       <c r="D139" t="n">
-        <v>45.3524</v>
+        <v>46.9103</v>
       </c>
       <c r="E139" t="n">
-        <v>32.8543</v>
+        <v>34.8315</v>
       </c>
       <c r="F139" t="n">
-        <v>32.1463</v>
+        <v>33.0199</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>37.7457</v>
+        <v>38.9903</v>
       </c>
       <c r="C140" t="n">
-        <v>25.7305</v>
+        <v>27.0492</v>
       </c>
       <c r="D140" t="n">
-        <v>46.3737</v>
+        <v>47.7861</v>
       </c>
       <c r="E140" t="n">
-        <v>33.1573</v>
+        <v>34.9994</v>
       </c>
       <c r="F140" t="n">
-        <v>32.3648</v>
+        <v>33.376</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>37.7668</v>
+        <v>38.9702</v>
       </c>
       <c r="C141" t="n">
-        <v>25.9846</v>
+        <v>27.6366</v>
       </c>
       <c r="D141" t="n">
-        <v>47.4631</v>
+        <v>48.7645</v>
       </c>
       <c r="E141" t="n">
-        <v>33.4683</v>
+        <v>35.1841</v>
       </c>
       <c r="F141" t="n">
-        <v>32.5866</v>
+        <v>33.3736</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>37.7993</v>
+        <v>38.791</v>
       </c>
       <c r="C142" t="n">
-        <v>26.1201</v>
+        <v>27.325</v>
       </c>
       <c r="D142" t="n">
-        <v>48.1054</v>
+        <v>49.5713</v>
       </c>
       <c r="E142" t="n">
-        <v>33.8128</v>
+        <v>35.5095</v>
       </c>
       <c r="F142" t="n">
-        <v>33.0193</v>
+        <v>33.7636</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>37.8768</v>
+        <v>38.8487</v>
       </c>
       <c r="C143" t="n">
-        <v>26.3983</v>
+        <v>27.5807</v>
       </c>
       <c r="D143" t="n">
-        <v>49.6761</v>
+        <v>50.4823</v>
       </c>
       <c r="E143" t="n">
-        <v>34.1934</v>
+        <v>35.9519</v>
       </c>
       <c r="F143" t="n">
-        <v>33.38</v>
+        <v>34.1616</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Scattered successful looukp.xlsx
+++ b/gcc-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>3.83293</v>
+        <v>3.58893</v>
       </c>
       <c r="C2" t="n">
-        <v>3.30816</v>
+        <v>3.53055</v>
       </c>
       <c r="D2" t="n">
-        <v>8.12771</v>
+        <v>7.61626</v>
       </c>
       <c r="E2" t="n">
-        <v>4.00489</v>
+        <v>4.12625</v>
       </c>
       <c r="F2" t="n">
-        <v>3.46671</v>
+        <v>3.88068</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>4.08629</v>
+        <v>3.37489</v>
       </c>
       <c r="C3" t="n">
-        <v>3.25217</v>
+        <v>3.38197</v>
       </c>
       <c r="D3" t="n">
-        <v>8.59366</v>
+        <v>8.09277</v>
       </c>
       <c r="E3" t="n">
-        <v>3.35329</v>
+        <v>3.99837</v>
       </c>
       <c r="F3" t="n">
-        <v>4.42473</v>
+        <v>4.19401</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.40294</v>
+        <v>3.4607</v>
       </c>
       <c r="C4" t="n">
-        <v>2.95596</v>
+        <v>3.39149</v>
       </c>
       <c r="D4" t="n">
-        <v>9.34075</v>
+        <v>9.137549999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>3.23746</v>
+        <v>4.01004</v>
       </c>
       <c r="F4" t="n">
-        <v>4.50614</v>
+        <v>4.23298</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.86381</v>
+        <v>3.52728</v>
       </c>
       <c r="C5" t="n">
-        <v>3.23761</v>
+        <v>3.51939</v>
       </c>
       <c r="D5" t="n">
-        <v>10.3089</v>
+        <v>9.79182</v>
       </c>
       <c r="E5" t="n">
-        <v>3.26692</v>
+        <v>4.1295</v>
       </c>
       <c r="F5" t="n">
-        <v>4.44979</v>
+        <v>3.96462</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>3.9907</v>
+        <v>3.27265</v>
       </c>
       <c r="C6" t="n">
-        <v>3.2574</v>
+        <v>3.35663</v>
       </c>
       <c r="D6" t="n">
-        <v>11.0128</v>
+        <v>10.4105</v>
       </c>
       <c r="E6" t="n">
-        <v>3.67094</v>
+        <v>3.8728</v>
       </c>
       <c r="F6" t="n">
-        <v>4.06037</v>
+        <v>4.28618</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>4.13665</v>
+        <v>3.55342</v>
       </c>
       <c r="C7" t="n">
-        <v>3.41107</v>
+        <v>3.60927</v>
       </c>
       <c r="D7" t="n">
-        <v>7.01575</v>
+        <v>6.69397</v>
       </c>
       <c r="E7" t="n">
-        <v>4.02397</v>
+        <v>4.89252</v>
       </c>
       <c r="F7" t="n">
-        <v>3.68316</v>
+        <v>4.15029</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>4.1654</v>
+        <v>3.53302</v>
       </c>
       <c r="C8" t="n">
-        <v>3.47663</v>
+        <v>4.24938</v>
       </c>
       <c r="D8" t="n">
-        <v>7.3939</v>
+        <v>6.93067</v>
       </c>
       <c r="E8" t="n">
-        <v>4.10915</v>
+        <v>4.88127</v>
       </c>
       <c r="F8" t="n">
-        <v>3.70676</v>
+        <v>4.19263</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>3.49878</v>
+        <v>3.56209</v>
       </c>
       <c r="C9" t="n">
-        <v>3.65662</v>
+        <v>4.27497</v>
       </c>
       <c r="D9" t="n">
-        <v>7.69679</v>
+        <v>7.46607</v>
       </c>
       <c r="E9" t="n">
-        <v>4.1407</v>
+        <v>4.96439</v>
       </c>
       <c r="F9" t="n">
-        <v>3.72308</v>
+        <v>4.20357</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>4.22227</v>
+        <v>4.02761</v>
       </c>
       <c r="C10" t="n">
-        <v>3.66907</v>
+        <v>4.31218</v>
       </c>
       <c r="D10" t="n">
-        <v>8.18088</v>
+        <v>7.91595</v>
       </c>
       <c r="E10" t="n">
-        <v>4.16583</v>
+        <v>5.00567</v>
       </c>
       <c r="F10" t="n">
-        <v>3.7638</v>
+        <v>4.23354</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>4.97958</v>
+        <v>4.30363</v>
       </c>
       <c r="C11" t="n">
-        <v>3.69843</v>
+        <v>4.21726</v>
       </c>
       <c r="D11" t="n">
-        <v>8.6152</v>
+        <v>8.488160000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>4.4801</v>
+        <v>5.0352</v>
       </c>
       <c r="F11" t="n">
-        <v>3.75333</v>
+        <v>4.25901</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>4.05362</v>
+        <v>4.30215</v>
       </c>
       <c r="C12" t="n">
-        <v>3.59664</v>
+        <v>4.2297</v>
       </c>
       <c r="D12" t="n">
-        <v>9.18507</v>
+        <v>8.99924</v>
       </c>
       <c r="E12" t="n">
-        <v>4.50559</v>
+        <v>5.11261</v>
       </c>
       <c r="F12" t="n">
-        <v>3.76049</v>
+        <v>4.29425</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>4.97743</v>
+        <v>4.91917</v>
       </c>
       <c r="C13" t="n">
-        <v>3.78554</v>
+        <v>4.2946</v>
       </c>
       <c r="D13" t="n">
-        <v>9.726839999999999</v>
+        <v>9.55865</v>
       </c>
       <c r="E13" t="n">
-        <v>4.33834</v>
+        <v>5.12443</v>
       </c>
       <c r="F13" t="n">
-        <v>3.92781</v>
+        <v>4.31663</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>5.02528</v>
+        <v>5.0293</v>
       </c>
       <c r="C14" t="n">
-        <v>3.79566</v>
+        <v>4.42564</v>
       </c>
       <c r="D14" t="n">
-        <v>10.1411</v>
+        <v>10.0055</v>
       </c>
       <c r="E14" t="n">
-        <v>4.28286</v>
+        <v>5.13182</v>
       </c>
       <c r="F14" t="n">
-        <v>3.84732</v>
+        <v>4.36553</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>4.98899</v>
+        <v>5.04103</v>
       </c>
       <c r="C15" t="n">
-        <v>3.83883</v>
+        <v>4.40784</v>
       </c>
       <c r="D15" t="n">
-        <v>10.5866</v>
+        <v>10.5549</v>
       </c>
       <c r="E15" t="n">
-        <v>4.38674</v>
+        <v>5.15755</v>
       </c>
       <c r="F15" t="n">
-        <v>3.96059</v>
+        <v>4.39985</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>5.04379</v>
+        <v>4.2459</v>
       </c>
       <c r="C16" t="n">
-        <v>3.83838</v>
+        <v>4.42733</v>
       </c>
       <c r="D16" t="n">
-        <v>11.1959</v>
+        <v>11.0891</v>
       </c>
       <c r="E16" t="n">
-        <v>4.62979</v>
+        <v>5.20613</v>
       </c>
       <c r="F16" t="n">
-        <v>4.04992</v>
+        <v>4.41031</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>5.00717</v>
+        <v>4.46288</v>
       </c>
       <c r="C17" t="n">
-        <v>3.92366</v>
+        <v>4.4033</v>
       </c>
       <c r="D17" t="n">
-        <v>11.6037</v>
+        <v>11.5151</v>
       </c>
       <c r="E17" t="n">
-        <v>4.35995</v>
+        <v>5.30445</v>
       </c>
       <c r="F17" t="n">
-        <v>3.92879</v>
+        <v>4.64895</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>5.0165</v>
+        <v>5.07793</v>
       </c>
       <c r="C18" t="n">
-        <v>3.96701</v>
+        <v>4.58155</v>
       </c>
       <c r="D18" t="n">
-        <v>12.0007</v>
+        <v>11.9752</v>
       </c>
       <c r="E18" t="n">
-        <v>4.68832</v>
+        <v>5.30113</v>
       </c>
       <c r="F18" t="n">
-        <v>3.93594</v>
+        <v>4.47105</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>5.0299</v>
+        <v>5.10503</v>
       </c>
       <c r="C19" t="n">
-        <v>4.01446</v>
+        <v>4.59194</v>
       </c>
       <c r="D19" t="n">
-        <v>12.6031</v>
+        <v>12.4984</v>
       </c>
       <c r="E19" t="n">
-        <v>4.43303</v>
+        <v>5.30097</v>
       </c>
       <c r="F19" t="n">
-        <v>3.98162</v>
+        <v>4.50672</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>4.90745</v>
+        <v>5.08228</v>
       </c>
       <c r="C20" t="n">
-        <v>4.08882</v>
+        <v>4.64438</v>
       </c>
       <c r="D20" t="n">
-        <v>13.033</v>
+        <v>12.8002</v>
       </c>
       <c r="E20" t="n">
-        <v>4.8091</v>
+        <v>5.48888</v>
       </c>
       <c r="F20" t="n">
-        <v>4.13163</v>
+        <v>4.563</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>5.07075</v>
+        <v>5.09661</v>
       </c>
       <c r="C21" t="n">
-        <v>4.13786</v>
+        <v>4.70995</v>
       </c>
       <c r="D21" t="n">
-        <v>9.222950000000001</v>
+        <v>9.2004</v>
       </c>
       <c r="E21" t="n">
-        <v>4.38186</v>
+        <v>5.06019</v>
       </c>
       <c r="F21" t="n">
-        <v>4.72082</v>
+        <v>5.25154</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>5.10566</v>
+        <v>5.15151</v>
       </c>
       <c r="C22" t="n">
-        <v>3.62899</v>
+        <v>4.23563</v>
       </c>
       <c r="D22" t="n">
-        <v>9.45016</v>
+        <v>9.443049999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>4.36372</v>
+        <v>4.93479</v>
       </c>
       <c r="F22" t="n">
-        <v>4.84298</v>
+        <v>5.2719</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>5.13215</v>
+        <v>5.20313</v>
       </c>
       <c r="C23" t="n">
-        <v>3.6637</v>
+        <v>4.25435</v>
       </c>
       <c r="D23" t="n">
-        <v>9.8466</v>
+        <v>9.80387</v>
       </c>
       <c r="E23" t="n">
-        <v>4.45824</v>
+        <v>5.03759</v>
       </c>
       <c r="F23" t="n">
-        <v>4.80893</v>
+        <v>5.24815</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>5.11934</v>
+        <v>5.06855</v>
       </c>
       <c r="C24" t="n">
-        <v>3.68657</v>
+        <v>4.26024</v>
       </c>
       <c r="D24" t="n">
-        <v>10.1382</v>
+        <v>10.1434</v>
       </c>
       <c r="E24" t="n">
-        <v>4.49632</v>
+        <v>4.95275</v>
       </c>
       <c r="F24" t="n">
-        <v>4.84238</v>
+        <v>5.10458</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>5.17498</v>
+        <v>5.01933</v>
       </c>
       <c r="C25" t="n">
-        <v>3.69653</v>
+        <v>4.25993</v>
       </c>
       <c r="D25" t="n">
-        <v>10.5213</v>
+        <v>10.5295</v>
       </c>
       <c r="E25" t="n">
-        <v>4.48344</v>
+        <v>4.95866</v>
       </c>
       <c r="F25" t="n">
-        <v>4.90209</v>
+        <v>5.35962</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>5.18452</v>
+        <v>5.06811</v>
       </c>
       <c r="C26" t="n">
-        <v>3.70713</v>
+        <v>4.24461</v>
       </c>
       <c r="D26" t="n">
-        <v>10.901</v>
+        <v>10.8853</v>
       </c>
       <c r="E26" t="n">
-        <v>4.47805</v>
+        <v>5.06813</v>
       </c>
       <c r="F26" t="n">
-        <v>4.6797</v>
+        <v>5.00131</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>4.97534</v>
+        <v>5.07872</v>
       </c>
       <c r="C27" t="n">
-        <v>3.7542</v>
+        <v>4.30658</v>
       </c>
       <c r="D27" t="n">
-        <v>11.3483</v>
+        <v>11.3526</v>
       </c>
       <c r="E27" t="n">
-        <v>4.55392</v>
+        <v>5.05615</v>
       </c>
       <c r="F27" t="n">
-        <v>4.71283</v>
+        <v>5.03998</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>4.98967</v>
+        <v>5.08467</v>
       </c>
       <c r="C28" t="n">
-        <v>3.77239</v>
+        <v>4.33997</v>
       </c>
       <c r="D28" t="n">
-        <v>11.7377</v>
+        <v>11.7451</v>
       </c>
       <c r="E28" t="n">
-        <v>4.59384</v>
+        <v>5.08181</v>
       </c>
       <c r="F28" t="n">
-        <v>4.71711</v>
+        <v>5.06706</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>4.99483</v>
+        <v>4.7654</v>
       </c>
       <c r="C29" t="n">
-        <v>3.78824</v>
+        <v>4.26657</v>
       </c>
       <c r="D29" t="n">
-        <v>12.172</v>
+        <v>12.2247</v>
       </c>
       <c r="E29" t="n">
-        <v>4.62089</v>
+        <v>5.12235</v>
       </c>
       <c r="F29" t="n">
-        <v>4.7663</v>
+        <v>5.06282</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>5.20969</v>
+        <v>4.61452</v>
       </c>
       <c r="C30" t="n">
-        <v>3.88358</v>
+        <v>4.39543</v>
       </c>
       <c r="D30" t="n">
-        <v>12.637</v>
+        <v>12.5222</v>
       </c>
       <c r="E30" t="n">
-        <v>4.66181</v>
+        <v>5.25328</v>
       </c>
       <c r="F30" t="n">
-        <v>4.78583</v>
+        <v>5.25431</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>5.24138</v>
+        <v>4.61782</v>
       </c>
       <c r="C31" t="n">
-        <v>3.84193</v>
+        <v>4.4491</v>
       </c>
       <c r="D31" t="n">
-        <v>13.1231</v>
+        <v>12.9787</v>
       </c>
       <c r="E31" t="n">
-        <v>4.56997</v>
+        <v>5.28137</v>
       </c>
       <c r="F31" t="n">
-        <v>4.84377</v>
+        <v>5.38462</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>5.03706</v>
+        <v>4.67308</v>
       </c>
       <c r="C32" t="n">
-        <v>3.92146</v>
+        <v>4.50841</v>
       </c>
       <c r="D32" t="n">
-        <v>13.4593</v>
+        <v>13.3164</v>
       </c>
       <c r="E32" t="n">
-        <v>4.7238</v>
+        <v>5.3377</v>
       </c>
       <c r="F32" t="n">
-        <v>4.89591</v>
+        <v>5.62186</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.97185</v>
+        <v>4.47629</v>
       </c>
       <c r="C33" t="n">
-        <v>3.96474</v>
+        <v>4.23008</v>
       </c>
       <c r="D33" t="n">
-        <v>13.8454</v>
+        <v>13.7417</v>
       </c>
       <c r="E33" t="n">
-        <v>4.72538</v>
+        <v>5.34856</v>
       </c>
       <c r="F33" t="n">
-        <v>5.00206</v>
+        <v>5.23824</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.0727</v>
+        <v>4.70235</v>
       </c>
       <c r="C34" t="n">
-        <v>4.02919</v>
+        <v>4.59689</v>
       </c>
       <c r="D34" t="n">
-        <v>14.1712</v>
+        <v>14.0477</v>
       </c>
       <c r="E34" t="n">
-        <v>4.88215</v>
+        <v>5.30182</v>
       </c>
       <c r="F34" t="n">
-        <v>4.99091</v>
+        <v>5.50567</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>5.28793</v>
+        <v>4.67573</v>
       </c>
       <c r="C35" t="n">
-        <v>4.0177</v>
+        <v>4.65504</v>
       </c>
       <c r="D35" t="n">
-        <v>10.0995</v>
+        <v>9.875830000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>4.58205</v>
+        <v>5.06863</v>
       </c>
       <c r="F35" t="n">
-        <v>4.81822</v>
+        <v>5.08596</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>5.16119</v>
+        <v>4.74438</v>
       </c>
       <c r="C36" t="n">
-        <v>4.19893</v>
+        <v>4.66937</v>
       </c>
       <c r="D36" t="n">
-        <v>10.5546</v>
+        <v>10.0668</v>
       </c>
       <c r="E36" t="n">
-        <v>4.6245</v>
+        <v>4.96157</v>
       </c>
       <c r="F36" t="n">
-        <v>5.13876</v>
+        <v>5.08978</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>5.34439</v>
+        <v>5.45365</v>
       </c>
       <c r="C37" t="n">
-        <v>3.94468</v>
+        <v>4.27331</v>
       </c>
       <c r="D37" t="n">
-        <v>11.3472</v>
+        <v>10.2582</v>
       </c>
       <c r="E37" t="n">
-        <v>4.65163</v>
+        <v>4.98472</v>
       </c>
       <c r="F37" t="n">
-        <v>5.20335</v>
+        <v>5.13099</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>5.30262</v>
+        <v>5.1939</v>
       </c>
       <c r="C38" t="n">
-        <v>3.87615</v>
+        <v>4.27383</v>
       </c>
       <c r="D38" t="n">
-        <v>11.1705</v>
+        <v>10.5375</v>
       </c>
       <c r="E38" t="n">
-        <v>4.68101</v>
+        <v>5.10884</v>
       </c>
       <c r="F38" t="n">
-        <v>5.10588</v>
+        <v>5.15058</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>5.32162</v>
+        <v>5.06433</v>
       </c>
       <c r="C39" t="n">
-        <v>3.95004</v>
+        <v>4.57189</v>
       </c>
       <c r="D39" t="n">
-        <v>11.9319</v>
+        <v>10.8617</v>
       </c>
       <c r="E39" t="n">
-        <v>4.71905</v>
+        <v>5.36613</v>
       </c>
       <c r="F39" t="n">
-        <v>5.17563</v>
+        <v>5.07581</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>5.3361</v>
+        <v>5.08821</v>
       </c>
       <c r="C40" t="n">
-        <v>3.86823</v>
+        <v>4.49319</v>
       </c>
       <c r="D40" t="n">
-        <v>12.8806</v>
+        <v>11.2607</v>
       </c>
       <c r="E40" t="n">
-        <v>4.74608</v>
+        <v>5.35861</v>
       </c>
       <c r="F40" t="n">
-        <v>5.29998</v>
+        <v>5.11386</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>4.9242</v>
+        <v>4.64944</v>
       </c>
       <c r="C41" t="n">
-        <v>4.00844</v>
+        <v>4.58794</v>
       </c>
       <c r="D41" t="n">
-        <v>13.3863</v>
+        <v>11.6018</v>
       </c>
       <c r="E41" t="n">
-        <v>4.78328</v>
+        <v>5.28589</v>
       </c>
       <c r="F41" t="n">
-        <v>5.00057</v>
+        <v>5.3028</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>5.23015</v>
+        <v>5.13985</v>
       </c>
       <c r="C42" t="n">
-        <v>3.9405</v>
+        <v>4.57894</v>
       </c>
       <c r="D42" t="n">
-        <v>13.7797</v>
+        <v>11.9969</v>
       </c>
       <c r="E42" t="n">
-        <v>4.80295</v>
+        <v>5.40815</v>
       </c>
       <c r="F42" t="n">
-        <v>5.37106</v>
+        <v>5.20689</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>5.34522</v>
+        <v>5.10269</v>
       </c>
       <c r="C43" t="n">
-        <v>4.05459</v>
+        <v>4.66823</v>
       </c>
       <c r="D43" t="n">
-        <v>14.081</v>
+        <v>12.3507</v>
       </c>
       <c r="E43" t="n">
-        <v>4.84446</v>
+        <v>5.18441</v>
       </c>
       <c r="F43" t="n">
-        <v>5.10075</v>
+        <v>5.24151</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>5.25853</v>
+        <v>5.14051</v>
       </c>
       <c r="C44" t="n">
-        <v>3.96767</v>
+        <v>4.60707</v>
       </c>
       <c r="D44" t="n">
-        <v>14.26</v>
+        <v>12.7717</v>
       </c>
       <c r="E44" t="n">
-        <v>4.88704</v>
+        <v>5.21281</v>
       </c>
       <c r="F44" t="n">
-        <v>5.12188</v>
+        <v>5.405</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>5.46458</v>
+        <v>5.14858</v>
       </c>
       <c r="C45" t="n">
-        <v>4.12598</v>
+        <v>4.60835</v>
       </c>
       <c r="D45" t="n">
-        <v>14.2619</v>
+        <v>13.1614</v>
       </c>
       <c r="E45" t="n">
-        <v>4.93874</v>
+        <v>5.53181</v>
       </c>
       <c r="F45" t="n">
-        <v>5.43195</v>
+        <v>5.43659</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.87401</v>
+        <v>5.15178</v>
       </c>
       <c r="C46" t="n">
-        <v>4.18505</v>
+        <v>4.73277</v>
       </c>
       <c r="D46" t="n">
-        <v>14.8997</v>
+        <v>13.5076</v>
       </c>
       <c r="E46" t="n">
-        <v>4.96063</v>
+        <v>5.5477</v>
       </c>
       <c r="F46" t="n">
-        <v>5.54379</v>
+        <v>5.50849</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>5.00581</v>
+        <v>5.15756</v>
       </c>
       <c r="C47" t="n">
-        <v>4.23805</v>
+        <v>4.78984</v>
       </c>
       <c r="D47" t="n">
-        <v>15.0282</v>
+        <v>13.8443</v>
       </c>
       <c r="E47" t="n">
-        <v>5.19202</v>
+        <v>5.63153</v>
       </c>
       <c r="F47" t="n">
-        <v>5.75635</v>
+        <v>5.89287</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.36463</v>
+        <v>5.08283</v>
       </c>
       <c r="C48" t="n">
-        <v>4.32737</v>
+        <v>4.98701</v>
       </c>
       <c r="D48" t="n">
-        <v>15.7804</v>
+        <v>14.2764</v>
       </c>
       <c r="E48" t="n">
-        <v>5.54316</v>
+        <v>5.93193</v>
       </c>
       <c r="F48" t="n">
-        <v>6.14919</v>
+        <v>6.22679</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>5.10357</v>
+        <v>5.2889</v>
       </c>
       <c r="C49" t="n">
-        <v>4.31947</v>
+        <v>5.11032</v>
       </c>
       <c r="D49" t="n">
-        <v>16.4207</v>
+        <v>14.9169</v>
       </c>
       <c r="E49" t="n">
-        <v>5.8721</v>
+        <v>6.33561</v>
       </c>
       <c r="F49" t="n">
-        <v>6.64564</v>
+        <v>6.61047</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>5.25788</v>
+        <v>4.98768</v>
       </c>
       <c r="C50" t="n">
-        <v>4.55567</v>
+        <v>5.10342</v>
       </c>
       <c r="D50" t="n">
-        <v>14.0859</v>
+        <v>11.8941</v>
       </c>
       <c r="E50" t="n">
-        <v>4.61772</v>
+        <v>5.1654</v>
       </c>
       <c r="F50" t="n">
-        <v>6.78017</v>
+        <v>6.28196</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>5.37675</v>
+        <v>6.5029</v>
       </c>
       <c r="C51" t="n">
-        <v>3.8458</v>
+        <v>4.49154</v>
       </c>
       <c r="D51" t="n">
-        <v>14.982</v>
+        <v>13.0116</v>
       </c>
       <c r="E51" t="n">
-        <v>4.63743</v>
+        <v>5.14908</v>
       </c>
       <c r="F51" t="n">
-        <v>6.79247</v>
+        <v>5.97984</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>6.76903</v>
+        <v>6.27929</v>
       </c>
       <c r="C52" t="n">
-        <v>3.98451</v>
+        <v>4.41755</v>
       </c>
       <c r="D52" t="n">
-        <v>15.7967</v>
+        <v>14.4743</v>
       </c>
       <c r="E52" t="n">
-        <v>4.68378</v>
+        <v>5.21222</v>
       </c>
       <c r="F52" t="n">
-        <v>5.75902</v>
+        <v>6.87509</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>5.54028</v>
+        <v>5.25433</v>
       </c>
       <c r="C53" t="n">
-        <v>3.9308</v>
+        <v>4.51392</v>
       </c>
       <c r="D53" t="n">
-        <v>16.7016</v>
+        <v>14.9395</v>
       </c>
       <c r="E53" t="n">
-        <v>4.72582</v>
+        <v>5.23548</v>
       </c>
       <c r="F53" t="n">
-        <v>7.26609</v>
+        <v>6.56636</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>5.52582</v>
+        <v>5.25644</v>
       </c>
       <c r="C54" t="n">
-        <v>3.91968</v>
+        <v>4.53545</v>
       </c>
       <c r="D54" t="n">
-        <v>17.9485</v>
+        <v>16.0288</v>
       </c>
       <c r="E54" t="n">
-        <v>4.76925</v>
+        <v>5.28468</v>
       </c>
       <c r="F54" t="n">
-        <v>7.38772</v>
+        <v>6.45506</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>5.53615</v>
+        <v>5.58463</v>
       </c>
       <c r="C55" t="n">
-        <v>4.00526</v>
+        <v>4.51809</v>
       </c>
       <c r="D55" t="n">
-        <v>18.6009</v>
+        <v>16.5355</v>
       </c>
       <c r="E55" t="n">
-        <v>4.81126</v>
+        <v>5.35363</v>
       </c>
       <c r="F55" t="n">
-        <v>5.59628</v>
+        <v>5.78565</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>5.3355</v>
+        <v>5.27797</v>
       </c>
       <c r="C56" t="n">
-        <v>4.02611</v>
+        <v>4.59433</v>
       </c>
       <c r="D56" t="n">
-        <v>17.6608</v>
+        <v>18.1904</v>
       </c>
       <c r="E56" t="n">
-        <v>4.82036</v>
+        <v>5.33485</v>
       </c>
       <c r="F56" t="n">
-        <v>7.57909</v>
+        <v>6.30377</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>5.57556</v>
+        <v>5.29094</v>
       </c>
       <c r="C57" t="n">
-        <v>4.05722</v>
+        <v>4.69263</v>
       </c>
       <c r="D57" t="n">
-        <v>21.1035</v>
+        <v>18.6927</v>
       </c>
       <c r="E57" t="n">
-        <v>4.91654</v>
+        <v>5.40805</v>
       </c>
       <c r="F57" t="n">
-        <v>5.88526</v>
+        <v>6.92973</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>5.5801</v>
+        <v>5.30334</v>
       </c>
       <c r="C58" t="n">
-        <v>3.97641</v>
+        <v>4.72073</v>
       </c>
       <c r="D58" t="n">
-        <v>21.3673</v>
+        <v>18.6344</v>
       </c>
       <c r="E58" t="n">
-        <v>4.99532</v>
+        <v>5.57348</v>
       </c>
       <c r="F58" t="n">
-        <v>5.74319</v>
+        <v>6.05929</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>5.61796</v>
+        <v>5.31131</v>
       </c>
       <c r="C59" t="n">
-        <v>4.11626</v>
+        <v>5.00524</v>
       </c>
       <c r="D59" t="n">
-        <v>21.7175</v>
+        <v>18.449</v>
       </c>
       <c r="E59" t="n">
-        <v>5.07521</v>
+        <v>5.6181</v>
       </c>
       <c r="F59" t="n">
-        <v>7.98693</v>
+        <v>6.8545</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>5.42279</v>
+        <v>5.33622</v>
       </c>
       <c r="C60" t="n">
-        <v>4.22527</v>
+        <v>5.05211</v>
       </c>
       <c r="D60" t="n">
-        <v>21.4132</v>
+        <v>19.4583</v>
       </c>
       <c r="E60" t="n">
-        <v>5.21002</v>
+        <v>5.68979</v>
       </c>
       <c r="F60" t="n">
-        <v>7.27033</v>
+        <v>6.48326</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>5.70482</v>
+        <v>5.35666</v>
       </c>
       <c r="C61" t="n">
-        <v>4.14791</v>
+        <v>5.25866</v>
       </c>
       <c r="D61" t="n">
-        <v>21.7318</v>
+        <v>20.4653</v>
       </c>
       <c r="E61" t="n">
-        <v>5.27833</v>
+        <v>6.12992</v>
       </c>
       <c r="F61" t="n">
-        <v>7.60693</v>
+        <v>7.73245</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.50274</v>
+        <v>5.43407</v>
       </c>
       <c r="C62" t="n">
-        <v>4.29426</v>
+        <v>5.20864</v>
       </c>
       <c r="D62" t="n">
-        <v>21.9697</v>
+        <v>20.3688</v>
       </c>
       <c r="E62" t="n">
-        <v>5.55344</v>
+        <v>6.35906</v>
       </c>
       <c r="F62" t="n">
-        <v>7.57382</v>
+        <v>7.51289</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>5.61158</v>
+        <v>5.49232</v>
       </c>
       <c r="C63" t="n">
-        <v>4.44696</v>
+        <v>5.34762</v>
       </c>
       <c r="D63" t="n">
-        <v>21.9866</v>
+        <v>20.6786</v>
       </c>
       <c r="E63" t="n">
-        <v>5.84271</v>
+        <v>6.70267</v>
       </c>
       <c r="F63" t="n">
-        <v>8.62017</v>
+        <v>7.76597</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>6.02597</v>
+        <v>5.71661</v>
       </c>
       <c r="C64" t="n">
-        <v>4.50369</v>
+        <v>5.36338</v>
       </c>
       <c r="D64" t="n">
-        <v>14.9859</v>
+        <v>15.3689</v>
       </c>
       <c r="E64" t="n">
-        <v>5.29933</v>
+        <v>5.70506</v>
       </c>
       <c r="F64" t="n">
-        <v>5.96268</v>
+        <v>6.56328</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>6.35163</v>
+        <v>6.00649</v>
       </c>
       <c r="C65" t="n">
-        <v>8.074210000000001</v>
+        <v>6.88946</v>
       </c>
       <c r="D65" t="n">
-        <v>15.9233</v>
+        <v>14.6297</v>
       </c>
       <c r="E65" t="n">
-        <v>5.26981</v>
+        <v>5.74484</v>
       </c>
       <c r="F65" t="n">
-        <v>6.06511</v>
+        <v>6.69122</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>6.81437</v>
+        <v>6.4303</v>
       </c>
       <c r="C66" t="n">
-        <v>8.19242</v>
+        <v>7.00243</v>
       </c>
       <c r="D66" t="n">
-        <v>16.9359</v>
+        <v>16.2594</v>
       </c>
       <c r="E66" t="n">
-        <v>5.71794</v>
+        <v>5.75157</v>
       </c>
       <c r="F66" t="n">
-        <v>6.39625</v>
+        <v>6.85766</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>9.65127</v>
+        <v>8.11157</v>
       </c>
       <c r="C67" t="n">
-        <v>7.93876</v>
+        <v>7.13466</v>
       </c>
       <c r="D67" t="n">
-        <v>18.0782</v>
+        <v>17.2902</v>
       </c>
       <c r="E67" t="n">
-        <v>5.6043</v>
+        <v>5.83196</v>
       </c>
       <c r="F67" t="n">
-        <v>6.51495</v>
+        <v>7.03967</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>9.5662</v>
+        <v>11.1275</v>
       </c>
       <c r="C68" t="n">
-        <v>7.87808</v>
+        <v>10.2413</v>
       </c>
       <c r="D68" t="n">
-        <v>18.9461</v>
+        <v>18.5407</v>
       </c>
       <c r="E68" t="n">
-        <v>6.5073</v>
+        <v>6.08765</v>
       </c>
       <c r="F68" t="n">
-        <v>6.63415</v>
+        <v>7.09922</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>10.4852</v>
+        <v>7.3508</v>
       </c>
       <c r="C69" t="n">
-        <v>8.660450000000001</v>
+        <v>6.39731</v>
       </c>
       <c r="D69" t="n">
-        <v>19.5695</v>
+        <v>18.8397</v>
       </c>
       <c r="E69" t="n">
-        <v>6.10313</v>
+        <v>6.00196</v>
       </c>
       <c r="F69" t="n">
-        <v>6.71925</v>
+        <v>7.21038</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>10.8023</v>
+        <v>11.0957</v>
       </c>
       <c r="C70" t="n">
-        <v>8.937290000000001</v>
+        <v>10.1285</v>
       </c>
       <c r="D70" t="n">
-        <v>19.3721</v>
+        <v>19.2796</v>
       </c>
       <c r="E70" t="n">
-        <v>6.49906</v>
+        <v>5.81738</v>
       </c>
       <c r="F70" t="n">
-        <v>6.66916</v>
+        <v>7.36416</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>10.7401</v>
+        <v>12.1191</v>
       </c>
       <c r="C71" t="n">
-        <v>8.890370000000001</v>
+        <v>11.2053</v>
       </c>
       <c r="D71" t="n">
-        <v>19.7653</v>
+        <v>19.0539</v>
       </c>
       <c r="E71" t="n">
-        <v>7.02996</v>
+        <v>7.4007</v>
       </c>
       <c r="F71" t="n">
-        <v>6.90249</v>
+        <v>6.87095</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>10.6074</v>
+        <v>13.2606</v>
       </c>
       <c r="C72" t="n">
-        <v>8.865769999999999</v>
+        <v>12.2498</v>
       </c>
       <c r="D72" t="n">
-        <v>20.129</v>
+        <v>19.3516</v>
       </c>
       <c r="E72" t="n">
-        <v>7.26363</v>
+        <v>7.61431</v>
       </c>
       <c r="F72" t="n">
-        <v>7.13718</v>
+        <v>7.021</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>10.7816</v>
+        <v>8.623010000000001</v>
       </c>
       <c r="C73" t="n">
-        <v>8.90554</v>
+        <v>7.60497</v>
       </c>
       <c r="D73" t="n">
-        <v>20.1313</v>
+        <v>19.8024</v>
       </c>
       <c r="E73" t="n">
-        <v>7.47144</v>
+        <v>7.77723</v>
       </c>
       <c r="F73" t="n">
-        <v>7.29427</v>
+        <v>7.22926</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>9.590120000000001</v>
+        <v>13.6728</v>
       </c>
       <c r="C74" t="n">
-        <v>7.85835</v>
+        <v>12.501</v>
       </c>
       <c r="D74" t="n">
-        <v>20.6887</v>
+        <v>21.2114</v>
       </c>
       <c r="E74" t="n">
-        <v>7.05103</v>
+        <v>10.032</v>
       </c>
       <c r="F74" t="n">
-        <v>7.13408</v>
+        <v>7.54534</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>10.4818</v>
+        <v>13.7066</v>
       </c>
       <c r="C75" t="n">
-        <v>8.55273</v>
+        <v>12.538</v>
       </c>
       <c r="D75" t="n">
-        <v>20.7434</v>
+        <v>21.548</v>
       </c>
       <c r="E75" t="n">
-        <v>7.26915</v>
+        <v>10.3514</v>
       </c>
       <c r="F75" t="n">
-        <v>7.47911</v>
+        <v>7.98021</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>10.1344</v>
+        <v>13.8083</v>
       </c>
       <c r="C76" t="n">
-        <v>8.34315</v>
+        <v>12.5908</v>
       </c>
       <c r="D76" t="n">
-        <v>21.0445</v>
+        <v>21.1429</v>
       </c>
       <c r="E76" t="n">
-        <v>7.36099</v>
+        <v>10.2382</v>
       </c>
       <c r="F76" t="n">
-        <v>8.516389999999999</v>
+        <v>8.18618</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>9.996270000000001</v>
+        <v>13.7986</v>
       </c>
       <c r="C77" t="n">
-        <v>8.235810000000001</v>
+        <v>12.4391</v>
       </c>
       <c r="D77" t="n">
-        <v>24.1244</v>
+        <v>22.0836</v>
       </c>
       <c r="E77" t="n">
-        <v>7.657</v>
+        <v>10.5633</v>
       </c>
       <c r="F77" t="n">
-        <v>11.4275</v>
+        <v>10.572</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>11.3492</v>
+        <v>13.1485</v>
       </c>
       <c r="C78" t="n">
-        <v>9.57896</v>
+        <v>12.099</v>
       </c>
       <c r="D78" t="n">
-        <v>21.5539</v>
+        <v>21.5979</v>
       </c>
       <c r="E78" t="n">
-        <v>10.0011</v>
+        <v>11.0482</v>
       </c>
       <c r="F78" t="n">
-        <v>11.9553</v>
+        <v>14.475</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>9.454510000000001</v>
+        <v>13.6914</v>
       </c>
       <c r="C79" t="n">
-        <v>13.9244</v>
+        <v>15.4678</v>
       </c>
       <c r="D79" t="n">
-        <v>22.0851</v>
+        <v>22.2931</v>
       </c>
       <c r="E79" t="n">
-        <v>10.6957</v>
+        <v>11.4215</v>
       </c>
       <c r="F79" t="n">
-        <v>11.6153</v>
+        <v>13.1524</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>9.707520000000001</v>
+        <v>13.1139</v>
       </c>
       <c r="C80" t="n">
-        <v>14.5987</v>
+        <v>16.0933</v>
       </c>
       <c r="D80" t="n">
-        <v>23.386</v>
+        <v>22.7332</v>
       </c>
       <c r="E80" t="n">
-        <v>10.5914</v>
+        <v>11.667</v>
       </c>
       <c r="F80" t="n">
-        <v>12.0427</v>
+        <v>14.4246</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>17.4348</v>
+        <v>17.2725</v>
       </c>
       <c r="C81" t="n">
-        <v>14.6933</v>
+        <v>16.0406</v>
       </c>
       <c r="D81" t="n">
-        <v>24.3836</v>
+        <v>24.0714</v>
       </c>
       <c r="E81" t="n">
-        <v>10.2663</v>
+        <v>11.8873</v>
       </c>
       <c r="F81" t="n">
-        <v>13.1465</v>
+        <v>14.5155</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>17.5442</v>
+        <v>17.2952</v>
       </c>
       <c r="C82" t="n">
-        <v>14.7763</v>
+        <v>16.0315</v>
       </c>
       <c r="D82" t="n">
-        <v>25.1886</v>
+        <v>24.66</v>
       </c>
       <c r="E82" t="n">
-        <v>11.2108</v>
+        <v>12.1691</v>
       </c>
       <c r="F82" t="n">
-        <v>12.2155</v>
+        <v>14.4619</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>17.5874</v>
+        <v>17.4211</v>
       </c>
       <c r="C83" t="n">
-        <v>14.8493</v>
+        <v>16.1323</v>
       </c>
       <c r="D83" t="n">
-        <v>26.3459</v>
+        <v>25.7278</v>
       </c>
       <c r="E83" t="n">
-        <v>11.3006</v>
+        <v>12.4044</v>
       </c>
       <c r="F83" t="n">
-        <v>12.3404</v>
+        <v>14.54</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>17.6745</v>
+        <v>17.4477</v>
       </c>
       <c r="C84" t="n">
-        <v>14.9391</v>
+        <v>16.1574</v>
       </c>
       <c r="D84" t="n">
-        <v>26.9978</v>
+        <v>26.6896</v>
       </c>
       <c r="E84" t="n">
-        <v>12.0756</v>
+        <v>12.6477</v>
       </c>
       <c r="F84" t="n">
-        <v>12.5586</v>
+        <v>14.6582</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>17.867</v>
+        <v>17.4814</v>
       </c>
       <c r="C85" t="n">
-        <v>15.1645</v>
+        <v>16.2021</v>
       </c>
       <c r="D85" t="n">
-        <v>28.2851</v>
+        <v>28.0459</v>
       </c>
       <c r="E85" t="n">
-        <v>11.7598</v>
+        <v>12.8221</v>
       </c>
       <c r="F85" t="n">
-        <v>13.0364</v>
+        <v>13.2262</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>17.8055</v>
+        <v>17.6587</v>
       </c>
       <c r="C86" t="n">
-        <v>15.0643</v>
+        <v>16.3767</v>
       </c>
       <c r="D86" t="n">
-        <v>29.5427</v>
+        <v>29.3486</v>
       </c>
       <c r="E86" t="n">
-        <v>12.0534</v>
+        <v>13.0773</v>
       </c>
       <c r="F86" t="n">
-        <v>13.3314</v>
+        <v>13.6436</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>17.8424</v>
+        <v>17.6363</v>
       </c>
       <c r="C87" t="n">
-        <v>15.1417</v>
+        <v>16.357</v>
       </c>
       <c r="D87" t="n">
-        <v>30.0164</v>
+        <v>30.1178</v>
       </c>
       <c r="E87" t="n">
-        <v>12.0917</v>
+        <v>13.2521</v>
       </c>
       <c r="F87" t="n">
-        <v>12.7008</v>
+        <v>13.4706</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>17.7782</v>
+        <v>17.6314</v>
       </c>
       <c r="C88" t="n">
-        <v>15.1322</v>
+        <v>16.2805</v>
       </c>
       <c r="D88" t="n">
-        <v>32.4458</v>
+        <v>31.6706</v>
       </c>
       <c r="E88" t="n">
-        <v>12.1365</v>
+        <v>13.639</v>
       </c>
       <c r="F88" t="n">
-        <v>18.0142</v>
+        <v>17.4443</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>17.7829</v>
+        <v>17.6782</v>
       </c>
       <c r="C89" t="n">
-        <v>15.1287</v>
+        <v>16.3658</v>
       </c>
       <c r="D89" t="n">
-        <v>31.6914</v>
+        <v>32.4378</v>
       </c>
       <c r="E89" t="n">
-        <v>12.3858</v>
+        <v>13.8695</v>
       </c>
       <c r="F89" t="n">
-        <v>13.015</v>
+        <v>17.7272</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>17.7927</v>
+        <v>17.7373</v>
       </c>
       <c r="C90" t="n">
-        <v>15.16</v>
+        <v>16.3572</v>
       </c>
       <c r="D90" t="n">
-        <v>33.3411</v>
+        <v>33.4125</v>
       </c>
       <c r="E90" t="n">
-        <v>12.6209</v>
+        <v>14.1039</v>
       </c>
       <c r="F90" t="n">
-        <v>13.4425</v>
+        <v>17.9209</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>18.1136</v>
+        <v>17.6239</v>
       </c>
       <c r="C91" t="n">
-        <v>15.5115</v>
+        <v>16.2993</v>
       </c>
       <c r="D91" t="n">
-        <v>34.4982</v>
+        <v>34.886</v>
       </c>
       <c r="E91" t="n">
-        <v>12.9407</v>
+        <v>14.3419</v>
       </c>
       <c r="F91" t="n">
-        <v>14.6761</v>
+        <v>18.5754</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>18.0764</v>
+        <v>17.8483</v>
       </c>
       <c r="C92" t="n">
-        <v>15.5431</v>
+        <v>16.4274</v>
       </c>
       <c r="D92" t="n">
-        <v>31.909</v>
+        <v>31.6998</v>
       </c>
       <c r="E92" t="n">
-        <v>19.8388</v>
+        <v>21.7594</v>
       </c>
       <c r="F92" t="n">
-        <v>20.0075</v>
+        <v>22.1214</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>18.2059</v>
+        <v>17.937</v>
       </c>
       <c r="C93" t="n">
-        <v>15.6339</v>
+        <v>16.5752</v>
       </c>
       <c r="D93" t="n">
-        <v>32.6326</v>
+        <v>32.5236</v>
       </c>
       <c r="E93" t="n">
-        <v>19.9092</v>
+        <v>21.7204</v>
       </c>
       <c r="F93" t="n">
-        <v>20.1315</v>
+        <v>22.2447</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>18.4689</v>
+        <v>18.2042</v>
       </c>
       <c r="C94" t="n">
-        <v>19.455</v>
+        <v>21.425</v>
       </c>
       <c r="D94" t="n">
-        <v>33.5162</v>
+        <v>33.5077</v>
       </c>
       <c r="E94" t="n">
-        <v>19.46</v>
+        <v>21.8386</v>
       </c>
       <c r="F94" t="n">
-        <v>20.2653</v>
+        <v>22.2714</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>22.8318</v>
+        <v>22.4344</v>
       </c>
       <c r="C95" t="n">
-        <v>19.6169</v>
+        <v>21.6905</v>
       </c>
       <c r="D95" t="n">
-        <v>34.482</v>
+        <v>33.9161</v>
       </c>
       <c r="E95" t="n">
-        <v>20.4068</v>
+        <v>22.5456</v>
       </c>
       <c r="F95" t="n">
-        <v>20.3499</v>
+        <v>22.4594</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>23.0845</v>
+        <v>22.4624</v>
       </c>
       <c r="C96" t="n">
-        <v>19.5898</v>
+        <v>21.6841</v>
       </c>
       <c r="D96" t="n">
-        <v>35.2576</v>
+        <v>34.5383</v>
       </c>
       <c r="E96" t="n">
-        <v>20.5837</v>
+        <v>22.8541</v>
       </c>
       <c r="F96" t="n">
-        <v>20.4709</v>
+        <v>22.5539</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>23.0241</v>
+        <v>22.4773</v>
       </c>
       <c r="C97" t="n">
-        <v>19.6647</v>
+        <v>21.817</v>
       </c>
       <c r="D97" t="n">
-        <v>36.2269</v>
+        <v>35.6073</v>
       </c>
       <c r="E97" t="n">
-        <v>20.7679</v>
+        <v>22.9763</v>
       </c>
       <c r="F97" t="n">
-        <v>20.5588</v>
+        <v>22.6733</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>23.1288</v>
+        <v>22.5276</v>
       </c>
       <c r="C98" t="n">
-        <v>19.6285</v>
+        <v>21.7621</v>
       </c>
       <c r="D98" t="n">
-        <v>36.9297</v>
+        <v>36.3474</v>
       </c>
       <c r="E98" t="n">
-        <v>20.8968</v>
+        <v>23.2049</v>
       </c>
       <c r="F98" t="n">
-        <v>20.7073</v>
+        <v>22.7669</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>23.0903</v>
+        <v>22.5883</v>
       </c>
       <c r="C99" t="n">
-        <v>19.684</v>
+        <v>21.8407</v>
       </c>
       <c r="D99" t="n">
-        <v>37.8944</v>
+        <v>37.3332</v>
       </c>
       <c r="E99" t="n">
-        <v>21.2024</v>
+        <v>23.4474</v>
       </c>
       <c r="F99" t="n">
-        <v>20.8377</v>
+        <v>22.8543</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>22.984</v>
+        <v>22.5848</v>
       </c>
       <c r="C100" t="n">
-        <v>19.7754</v>
+        <v>21.8404</v>
       </c>
       <c r="D100" t="n">
-        <v>38.8997</v>
+        <v>38.5801</v>
       </c>
       <c r="E100" t="n">
-        <v>21.1652</v>
+        <v>23.454</v>
       </c>
       <c r="F100" t="n">
-        <v>20.9471</v>
+        <v>22.9688</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>23.0332</v>
+        <v>22.5952</v>
       </c>
       <c r="C101" t="n">
-        <v>19.8711</v>
+        <v>21.8535</v>
       </c>
       <c r="D101" t="n">
-        <v>40.0672</v>
+        <v>39.4847</v>
       </c>
       <c r="E101" t="n">
-        <v>21.3174</v>
+        <v>23.7369</v>
       </c>
       <c r="F101" t="n">
-        <v>21.1487</v>
+        <v>23.066</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>23.2452</v>
+        <v>22.4841</v>
       </c>
       <c r="C102" t="n">
-        <v>19.762</v>
+        <v>21.8624</v>
       </c>
       <c r="D102" t="n">
-        <v>40.9455</v>
+        <v>40.0958</v>
       </c>
       <c r="E102" t="n">
-        <v>21.5717</v>
+        <v>23.8393</v>
       </c>
       <c r="F102" t="n">
-        <v>21.2739</v>
+        <v>23.402</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>23.2824</v>
+        <v>22.6266</v>
       </c>
       <c r="C103" t="n">
-        <v>19.8747</v>
+        <v>21.9112</v>
       </c>
       <c r="D103" t="n">
-        <v>42.111</v>
+        <v>41.1505</v>
       </c>
       <c r="E103" t="n">
-        <v>21.6786</v>
+        <v>23.9847</v>
       </c>
       <c r="F103" t="n">
-        <v>21.5108</v>
+        <v>23.5712</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>23.2549</v>
+        <v>22.6442</v>
       </c>
       <c r="C104" t="n">
-        <v>19.9707</v>
+        <v>22.0073</v>
       </c>
       <c r="D104" t="n">
-        <v>43.1118</v>
+        <v>42.1322</v>
       </c>
       <c r="E104" t="n">
-        <v>21.9856</v>
+        <v>24.3039</v>
       </c>
       <c r="F104" t="n">
-        <v>21.7315</v>
+        <v>23.887</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>23.2266</v>
+        <v>22.7002</v>
       </c>
       <c r="C105" t="n">
-        <v>20.1227</v>
+        <v>22.0924</v>
       </c>
       <c r="D105" t="n">
-        <v>44.2341</v>
+        <v>43.6362</v>
       </c>
       <c r="E105" t="n">
-        <v>22.1763</v>
+        <v>24.557</v>
       </c>
       <c r="F105" t="n">
-        <v>22.4613</v>
+        <v>24.1852</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>23.4023</v>
+        <v>22.9278</v>
       </c>
       <c r="C106" t="n">
-        <v>20.2249</v>
+        <v>22.2848</v>
       </c>
       <c r="D106" t="n">
-        <v>45.7459</v>
+        <v>44.6633</v>
       </c>
       <c r="E106" t="n">
-        <v>22.463</v>
+        <v>24.8324</v>
       </c>
       <c r="F106" t="n">
-        <v>22.466</v>
+        <v>24.6112</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>23.5697</v>
+        <v>23.0293</v>
       </c>
       <c r="C107" t="n">
-        <v>20.5346</v>
+        <v>22.5441</v>
       </c>
       <c r="D107" t="n">
-        <v>39.1766</v>
+        <v>38.4346</v>
       </c>
       <c r="E107" t="n">
-        <v>25.899</v>
+        <v>28.2744</v>
       </c>
       <c r="F107" t="n">
-        <v>25.6534</v>
+        <v>27.7781</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>23.8996</v>
+        <v>23.1151</v>
       </c>
       <c r="C108" t="n">
-        <v>21.184</v>
+        <v>23.4038</v>
       </c>
       <c r="D108" t="n">
-        <v>40.0494</v>
+        <v>38.586</v>
       </c>
       <c r="E108" t="n">
-        <v>26.2033</v>
+        <v>28.592</v>
       </c>
       <c r="F108" t="n">
-        <v>25.6393</v>
+        <v>28.0856</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>24.4411</v>
+        <v>23.5416</v>
       </c>
       <c r="C109" t="n">
-        <v>21.2863</v>
+        <v>23.3695</v>
       </c>
       <c r="D109" t="n">
-        <v>40.8602</v>
+        <v>39.1508</v>
       </c>
       <c r="E109" t="n">
-        <v>26.067</v>
+        <v>28.6218</v>
       </c>
       <c r="F109" t="n">
-        <v>25.4351</v>
+        <v>28.0091</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>26.0598</v>
+        <v>25.2557</v>
       </c>
       <c r="C110" t="n">
-        <v>21.3168</v>
+        <v>23.5004</v>
       </c>
       <c r="D110" t="n">
-        <v>41.5952</v>
+        <v>40.023</v>
       </c>
       <c r="E110" t="n">
-        <v>26.232</v>
+        <v>28.9729</v>
       </c>
       <c r="F110" t="n">
-        <v>26.2105</v>
+        <v>28.5177</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>26.1729</v>
+        <v>25.3697</v>
       </c>
       <c r="C111" t="n">
-        <v>21.2713</v>
+        <v>23.5709</v>
       </c>
       <c r="D111" t="n">
-        <v>42.4719</v>
+        <v>40.8087</v>
       </c>
       <c r="E111" t="n">
-        <v>26.8921</v>
+        <v>29.2304</v>
       </c>
       <c r="F111" t="n">
-        <v>25.8885</v>
+        <v>28.5641</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>25.7923</v>
+        <v>25.4343</v>
       </c>
       <c r="C112" t="n">
-        <v>21.4068</v>
+        <v>23.6566</v>
       </c>
       <c r="D112" t="n">
-        <v>43.1887</v>
+        <v>41.6589</v>
       </c>
       <c r="E112" t="n">
-        <v>27.1426</v>
+        <v>29.6067</v>
       </c>
       <c r="F112" t="n">
-        <v>26.7467</v>
+        <v>28.996</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>26.2934</v>
+        <v>25.4085</v>
       </c>
       <c r="C113" t="n">
-        <v>21.4104</v>
+        <v>23.7466</v>
       </c>
       <c r="D113" t="n">
-        <v>44.1635</v>
+        <v>42.4748</v>
       </c>
       <c r="E113" t="n">
-        <v>27.2302</v>
+        <v>29.7777</v>
       </c>
       <c r="F113" t="n">
-        <v>26.9872</v>
+        <v>29.2423</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>26.1931</v>
+        <v>25.3373</v>
       </c>
       <c r="C114" t="n">
-        <v>21.5224</v>
+        <v>23.8744</v>
       </c>
       <c r="D114" t="n">
-        <v>45.02</v>
+        <v>43.5185</v>
       </c>
       <c r="E114" t="n">
-        <v>27.3666</v>
+        <v>30.0533</v>
       </c>
       <c r="F114" t="n">
-        <v>27.1693</v>
+        <v>29.4884</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>26.2132</v>
+        <v>25.4962</v>
       </c>
       <c r="C115" t="n">
-        <v>21.6076</v>
+        <v>23.937</v>
       </c>
       <c r="D115" t="n">
-        <v>45.9534</v>
+        <v>44.3694</v>
       </c>
       <c r="E115" t="n">
-        <v>27.6017</v>
+        <v>30.2616</v>
       </c>
       <c r="F115" t="n">
-        <v>27.4595</v>
+        <v>29.8149</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>26.2634</v>
+        <v>25.3157</v>
       </c>
       <c r="C116" t="n">
-        <v>21.6748</v>
+        <v>24.0586</v>
       </c>
       <c r="D116" t="n">
-        <v>46.9246</v>
+        <v>45.271</v>
       </c>
       <c r="E116" t="n">
-        <v>27.8718</v>
+        <v>30.6274</v>
       </c>
       <c r="F116" t="n">
-        <v>27.7735</v>
+        <v>30.0771</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>26.3452</v>
+        <v>25.3831</v>
       </c>
       <c r="C117" t="n">
-        <v>21.8351</v>
+        <v>24.1441</v>
       </c>
       <c r="D117" t="n">
-        <v>47.8806</v>
+        <v>46.2602</v>
       </c>
       <c r="E117" t="n">
-        <v>28.1912</v>
+        <v>30.9272</v>
       </c>
       <c r="F117" t="n">
-        <v>28.215</v>
+        <v>30.553</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>26.3335</v>
+        <v>25.6241</v>
       </c>
       <c r="C118" t="n">
-        <v>21.9695</v>
+        <v>24.3116</v>
       </c>
       <c r="D118" t="n">
-        <v>49.0624</v>
+        <v>47.6075</v>
       </c>
       <c r="E118" t="n">
-        <v>28.4002</v>
+        <v>31.2725</v>
       </c>
       <c r="F118" t="n">
-        <v>28.1008</v>
+        <v>31.0609</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>26.6321</v>
+        <v>25.8082</v>
       </c>
       <c r="C119" t="n">
-        <v>22.1019</v>
+        <v>24.5791</v>
       </c>
       <c r="D119" t="n">
-        <v>49.984</v>
+        <v>48.9301</v>
       </c>
       <c r="E119" t="n">
-        <v>28.6403</v>
+        <v>31.6204</v>
       </c>
       <c r="F119" t="n">
-        <v>28.9124</v>
+        <v>31.4986</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>26.549</v>
+        <v>25.6858</v>
       </c>
       <c r="C120" t="n">
-        <v>22.4226</v>
+        <v>24.8362</v>
       </c>
       <c r="D120" t="n">
-        <v>51.3031</v>
+        <v>49.7017</v>
       </c>
       <c r="E120" t="n">
-        <v>29.1061</v>
+        <v>32.0836</v>
       </c>
       <c r="F120" t="n">
-        <v>29.7864</v>
+        <v>32.2577</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>26.7671</v>
+        <v>25.9809</v>
       </c>
       <c r="C121" t="n">
-        <v>22.6667</v>
+        <v>25.1542</v>
       </c>
       <c r="D121" t="n">
-        <v>42.5841</v>
+        <v>41.3065</v>
       </c>
       <c r="E121" t="n">
-        <v>30.8312</v>
+        <v>32.6442</v>
       </c>
       <c r="F121" t="n">
-        <v>29.8023</v>
+        <v>32.3395</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>26.8577</v>
+        <v>25.7686</v>
       </c>
       <c r="C122" t="n">
-        <v>23.7316</v>
+        <v>25.7461</v>
       </c>
       <c r="D122" t="n">
-        <v>43.4043</v>
+        <v>41.508</v>
       </c>
       <c r="E122" t="n">
-        <v>31.1655</v>
+        <v>32.7426</v>
       </c>
       <c r="F122" t="n">
-        <v>29.7614</v>
+        <v>32.462</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>27.3501</v>
+        <v>26.8941</v>
       </c>
       <c r="C123" t="n">
-        <v>23.8459</v>
+        <v>25.8684</v>
       </c>
       <c r="D123" t="n">
-        <v>43.737</v>
+        <v>42.6546</v>
       </c>
       <c r="E123" t="n">
-        <v>31.5618</v>
+        <v>32.9722</v>
       </c>
       <c r="F123" t="n">
-        <v>30.1394</v>
+        <v>32.8047</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>33.8251</v>
+        <v>32.7957</v>
       </c>
       <c r="C124" t="n">
-        <v>23.919</v>
+        <v>25.9024</v>
       </c>
       <c r="D124" t="n">
-        <v>44.9542</v>
+        <v>43.5691</v>
       </c>
       <c r="E124" t="n">
-        <v>31.7624</v>
+        <v>33.4466</v>
       </c>
       <c r="F124" t="n">
-        <v>30.1942</v>
+        <v>32.9717</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>33.0034</v>
+        <v>32.7835</v>
       </c>
       <c r="C125" t="n">
-        <v>24.0902</v>
+        <v>26.0326</v>
       </c>
       <c r="D125" t="n">
-        <v>45.5195</v>
+        <v>44.1856</v>
       </c>
       <c r="E125" t="n">
-        <v>31.9788</v>
+        <v>33.7494</v>
       </c>
       <c r="F125" t="n">
-        <v>30.7166</v>
+        <v>33.1838</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>33.5996</v>
+        <v>32.8231</v>
       </c>
       <c r="C126" t="n">
-        <v>24.2696</v>
+        <v>26.2092</v>
       </c>
       <c r="D126" t="n">
-        <v>46.3321</v>
+        <v>44.9106</v>
       </c>
       <c r="E126" t="n">
-        <v>32.4145</v>
+        <v>34.0866</v>
       </c>
       <c r="F126" t="n">
-        <v>31.0212</v>
+        <v>33.515</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>34.0124</v>
+        <v>32.7935</v>
       </c>
       <c r="C127" t="n">
-        <v>24.3267</v>
+        <v>26.367</v>
       </c>
       <c r="D127" t="n">
-        <v>47.1623</v>
+        <v>45.7223</v>
       </c>
       <c r="E127" t="n">
-        <v>32.6844</v>
+        <v>34.4725</v>
       </c>
       <c r="F127" t="n">
-        <v>31.1833</v>
+        <v>33.7567</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>33.8571</v>
+        <v>32.8379</v>
       </c>
       <c r="C128" t="n">
-        <v>24.5076</v>
+        <v>26.4986</v>
       </c>
       <c r="D128" t="n">
-        <v>48.0792</v>
+        <v>46.6922</v>
       </c>
       <c r="E128" t="n">
-        <v>32.9679</v>
+        <v>34.8537</v>
       </c>
       <c r="F128" t="n">
-        <v>31.6008</v>
+        <v>34.0237</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>33.9515</v>
+        <v>32.8854</v>
       </c>
       <c r="C129" t="n">
-        <v>24.6552</v>
+        <v>26.7667</v>
       </c>
       <c r="D129" t="n">
-        <v>49.0401</v>
+        <v>47.439</v>
       </c>
       <c r="E129" t="n">
-        <v>33.3056</v>
+        <v>35.1728</v>
       </c>
       <c r="F129" t="n">
-        <v>31.8817</v>
+        <v>34.4946</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>33.9875</v>
+        <v>32.8748</v>
       </c>
       <c r="C130" t="n">
-        <v>24.8961</v>
+        <v>26.8866</v>
       </c>
       <c r="D130" t="n">
-        <v>49.9703</v>
+        <v>48.3332</v>
       </c>
       <c r="E130" t="n">
-        <v>33.5617</v>
+        <v>35.5495</v>
       </c>
       <c r="F130" t="n">
-        <v>32.3318</v>
+        <v>35.0976</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>34.0498</v>
+        <v>32.8698</v>
       </c>
       <c r="C131" t="n">
-        <v>25.0903</v>
+        <v>27.1072</v>
       </c>
       <c r="D131" t="n">
-        <v>50.8809</v>
+        <v>49.587</v>
       </c>
       <c r="E131" t="n">
-        <v>33.8848</v>
+        <v>35.8914</v>
       </c>
       <c r="F131" t="n">
-        <v>32.5184</v>
+        <v>35.5991</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>34.0244</v>
+        <v>32.9046</v>
       </c>
       <c r="C132" t="n">
-        <v>25.3881</v>
+        <v>27.4691</v>
       </c>
       <c r="D132" t="n">
-        <v>51.9611</v>
+        <v>50.6411</v>
       </c>
       <c r="E132" t="n">
-        <v>34.4153</v>
+        <v>36.3309</v>
       </c>
       <c r="F132" t="n">
-        <v>33.2767</v>
+        <v>36.062</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>34.1833</v>
+        <v>32.8623</v>
       </c>
       <c r="C133" t="n">
-        <v>25.6968</v>
+        <v>27.776</v>
       </c>
       <c r="D133" t="n">
-        <v>52.9491</v>
+        <v>51.7239</v>
       </c>
       <c r="E133" t="n">
-        <v>34.744</v>
+        <v>36.8423</v>
       </c>
       <c r="F133" t="n">
-        <v>33.9358</v>
+        <v>36.755</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>34.2575</v>
+        <v>33.116</v>
       </c>
       <c r="C134" t="n">
-        <v>26.0774</v>
+        <v>28.1714</v>
       </c>
       <c r="D134" t="n">
-        <v>54.1817</v>
+        <v>52.9254</v>
       </c>
       <c r="E134" t="n">
-        <v>35.1891</v>
+        <v>37.3447</v>
       </c>
       <c r="F134" t="n">
-        <v>34.5628</v>
+        <v>37.6099</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>33.7924</v>
+        <v>33.2353</v>
       </c>
       <c r="C135" t="n">
-        <v>26.5256</v>
+        <v>28.6053</v>
       </c>
       <c r="D135" t="n">
-        <v>44.6069</v>
+        <v>43.2166</v>
       </c>
       <c r="E135" t="n">
-        <v>33.3872</v>
+        <v>34.7813</v>
       </c>
       <c r="F135" t="n">
-        <v>32.1842</v>
+        <v>34.9699</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>33.6404</v>
+        <v>33.0465</v>
       </c>
       <c r="C136" t="n">
-        <v>26.3746</v>
+        <v>28.0056</v>
       </c>
       <c r="D136" t="n">
-        <v>44.8912</v>
+        <v>43.8997</v>
       </c>
       <c r="E136" t="n">
-        <v>33.7023</v>
+        <v>35.1797</v>
       </c>
       <c r="F136" t="n">
-        <v>32.3764</v>
+        <v>35.1612</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>34.3924</v>
+        <v>33.4653</v>
       </c>
       <c r="C137" t="n">
-        <v>26.5615</v>
+        <v>27.8989</v>
       </c>
       <c r="D137" t="n">
-        <v>45.608</v>
+        <v>44.3218</v>
       </c>
       <c r="E137" t="n">
-        <v>34.0856</v>
+        <v>35.5831</v>
       </c>
       <c r="F137" t="n">
-        <v>32.4762</v>
+        <v>35.4118</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>38.9049</v>
+        <v>37.7928</v>
       </c>
       <c r="C138" t="n">
-        <v>26.6466</v>
+        <v>28.2686</v>
       </c>
       <c r="D138" t="n">
-        <v>46.6595</v>
+        <v>45.5392</v>
       </c>
       <c r="E138" t="n">
-        <v>34.47</v>
+        <v>35.9082</v>
       </c>
       <c r="F138" t="n">
-        <v>32.7511</v>
+        <v>35.7823</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>38.2825</v>
+        <v>37.776</v>
       </c>
       <c r="C139" t="n">
-        <v>26.8611</v>
+        <v>28.1272</v>
       </c>
       <c r="D139" t="n">
-        <v>46.9103</v>
+        <v>45.6901</v>
       </c>
       <c r="E139" t="n">
-        <v>34.8315</v>
+        <v>36.1475</v>
       </c>
       <c r="F139" t="n">
-        <v>33.0199</v>
+        <v>35.8418</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>38.9903</v>
+        <v>37.4607</v>
       </c>
       <c r="C140" t="n">
-        <v>27.0492</v>
+        <v>28.4009</v>
       </c>
       <c r="D140" t="n">
-        <v>47.7861</v>
+        <v>46.3467</v>
       </c>
       <c r="E140" t="n">
-        <v>34.9994</v>
+        <v>36.4651</v>
       </c>
       <c r="F140" t="n">
-        <v>33.376</v>
+        <v>36.0416</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>38.9702</v>
+        <v>37.8161</v>
       </c>
       <c r="C141" t="n">
-        <v>27.6366</v>
+        <v>28.6656</v>
       </c>
       <c r="D141" t="n">
-        <v>48.7645</v>
+        <v>47.2554</v>
       </c>
       <c r="E141" t="n">
-        <v>35.1841</v>
+        <v>36.8575</v>
       </c>
       <c r="F141" t="n">
-        <v>33.3736</v>
+        <v>36.4298</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>38.791</v>
+        <v>37.7976</v>
       </c>
       <c r="C142" t="n">
-        <v>27.325</v>
+        <v>28.8703</v>
       </c>
       <c r="D142" t="n">
-        <v>49.5713</v>
+        <v>48.0425</v>
       </c>
       <c r="E142" t="n">
-        <v>35.5095</v>
+        <v>37.0595</v>
       </c>
       <c r="F142" t="n">
-        <v>33.7636</v>
+        <v>36.6504</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>38.8487</v>
+        <v>38.0287</v>
       </c>
       <c r="C143" t="n">
-        <v>27.5807</v>
+        <v>29.4901</v>
       </c>
       <c r="D143" t="n">
-        <v>50.4823</v>
+        <v>49.5242</v>
       </c>
       <c r="E143" t="n">
-        <v>35.9519</v>
+        <v>38.1796</v>
       </c>
       <c r="F143" t="n">
-        <v>34.1616</v>
+        <v>37.6374</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Scattered successful looukp.xlsx
+++ b/gcc-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>3.58893</v>
+        <v>3.90509</v>
       </c>
       <c r="C2" t="n">
-        <v>3.53055</v>
+        <v>3.35075</v>
       </c>
       <c r="D2" t="n">
-        <v>7.61626</v>
+        <v>8.66661</v>
       </c>
       <c r="E2" t="n">
-        <v>4.12625</v>
+        <v>3.7934</v>
       </c>
       <c r="F2" t="n">
-        <v>3.88068</v>
+        <v>3.34815</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>3.37489</v>
+        <v>3.84714</v>
       </c>
       <c r="C3" t="n">
-        <v>3.38197</v>
+        <v>3.35313</v>
       </c>
       <c r="D3" t="n">
-        <v>8.09277</v>
+        <v>8.843109999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>3.99837</v>
+        <v>3.87773</v>
       </c>
       <c r="F3" t="n">
-        <v>4.19401</v>
+        <v>3.89461</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.4607</v>
+        <v>3.87438</v>
       </c>
       <c r="C4" t="n">
-        <v>3.39149</v>
+        <v>3.35991</v>
       </c>
       <c r="D4" t="n">
-        <v>9.137549999999999</v>
+        <v>9.82701</v>
       </c>
       <c r="E4" t="n">
-        <v>4.01004</v>
+        <v>3.6828</v>
       </c>
       <c r="F4" t="n">
-        <v>4.23298</v>
+        <v>3.36899</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.52728</v>
+        <v>3.8776</v>
       </c>
       <c r="C5" t="n">
-        <v>3.51939</v>
+        <v>3.35483</v>
       </c>
       <c r="D5" t="n">
-        <v>9.79182</v>
+        <v>10.2088</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1295</v>
+        <v>3.84482</v>
       </c>
       <c r="F5" t="n">
-        <v>3.96462</v>
+        <v>3.68702</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>3.27265</v>
+        <v>3.67634</v>
       </c>
       <c r="C6" t="n">
-        <v>3.35663</v>
+        <v>3.18574</v>
       </c>
       <c r="D6" t="n">
-        <v>10.4105</v>
+        <v>10.7822</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8728</v>
+        <v>4.148</v>
       </c>
       <c r="F6" t="n">
-        <v>4.28618</v>
+        <v>3.72442</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>3.55342</v>
+        <v>3.68283</v>
       </c>
       <c r="C7" t="n">
-        <v>3.60927</v>
+        <v>3.2129</v>
       </c>
       <c r="D7" t="n">
-        <v>6.69397</v>
+        <v>7.75753</v>
       </c>
       <c r="E7" t="n">
-        <v>4.89252</v>
+        <v>3.89476</v>
       </c>
       <c r="F7" t="n">
-        <v>4.15029</v>
+        <v>3.76634</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>3.53302</v>
+        <v>3.70478</v>
       </c>
       <c r="C8" t="n">
-        <v>4.24938</v>
+        <v>3.79962</v>
       </c>
       <c r="D8" t="n">
-        <v>6.93067</v>
+        <v>7.91826</v>
       </c>
       <c r="E8" t="n">
-        <v>4.88127</v>
+        <v>3.87704</v>
       </c>
       <c r="F8" t="n">
-        <v>4.19263</v>
+        <v>3.74217</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>3.56209</v>
+        <v>3.73975</v>
       </c>
       <c r="C9" t="n">
-        <v>4.27497</v>
+        <v>3.80895</v>
       </c>
       <c r="D9" t="n">
-        <v>7.46607</v>
+        <v>8.296010000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>4.96439</v>
+        <v>3.94177</v>
       </c>
       <c r="F9" t="n">
-        <v>4.20357</v>
+        <v>3.75715</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>4.02761</v>
+        <v>4.4719</v>
       </c>
       <c r="C10" t="n">
-        <v>4.31218</v>
+        <v>3.83966</v>
       </c>
       <c r="D10" t="n">
-        <v>7.91595</v>
+        <v>8.59634</v>
       </c>
       <c r="E10" t="n">
-        <v>5.00567</v>
+        <v>4.13533</v>
       </c>
       <c r="F10" t="n">
-        <v>4.23354</v>
+        <v>3.79055</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>4.30363</v>
+        <v>4.48247</v>
       </c>
       <c r="C11" t="n">
-        <v>4.21726</v>
+        <v>3.86231</v>
       </c>
       <c r="D11" t="n">
-        <v>8.488160000000001</v>
+        <v>9.11744</v>
       </c>
       <c r="E11" t="n">
-        <v>5.0352</v>
+        <v>4.19511</v>
       </c>
       <c r="F11" t="n">
-        <v>4.25901</v>
+        <v>3.65487</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>4.30215</v>
+        <v>4.33319</v>
       </c>
       <c r="C12" t="n">
-        <v>4.2297</v>
+        <v>3.71146</v>
       </c>
       <c r="D12" t="n">
-        <v>8.99924</v>
+        <v>9.397259999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>5.11261</v>
+        <v>4.38476</v>
       </c>
       <c r="F12" t="n">
-        <v>4.29425</v>
+        <v>3.80852</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>4.91917</v>
+        <v>4.32644</v>
       </c>
       <c r="C13" t="n">
-        <v>4.2946</v>
+        <v>3.82435</v>
       </c>
       <c r="D13" t="n">
-        <v>9.55865</v>
+        <v>9.868690000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>5.12443</v>
+        <v>4.21669</v>
       </c>
       <c r="F13" t="n">
-        <v>4.31663</v>
+        <v>3.86459</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>5.0293</v>
+        <v>4.4944</v>
       </c>
       <c r="C14" t="n">
-        <v>4.42564</v>
+        <v>3.91279</v>
       </c>
       <c r="D14" t="n">
-        <v>10.0055</v>
+        <v>10.2274</v>
       </c>
       <c r="E14" t="n">
-        <v>5.13182</v>
+        <v>4.35478</v>
       </c>
       <c r="F14" t="n">
-        <v>4.36553</v>
+        <v>3.87515</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>5.04103</v>
+        <v>4.49824</v>
       </c>
       <c r="C15" t="n">
-        <v>4.40784</v>
+        <v>3.9253</v>
       </c>
       <c r="D15" t="n">
-        <v>10.5549</v>
+        <v>10.6931</v>
       </c>
       <c r="E15" t="n">
-        <v>5.15755</v>
+        <v>4.28601</v>
       </c>
       <c r="F15" t="n">
-        <v>4.39985</v>
+        <v>3.90261</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>4.2459</v>
+        <v>4.51184</v>
       </c>
       <c r="C16" t="n">
-        <v>4.42733</v>
+        <v>3.96427</v>
       </c>
       <c r="D16" t="n">
-        <v>11.0891</v>
+        <v>11.1846</v>
       </c>
       <c r="E16" t="n">
-        <v>5.20613</v>
+        <v>4.13261</v>
       </c>
       <c r="F16" t="n">
-        <v>4.41031</v>
+        <v>3.89792</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>4.46288</v>
+        <v>4.52129</v>
       </c>
       <c r="C17" t="n">
-        <v>4.4033</v>
+        <v>4.00347</v>
       </c>
       <c r="D17" t="n">
-        <v>11.5151</v>
+        <v>11.5829</v>
       </c>
       <c r="E17" t="n">
-        <v>5.30445</v>
+        <v>4.27032</v>
       </c>
       <c r="F17" t="n">
-        <v>4.64895</v>
+        <v>3.94938</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>5.07793</v>
+        <v>4.52906</v>
       </c>
       <c r="C18" t="n">
-        <v>4.58155</v>
+        <v>4.04154</v>
       </c>
       <c r="D18" t="n">
-        <v>11.9752</v>
+        <v>12.2105</v>
       </c>
       <c r="E18" t="n">
-        <v>5.30113</v>
+        <v>4.27363</v>
       </c>
       <c r="F18" t="n">
-        <v>4.47105</v>
+        <v>3.94009</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>5.10503</v>
+        <v>4.54403</v>
       </c>
       <c r="C19" t="n">
-        <v>4.59194</v>
+        <v>4.08997</v>
       </c>
       <c r="D19" t="n">
-        <v>12.4984</v>
+        <v>12.5764</v>
       </c>
       <c r="E19" t="n">
-        <v>5.30097</v>
+        <v>4.39622</v>
       </c>
       <c r="F19" t="n">
-        <v>4.50672</v>
+        <v>4.12869</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>5.08228</v>
+        <v>4.41148</v>
       </c>
       <c r="C20" t="n">
-        <v>4.64438</v>
+        <v>4.09206</v>
       </c>
       <c r="D20" t="n">
-        <v>12.8002</v>
+        <v>13.0081</v>
       </c>
       <c r="E20" t="n">
-        <v>5.48888</v>
+        <v>4.55332</v>
       </c>
       <c r="F20" t="n">
-        <v>4.563</v>
+        <v>4.4442</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>5.09661</v>
+        <v>5.29184</v>
       </c>
       <c r="C21" t="n">
-        <v>4.70995</v>
+        <v>4.20644</v>
       </c>
       <c r="D21" t="n">
-        <v>9.2004</v>
+        <v>9.38439</v>
       </c>
       <c r="E21" t="n">
-        <v>5.06019</v>
+        <v>4.57882</v>
       </c>
       <c r="F21" t="n">
-        <v>5.25154</v>
+        <v>4.30378</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>5.15151</v>
+        <v>5.35667</v>
       </c>
       <c r="C22" t="n">
-        <v>4.23563</v>
+        <v>3.91929</v>
       </c>
       <c r="D22" t="n">
-        <v>9.443049999999999</v>
+        <v>9.69003</v>
       </c>
       <c r="E22" t="n">
-        <v>4.93479</v>
+        <v>4.59837</v>
       </c>
       <c r="F22" t="n">
-        <v>5.2719</v>
+        <v>4.35105</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>5.20313</v>
+        <v>5.23042</v>
       </c>
       <c r="C23" t="n">
-        <v>4.25435</v>
+        <v>3.8956</v>
       </c>
       <c r="D23" t="n">
-        <v>9.80387</v>
+        <v>9.96552</v>
       </c>
       <c r="E23" t="n">
-        <v>5.03759</v>
+        <v>4.63359</v>
       </c>
       <c r="F23" t="n">
-        <v>5.24815</v>
+        <v>4.52739</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>5.06855</v>
+        <v>5.48735</v>
       </c>
       <c r="C24" t="n">
-        <v>4.26024</v>
+        <v>3.90409</v>
       </c>
       <c r="D24" t="n">
-        <v>10.1434</v>
+        <v>10.2493</v>
       </c>
       <c r="E24" t="n">
-        <v>4.95275</v>
+        <v>4.69974</v>
       </c>
       <c r="F24" t="n">
-        <v>5.10458</v>
+        <v>4.41419</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>5.01933</v>
+        <v>5.22596</v>
       </c>
       <c r="C25" t="n">
-        <v>4.25993</v>
+        <v>3.83592</v>
       </c>
       <c r="D25" t="n">
-        <v>10.5295</v>
+        <v>10.7117</v>
       </c>
       <c r="E25" t="n">
-        <v>4.95866</v>
+        <v>4.56743</v>
       </c>
       <c r="F25" t="n">
-        <v>5.35962</v>
+        <v>4.56029</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>5.06811</v>
+        <v>5.42876</v>
       </c>
       <c r="C26" t="n">
-        <v>4.24461</v>
+        <v>3.97898</v>
       </c>
       <c r="D26" t="n">
-        <v>10.8853</v>
+        <v>10.9838</v>
       </c>
       <c r="E26" t="n">
-        <v>5.06813</v>
+        <v>4.74038</v>
       </c>
       <c r="F26" t="n">
-        <v>5.00131</v>
+        <v>4.48075</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>5.07872</v>
+        <v>5.25828</v>
       </c>
       <c r="C27" t="n">
-        <v>4.30658</v>
+        <v>3.86393</v>
       </c>
       <c r="D27" t="n">
-        <v>11.3526</v>
+        <v>11.4233</v>
       </c>
       <c r="E27" t="n">
-        <v>5.05615</v>
+        <v>4.69991</v>
       </c>
       <c r="F27" t="n">
-        <v>5.03998</v>
+        <v>4.52198</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>5.08467</v>
+        <v>5.39005</v>
       </c>
       <c r="C28" t="n">
-        <v>4.33997</v>
+        <v>3.96799</v>
       </c>
       <c r="D28" t="n">
-        <v>11.7451</v>
+        <v>11.8952</v>
       </c>
       <c r="E28" t="n">
-        <v>5.08181</v>
+        <v>4.76776</v>
       </c>
       <c r="F28" t="n">
-        <v>5.06706</v>
+        <v>4.56309</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>4.7654</v>
+        <v>5.08484</v>
       </c>
       <c r="C29" t="n">
-        <v>4.26657</v>
+        <v>4.01096</v>
       </c>
       <c r="D29" t="n">
-        <v>12.2247</v>
+        <v>12.3489</v>
       </c>
       <c r="E29" t="n">
-        <v>5.12235</v>
+        <v>4.76068</v>
       </c>
       <c r="F29" t="n">
-        <v>5.06282</v>
+        <v>4.58601</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>4.61452</v>
+        <v>5.43964</v>
       </c>
       <c r="C30" t="n">
-        <v>4.39543</v>
+        <v>4.08121</v>
       </c>
       <c r="D30" t="n">
-        <v>12.5222</v>
+        <v>12.6877</v>
       </c>
       <c r="E30" t="n">
-        <v>5.25328</v>
+        <v>4.77439</v>
       </c>
       <c r="F30" t="n">
-        <v>5.25431</v>
+        <v>4.59459</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>4.61782</v>
+        <v>5.25696</v>
       </c>
       <c r="C31" t="n">
-        <v>4.4491</v>
+        <v>3.69608</v>
       </c>
       <c r="D31" t="n">
-        <v>12.9787</v>
+        <v>13.1568</v>
       </c>
       <c r="E31" t="n">
-        <v>5.28137</v>
+        <v>4.86926</v>
       </c>
       <c r="F31" t="n">
-        <v>5.38462</v>
+        <v>4.62944</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.67308</v>
+        <v>5.49767</v>
       </c>
       <c r="C32" t="n">
-        <v>4.50841</v>
+        <v>4.18763</v>
       </c>
       <c r="D32" t="n">
-        <v>13.3164</v>
+        <v>13.5155</v>
       </c>
       <c r="E32" t="n">
-        <v>5.3377</v>
+        <v>4.843</v>
       </c>
       <c r="F32" t="n">
-        <v>5.62186</v>
+        <v>4.66331</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.47629</v>
+        <v>5.30121</v>
       </c>
       <c r="C33" t="n">
-        <v>4.23008</v>
+        <v>4.12452</v>
       </c>
       <c r="D33" t="n">
-        <v>13.7417</v>
+        <v>13.8934</v>
       </c>
       <c r="E33" t="n">
-        <v>5.34856</v>
+        <v>4.96973</v>
       </c>
       <c r="F33" t="n">
-        <v>5.23824</v>
+        <v>4.71408</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>4.70235</v>
+        <v>5.32008</v>
       </c>
       <c r="C34" t="n">
-        <v>4.59689</v>
+        <v>4.16115</v>
       </c>
       <c r="D34" t="n">
-        <v>14.0477</v>
+        <v>14.1964</v>
       </c>
       <c r="E34" t="n">
-        <v>5.30182</v>
+        <v>4.39297</v>
       </c>
       <c r="F34" t="n">
-        <v>5.50567</v>
+        <v>4.44812</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>4.67573</v>
+        <v>5.04831</v>
       </c>
       <c r="C35" t="n">
-        <v>4.65504</v>
+        <v>3.95539</v>
       </c>
       <c r="D35" t="n">
-        <v>9.875830000000001</v>
+        <v>10.1614</v>
       </c>
       <c r="E35" t="n">
-        <v>5.06863</v>
+        <v>4.61514</v>
       </c>
       <c r="F35" t="n">
-        <v>5.08596</v>
+        <v>4.51665</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>4.74438</v>
+        <v>5.19238</v>
       </c>
       <c r="C36" t="n">
-        <v>4.66937</v>
+        <v>4.41639</v>
       </c>
       <c r="D36" t="n">
-        <v>10.0668</v>
+        <v>10.3523</v>
       </c>
       <c r="E36" t="n">
-        <v>4.96157</v>
+        <v>4.69933</v>
       </c>
       <c r="F36" t="n">
-        <v>5.08978</v>
+        <v>4.53529</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>5.45365</v>
+        <v>5.66011</v>
       </c>
       <c r="C37" t="n">
-        <v>4.27331</v>
+        <v>4.12177</v>
       </c>
       <c r="D37" t="n">
-        <v>10.2582</v>
+        <v>10.7775</v>
       </c>
       <c r="E37" t="n">
-        <v>4.98472</v>
+        <v>4.72333</v>
       </c>
       <c r="F37" t="n">
-        <v>5.13099</v>
+        <v>4.52714</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>5.1939</v>
+        <v>5.17582</v>
       </c>
       <c r="C38" t="n">
-        <v>4.27383</v>
+        <v>3.85701</v>
       </c>
       <c r="D38" t="n">
-        <v>10.5375</v>
+        <v>11.0283</v>
       </c>
       <c r="E38" t="n">
-        <v>5.10884</v>
+        <v>4.48752</v>
       </c>
       <c r="F38" t="n">
-        <v>5.15058</v>
+        <v>4.54634</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>5.06433</v>
+        <v>5.33419</v>
       </c>
       <c r="C39" t="n">
-        <v>4.57189</v>
+        <v>4.08597</v>
       </c>
       <c r="D39" t="n">
-        <v>10.8617</v>
+        <v>11.4289</v>
       </c>
       <c r="E39" t="n">
-        <v>5.36613</v>
+        <v>4.55153</v>
       </c>
       <c r="F39" t="n">
-        <v>5.07581</v>
+        <v>4.59287</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>5.08821</v>
+        <v>5.53882</v>
       </c>
       <c r="C40" t="n">
-        <v>4.49319</v>
+        <v>4.09264</v>
       </c>
       <c r="D40" t="n">
-        <v>11.2607</v>
+        <v>11.864</v>
       </c>
       <c r="E40" t="n">
-        <v>5.35861</v>
+        <v>4.58428</v>
       </c>
       <c r="F40" t="n">
-        <v>5.11386</v>
+        <v>4.64956</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>4.64944</v>
+        <v>5.54684</v>
       </c>
       <c r="C41" t="n">
-        <v>4.58794</v>
+        <v>4.23513</v>
       </c>
       <c r="D41" t="n">
-        <v>11.6018</v>
+        <v>12.2839</v>
       </c>
       <c r="E41" t="n">
-        <v>5.28589</v>
+        <v>4.58879</v>
       </c>
       <c r="F41" t="n">
-        <v>5.3028</v>
+        <v>4.67857</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>5.13985</v>
+        <v>5.2428</v>
       </c>
       <c r="C42" t="n">
-        <v>4.57894</v>
+        <v>4.18251</v>
       </c>
       <c r="D42" t="n">
-        <v>11.9969</v>
+        <v>12.7811</v>
       </c>
       <c r="E42" t="n">
-        <v>5.40815</v>
+        <v>4.88204</v>
       </c>
       <c r="F42" t="n">
-        <v>5.20689</v>
+        <v>4.78046</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>5.10269</v>
+        <v>5.23969</v>
       </c>
       <c r="C43" t="n">
-        <v>4.66823</v>
+        <v>4.2206</v>
       </c>
       <c r="D43" t="n">
-        <v>12.3507</v>
+        <v>13.0773</v>
       </c>
       <c r="E43" t="n">
-        <v>5.18441</v>
+        <v>4.94387</v>
       </c>
       <c r="F43" t="n">
-        <v>5.24151</v>
+        <v>4.80618</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>5.14051</v>
+        <v>5.58357</v>
       </c>
       <c r="C44" t="n">
-        <v>4.60707</v>
+        <v>4.18379</v>
       </c>
       <c r="D44" t="n">
-        <v>12.7717</v>
+        <v>13.4815</v>
       </c>
       <c r="E44" t="n">
-        <v>5.21281</v>
+        <v>4.92751</v>
       </c>
       <c r="F44" t="n">
-        <v>5.405</v>
+        <v>4.8574</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>5.14858</v>
+        <v>5.61827</v>
       </c>
       <c r="C45" t="n">
-        <v>4.60835</v>
+        <v>4.2781</v>
       </c>
       <c r="D45" t="n">
-        <v>13.1614</v>
+        <v>13.8048</v>
       </c>
       <c r="E45" t="n">
-        <v>5.53181</v>
+        <v>4.97938</v>
       </c>
       <c r="F45" t="n">
-        <v>5.43659</v>
+        <v>4.88855</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>5.15178</v>
+        <v>5.06617</v>
       </c>
       <c r="C46" t="n">
-        <v>4.73277</v>
+        <v>4.364</v>
       </c>
       <c r="D46" t="n">
-        <v>13.5076</v>
+        <v>14.1755</v>
       </c>
       <c r="E46" t="n">
-        <v>5.5477</v>
+        <v>5.11248</v>
       </c>
       <c r="F46" t="n">
-        <v>5.50849</v>
+        <v>4.99626</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>5.15756</v>
+        <v>5.63212</v>
       </c>
       <c r="C47" t="n">
-        <v>4.78984</v>
+        <v>4.3927</v>
       </c>
       <c r="D47" t="n">
-        <v>13.8443</v>
+        <v>14.5194</v>
       </c>
       <c r="E47" t="n">
-        <v>5.63153</v>
+        <v>5.22703</v>
       </c>
       <c r="F47" t="n">
-        <v>5.89287</v>
+        <v>5.46411</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.08283</v>
+        <v>5.12562</v>
       </c>
       <c r="C48" t="n">
-        <v>4.98701</v>
+        <v>4.49455</v>
       </c>
       <c r="D48" t="n">
-        <v>14.2764</v>
+        <v>15.1743</v>
       </c>
       <c r="E48" t="n">
-        <v>5.93193</v>
+        <v>4.72906</v>
       </c>
       <c r="F48" t="n">
-        <v>6.22679</v>
+        <v>5.76416</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>5.2889</v>
+        <v>5.14733</v>
       </c>
       <c r="C49" t="n">
-        <v>5.11032</v>
+        <v>4.61838</v>
       </c>
       <c r="D49" t="n">
-        <v>14.9169</v>
+        <v>16.1798</v>
       </c>
       <c r="E49" t="n">
-        <v>6.33561</v>
+        <v>4.64999</v>
       </c>
       <c r="F49" t="n">
-        <v>6.61047</v>
+        <v>5.88343</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>4.98768</v>
+        <v>5.44197</v>
       </c>
       <c r="C50" t="n">
-        <v>5.10342</v>
+        <v>4.36976</v>
       </c>
       <c r="D50" t="n">
-        <v>11.8941</v>
+        <v>13.4397</v>
       </c>
       <c r="E50" t="n">
-        <v>5.1654</v>
+        <v>4.64241</v>
       </c>
       <c r="F50" t="n">
-        <v>6.28196</v>
+        <v>5.96754</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>6.5029</v>
+        <v>5.64719</v>
       </c>
       <c r="C51" t="n">
-        <v>4.49154</v>
+        <v>4.06271</v>
       </c>
       <c r="D51" t="n">
-        <v>13.0116</v>
+        <v>14.3984</v>
       </c>
       <c r="E51" t="n">
-        <v>5.14908</v>
+        <v>4.81027</v>
       </c>
       <c r="F51" t="n">
-        <v>5.97984</v>
+        <v>6.29167</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>6.27929</v>
+        <v>6.62846</v>
       </c>
       <c r="C52" t="n">
-        <v>4.41755</v>
+        <v>4.24308</v>
       </c>
       <c r="D52" t="n">
-        <v>14.4743</v>
+        <v>15.6099</v>
       </c>
       <c r="E52" t="n">
-        <v>5.21222</v>
+        <v>4.66287</v>
       </c>
       <c r="F52" t="n">
-        <v>6.87509</v>
+        <v>6.17688</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>5.25433</v>
+        <v>5.62558</v>
       </c>
       <c r="C53" t="n">
-        <v>4.51392</v>
+        <v>4.00741</v>
       </c>
       <c r="D53" t="n">
-        <v>14.9395</v>
+        <v>16.8134</v>
       </c>
       <c r="E53" t="n">
-        <v>5.23548</v>
+        <v>4.94253</v>
       </c>
       <c r="F53" t="n">
-        <v>6.56636</v>
+        <v>5.22489</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>5.25644</v>
+        <v>5.61624</v>
       </c>
       <c r="C54" t="n">
-        <v>4.53545</v>
+        <v>4.16064</v>
       </c>
       <c r="D54" t="n">
-        <v>16.0288</v>
+        <v>17.7963</v>
       </c>
       <c r="E54" t="n">
-        <v>5.28468</v>
+        <v>4.88271</v>
       </c>
       <c r="F54" t="n">
-        <v>6.45506</v>
+        <v>5.36369</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>5.58463</v>
+        <v>5.65374</v>
       </c>
       <c r="C55" t="n">
-        <v>4.51809</v>
+        <v>4.02583</v>
       </c>
       <c r="D55" t="n">
-        <v>16.5355</v>
+        <v>18.527</v>
       </c>
       <c r="E55" t="n">
-        <v>5.35363</v>
+        <v>5.09265</v>
       </c>
       <c r="F55" t="n">
-        <v>5.78565</v>
+        <v>5.30363</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>5.27797</v>
+        <v>5.65888</v>
       </c>
       <c r="C56" t="n">
-        <v>4.59433</v>
+        <v>4.06456</v>
       </c>
       <c r="D56" t="n">
-        <v>18.1904</v>
+        <v>19.6125</v>
       </c>
       <c r="E56" t="n">
-        <v>5.33485</v>
+        <v>5.00309</v>
       </c>
       <c r="F56" t="n">
-        <v>6.30377</v>
+        <v>5.34074</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>5.29094</v>
+        <v>5.73831</v>
       </c>
       <c r="C57" t="n">
-        <v>4.69263</v>
+        <v>4.18658</v>
       </c>
       <c r="D57" t="n">
-        <v>18.6927</v>
+        <v>19.9846</v>
       </c>
       <c r="E57" t="n">
-        <v>5.40805</v>
+        <v>5.03706</v>
       </c>
       <c r="F57" t="n">
-        <v>6.92973</v>
+        <v>5.5358</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>5.30334</v>
+        <v>5.52613</v>
       </c>
       <c r="C58" t="n">
-        <v>4.72073</v>
+        <v>4.27867</v>
       </c>
       <c r="D58" t="n">
-        <v>18.6344</v>
+        <v>19.3756</v>
       </c>
       <c r="E58" t="n">
-        <v>5.57348</v>
+        <v>4.96668</v>
       </c>
       <c r="F58" t="n">
-        <v>6.05929</v>
+        <v>5.56004</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>5.31131</v>
+        <v>5.50933</v>
       </c>
       <c r="C59" t="n">
-        <v>5.00524</v>
+        <v>4.27054</v>
       </c>
       <c r="D59" t="n">
-        <v>18.449</v>
+        <v>20.5825</v>
       </c>
       <c r="E59" t="n">
-        <v>5.6181</v>
+        <v>5.14495</v>
       </c>
       <c r="F59" t="n">
-        <v>6.8545</v>
+        <v>5.65196</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>5.33622</v>
+        <v>5.79531</v>
       </c>
       <c r="C60" t="n">
-        <v>5.05211</v>
+        <v>4.36982</v>
       </c>
       <c r="D60" t="n">
-        <v>19.4583</v>
+        <v>20.3058</v>
       </c>
       <c r="E60" t="n">
-        <v>5.68979</v>
+        <v>5.25026</v>
       </c>
       <c r="F60" t="n">
-        <v>6.48326</v>
+        <v>6.70642</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>5.35666</v>
+        <v>5.58302</v>
       </c>
       <c r="C61" t="n">
-        <v>5.25866</v>
+        <v>4.49213</v>
       </c>
       <c r="D61" t="n">
-        <v>20.4653</v>
+        <v>20.9702</v>
       </c>
       <c r="E61" t="n">
-        <v>6.12992</v>
+        <v>5.55028</v>
       </c>
       <c r="F61" t="n">
-        <v>7.73245</v>
+        <v>6.87826</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.43407</v>
+        <v>5.59311</v>
       </c>
       <c r="C62" t="n">
-        <v>5.20864</v>
+        <v>4.37863</v>
       </c>
       <c r="D62" t="n">
-        <v>20.3688</v>
+        <v>21.1239</v>
       </c>
       <c r="E62" t="n">
-        <v>6.35906</v>
+        <v>5.7802</v>
       </c>
       <c r="F62" t="n">
-        <v>7.51289</v>
+        <v>7.25568</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>5.49232</v>
+        <v>5.89582</v>
       </c>
       <c r="C63" t="n">
-        <v>5.34762</v>
+        <v>4.75607</v>
       </c>
       <c r="D63" t="n">
-        <v>20.6786</v>
+        <v>21.5873</v>
       </c>
       <c r="E63" t="n">
-        <v>6.70267</v>
+        <v>5.83631</v>
       </c>
       <c r="F63" t="n">
-        <v>7.76597</v>
+        <v>6.02107</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>5.71661</v>
+        <v>5.94757</v>
       </c>
       <c r="C64" t="n">
-        <v>5.36338</v>
+        <v>4.71082</v>
       </c>
       <c r="D64" t="n">
-        <v>15.3689</v>
+        <v>14.151</v>
       </c>
       <c r="E64" t="n">
-        <v>5.70506</v>
+        <v>6.07492</v>
       </c>
       <c r="F64" t="n">
-        <v>6.56328</v>
+        <v>6.39154</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>6.00649</v>
+        <v>6.19104</v>
       </c>
       <c r="C65" t="n">
-        <v>6.88946</v>
+        <v>8.585699999999999</v>
       </c>
       <c r="D65" t="n">
-        <v>14.6297</v>
+        <v>14.7651</v>
       </c>
       <c r="E65" t="n">
-        <v>5.74484</v>
+        <v>5.18576</v>
       </c>
       <c r="F65" t="n">
-        <v>6.69122</v>
+        <v>6.28139</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>6.4303</v>
+        <v>6.69755</v>
       </c>
       <c r="C66" t="n">
-        <v>7.00243</v>
+        <v>8.697649999999999</v>
       </c>
       <c r="D66" t="n">
-        <v>16.2594</v>
+        <v>15.9628</v>
       </c>
       <c r="E66" t="n">
-        <v>5.75157</v>
+        <v>5.41674</v>
       </c>
       <c r="F66" t="n">
-        <v>6.85766</v>
+        <v>6.45473</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>8.11157</v>
+        <v>10.5629</v>
       </c>
       <c r="C67" t="n">
-        <v>7.13466</v>
+        <v>8.6785</v>
       </c>
       <c r="D67" t="n">
-        <v>17.2902</v>
+        <v>17.6595</v>
       </c>
       <c r="E67" t="n">
-        <v>5.83196</v>
+        <v>5.43754</v>
       </c>
       <c r="F67" t="n">
-        <v>7.03967</v>
+        <v>6.56901</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>11.1275</v>
+        <v>10.6696</v>
       </c>
       <c r="C68" t="n">
-        <v>10.2413</v>
+        <v>9.10036</v>
       </c>
       <c r="D68" t="n">
-        <v>18.5407</v>
+        <v>18.7258</v>
       </c>
       <c r="E68" t="n">
-        <v>6.08765</v>
+        <v>6.84041</v>
       </c>
       <c r="F68" t="n">
-        <v>7.09922</v>
+        <v>6.67619</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>7.3508</v>
+        <v>12.1813</v>
       </c>
       <c r="C69" t="n">
-        <v>6.39731</v>
+        <v>10.2735</v>
       </c>
       <c r="D69" t="n">
-        <v>18.8397</v>
+        <v>18.8819</v>
       </c>
       <c r="E69" t="n">
-        <v>6.00196</v>
+        <v>6.86774</v>
       </c>
       <c r="F69" t="n">
-        <v>7.21038</v>
+        <v>6.75742</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>11.0957</v>
+        <v>11.9784</v>
       </c>
       <c r="C70" t="n">
-        <v>10.1285</v>
+        <v>10.1574</v>
       </c>
       <c r="D70" t="n">
-        <v>19.2796</v>
+        <v>18.5216</v>
       </c>
       <c r="E70" t="n">
-        <v>5.81738</v>
+        <v>7.09637</v>
       </c>
       <c r="F70" t="n">
-        <v>7.36416</v>
+        <v>6.73861</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>12.1191</v>
+        <v>10.2506</v>
       </c>
       <c r="C71" t="n">
-        <v>11.2053</v>
+        <v>8.76275</v>
       </c>
       <c r="D71" t="n">
-        <v>19.0539</v>
+        <v>20.1956</v>
       </c>
       <c r="E71" t="n">
-        <v>7.4007</v>
+        <v>7.76882</v>
       </c>
       <c r="F71" t="n">
-        <v>6.87095</v>
+        <v>6.54153</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>13.2606</v>
+        <v>12.0729</v>
       </c>
       <c r="C72" t="n">
-        <v>12.2498</v>
+        <v>10.3555</v>
       </c>
       <c r="D72" t="n">
-        <v>19.3516</v>
+        <v>19.9214</v>
       </c>
       <c r="E72" t="n">
-        <v>7.61431</v>
+        <v>8.080819999999999</v>
       </c>
       <c r="F72" t="n">
-        <v>7.021</v>
+        <v>6.68188</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>8.623010000000001</v>
+        <v>11.0873</v>
       </c>
       <c r="C73" t="n">
-        <v>7.60497</v>
+        <v>9.23582</v>
       </c>
       <c r="D73" t="n">
-        <v>19.8024</v>
+        <v>20.7092</v>
       </c>
       <c r="E73" t="n">
-        <v>7.77723</v>
+        <v>8.313129999999999</v>
       </c>
       <c r="F73" t="n">
-        <v>7.22926</v>
+        <v>6.97615</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>13.6728</v>
+        <v>12.5118</v>
       </c>
       <c r="C74" t="n">
-        <v>12.501</v>
+        <v>10.7361</v>
       </c>
       <c r="D74" t="n">
-        <v>21.2114</v>
+        <v>20.6331</v>
       </c>
       <c r="E74" t="n">
-        <v>10.032</v>
+        <v>8.849</v>
       </c>
       <c r="F74" t="n">
-        <v>7.54534</v>
+        <v>7.20568</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>13.7066</v>
+        <v>13.1835</v>
       </c>
       <c r="C75" t="n">
-        <v>12.538</v>
+        <v>11.3269</v>
       </c>
       <c r="D75" t="n">
-        <v>21.548</v>
+        <v>21.1881</v>
       </c>
       <c r="E75" t="n">
-        <v>10.3514</v>
+        <v>9.20332</v>
       </c>
       <c r="F75" t="n">
-        <v>7.98021</v>
+        <v>7.471</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>13.8083</v>
+        <v>13.517</v>
       </c>
       <c r="C76" t="n">
-        <v>12.5908</v>
+        <v>11.6629</v>
       </c>
       <c r="D76" t="n">
-        <v>21.1429</v>
+        <v>21.4851</v>
       </c>
       <c r="E76" t="n">
-        <v>10.2382</v>
+        <v>8.832240000000001</v>
       </c>
       <c r="F76" t="n">
-        <v>8.18618</v>
+        <v>7.80917</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>13.7986</v>
+        <v>13.4397</v>
       </c>
       <c r="C77" t="n">
-        <v>12.4391</v>
+        <v>11.2222</v>
       </c>
       <c r="D77" t="n">
-        <v>22.0836</v>
+        <v>21.8738</v>
       </c>
       <c r="E77" t="n">
-        <v>10.5633</v>
+        <v>10.6513</v>
       </c>
       <c r="F77" t="n">
-        <v>10.572</v>
+        <v>12.4574</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>13.1485</v>
+        <v>11.4275</v>
       </c>
       <c r="C78" t="n">
-        <v>12.099</v>
+        <v>9.39184</v>
       </c>
       <c r="D78" t="n">
-        <v>21.5979</v>
+        <v>21.8946</v>
       </c>
       <c r="E78" t="n">
-        <v>11.0482</v>
+        <v>10.6899</v>
       </c>
       <c r="F78" t="n">
-        <v>14.475</v>
+        <v>12.3973</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>13.6914</v>
+        <v>11.7053</v>
       </c>
       <c r="C79" t="n">
-        <v>15.4678</v>
+        <v>14.6613</v>
       </c>
       <c r="D79" t="n">
-        <v>22.2931</v>
+        <v>23.0037</v>
       </c>
       <c r="E79" t="n">
-        <v>11.4215</v>
+        <v>11.1815</v>
       </c>
       <c r="F79" t="n">
-        <v>13.1524</v>
+        <v>12.1906</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>13.1139</v>
+        <v>11.7174</v>
       </c>
       <c r="C80" t="n">
-        <v>16.0933</v>
+        <v>15.8581</v>
       </c>
       <c r="D80" t="n">
-        <v>22.7332</v>
+        <v>25.0984</v>
       </c>
       <c r="E80" t="n">
-        <v>11.667</v>
+        <v>11.8889</v>
       </c>
       <c r="F80" t="n">
-        <v>14.4246</v>
+        <v>12.3413</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>17.2725</v>
+        <v>17.8975</v>
       </c>
       <c r="C81" t="n">
-        <v>16.0406</v>
+        <v>15.6467</v>
       </c>
       <c r="D81" t="n">
-        <v>24.0714</v>
+        <v>25.6304</v>
       </c>
       <c r="E81" t="n">
-        <v>11.8873</v>
+        <v>12.1843</v>
       </c>
       <c r="F81" t="n">
-        <v>14.5155</v>
+        <v>12.4298</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>17.2952</v>
+        <v>17.9706</v>
       </c>
       <c r="C82" t="n">
-        <v>16.0315</v>
+        <v>15.7374</v>
       </c>
       <c r="D82" t="n">
-        <v>24.66</v>
+        <v>25.7187</v>
       </c>
       <c r="E82" t="n">
-        <v>12.1691</v>
+        <v>11.7412</v>
       </c>
       <c r="F82" t="n">
-        <v>14.4619</v>
+        <v>12.6109</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>17.4211</v>
+        <v>18.1336</v>
       </c>
       <c r="C83" t="n">
-        <v>16.1323</v>
+        <v>15.8985</v>
       </c>
       <c r="D83" t="n">
-        <v>25.7278</v>
+        <v>27.0328</v>
       </c>
       <c r="E83" t="n">
-        <v>12.4044</v>
+        <v>11.8787</v>
       </c>
       <c r="F83" t="n">
-        <v>14.54</v>
+        <v>12.4795</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>17.4477</v>
+        <v>18.1939</v>
       </c>
       <c r="C84" t="n">
-        <v>16.1574</v>
+        <v>15.962</v>
       </c>
       <c r="D84" t="n">
-        <v>26.6896</v>
+        <v>28.775</v>
       </c>
       <c r="E84" t="n">
-        <v>12.6477</v>
+        <v>12.4631</v>
       </c>
       <c r="F84" t="n">
-        <v>14.6582</v>
+        <v>13.0542</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>17.4814</v>
+        <v>18.4644</v>
       </c>
       <c r="C85" t="n">
-        <v>16.2021</v>
+        <v>16.3399</v>
       </c>
       <c r="D85" t="n">
-        <v>28.0459</v>
+        <v>29.4058</v>
       </c>
       <c r="E85" t="n">
-        <v>12.8221</v>
+        <v>12.4183</v>
       </c>
       <c r="F85" t="n">
-        <v>13.2262</v>
+        <v>12.3011</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>17.6587</v>
+        <v>18.2864</v>
       </c>
       <c r="C86" t="n">
-        <v>16.3767</v>
+        <v>16.1179</v>
       </c>
       <c r="D86" t="n">
-        <v>29.3486</v>
+        <v>30.9599</v>
       </c>
       <c r="E86" t="n">
-        <v>13.0773</v>
+        <v>12.6146</v>
       </c>
       <c r="F86" t="n">
-        <v>13.6436</v>
+        <v>12.9864</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>17.6363</v>
+        <v>18.3109</v>
       </c>
       <c r="C87" t="n">
-        <v>16.357</v>
+        <v>16.2825</v>
       </c>
       <c r="D87" t="n">
-        <v>30.1178</v>
+        <v>31.4347</v>
       </c>
       <c r="E87" t="n">
-        <v>13.2521</v>
+        <v>12.9385</v>
       </c>
       <c r="F87" t="n">
-        <v>13.4706</v>
+        <v>14.8138</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>17.6314</v>
+        <v>18.364</v>
       </c>
       <c r="C88" t="n">
-        <v>16.2805</v>
+        <v>16.0916</v>
       </c>
       <c r="D88" t="n">
-        <v>31.6706</v>
+        <v>32.5708</v>
       </c>
       <c r="E88" t="n">
-        <v>13.639</v>
+        <v>13.7276</v>
       </c>
       <c r="F88" t="n">
-        <v>17.4443</v>
+        <v>15.2611</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>17.6782</v>
+        <v>18.6521</v>
       </c>
       <c r="C89" t="n">
-        <v>16.3658</v>
+        <v>16.5832</v>
       </c>
       <c r="D89" t="n">
-        <v>32.4378</v>
+        <v>33.1583</v>
       </c>
       <c r="E89" t="n">
-        <v>13.8695</v>
+        <v>13.9064</v>
       </c>
       <c r="F89" t="n">
-        <v>17.7272</v>
+        <v>14.8046</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>17.7373</v>
+        <v>18.3814</v>
       </c>
       <c r="C90" t="n">
-        <v>16.3572</v>
+        <v>16.2648</v>
       </c>
       <c r="D90" t="n">
-        <v>33.4125</v>
+        <v>35.4415</v>
       </c>
       <c r="E90" t="n">
-        <v>14.1039</v>
+        <v>14.1468</v>
       </c>
       <c r="F90" t="n">
-        <v>17.9209</v>
+        <v>15.9818</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>17.6239</v>
+        <v>18.565</v>
       </c>
       <c r="C91" t="n">
-        <v>16.2993</v>
+        <v>16.3163</v>
       </c>
       <c r="D91" t="n">
-        <v>34.886</v>
+        <v>36.8209</v>
       </c>
       <c r="E91" t="n">
-        <v>14.3419</v>
+        <v>19.2085</v>
       </c>
       <c r="F91" t="n">
-        <v>18.5754</v>
+        <v>19.2978</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>17.8483</v>
+        <v>19.8015</v>
       </c>
       <c r="C92" t="n">
-        <v>16.4274</v>
+        <v>17.7272</v>
       </c>
       <c r="D92" t="n">
-        <v>31.6998</v>
+        <v>33.7453</v>
       </c>
       <c r="E92" t="n">
-        <v>21.7594</v>
+        <v>19.8493</v>
       </c>
       <c r="F92" t="n">
-        <v>22.1214</v>
+        <v>20.1656</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.937</v>
+        <v>19.7191</v>
       </c>
       <c r="C93" t="n">
-        <v>16.5752</v>
+        <v>17.477</v>
       </c>
       <c r="D93" t="n">
-        <v>32.5236</v>
+        <v>34.5247</v>
       </c>
       <c r="E93" t="n">
-        <v>21.7204</v>
+        <v>19.83</v>
       </c>
       <c r="F93" t="n">
-        <v>22.2447</v>
+        <v>20.245</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>18.2042</v>
+        <v>19.7666</v>
       </c>
       <c r="C94" t="n">
-        <v>21.425</v>
+        <v>20.9806</v>
       </c>
       <c r="D94" t="n">
-        <v>33.5077</v>
+        <v>35.1778</v>
       </c>
       <c r="E94" t="n">
-        <v>21.8386</v>
+        <v>20.227</v>
       </c>
       <c r="F94" t="n">
-        <v>22.2714</v>
+        <v>20.0086</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>22.4344</v>
+        <v>24.0096</v>
       </c>
       <c r="C95" t="n">
-        <v>21.6905</v>
+        <v>21.2141</v>
       </c>
       <c r="D95" t="n">
-        <v>33.9161</v>
+        <v>36.0846</v>
       </c>
       <c r="E95" t="n">
-        <v>22.5456</v>
+        <v>20.3616</v>
       </c>
       <c r="F95" t="n">
-        <v>22.4594</v>
+        <v>20.4729</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>22.4624</v>
+        <v>24.0312</v>
       </c>
       <c r="C96" t="n">
-        <v>21.6841</v>
+        <v>21.2106</v>
       </c>
       <c r="D96" t="n">
-        <v>34.5383</v>
+        <v>36.9806</v>
       </c>
       <c r="E96" t="n">
-        <v>22.8541</v>
+        <v>20.5521</v>
       </c>
       <c r="F96" t="n">
-        <v>22.5539</v>
+        <v>19.1094</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>22.4773</v>
+        <v>24.0278</v>
       </c>
       <c r="C97" t="n">
-        <v>21.817</v>
+        <v>21.2516</v>
       </c>
       <c r="D97" t="n">
-        <v>35.6073</v>
+        <v>37.987</v>
       </c>
       <c r="E97" t="n">
-        <v>22.9763</v>
+        <v>20.6952</v>
       </c>
       <c r="F97" t="n">
-        <v>22.6733</v>
+        <v>19.2276</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.5276</v>
+        <v>24.1314</v>
       </c>
       <c r="C98" t="n">
-        <v>21.7621</v>
+        <v>21.2939</v>
       </c>
       <c r="D98" t="n">
-        <v>36.3474</v>
+        <v>38.7412</v>
       </c>
       <c r="E98" t="n">
-        <v>23.2049</v>
+        <v>20.8954</v>
       </c>
       <c r="F98" t="n">
-        <v>22.7669</v>
+        <v>19.2692</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>22.5883</v>
+        <v>24.076</v>
       </c>
       <c r="C99" t="n">
-        <v>21.8407</v>
+        <v>21.2699</v>
       </c>
       <c r="D99" t="n">
-        <v>37.3332</v>
+        <v>40.0316</v>
       </c>
       <c r="E99" t="n">
-        <v>23.4474</v>
+        <v>21.0374</v>
       </c>
       <c r="F99" t="n">
-        <v>22.8543</v>
+        <v>20.4694</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>22.5848</v>
+        <v>24.1972</v>
       </c>
       <c r="C100" t="n">
-        <v>21.8404</v>
+        <v>21.3381</v>
       </c>
       <c r="D100" t="n">
-        <v>38.5801</v>
+        <v>40.5137</v>
       </c>
       <c r="E100" t="n">
-        <v>23.454</v>
+        <v>21.5484</v>
       </c>
       <c r="F100" t="n">
-        <v>22.9688</v>
+        <v>19.4121</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>22.5952</v>
+        <v>24.0552</v>
       </c>
       <c r="C101" t="n">
-        <v>21.8535</v>
+        <v>21.3833</v>
       </c>
       <c r="D101" t="n">
-        <v>39.4847</v>
+        <v>41.5109</v>
       </c>
       <c r="E101" t="n">
-        <v>23.7369</v>
+        <v>21.4235</v>
       </c>
       <c r="F101" t="n">
-        <v>23.066</v>
+        <v>19.548</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>22.4841</v>
+        <v>24.1791</v>
       </c>
       <c r="C102" t="n">
-        <v>21.8624</v>
+        <v>21.4034</v>
       </c>
       <c r="D102" t="n">
-        <v>40.0958</v>
+        <v>42.3905</v>
       </c>
       <c r="E102" t="n">
-        <v>23.8393</v>
+        <v>21.6039</v>
       </c>
       <c r="F102" t="n">
-        <v>23.402</v>
+        <v>21.0141</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>22.6266</v>
+        <v>24.0934</v>
       </c>
       <c r="C103" t="n">
-        <v>21.9112</v>
+        <v>21.4394</v>
       </c>
       <c r="D103" t="n">
-        <v>41.1505</v>
+        <v>43.4856</v>
       </c>
       <c r="E103" t="n">
-        <v>23.9847</v>
+        <v>21.846</v>
       </c>
       <c r="F103" t="n">
-        <v>23.5712</v>
+        <v>21.3515</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>22.6442</v>
+        <v>24.132</v>
       </c>
       <c r="C104" t="n">
-        <v>22.0073</v>
+        <v>21.5439</v>
       </c>
       <c r="D104" t="n">
-        <v>42.1322</v>
+        <v>44.4938</v>
       </c>
       <c r="E104" t="n">
-        <v>24.3039</v>
+        <v>21.9732</v>
       </c>
       <c r="F104" t="n">
-        <v>23.887</v>
+        <v>20.1865</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>22.7002</v>
+        <v>24.2499</v>
       </c>
       <c r="C105" t="n">
-        <v>22.0924</v>
+        <v>21.6115</v>
       </c>
       <c r="D105" t="n">
-        <v>43.6362</v>
+        <v>45.624</v>
       </c>
       <c r="E105" t="n">
-        <v>24.557</v>
+        <v>24.9817</v>
       </c>
       <c r="F105" t="n">
-        <v>24.1852</v>
+        <v>22.6869</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>22.9278</v>
+        <v>24.3044</v>
       </c>
       <c r="C106" t="n">
-        <v>22.2848</v>
+        <v>21.7446</v>
       </c>
       <c r="D106" t="n">
-        <v>44.6633</v>
+        <v>46.5471</v>
       </c>
       <c r="E106" t="n">
-        <v>24.8324</v>
+        <v>25.0303</v>
       </c>
       <c r="F106" t="n">
-        <v>24.6112</v>
+        <v>23.8483</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>23.0293</v>
+        <v>24.4829</v>
       </c>
       <c r="C107" t="n">
-        <v>22.5441</v>
+        <v>21.931</v>
       </c>
       <c r="D107" t="n">
-        <v>38.4346</v>
+        <v>40.4514</v>
       </c>
       <c r="E107" t="n">
-        <v>28.2744</v>
+        <v>25.3942</v>
       </c>
       <c r="F107" t="n">
-        <v>27.7781</v>
+        <v>23.2576</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>23.1151</v>
+        <v>24.7421</v>
       </c>
       <c r="C108" t="n">
-        <v>23.4038</v>
+        <v>22.9329</v>
       </c>
       <c r="D108" t="n">
-        <v>38.586</v>
+        <v>40.7401</v>
       </c>
       <c r="E108" t="n">
-        <v>28.592</v>
+        <v>25.88</v>
       </c>
       <c r="F108" t="n">
-        <v>28.0856</v>
+        <v>23.3802</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>23.5416</v>
+        <v>24.9138</v>
       </c>
       <c r="C109" t="n">
-        <v>23.3695</v>
+        <v>22.9398</v>
       </c>
       <c r="D109" t="n">
-        <v>39.1508</v>
+        <v>41.5445</v>
       </c>
       <c r="E109" t="n">
-        <v>28.6218</v>
+        <v>25.8269</v>
       </c>
       <c r="F109" t="n">
-        <v>28.0091</v>
+        <v>23.5803</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>25.2557</v>
+        <v>27.4029</v>
       </c>
       <c r="C110" t="n">
-        <v>23.5004</v>
+        <v>23.0365</v>
       </c>
       <c r="D110" t="n">
-        <v>40.023</v>
+        <v>42.085</v>
       </c>
       <c r="E110" t="n">
-        <v>28.9729</v>
+        <v>26.0603</v>
       </c>
       <c r="F110" t="n">
-        <v>28.5177</v>
+        <v>23.7597</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>25.3697</v>
+        <v>27.4949</v>
       </c>
       <c r="C111" t="n">
-        <v>23.5709</v>
+        <v>23.047</v>
       </c>
       <c r="D111" t="n">
-        <v>40.8087</v>
+        <v>43.101</v>
       </c>
       <c r="E111" t="n">
-        <v>29.2304</v>
+        <v>26.2627</v>
       </c>
       <c r="F111" t="n">
-        <v>28.5641</v>
+        <v>23.8269</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>25.4343</v>
+        <v>27.5572</v>
       </c>
       <c r="C112" t="n">
-        <v>23.6566</v>
+        <v>23.1875</v>
       </c>
       <c r="D112" t="n">
-        <v>41.6589</v>
+        <v>43.9678</v>
       </c>
       <c r="E112" t="n">
-        <v>29.6067</v>
+        <v>26.5793</v>
       </c>
       <c r="F112" t="n">
-        <v>28.996</v>
+        <v>25.9519</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>25.4085</v>
+        <v>27.4184</v>
       </c>
       <c r="C113" t="n">
-        <v>23.7466</v>
+        <v>23.2195</v>
       </c>
       <c r="D113" t="n">
-        <v>42.4748</v>
+        <v>44.4868</v>
       </c>
       <c r="E113" t="n">
-        <v>29.7777</v>
+        <v>26.7537</v>
       </c>
       <c r="F113" t="n">
-        <v>29.2423</v>
+        <v>24.4028</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>25.3373</v>
+        <v>27.5182</v>
       </c>
       <c r="C114" t="n">
-        <v>23.8744</v>
+        <v>23.4405</v>
       </c>
       <c r="D114" t="n">
-        <v>43.5185</v>
+        <v>45.617</v>
       </c>
       <c r="E114" t="n">
-        <v>30.0533</v>
+        <v>27.162</v>
       </c>
       <c r="F114" t="n">
-        <v>29.4884</v>
+        <v>24.7158</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>25.4962</v>
+        <v>27.6754</v>
       </c>
       <c r="C115" t="n">
-        <v>23.937</v>
+        <v>23.3881</v>
       </c>
       <c r="D115" t="n">
-        <v>44.3694</v>
+        <v>46.5258</v>
       </c>
       <c r="E115" t="n">
-        <v>30.2616</v>
+        <v>27.4149</v>
       </c>
       <c r="F115" t="n">
-        <v>29.8149</v>
+        <v>25.0231</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>25.3157</v>
+        <v>27.6441</v>
       </c>
       <c r="C116" t="n">
-        <v>24.0586</v>
+        <v>23.5114</v>
       </c>
       <c r="D116" t="n">
-        <v>45.271</v>
+        <v>47.5473</v>
       </c>
       <c r="E116" t="n">
-        <v>30.6274</v>
+        <v>27.8511</v>
       </c>
       <c r="F116" t="n">
-        <v>30.0771</v>
+        <v>25.715</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>25.3831</v>
+        <v>27.6562</v>
       </c>
       <c r="C117" t="n">
-        <v>24.1441</v>
+        <v>23.5905</v>
       </c>
       <c r="D117" t="n">
-        <v>46.2602</v>
+        <v>48.4584</v>
       </c>
       <c r="E117" t="n">
-        <v>30.9272</v>
+        <v>27.9272</v>
       </c>
       <c r="F117" t="n">
-        <v>30.553</v>
+        <v>25.7118</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>25.6241</v>
+        <v>27.7005</v>
       </c>
       <c r="C118" t="n">
-        <v>24.3116</v>
+        <v>23.7208</v>
       </c>
       <c r="D118" t="n">
-        <v>47.6075</v>
+        <v>49.7453</v>
       </c>
       <c r="E118" t="n">
-        <v>31.2725</v>
+        <v>28.4065</v>
       </c>
       <c r="F118" t="n">
-        <v>31.0609</v>
+        <v>27.1611</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>25.8082</v>
+        <v>27.8297</v>
       </c>
       <c r="C119" t="n">
-        <v>24.5791</v>
+        <v>23.9345</v>
       </c>
       <c r="D119" t="n">
-        <v>48.9301</v>
+        <v>50.6425</v>
       </c>
       <c r="E119" t="n">
-        <v>31.6204</v>
+        <v>28.8445</v>
       </c>
       <c r="F119" t="n">
-        <v>31.4986</v>
+        <v>26.6235</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>25.6858</v>
+        <v>27.7172</v>
       </c>
       <c r="C120" t="n">
-        <v>24.8362</v>
+        <v>24.1227</v>
       </c>
       <c r="D120" t="n">
-        <v>49.7017</v>
+        <v>51.9566</v>
       </c>
       <c r="E120" t="n">
-        <v>32.0836</v>
+        <v>29.0838</v>
       </c>
       <c r="F120" t="n">
-        <v>32.2577</v>
+        <v>27.9738</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>25.9809</v>
+        <v>28.0369</v>
       </c>
       <c r="C121" t="n">
-        <v>25.1542</v>
+        <v>24.4402</v>
       </c>
       <c r="D121" t="n">
-        <v>41.3065</v>
+        <v>43.371</v>
       </c>
       <c r="E121" t="n">
-        <v>32.6442</v>
+        <v>29.4667</v>
       </c>
       <c r="F121" t="n">
-        <v>32.3395</v>
+        <v>27.2243</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>25.7686</v>
+        <v>27.6791</v>
       </c>
       <c r="C122" t="n">
-        <v>25.7461</v>
+        <v>24.8962</v>
       </c>
       <c r="D122" t="n">
-        <v>41.508</v>
+        <v>44.3706</v>
       </c>
       <c r="E122" t="n">
-        <v>32.7426</v>
+        <v>29.6995</v>
       </c>
       <c r="F122" t="n">
-        <v>32.462</v>
+        <v>27.6621</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>26.8941</v>
+        <v>28.4078</v>
       </c>
       <c r="C123" t="n">
-        <v>25.8684</v>
+        <v>24.9568</v>
       </c>
       <c r="D123" t="n">
-        <v>42.6546</v>
+        <v>44.8234</v>
       </c>
       <c r="E123" t="n">
-        <v>32.9722</v>
+        <v>29.9676</v>
       </c>
       <c r="F123" t="n">
-        <v>32.8047</v>
+        <v>28.287</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>32.7957</v>
+        <v>35.7554</v>
       </c>
       <c r="C124" t="n">
-        <v>25.9024</v>
+        <v>25.1289</v>
       </c>
       <c r="D124" t="n">
-        <v>43.5691</v>
+        <v>45.4469</v>
       </c>
       <c r="E124" t="n">
-        <v>33.4466</v>
+        <v>30.1237</v>
       </c>
       <c r="F124" t="n">
-        <v>32.9717</v>
+        <v>27.7361</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>32.7835</v>
+        <v>35.6393</v>
       </c>
       <c r="C125" t="n">
-        <v>26.0326</v>
+        <v>25.2209</v>
       </c>
       <c r="D125" t="n">
-        <v>44.1856</v>
+        <v>46.1193</v>
       </c>
       <c r="E125" t="n">
-        <v>33.7494</v>
+        <v>30.899</v>
       </c>
       <c r="F125" t="n">
-        <v>33.1838</v>
+        <v>28.0672</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>32.8231</v>
+        <v>35.6972</v>
       </c>
       <c r="C126" t="n">
-        <v>26.2092</v>
+        <v>25.3511</v>
       </c>
       <c r="D126" t="n">
-        <v>44.9106</v>
+        <v>47.3385</v>
       </c>
       <c r="E126" t="n">
-        <v>34.0866</v>
+        <v>30.814</v>
       </c>
       <c r="F126" t="n">
-        <v>33.515</v>
+        <v>28.3143</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>32.7935</v>
+        <v>35.5117</v>
       </c>
       <c r="C127" t="n">
-        <v>26.367</v>
+        <v>25.475</v>
       </c>
       <c r="D127" t="n">
-        <v>45.7223</v>
+        <v>47.7501</v>
       </c>
       <c r="E127" t="n">
-        <v>34.4725</v>
+        <v>31.0599</v>
       </c>
       <c r="F127" t="n">
-        <v>33.7567</v>
+        <v>28.4917</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>32.8379</v>
+        <v>35.6368</v>
       </c>
       <c r="C128" t="n">
-        <v>26.4986</v>
+        <v>25.7378</v>
       </c>
       <c r="D128" t="n">
-        <v>46.6922</v>
+        <v>49.0158</v>
       </c>
       <c r="E128" t="n">
-        <v>34.8537</v>
+        <v>31.4152</v>
       </c>
       <c r="F128" t="n">
-        <v>34.0237</v>
+        <v>28.8494</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>32.8854</v>
+        <v>35.6688</v>
       </c>
       <c r="C129" t="n">
-        <v>26.7667</v>
+        <v>25.9088</v>
       </c>
       <c r="D129" t="n">
-        <v>47.439</v>
+        <v>49.8552</v>
       </c>
       <c r="E129" t="n">
-        <v>35.1728</v>
+        <v>31.768</v>
       </c>
       <c r="F129" t="n">
-        <v>34.4946</v>
+        <v>29.2505</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>32.8748</v>
+        <v>35.7315</v>
       </c>
       <c r="C130" t="n">
-        <v>26.8866</v>
+        <v>26.0874</v>
       </c>
       <c r="D130" t="n">
-        <v>48.3332</v>
+        <v>50.6904</v>
       </c>
       <c r="E130" t="n">
-        <v>35.5495</v>
+        <v>32.1052</v>
       </c>
       <c r="F130" t="n">
-        <v>35.0976</v>
+        <v>29.4894</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>32.8698</v>
+        <v>35.6972</v>
       </c>
       <c r="C131" t="n">
-        <v>27.1072</v>
+        <v>26.3465</v>
       </c>
       <c r="D131" t="n">
-        <v>49.587</v>
+        <v>51.1027</v>
       </c>
       <c r="E131" t="n">
-        <v>35.8914</v>
+        <v>32.4881</v>
       </c>
       <c r="F131" t="n">
-        <v>35.5991</v>
+        <v>30.2092</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>32.9046</v>
+        <v>35.7105</v>
       </c>
       <c r="C132" t="n">
-        <v>27.4691</v>
+        <v>26.6577</v>
       </c>
       <c r="D132" t="n">
-        <v>50.6411</v>
+        <v>52.6235</v>
       </c>
       <c r="E132" t="n">
-        <v>36.3309</v>
+        <v>32.8219</v>
       </c>
       <c r="F132" t="n">
-        <v>36.062</v>
+        <v>30.7211</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>32.8623</v>
+        <v>35.7295</v>
       </c>
       <c r="C133" t="n">
-        <v>27.776</v>
+        <v>26.8921</v>
       </c>
       <c r="D133" t="n">
-        <v>51.7239</v>
+        <v>54.0234</v>
       </c>
       <c r="E133" t="n">
-        <v>36.8423</v>
+        <v>33.1432</v>
       </c>
       <c r="F133" t="n">
-        <v>36.755</v>
+        <v>32.9755</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>33.116</v>
+        <v>35.7899</v>
       </c>
       <c r="C134" t="n">
-        <v>28.1714</v>
+        <v>27.3463</v>
       </c>
       <c r="D134" t="n">
-        <v>52.9254</v>
+        <v>54.8189</v>
       </c>
       <c r="E134" t="n">
-        <v>37.3447</v>
+        <v>31.3877</v>
       </c>
       <c r="F134" t="n">
-        <v>37.6099</v>
+        <v>29.3923</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>33.2353</v>
+        <v>35.8381</v>
       </c>
       <c r="C135" t="n">
-        <v>28.6053</v>
+        <v>27.7855</v>
       </c>
       <c r="D135" t="n">
-        <v>43.2166</v>
+        <v>44.8941</v>
       </c>
       <c r="E135" t="n">
-        <v>34.7813</v>
+        <v>31.7684</v>
       </c>
       <c r="F135" t="n">
-        <v>34.9699</v>
+        <v>29.4204</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>33.0465</v>
+        <v>35.6729</v>
       </c>
       <c r="C136" t="n">
-        <v>28.0056</v>
+        <v>27.0239</v>
       </c>
       <c r="D136" t="n">
-        <v>43.8997</v>
+        <v>45.7971</v>
       </c>
       <c r="E136" t="n">
-        <v>35.1797</v>
+        <v>32.1882</v>
       </c>
       <c r="F136" t="n">
-        <v>35.1612</v>
+        <v>31.7491</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>33.4653</v>
+        <v>36.1285</v>
       </c>
       <c r="C137" t="n">
-        <v>27.8989</v>
+        <v>27.1432</v>
       </c>
       <c r="D137" t="n">
-        <v>44.3218</v>
+        <v>45.78</v>
       </c>
       <c r="E137" t="n">
-        <v>35.5831</v>
+        <v>32.5469</v>
       </c>
       <c r="F137" t="n">
-        <v>35.4118</v>
+        <v>30.8644</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>37.7928</v>
+        <v>41.7498</v>
       </c>
       <c r="C138" t="n">
-        <v>28.2686</v>
+        <v>27.2765</v>
       </c>
       <c r="D138" t="n">
-        <v>45.5392</v>
+        <v>47.083</v>
       </c>
       <c r="E138" t="n">
-        <v>35.9082</v>
+        <v>32.6174</v>
       </c>
       <c r="F138" t="n">
-        <v>35.7823</v>
+        <v>30.3497</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>37.776</v>
+        <v>41.1813</v>
       </c>
       <c r="C139" t="n">
-        <v>28.1272</v>
+        <v>27.4535</v>
       </c>
       <c r="D139" t="n">
-        <v>45.6901</v>
+        <v>47.6506</v>
       </c>
       <c r="E139" t="n">
-        <v>36.1475</v>
+        <v>33.1139</v>
       </c>
       <c r="F139" t="n">
-        <v>35.8418</v>
+        <v>30.4149</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>37.4607</v>
+        <v>41.8049</v>
       </c>
       <c r="C140" t="n">
-        <v>28.4009</v>
+        <v>27.6843</v>
       </c>
       <c r="D140" t="n">
-        <v>46.3467</v>
+        <v>48.3957</v>
       </c>
       <c r="E140" t="n">
-        <v>36.4651</v>
+        <v>33.2009</v>
       </c>
       <c r="F140" t="n">
-        <v>36.0416</v>
+        <v>30.8483</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>37.8161</v>
+        <v>41.813</v>
       </c>
       <c r="C141" t="n">
-        <v>28.6656</v>
+        <v>27.781</v>
       </c>
       <c r="D141" t="n">
-        <v>47.2554</v>
+        <v>49.787</v>
       </c>
       <c r="E141" t="n">
-        <v>36.8575</v>
+        <v>33.6739</v>
       </c>
       <c r="F141" t="n">
-        <v>36.4298</v>
+        <v>32.0157</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>37.7976</v>
+        <v>41.7993</v>
       </c>
       <c r="C142" t="n">
-        <v>28.8703</v>
+        <v>28.0746</v>
       </c>
       <c r="D142" t="n">
-        <v>48.0425</v>
+        <v>49.328</v>
       </c>
       <c r="E142" t="n">
-        <v>37.0595</v>
+        <v>34.0325</v>
       </c>
       <c r="F142" t="n">
-        <v>36.6504</v>
+        <v>32.6408</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>38.0287</v>
+        <v>41.8256</v>
       </c>
       <c r="C143" t="n">
-        <v>29.4901</v>
+        <v>28.3201</v>
       </c>
       <c r="D143" t="n">
-        <v>49.5242</v>
+        <v>51.7232</v>
       </c>
       <c r="E143" t="n">
-        <v>38.1796</v>
+        <v>34.2308</v>
       </c>
       <c r="F143" t="n">
-        <v>37.6374</v>
+        <v>31.8286</v>
       </c>
     </row>
   </sheetData>
